--- a/PAB产品计划表.xlsx
+++ b/PAB产品计划表.xlsx
@@ -10,7 +10,7 @@
     <sheet name="时间节点计划表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'时间节点计划表'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'时间节点计划表'!$A$1:$G$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,11 +42,17 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,8 +69,18 @@
         <fgColor rgb="00F3F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEBD0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -86,13 +102,49 @@
         <color rgb="00B7C9D6"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9D6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7C9D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7C9D6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B7C9D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,7 +165,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -496,44 +551,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>任务</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>任务摘要</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>预估完成节点</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>实际完成节点</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>超时原因</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>任务责任人</t>
         </is>
@@ -542,994 +603,1048 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>第一期</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>第一期·零件图纸整理归档</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>四批型号单级和双级所涉零件图纸整理完毕并分类归档。范围：PAB060、PAB090、PAB115、PAB142。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>46258</v>
       </c>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>第一期·零件下单采购</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>各零件形成采购表单并填写数量，单级和双级各10台。范围：PAB060、PAB090、PAB115、PAB142。</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>46259</v>
       </c>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="6" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>第一期·标准件下单采购</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>各标准件形成采购表单并填写数量。范围：PAB060、PAB090、PAB115、PAB142。</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>46259</v>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>装配线布局</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>装配线布局完成。协助人：吴金平、王杰、吴晨阳。</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>46280</v>
       </c>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>莫华华</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>装配工具到位</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>轴用卡钳、孔用卡钳、镊子、压机、润滑脂、螺纹禁锢胶、密封厌氧胶等装配工具到位。协助人：王杰。</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>46275</v>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>吴晨阳</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>PAB060·零件到位</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>PAB060 零件到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>46289</v>
       </c>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>PAB060·工装图纸绘制</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>PAB060 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>46262</v>
       </c>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>PAB060·工装实物到位</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>PAB060 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <v>46280</v>
       </c>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>PAB060·排针机安装调试</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>排针机1安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>46289</v>
       </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>PAB060·单级样机</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>完成 PAB060 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>46291</v>
       </c>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>PAB060·双级样机</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>完成 PAB060 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>46293</v>
       </c>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>PAB090·零件到位</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>PAB090 零件到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>46292</v>
       </c>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>PAB090·工装图纸绘制</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>PAB090 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>46266</v>
       </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>PAB090·工装实物到位</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>PAB090 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <v>46285</v>
       </c>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>PAB090·排针机安装调试</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>排针机1安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>46292</v>
       </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>PAB090·单级样机</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>完成 PAB090 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>46294</v>
       </c>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>PAB090·双级样机</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>完成 PAB090 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>46295</v>
       </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>PAB115·零件到位</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>PAB115 零件到位（原文标注：国庆假期）。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <v>46303</v>
       </c>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PAB115·工装图纸绘制</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>PAB115 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>46269</v>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>PAB115·工装实物到位</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>PAB115 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>46290</v>
       </c>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>PAB115·排针机安装调试</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>排针机1安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="4" t="n">
         <v>46303</v>
       </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>PAB115·单级样机</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>完成 PAB115 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <v>46304</v>
       </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>PAB115·双级样机</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>完成 PAB115 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>46306</v>
       </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>PAB142·零件到位</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>PAB142 零件到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="D25" s="7" t="n">
         <v>46307</v>
       </c>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>PAB142·工装图纸绘制</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>PAB142 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>46269</v>
       </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>PAB142·工装实物到位</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>PAB142 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <v>46294</v>
       </c>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>PAB142·排针机安装调试</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>排针机1、排针机2安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>46307</v>
       </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>PAB142·单级样机</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>完成 PAB142 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="D29" s="7" t="n">
         <v>46308</v>
       </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>PAB142·双级样机</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>完成 PAB142 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>第二期</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>第二期·零件图纸整理归档</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>四批型号单级和双级所涉零件图纸整理完毕并分类归档。范围：PAB180、PAB220。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="D31" s="7" t="n">
         <v>46272</v>
       </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="n"/>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="9" t="n"/>
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>第二期·零件下单采购</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>各零件形成采购表单并填写数量，单级和双级各10台。范围：PAB180、PAB220。</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>46275</v>
       </c>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>第二期·标准件下单采购</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>各标准件形成采购表单并填写数量。范围：PAB180、PAB220。</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n">
+      <c r="D33" s="7" t="n">
         <v>46275</v>
       </c>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>PAB180·零件到位</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>PAB180 零件到位（原文标注：国庆假期）。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>46310</v>
       </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="9" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>PAB180·工装图纸绘制</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>PAB180 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C35" s="6" t="n">
+      <c r="D35" s="7" t="n">
         <v>46276</v>
       </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>PAB180·工装实物到位</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>PAB180 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>46303</v>
       </c>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>PAB180·排针机安装调试</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>排针机1、排针机2安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="D37" s="7" t="n">
         <v>46310</v>
       </c>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>PAB180·单级样机</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>完成 PAB180 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>46311</v>
       </c>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="3" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="9" t="n"/>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>PAB180·双级样机</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>完成 PAB180 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="D39" s="7" t="n">
         <v>46314</v>
       </c>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>PAB220·零件到位</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>PAB220 零件到位（原文标注：国庆假期）。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="4" t="n">
         <v>46315</v>
       </c>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>PAB220·工装图纸绘制</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>PAB220 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="D41" s="7" t="n">
         <v>46279</v>
       </c>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>PAB220·工装实物到位</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>PAB220 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>46305</v>
       </c>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="9" t="n"/>
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>PAB220·排针机安装调试</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>排针机1、排针机2安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="D43" s="7" t="n">
         <v>46315</v>
       </c>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>PAB220·单级样机</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>完成 PAB220 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>46316</v>
       </c>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>PAB220·双级样机</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>完成 PAB220 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="D45" s="7" t="n">
         <v>46318</v>
       </c>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>说明：数据来自《PAB产品计划表》Word原文。原文仅有预估节点，实际完成节点留空待填；填写后若实际完成节点晚于预估完成节点，D列单元格自动红色底纹。协助人写入任务摘要；任务责任人取原文「责任人」。</t>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>说明：数据来自《PAB产品计划表》Word原文。A列按第一期/第二期合并。原文仅有预估节点，实际完成节点留空待填；填写后若实际完成节点晚于预估完成节点，E列单元格自动红色底纹。协助人写入任务摘要；任务责任人取原文「责任人」。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F45">
-    <sortState ref="A1:F45">
-      <sortCondition descending="0" ref="C2:C45"/>
+  <autoFilter ref="A1:G45">
+    <sortState ref="A1:G45">
+      <sortCondition descending="0" ref="D2:D45"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="A47:F47"/>
+  <mergeCells count="3">
+    <mergeCell ref="A31:A45"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A2:A30"/>
   </mergeCells>
-  <conditionalFormatting sqref="D2:D200">
+  <conditionalFormatting sqref="E2:E200">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(D2),ISNUMBER(C2),D2&gt;C2)</formula>
+      <formula>AND(ISNUMBER(E2),ISNUMBER(D2),E2&gt;D2)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="D2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>

--- a/PAB产品计划表.xlsx
+++ b/PAB产品计划表.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="时间节点计划表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="时间轴" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'时间节点计划表'!$A$1:$G$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'时间节点计划表'!$A$1:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,11 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="M/D"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,11 +50,43 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="001F2937"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="001F4E78"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00334155"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00C2410C"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +111,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDEBD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C2410C"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,12 +183,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -156,6 +203,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -165,17 +215,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
     <dxf>
       <font>
         <name val="微软雅黑"/>
@@ -186,6 +261,30 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <color rgb="0014532D"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0086EFAC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -260,6 +359,208 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>PAB 目标轴（蓝）与实际轴（橙）</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>目标时间轴</v>
+          </tx>
+          <spPr>
+            <a:ln w="12000">
+              <a:solidFill>
+                <a:srgbClr val="1F4E78"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="diamond"/>
+            <size val="8"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'时间节点计划表'!$L$53:$L$96</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'时间节点计划表'!$M$52:$M$96</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>实际时间轴</v>
+          </tx>
+          <spPr>
+            <a:ln w="10000">
+              <a:solidFill>
+                <a:srgbClr val="C2410C"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'时间节点计划表'!$N$53:$N$96</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'时间节点计划表'!$O$52:$O$96</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>时间方向 →</v>
+          </tx>
+          <spPr>
+            <a:ln w="8000">
+              <a:solidFill>
+                <a:srgbClr val="94A3B8"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'时间节点计划表'!$L$53:$L$96</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'时间节点计划表'!$P$52:$P$96</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>完成节点</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="2.5"/>
+          <min val="0.5"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -551,16 +852,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="11" max="11"/>
+    <col hidden="1" width="13" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -576,31 +885,41 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>任务简要</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>任务摘要</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>预估完成节点</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>实际完成节点</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>超时原因</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>任务责任人</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>偏移天数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>第一期</t>
@@ -608,1046 +927,3907 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>第一期·零件图纸整理归档</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
+          <t>前期准备</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>一期零件图纸整理归档</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>四批型号单级和双级所涉零件图纸整理完毕并分类归档。范围：PAB060、PAB090、PAB115、PAB142。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>46258</v>
       </c>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
+      <c r="I2" s="7">
+        <f>IF(OR(E2="",F2=""),"待填",F2-E2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>第一期·零件下单采购</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>一期零件下单采购</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>各零件形成采购表单并填写数量，单级和双级各10台。范围：PAB060、PAB090、PAB115、PAB142。</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="E3" s="9" t="n">
         <v>46259</v>
       </c>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
+      <c r="I3" s="11">
+        <f>IF(OR(E3="",F3=""),"待填",F3-E3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>第一期·标准件下单采购</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>一期标准件下单采购</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>各标准件形成采购表单并填写数量。范围：PAB060、PAB090、PAB115、PAB142。</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>46259</v>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="36" customHeight="1">
+      <c r="I4" s="7">
+        <f>IF(OR(E4="",F4=""),"待填",F4-E4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="2" t="n"/>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>装配线布局</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>装配线布局完成</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>装配线布局完成。协助人：吴金平、王杰、吴晨阳。</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="E5" s="9" t="n">
         <v>46280</v>
       </c>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>莫华华</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+      <c r="I5" s="11">
+        <f>IF(OR(E5="",F5=""),"待填",F5-E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>装配工具到位</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>轴用卡钳、孔用卡钳、镊子、压机、润滑脂、螺纹禁锢胶、密封厌氧胶等装配工具到位。协助人：王杰。</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>46275</v>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>吴晨阳</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+      <c r="I6" s="7">
+        <f>IF(OR(E6="",F6=""),"待填",F6-E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="2" t="n"/>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>PAB060</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>PAB060·零件到位</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>PAB060 零件到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="E7" s="9" t="n">
         <v>46289</v>
       </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
+      <c r="I7" s="11">
+        <f>IF(OR(E7="",F7=""),"待填",F7-E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>PAB060·工装图纸绘制</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>PAB060 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>46262</v>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
+      <c r="I8" s="7">
+        <f>IF(OR(E8="",F8=""),"待填",F8-E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>PAB060·工装实物到位</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>PAB060 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="E9" s="9" t="n">
         <v>46280</v>
       </c>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
+      <c r="I9" s="11">
+        <f>IF(OR(E9="",F9=""),"待填",F9-E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>PAB060·排针机安装调试</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>排针机1安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>46289</v>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
+      <c r="I10" s="7">
+        <f>IF(OR(E10="",F10=""),"待填",F10-E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="2" t="n"/>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>PAB060·单级样机</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>完成 PAB060 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="E11" s="9" t="n">
         <v>46291</v>
       </c>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
+      <c r="I11" s="11">
+        <f>IF(OR(E11="",F11=""),"待填",F11-E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>PAB060·双级样机</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>完成 PAB060 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="5" t="n">
         <v>46293</v>
       </c>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+      <c r="I12" s="7">
+        <f>IF(OR(E12="",F12=""),"待填",F12-E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="2" t="n"/>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PAB090</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>PAB090·零件到位</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>PAB090 零件到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="E13" s="9" t="n">
         <v>46292</v>
       </c>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+      <c r="I13" s="11">
+        <f>IF(OR(E13="",F13=""),"待填",F13-E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>PAB090·工装图纸绘制</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>PAB090 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="5" t="n">
         <v>46266</v>
       </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
+      <c r="I14" s="7">
+        <f>IF(OR(E14="",F14=""),"待填",F14-E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>PAB090·工装实物到位</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>PAB090 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="E15" s="9" t="n">
         <v>46285</v>
       </c>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
+      <c r="I15" s="11">
+        <f>IF(OR(E15="",F15=""),"待填",F15-E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>PAB090·排针机安装调试</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>排针机1安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>46292</v>
       </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="36" customHeight="1">
+      <c r="I16" s="7">
+        <f>IF(OR(E16="",F16=""),"待填",F16-E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="2" t="n"/>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>PAB090·单级样机</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>完成 PAB090 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="E17" s="9" t="n">
         <v>46294</v>
       </c>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1">
+      <c r="I17" s="11">
+        <f>IF(OR(E17="",F17=""),"待填",F17-E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>PAB090·双级样机</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>完成 PAB090 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="E18" s="5" t="n">
         <v>46295</v>
       </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
+      <c r="I18" s="7">
+        <f>IF(OR(E18="",F18=""),"待填",F18-E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="2" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>PAB115</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>PAB115·零件到位</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>PAB115 零件到位（原文标注：国庆假期）。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="E19" s="9" t="n">
         <v>46303</v>
       </c>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
+      <c r="I19" s="11">
+        <f>IF(OR(E19="",F19=""),"待填",F19-E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>PAB115·工装图纸绘制</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>PAB115 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>46269</v>
       </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="I20" s="7">
+        <f>IF(OR(E20="",F20=""),"待填",F20-E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>PAB115·工装实物到位</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>PAB115 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="E21" s="9" t="n">
         <v>46290</v>
       </c>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="36" customHeight="1">
+      <c r="I21" s="11">
+        <f>IF(OR(E21="",F21=""),"待填",F21-E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>PAB115·排针机安装调试</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>排针机1安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="E22" s="5" t="n">
         <v>46303</v>
       </c>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+      <c r="I22" s="7">
+        <f>IF(OR(E22="",F22=""),"待填",F22-E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>PAB115·单级样机</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>完成 PAB115 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="E23" s="9" t="n">
         <v>46304</v>
       </c>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="36" customHeight="1">
+      <c r="I23" s="11">
+        <f>IF(OR(E23="",F23=""),"待填",F23-E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>PAB115·双级样机</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>完成 PAB115 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>46306</v>
       </c>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="I24" s="7">
+        <f>IF(OR(E24="",F24=""),"待填",F24-E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="2" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>PAB142</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>PAB142·零件到位</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>PAB142 零件到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
+      <c r="E25" s="9" t="n">
         <v>46307</v>
       </c>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
+      <c r="I25" s="11">
+        <f>IF(OR(E25="",F25=""),"待填",F25-E25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>PAB142·工装图纸绘制</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>PAB142 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="E26" s="5" t="n">
         <v>46269</v>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="36" customHeight="1">
+      <c r="I26" s="7">
+        <f>IF(OR(E26="",F26=""),"待填",F26-E26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>PAB142·工装实物到位</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>PAB142 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="E27" s="9" t="n">
         <v>46294</v>
       </c>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="36" customHeight="1">
+      <c r="I27" s="11">
+        <f>IF(OR(E27="",F27=""),"待填",F27-E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>PAB142·排针机安装调试</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>排针机1、排针机2安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="E28" s="5" t="n">
         <v>46307</v>
       </c>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
+      <c r="I28" s="7">
+        <f>IF(OR(E28="",F28=""),"待填",F28-E28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>PAB142·单级样机</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>完成 PAB142 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D29" s="7" t="n">
+      <c r="E29" s="9" t="n">
         <v>46308</v>
       </c>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="36" customHeight="1">
+      <c r="I29" s="11">
+        <f>IF(OR(E29="",F29=""),"待填",F29-E29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>PAB142·双级样机</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>完成 PAB142 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="E30" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="I30" s="7">
+        <f>IF(OR(E30="",F30=""),"待填",F30-E30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>第二期·零件图纸整理归档</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>前期准备</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>二期零件图纸整理归档</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>四批型号单级和双级所涉零件图纸整理完毕并分类归档。范围：PAB180、PAB220。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="E31" s="9" t="n">
         <v>46272</v>
       </c>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>第二期·零件下单采购</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="I31" s="11">
+        <f>IF(OR(E31="",F31=""),"待填",F31-E31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="12" t="n"/>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>二期零件下单采购</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>各零件形成采购表单并填写数量，单级和双级各10台。范围：PAB180、PAB220。</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="E32" s="5" t="n">
         <v>46275</v>
       </c>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>第二期·标准件下单采购</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="I32" s="7">
+        <f>IF(OR(E32="",F32=""),"待填",F32-E32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="12" t="n"/>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>二期标准件下单采购</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>各标准件形成采购表单并填写数量。范围：PAB180、PAB220。</t>
         </is>
       </c>
-      <c r="D33" s="7" t="n">
+      <c r="E33" s="9" t="n">
         <v>46275</v>
       </c>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="9" t="n"/>
+      <c r="I33" s="11">
+        <f>IF(OR(E33="",F33=""),"待填",F33-E33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="12" t="n"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>PAB180</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
           <t>PAB180·零件到位</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>PAB180 零件到位（原文标注：国庆假期）。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="E34" s="5" t="n">
         <v>46310</v>
       </c>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="I34" s="7">
+        <f>IF(OR(E34="",F34=""),"待填",F34-E34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="12" t="n"/>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>PAB180·工装图纸绘制</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>PAB180 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n">
+      <c r="E35" s="9" t="n">
         <v>46276</v>
       </c>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="6" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="I35" s="11">
+        <f>IF(OR(E35="",F35=""),"待填",F35-E35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="12" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>PAB180·工装实物到位</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>PAB180 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="E36" s="5" t="n">
         <v>46303</v>
       </c>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="I36" s="7">
+        <f>IF(OR(E36="",F36=""),"待填",F36-E36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="12" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>PAB180·排针机安装调试</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>排针机1、排针机2安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="D37" s="7" t="n">
+      <c r="E37" s="9" t="n">
         <v>46310</v>
       </c>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="I37" s="11">
+        <f>IF(OR(E37="",F37=""),"待填",F37-E37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="12" t="n"/>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>PAB180·单级样机</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>完成 PAB180 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="E38" s="5" t="n">
         <v>46311</v>
       </c>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="I38" s="7">
+        <f>IF(OR(E38="",F38=""),"待填",F38-E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="12" t="n"/>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>PAB180·双级样机</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>完成 PAB180 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="E39" s="9" t="n">
         <v>46314</v>
       </c>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="9" t="n"/>
+      <c r="I39" s="11">
+        <f>IF(OR(E39="",F39=""),"待填",F39-E39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="12" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
+          <t>PAB220</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
           <t>PAB220·零件到位</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>PAB220 零件到位（原文标注：国庆假期）。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="E40" s="5" t="n">
         <v>46315</v>
       </c>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="I40" s="7">
+        <f>IF(OR(E40="",F40=""),"待填",F40-E40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="12" t="n"/>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>PAB220·工装图纸绘制</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>PAB220 工装图纸绘制完成。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="E41" s="9" t="n">
         <v>46279</v>
       </c>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="I41" s="11">
+        <f>IF(OR(E41="",F41=""),"待填",F41-E41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="12" t="n"/>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>PAB220·工装实物到位</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>PAB220 工装实物到位。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="E42" s="5" t="n">
         <v>46305</v>
       </c>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="I42" s="7">
+        <f>IF(OR(E42="",F42=""),"待填",F42-E42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="12" t="n"/>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>PAB220·排针机安装调试</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>排针机1、排针机2安装到位并调试完毕。协助人：王杰。</t>
         </is>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="E43" s="9" t="n">
         <v>46315</v>
       </c>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="6" t="inlineStr"/>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>吴金平</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="9" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="I43" s="11">
+        <f>IF(OR(E43="",F43=""),"待填",F43-E43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="12" t="n"/>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>PAB220·单级样机</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>完成 PAB220 单级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="E44" s="5" t="n">
         <v>46316</v>
       </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="I44" s="7">
+        <f>IF(OR(E44="",F44=""),"待填",F44-E44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="12" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>PAB220·双级样机</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>完成 PAB220 双级样机。协助人：吴晨阳。</t>
         </is>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="E45" s="9" t="n">
         <v>46318</v>
       </c>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>王杰</t>
         </is>
       </c>
+      <c r="I45" s="11">
+        <f>IF(OR(E45="",F45=""),"待填",F45-E45)</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>说明：数据来自《PAB产品计划表》Word原文。A列按第一期/第二期合并。原文仅有预估节点，实际完成节点留空待填；填写后若实际完成节点晚于预估完成节点，E列单元格自动红色底纹。协助人写入任务摘要；任务责任人取原文「责任人」。</t>
-        </is>
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>说明：A列按第一期/第二期合并，B列按任务组合并。偏移天数=实际−预估（正值延期）。下方为时间轴图；同文件工作表「时间轴」为按日历天数展开的带箭头轴（目标轴在上、实际轴在下，两轴共用起止日期以对照偏移）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>目标时间轴 / 实际时间轴</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>下图按预估日期生成从左到右的目标轴；橙色点为实际完成（若已填写）。X 轴左端=首个任务日期，右端=最终任务日期。点相对目标点的左右位移即时间偏移。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>任务简要</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>预估</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>目标Y</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>实际</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>实际Y</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>轴Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>一期零件图纸整理归档</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="n">
+        <v>46258</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>一期零件下单采购</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>一期标准件下单采购</t>
+        </is>
+      </c>
+      <c r="L55" s="16" t="n">
+        <v>46259</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>装配线布局完成</t>
+        </is>
+      </c>
+      <c r="L56" s="16" t="n">
+        <v>46280</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>装配工具到位</t>
+        </is>
+      </c>
+      <c r="L57" s="16" t="n">
+        <v>46275</v>
+      </c>
+      <c r="M57" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>PAB060·零件到位</t>
+        </is>
+      </c>
+      <c r="L58" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>PAB060·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="L59" s="16" t="n">
+        <v>46262</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>PAB060·工装实物到位</t>
+        </is>
+      </c>
+      <c r="L60" s="16" t="n">
+        <v>46280</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>PAB060·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="L61" s="16" t="n">
+        <v>46289</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>PAB060·单级样机</t>
+        </is>
+      </c>
+      <c r="L62" s="16" t="n">
+        <v>46291</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>PAB060·双级样机</t>
+        </is>
+      </c>
+      <c r="L63" s="16" t="n">
+        <v>46293</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>PAB090·零件到位</t>
+        </is>
+      </c>
+      <c r="L64" s="16" t="n">
+        <v>46292</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>PAB090·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="L65" s="16" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>PAB090·工装实物到位</t>
+        </is>
+      </c>
+      <c r="L66" s="16" t="n">
+        <v>46285</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>PAB090·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="L67" s="16" t="n">
+        <v>46292</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>PAB090·单级样机</t>
+        </is>
+      </c>
+      <c r="L68" s="16" t="n">
+        <v>46294</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>PAB090·双级样机</t>
+        </is>
+      </c>
+      <c r="L69" s="16" t="n">
+        <v>46295</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>PAB115·零件到位</t>
+        </is>
+      </c>
+      <c r="L70" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>PAB115·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="L71" s="16" t="n">
+        <v>46269</v>
+      </c>
+      <c r="M71" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>PAB115·工装实物到位</t>
+        </is>
+      </c>
+      <c r="L72" s="16" t="n">
+        <v>46290</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>PAB115·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="L73" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="M73" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>PAB115·单级样机</t>
+        </is>
+      </c>
+      <c r="L74" s="16" t="n">
+        <v>46304</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>PAB115·双级样机</t>
+        </is>
+      </c>
+      <c r="L75" s="16" t="n">
+        <v>46306</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>PAB142·零件到位</t>
+        </is>
+      </c>
+      <c r="L76" s="16" t="n">
+        <v>46307</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>PAB142·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="L77" s="16" t="n">
+        <v>46269</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>PAB142·工装实物到位</t>
+        </is>
+      </c>
+      <c r="L78" s="16" t="n">
+        <v>46294</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>PAB142·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="L79" s="16" t="n">
+        <v>46307</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>PAB142·单级样机</t>
+        </is>
+      </c>
+      <c r="L80" s="16" t="n">
+        <v>46308</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>PAB142·双级样机</t>
+        </is>
+      </c>
+      <c r="L81" s="16" t="n">
+        <v>46310</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>二期零件图纸整理归档</t>
+        </is>
+      </c>
+      <c r="L82" s="16" t="n">
+        <v>46272</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>二期零件下单采购</t>
+        </is>
+      </c>
+      <c r="L83" s="16" t="n">
+        <v>46275</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>二期标准件下单采购</t>
+        </is>
+      </c>
+      <c r="L84" s="16" t="n">
+        <v>46275</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>PAB180·零件到位</t>
+        </is>
+      </c>
+      <c r="L85" s="16" t="n">
+        <v>46310</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>PAB180·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="L86" s="16" t="n">
+        <v>46276</v>
+      </c>
+      <c r="M86" t="n">
+        <v>2</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>PAB180·工装实物到位</t>
+        </is>
+      </c>
+      <c r="L87" s="16" t="n">
+        <v>46303</v>
+      </c>
+      <c r="M87" t="n">
+        <v>2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>PAB180·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="L88" s="16" t="n">
+        <v>46310</v>
+      </c>
+      <c r="M88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>PAB180·单级样机</t>
+        </is>
+      </c>
+      <c r="L89" s="16" t="n">
+        <v>46311</v>
+      </c>
+      <c r="M89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>PAB180·双级样机</t>
+        </is>
+      </c>
+      <c r="L90" s="16" t="n">
+        <v>46314</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>PAB220·零件到位</t>
+        </is>
+      </c>
+      <c r="L91" s="16" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>PAB220·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="L92" s="16" t="n">
+        <v>46279</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>PAB220·工装实物到位</t>
+        </is>
+      </c>
+      <c r="L93" s="16" t="n">
+        <v>46305</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>PAB220·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="L94" s="16" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>PAB220·单级样机</t>
+        </is>
+      </c>
+      <c r="L95" s="16" t="n">
+        <v>46316</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>PAB220·双级样机</t>
+        </is>
+      </c>
+      <c r="L96" s="16" t="n">
+        <v>46318</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G45">
-    <sortState ref="A1:G45">
-      <sortCondition descending="0" ref="D2:D45"/>
-    </sortState>
-  </autoFilter>
-  <mergeCells count="3">
+  <autoFilter ref="A1:I45"/>
+  <mergeCells count="13">
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="A2:A30"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="A50:I50"/>
     <mergeCell ref="A31:A45"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A2:A30"/>
+    <mergeCell ref="B2:B6"/>
   </mergeCells>
-  <conditionalFormatting sqref="E2:E200">
+  <conditionalFormatting sqref="F2:F200">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(E2),ISNUMBER(D2),E2&gt;D2)</formula>
+      <formula>AND(ISNUMBER(F2),ISNUMBER(E2),F2&gt;E2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I45">
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>AND(ISNUMBER(I2),I2&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>AND(ISNUMBER(I2),I2&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="E2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BK18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="3.2" customWidth="1" min="2" max="2"/>
+    <col width="3.2" customWidth="1" min="3" max="3"/>
+    <col width="3.2" customWidth="1" min="4" max="4"/>
+    <col width="3.2" customWidth="1" min="5" max="5"/>
+    <col width="3.2" customWidth="1" min="6" max="6"/>
+    <col width="3.2" customWidth="1" min="7" max="7"/>
+    <col width="3.2" customWidth="1" min="8" max="8"/>
+    <col width="3.2" customWidth="1" min="9" max="9"/>
+    <col width="3.2" customWidth="1" min="10" max="10"/>
+    <col width="3.2" customWidth="1" min="11" max="11"/>
+    <col width="3.2" customWidth="1" min="12" max="12"/>
+    <col width="3.2" customWidth="1" min="13" max="13"/>
+    <col width="3.2" customWidth="1" min="14" max="14"/>
+    <col width="3.2" customWidth="1" min="15" max="15"/>
+    <col width="3.2" customWidth="1" min="16" max="16"/>
+    <col width="3.2" customWidth="1" min="17" max="17"/>
+    <col width="3.2" customWidth="1" min="18" max="18"/>
+    <col width="3.2" customWidth="1" min="19" max="19"/>
+    <col width="3.2" customWidth="1" min="20" max="20"/>
+    <col width="3.2" customWidth="1" min="21" max="21"/>
+    <col width="3.2" customWidth="1" min="22" max="22"/>
+    <col width="3.2" customWidth="1" min="23" max="23"/>
+    <col width="3.2" customWidth="1" min="24" max="24"/>
+    <col width="3.2" customWidth="1" min="25" max="25"/>
+    <col width="3.2" customWidth="1" min="26" max="26"/>
+    <col width="3.2" customWidth="1" min="27" max="27"/>
+    <col width="3.2" customWidth="1" min="28" max="28"/>
+    <col width="3.2" customWidth="1" min="29" max="29"/>
+    <col width="3.2" customWidth="1" min="30" max="30"/>
+    <col width="3.2" customWidth="1" min="31" max="31"/>
+    <col width="3.2" customWidth="1" min="32" max="32"/>
+    <col width="3.2" customWidth="1" min="33" max="33"/>
+    <col width="3.2" customWidth="1" min="34" max="34"/>
+    <col width="3.2" customWidth="1" min="35" max="35"/>
+    <col width="3.2" customWidth="1" min="36" max="36"/>
+    <col width="3.2" customWidth="1" min="37" max="37"/>
+    <col width="3.2" customWidth="1" min="38" max="38"/>
+    <col width="3.2" customWidth="1" min="39" max="39"/>
+    <col width="3.2" customWidth="1" min="40" max="40"/>
+    <col width="3.2" customWidth="1" min="41" max="41"/>
+    <col width="3.2" customWidth="1" min="42" max="42"/>
+    <col width="3.2" customWidth="1" min="43" max="43"/>
+    <col width="3.2" customWidth="1" min="44" max="44"/>
+    <col width="3.2" customWidth="1" min="45" max="45"/>
+    <col width="3.2" customWidth="1" min="46" max="46"/>
+    <col width="3.2" customWidth="1" min="47" max="47"/>
+    <col width="3.2" customWidth="1" min="48" max="48"/>
+    <col width="3.2" customWidth="1" min="49" max="49"/>
+    <col width="3.2" customWidth="1" min="50" max="50"/>
+    <col width="3.2" customWidth="1" min="51" max="51"/>
+    <col width="3.2" customWidth="1" min="52" max="52"/>
+    <col width="3.2" customWidth="1" min="53" max="53"/>
+    <col width="3.2" customWidth="1" min="54" max="54"/>
+    <col width="3.2" customWidth="1" min="55" max="55"/>
+    <col width="3.2" customWidth="1" min="56" max="56"/>
+    <col width="3.2" customWidth="1" min="57" max="57"/>
+    <col width="3.2" customWidth="1" min="58" max="58"/>
+    <col width="3.2" customWidth="1" min="59" max="59"/>
+    <col width="3.2" customWidth="1" min="60" max="60"/>
+    <col width="3.2" customWidth="1" min="61" max="61"/>
+    <col width="3.2" customWidth="1" min="62" max="62"/>
+    <col width="14" customWidth="1" min="63" max="63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>目标时间轴（按预估完成节点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>左端为首个任务 2026-08-24，右端为最终任务 2026-10-23，其余任务按日历天数分段落在轴上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>一期零件图纸整理归档</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>一期零件下单采购</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>PAB060·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>PAB090·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>PAB115·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t>二期零件图纸整理归档</t>
+        </is>
+      </c>
+      <c r="S3" s="17" t="inlineStr">
+        <is>
+          <t>装配工具到位</t>
+        </is>
+      </c>
+      <c r="T3" s="17" t="inlineStr">
+        <is>
+          <t>PAB180·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="W3" s="17" t="inlineStr">
+        <is>
+          <t>PAB220·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="X3" s="17" t="inlineStr">
+        <is>
+          <t>装配线布局完成</t>
+        </is>
+      </c>
+      <c r="AC3" s="17" t="inlineStr">
+        <is>
+          <t>PAB090·工装实物到位</t>
+        </is>
+      </c>
+      <c r="AG3" s="17" t="inlineStr">
+        <is>
+          <t>PAB060·零件到位</t>
+        </is>
+      </c>
+      <c r="AH3" s="17" t="inlineStr">
+        <is>
+          <t>PAB115·工装实物到位</t>
+        </is>
+      </c>
+      <c r="AI3" s="17" t="inlineStr">
+        <is>
+          <t>PAB060·单级样机</t>
+        </is>
+      </c>
+      <c r="AJ3" s="17" t="inlineStr">
+        <is>
+          <t>PAB090·零件到位</t>
+        </is>
+      </c>
+      <c r="AK3" s="17" t="inlineStr">
+        <is>
+          <t>PAB060·双级样机</t>
+        </is>
+      </c>
+      <c r="AL3" s="17" t="inlineStr">
+        <is>
+          <t>PAB090·单级样机</t>
+        </is>
+      </c>
+      <c r="AM3" s="17" t="inlineStr">
+        <is>
+          <t>PAB090·双级样机</t>
+        </is>
+      </c>
+      <c r="AU3" s="17" t="inlineStr">
+        <is>
+          <t>PAB115·零件到位</t>
+        </is>
+      </c>
+      <c r="AV3" s="17" t="inlineStr">
+        <is>
+          <t>PAB115·单级样机</t>
+        </is>
+      </c>
+      <c r="AW3" s="17" t="inlineStr">
+        <is>
+          <t>PAB220·工装实物到位</t>
+        </is>
+      </c>
+      <c r="AX3" s="17" t="inlineStr">
+        <is>
+          <t>PAB115·双级样机</t>
+        </is>
+      </c>
+      <c r="AY3" s="17" t="inlineStr">
+        <is>
+          <t>PAB142·零件到位</t>
+        </is>
+      </c>
+      <c r="AZ3" s="17" t="inlineStr">
+        <is>
+          <t>PAB142·单级样机</t>
+        </is>
+      </c>
+      <c r="BB3" s="17" t="inlineStr">
+        <is>
+          <t>PAB142·双级样机</t>
+        </is>
+      </c>
+      <c r="BC3" s="17" t="inlineStr">
+        <is>
+          <t>PAB180·单级样机</t>
+        </is>
+      </c>
+      <c r="BF3" s="17" t="inlineStr">
+        <is>
+          <t>PAB180·双级样机</t>
+        </is>
+      </c>
+      <c r="BG3" s="17" t="inlineStr">
+        <is>
+          <t>PAB220·零件到位</t>
+        </is>
+      </c>
+      <c r="BH3" s="17" t="inlineStr">
+        <is>
+          <t>PAB220·单级样机</t>
+        </is>
+      </c>
+      <c r="BJ3" s="17" t="inlineStr">
+        <is>
+          <t>PAB220·双级样机</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>一期标准件下单采购</t>
+        </is>
+      </c>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>PAB142·工装图纸绘制</t>
+        </is>
+      </c>
+      <c r="S4" s="17" t="inlineStr">
+        <is>
+          <t>二期零件下单采购</t>
+        </is>
+      </c>
+      <c r="X4" s="17" t="inlineStr">
+        <is>
+          <t>PAB060·工装实物到位</t>
+        </is>
+      </c>
+      <c r="AG4" s="17" t="inlineStr">
+        <is>
+          <t>PAB060·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="AJ4" s="17" t="inlineStr">
+        <is>
+          <t>PAB090·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="AL4" s="17" t="inlineStr">
+        <is>
+          <t>PAB142·工装实物到位</t>
+        </is>
+      </c>
+      <c r="AU4" s="17" t="inlineStr">
+        <is>
+          <t>PAB115·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="AY4" s="17" t="inlineStr">
+        <is>
+          <t>PAB142·排针机安装调试</t>
+        </is>
+      </c>
+      <c r="BB4" s="17" t="inlineStr">
+        <is>
+          <t>PAB180·零件到位</t>
+        </is>
+      </c>
+      <c r="BG4" s="17" t="inlineStr">
+        <is>
+          <t>PAB220·排针机安装调试</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="S5" s="17" t="inlineStr">
+        <is>
+          <t>二期标准件下单采购</t>
+        </is>
+      </c>
+      <c r="AU5" s="17" t="inlineStr">
+        <is>
+          <t>PAB180·工装实物到位</t>
+        </is>
+      </c>
+      <c r="BB5" s="17" t="inlineStr">
+        <is>
+          <t>PAB180·排针机安装调试</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="O6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="Q6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="T6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="U6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="V6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="W6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="X6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="Y6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Z6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AA6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AB6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AC6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AD6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AE6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AF6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AG6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AH6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AI6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AJ6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AK6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AL6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AM6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AN6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AO6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AP6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AQ6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AR6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AS6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AT6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AU6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AV6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AW6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AX6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AY6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="BA6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BB6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="BC6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="BD6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BE6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BF6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="BG6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="BH6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="BI6" s="18" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BJ6" s="18" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-24 →</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="Q7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="R7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="S7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="T7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="U7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="V7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="W7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="X7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="Y7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="Z7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AA7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AB7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AC7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AD7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AE7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AF7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AG7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AH7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AI7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AJ7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AK7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AL7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AM7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AN7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AO7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AP7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AQ7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AR7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AS7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AT7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AU7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AV7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AW7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AX7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AY7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AZ7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BA7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BB7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BC7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BD7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BE7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BF7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BG7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BH7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BI7" s="20" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BJ7" s="20" t="inlineStr">
+        <is>
+          <t>▶</t>
+        </is>
+      </c>
+      <c r="BK7" s="19" t="inlineStr">
+        <is>
+          <t>→ 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="B8" s="21" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>46259</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>46262</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>46266</v>
+      </c>
+      <c r="M8" s="21" t="n">
+        <v>46269</v>
+      </c>
+      <c r="P8" s="21" t="n">
+        <v>46272</v>
+      </c>
+      <c r="S8" s="21" t="n">
+        <v>46275</v>
+      </c>
+      <c r="T8" s="21" t="n">
+        <v>46276</v>
+      </c>
+      <c r="W8" s="21" t="n">
+        <v>46279</v>
+      </c>
+      <c r="X8" s="21" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AC8" s="21" t="n">
+        <v>46285</v>
+      </c>
+      <c r="AG8" s="21" t="n">
+        <v>46289</v>
+      </c>
+      <c r="AH8" s="21" t="n">
+        <v>46290</v>
+      </c>
+      <c r="AI8" s="21" t="n">
+        <v>46291</v>
+      </c>
+      <c r="AJ8" s="21" t="n">
+        <v>46292</v>
+      </c>
+      <c r="AK8" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="AL8" s="21" t="n">
+        <v>46294</v>
+      </c>
+      <c r="AM8" s="21" t="n">
+        <v>46295</v>
+      </c>
+      <c r="AN8" s="21" t="n">
+        <v>46296</v>
+      </c>
+      <c r="AU8" s="21" t="n">
+        <v>46303</v>
+      </c>
+      <c r="AV8" s="21" t="n">
+        <v>46304</v>
+      </c>
+      <c r="AW8" s="21" t="n">
+        <v>46305</v>
+      </c>
+      <c r="AX8" s="21" t="n">
+        <v>46306</v>
+      </c>
+      <c r="AY8" s="21" t="n">
+        <v>46307</v>
+      </c>
+      <c r="AZ8" s="21" t="n">
+        <v>46308</v>
+      </c>
+      <c r="BB8" s="21" t="n">
+        <v>46310</v>
+      </c>
+      <c r="BC8" s="21" t="n">
+        <v>46311</v>
+      </c>
+      <c r="BF8" s="21" t="n">
+        <v>46314</v>
+      </c>
+      <c r="BG8" s="21" t="n">
+        <v>46315</v>
+      </c>
+      <c r="BH8" s="21" t="n">
+        <v>46316</v>
+      </c>
+      <c r="BJ8" s="21" t="n">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>实际时间轴（按实际完成节点；偏移度 = 实际 − 预估，正值延期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>尚无实际完成节点。填写主表「实际完成节点」后重新生成本表即可刷新本轴。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1"/>
+    <row r="13" ht="48" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="M14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="N14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="O14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="P14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="R14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="S14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="T14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="U14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="V14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="W14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="X14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Y14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="Z14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AA14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AB14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AC14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AD14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AE14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AF14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AG14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AH14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AI14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AJ14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AK14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AL14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AM14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AN14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AO14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AP14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AQ14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AR14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AS14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AT14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AU14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AV14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AW14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AX14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AY14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="AZ14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BA14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BB14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BC14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BD14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BE14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BF14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BG14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BH14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BI14" s="22" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="BJ14" s="22" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-24 →</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="O15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="S15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="T15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="U15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="V15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="W15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="X15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="Y15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="Z15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AA15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AB15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AC15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AD15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AE15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AF15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AG15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AH15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AI15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AJ15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AK15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AL15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AM15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AN15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AO15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AP15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AQ15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AR15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AS15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AT15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AU15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AV15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AW15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AX15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AY15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="AZ15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BA15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BB15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BC15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BD15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BE15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BF15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BG15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BH15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BI15" s="23" t="inlineStr">
+        <is>
+          <t>━</t>
+        </is>
+      </c>
+      <c r="BJ15" s="23" t="inlineStr">
+        <is>
+          <t>▶</t>
+        </is>
+      </c>
+      <c r="BK15" s="19" t="inlineStr">
+        <is>
+          <t>→ 2026-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="21" t="n">
+        <v>46258</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>46266</v>
+      </c>
+      <c r="X16" s="21" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AN16" s="21" t="n">
+        <v>46296</v>
+      </c>
+      <c r="BB16" s="21" t="n">
+        <v>46310</v>
+      </c>
+      <c r="BJ16" s="21" t="n">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>偏移图例：+N天=延期（红）；-N天=提前（绿）；0天=按期；待填=主表实际完成节点为空。两轴共用同一起止日期，便于对照时间偏移。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/PAB产品计划表.xlsx
+++ b/PAB产品计划表.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="166" formatCode="D"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,12 @@
     <font>
       <name val="微软雅黑"/>
       <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
@@ -79,17 +85,6 @@
     <font>
       <name val="微软雅黑"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="00334155"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -142,12 +137,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005B8BD5"/>
+        <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="002F80ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -166,7 +161,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -221,55 +216,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00B7C9D6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00B7C9D6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B7C9D6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00B7C9D6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B7C9D6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00B7C9D6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B7C9D6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B7C9D6"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -310,83 +261,68 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="13">
     <dxf>
       <font>
         <name val="微软雅黑"/>
         <b val="1"/>
-        <color rgb="00FFFFFF"/>
-        <sz val="10"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
         <color rgb="00FFFFFF"/>
         <sz val="10"/>
       </font>
@@ -405,6 +341,122 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="0086EFAC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="002F80ED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="002F80ED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DC2626"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0016A34A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="002F80ED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DC2626"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0016A34A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F59E0B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <color rgb="0014532D"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="0016A34A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2103,10 +2155,10 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="40" customHeight="1">
+    <row r="47" ht="48" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>说明：A列按第一期/第二期合并，B列按任务组合并。偏移天数=实际−预估（正值延期）。进度条见工作表「甘特图」：横轴每一格为 1 个自然日，色条长度等于从项目起始日到完成节点的日历天数。</t>
+          <t>说明：A列按第一期/第二期合并，B列按任务组合并。偏移天数=实际−预估（正值延期）。日期请在本表 E/F 列填写（不要手工涂色）：预估有日期后自动蓝底，实际填写后按时绿底、超时红底。甘特图色条随本表日期自动变长/变色，见工作表「甘特图」（向右滚动查看按天色条）。</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2181,20 @@
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(F2),ISNUMBER(E2),F2&gt;E2)</formula>
     </cfRule>
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>AND(ISNUMBER(F2),ISNUMBER(E2),F2&lt;=E2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E45">
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>ISNUMBER(E2)</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I45">
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="4" dxfId="3">
       <formula>AND(ISNUMBER(I2),I2&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="5" dxfId="1">
       <formula>AND(ISNUMBER(I2),I2&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2162,73 +2222,73 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="2.6" customWidth="1" min="7" max="7"/>
-    <col width="2.6" customWidth="1" min="8" max="8"/>
-    <col width="2.6" customWidth="1" min="9" max="9"/>
-    <col width="2.6" customWidth="1" min="10" max="10"/>
-    <col width="2.6" customWidth="1" min="11" max="11"/>
-    <col width="2.6" customWidth="1" min="12" max="12"/>
-    <col width="2.6" customWidth="1" min="13" max="13"/>
-    <col width="2.6" customWidth="1" min="14" max="14"/>
-    <col width="2.6" customWidth="1" min="15" max="15"/>
-    <col width="2.6" customWidth="1" min="16" max="16"/>
-    <col width="2.6" customWidth="1" min="17" max="17"/>
-    <col width="2.6" customWidth="1" min="18" max="18"/>
-    <col width="2.6" customWidth="1" min="19" max="19"/>
-    <col width="2.6" customWidth="1" min="20" max="20"/>
-    <col width="2.6" customWidth="1" min="21" max="21"/>
-    <col width="2.6" customWidth="1" min="22" max="22"/>
-    <col width="2.6" customWidth="1" min="23" max="23"/>
-    <col width="2.6" customWidth="1" min="24" max="24"/>
-    <col width="2.6" customWidth="1" min="25" max="25"/>
-    <col width="2.6" customWidth="1" min="26" max="26"/>
-    <col width="2.6" customWidth="1" min="27" max="27"/>
-    <col width="2.6" customWidth="1" min="28" max="28"/>
-    <col width="2.6" customWidth="1" min="29" max="29"/>
-    <col width="2.6" customWidth="1" min="30" max="30"/>
-    <col width="2.6" customWidth="1" min="31" max="31"/>
-    <col width="2.6" customWidth="1" min="32" max="32"/>
-    <col width="2.6" customWidth="1" min="33" max="33"/>
-    <col width="2.6" customWidth="1" min="34" max="34"/>
-    <col width="2.6" customWidth="1" min="35" max="35"/>
-    <col width="2.6" customWidth="1" min="36" max="36"/>
-    <col width="2.6" customWidth="1" min="37" max="37"/>
-    <col width="2.6" customWidth="1" min="38" max="38"/>
-    <col width="2.6" customWidth="1" min="39" max="39"/>
-    <col width="2.6" customWidth="1" min="40" max="40"/>
-    <col width="2.6" customWidth="1" min="41" max="41"/>
-    <col width="2.6" customWidth="1" min="42" max="42"/>
-    <col width="2.6" customWidth="1" min="43" max="43"/>
-    <col width="2.6" customWidth="1" min="44" max="44"/>
-    <col width="2.6" customWidth="1" min="45" max="45"/>
-    <col width="2.6" customWidth="1" min="46" max="46"/>
-    <col width="2.6" customWidth="1" min="47" max="47"/>
-    <col width="2.6" customWidth="1" min="48" max="48"/>
-    <col width="2.6" customWidth="1" min="49" max="49"/>
-    <col width="2.6" customWidth="1" min="50" max="50"/>
-    <col width="2.6" customWidth="1" min="51" max="51"/>
-    <col width="2.6" customWidth="1" min="52" max="52"/>
-    <col width="2.6" customWidth="1" min="53" max="53"/>
-    <col width="2.6" customWidth="1" min="54" max="54"/>
-    <col width="2.6" customWidth="1" min="55" max="55"/>
-    <col width="2.6" customWidth="1" min="56" max="56"/>
-    <col width="2.6" customWidth="1" min="57" max="57"/>
-    <col width="2.6" customWidth="1" min="58" max="58"/>
-    <col width="2.6" customWidth="1" min="59" max="59"/>
-    <col width="2.6" customWidth="1" min="60" max="60"/>
-    <col width="2.6" customWidth="1" min="61" max="61"/>
-    <col width="2.6" customWidth="1" min="62" max="62"/>
-    <col width="2.6" customWidth="1" min="63" max="63"/>
-    <col width="2.6" customWidth="1" min="64" max="64"/>
-    <col width="2.6" customWidth="1" min="65" max="65"/>
-    <col width="2.6" customWidth="1" min="66" max="66"/>
-    <col width="2.6" customWidth="1" min="67" max="67"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+    <col width="3" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
+    <col width="3" customWidth="1" min="16" max="16"/>
+    <col width="3" customWidth="1" min="17" max="17"/>
+    <col width="3" customWidth="1" min="18" max="18"/>
+    <col width="3" customWidth="1" min="19" max="19"/>
+    <col width="3" customWidth="1" min="20" max="20"/>
+    <col width="3" customWidth="1" min="21" max="21"/>
+    <col width="3" customWidth="1" min="22" max="22"/>
+    <col width="3" customWidth="1" min="23" max="23"/>
+    <col width="3" customWidth="1" min="24" max="24"/>
+    <col width="3" customWidth="1" min="25" max="25"/>
+    <col width="3" customWidth="1" min="26" max="26"/>
+    <col width="3" customWidth="1" min="27" max="27"/>
+    <col width="3" customWidth="1" min="28" max="28"/>
+    <col width="3" customWidth="1" min="29" max="29"/>
+    <col width="3" customWidth="1" min="30" max="30"/>
+    <col width="3" customWidth="1" min="31" max="31"/>
+    <col width="3" customWidth="1" min="32" max="32"/>
+    <col width="3" customWidth="1" min="33" max="33"/>
+    <col width="3" customWidth="1" min="34" max="34"/>
+    <col width="3" customWidth="1" min="35" max="35"/>
+    <col width="3" customWidth="1" min="36" max="36"/>
+    <col width="3" customWidth="1" min="37" max="37"/>
+    <col width="3" customWidth="1" min="38" max="38"/>
+    <col width="3" customWidth="1" min="39" max="39"/>
+    <col width="3" customWidth="1" min="40" max="40"/>
+    <col width="3" customWidth="1" min="41" max="41"/>
+    <col width="3" customWidth="1" min="42" max="42"/>
+    <col width="3" customWidth="1" min="43" max="43"/>
+    <col width="3" customWidth="1" min="44" max="44"/>
+    <col width="3" customWidth="1" min="45" max="45"/>
+    <col width="3" customWidth="1" min="46" max="46"/>
+    <col width="3" customWidth="1" min="47" max="47"/>
+    <col width="3" customWidth="1" min="48" max="48"/>
+    <col width="3" customWidth="1" min="49" max="49"/>
+    <col width="3" customWidth="1" min="50" max="50"/>
+    <col width="3" customWidth="1" min="51" max="51"/>
+    <col width="3" customWidth="1" min="52" max="52"/>
+    <col width="3" customWidth="1" min="53" max="53"/>
+    <col width="3" customWidth="1" min="54" max="54"/>
+    <col width="3" customWidth="1" min="55" max="55"/>
+    <col width="3" customWidth="1" min="56" max="56"/>
+    <col width="3" customWidth="1" min="57" max="57"/>
+    <col width="3" customWidth="1" min="58" max="58"/>
+    <col width="3" customWidth="1" min="59" max="59"/>
+    <col width="3" customWidth="1" min="60" max="60"/>
+    <col width="3" customWidth="1" min="61" max="61"/>
+    <col width="3" customWidth="1" min="62" max="62"/>
+    <col width="3" customWidth="1" min="63" max="63"/>
+    <col width="3" customWidth="1" min="64" max="64"/>
+    <col width="3" customWidth="1" min="65" max="65"/>
+    <col width="3" customWidth="1" min="66" max="66"/>
+    <col width="3" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>PAB 甘特图（2026-08-24 → 2026-10-23，每格 1 天；条长 = 日历天数）</t>
+          <t>PAB 甘特图（2026-08-24 → 2026-10-23，每格 1 天）。色条由条件格式自动生成：请在「时间节点计划表」填写预估/实际日期，无需手工涂色。</t>
         </is>
       </c>
       <c r="G1" s="15" t="inlineStr">
@@ -2520,7 +2580,7 @@
         <v>46318</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -2536,18 +2596,16 @@
           <t>一期零件图纸整理归档</t>
         </is>
       </c>
-      <c r="D3" s="22" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr"/>
-      <c r="G3" s="23" t="n">
-        <v>24</v>
-      </c>
+      <c r="D3" s="22">
+        <f>IF('时间节点计划表'!E2="","",'时间节点计划表'!E2)</f>
+        <v/>
+      </c>
+      <c r="E3" s="22">
+        <f>IF('时间节点计划表'!F2="","",'时间节点计划表'!F2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="23" t="inlineStr"/>
+      <c r="G3" s="24" t="n"/>
       <c r="H3" s="24" t="n"/>
       <c r="I3" s="24" t="n"/>
       <c r="J3" s="24" t="n"/>
@@ -2609,7 +2667,7 @@
       <c r="BN3" s="24" t="n"/>
       <c r="BO3" s="24" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -2625,38 +2683,33 @@
           <t>一期零件图纸整理归档</t>
         </is>
       </c>
-      <c r="D4" s="27" t="n">
-        <v>46258</v>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G4" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H4" s="29" t="n"/>
-      <c r="I4" s="29" t="n"/>
-      <c r="J4" s="29" t="n"/>
-      <c r="K4" s="29" t="n"/>
-      <c r="L4" s="29" t="n"/>
-      <c r="M4" s="29" t="n"/>
-      <c r="N4" s="29" t="n"/>
-      <c r="O4" s="29" t="n"/>
-      <c r="P4" s="29" t="n"/>
-      <c r="Q4" s="29" t="n"/>
-      <c r="R4" s="29" t="n"/>
-      <c r="S4" s="29" t="n"/>
-      <c r="T4" s="29" t="n"/>
-      <c r="U4" s="30" t="n"/>
+      <c r="D4" s="27">
+        <f>IF('时间节点计划表'!E2="","",'时间节点计划表'!E2)</f>
+        <v/>
+      </c>
+      <c r="E4" s="27">
+        <f>IF('时间节点计划表'!F2="","",'时间节点计划表'!F2)</f>
+        <v/>
+      </c>
+      <c r="F4" s="28">
+        <f>IF(OR(D4="",E4=""),"待填",E4-D4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="24" t="n"/>
+      <c r="H4" s="24" t="n"/>
+      <c r="I4" s="24" t="n"/>
+      <c r="J4" s="24" t="n"/>
+      <c r="K4" s="24" t="n"/>
+      <c r="L4" s="24" t="n"/>
+      <c r="M4" s="24" t="n"/>
+      <c r="N4" s="24" t="n"/>
+      <c r="O4" s="24" t="n"/>
+      <c r="P4" s="24" t="n"/>
+      <c r="Q4" s="24" t="n"/>
+      <c r="R4" s="24" t="n"/>
+      <c r="S4" s="24" t="n"/>
+      <c r="T4" s="24" t="n"/>
+      <c r="U4" s="24" t="n"/>
       <c r="V4" s="24" t="n"/>
       <c r="W4" s="24" t="n"/>
       <c r="X4" s="24" t="n"/>
@@ -2704,7 +2757,7 @@
       <c r="BN4" s="24" t="n"/>
       <c r="BO4" s="24" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1">
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -2720,19 +2773,17 @@
           <t>一期零件下单采购</t>
         </is>
       </c>
-      <c r="D5" s="22" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="23" t="n">
-        <v>25</v>
-      </c>
+      <c r="D5" s="22">
+        <f>IF('时间节点计划表'!E3="","",'时间节点计划表'!E3)</f>
+        <v/>
+      </c>
+      <c r="E5" s="22">
+        <f>IF('时间节点计划表'!F3="","",'时间节点计划表'!F3)</f>
+        <v/>
+      </c>
+      <c r="F5" s="23" t="inlineStr"/>
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n"/>
       <c r="I5" s="24" t="n"/>
       <c r="J5" s="24" t="n"/>
       <c r="K5" s="24" t="n"/>
@@ -2793,7 +2844,7 @@
       <c r="BN5" s="24" t="n"/>
       <c r="BO5" s="24" t="n"/>
     </row>
-    <row r="6" ht="16" customHeight="1">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -2809,38 +2860,33 @@
           <t>一期零件下单采购</t>
         </is>
       </c>
-      <c r="D6" s="27" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H6" s="29" t="n"/>
-      <c r="I6" s="29" t="n"/>
-      <c r="J6" s="29" t="n"/>
-      <c r="K6" s="29" t="n"/>
-      <c r="L6" s="29" t="n"/>
-      <c r="M6" s="29" t="n"/>
-      <c r="N6" s="29" t="n"/>
-      <c r="O6" s="29" t="n"/>
-      <c r="P6" s="29" t="n"/>
-      <c r="Q6" s="29" t="n"/>
-      <c r="R6" s="29" t="n"/>
-      <c r="S6" s="29" t="n"/>
-      <c r="T6" s="29" t="n"/>
-      <c r="U6" s="30" t="n"/>
+      <c r="D6" s="27">
+        <f>IF('时间节点计划表'!E3="","",'时间节点计划表'!E3)</f>
+        <v/>
+      </c>
+      <c r="E6" s="27">
+        <f>IF('时间节点计划表'!F3="","",'时间节点计划表'!F3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="28">
+        <f>IF(OR(D6="",E6=""),"待填",E6-D6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="24" t="n"/>
+      <c r="H6" s="24" t="n"/>
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="24" t="n"/>
+      <c r="K6" s="24" t="n"/>
+      <c r="L6" s="24" t="n"/>
+      <c r="M6" s="24" t="n"/>
+      <c r="N6" s="24" t="n"/>
+      <c r="O6" s="24" t="n"/>
+      <c r="P6" s="24" t="n"/>
+      <c r="Q6" s="24" t="n"/>
+      <c r="R6" s="24" t="n"/>
+      <c r="S6" s="24" t="n"/>
+      <c r="T6" s="24" t="n"/>
+      <c r="U6" s="24" t="n"/>
       <c r="V6" s="24" t="n"/>
       <c r="W6" s="24" t="n"/>
       <c r="X6" s="24" t="n"/>
@@ -2888,7 +2934,7 @@
       <c r="BN6" s="24" t="n"/>
       <c r="BO6" s="24" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -2904,19 +2950,17 @@
           <t>一期标准件下单采购</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="23" t="n">
-        <v>25</v>
-      </c>
+      <c r="D7" s="22">
+        <f>IF('时间节点计划表'!E4="","",'时间节点计划表'!E4)</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>IF('时间节点计划表'!F4="","",'时间节点计划表'!F4)</f>
+        <v/>
+      </c>
+      <c r="F7" s="23" t="inlineStr"/>
+      <c r="G7" s="24" t="n"/>
+      <c r="H7" s="24" t="n"/>
       <c r="I7" s="24" t="n"/>
       <c r="J7" s="24" t="n"/>
       <c r="K7" s="24" t="n"/>
@@ -2977,7 +3021,7 @@
       <c r="BN7" s="24" t="n"/>
       <c r="BO7" s="24" t="n"/>
     </row>
-    <row r="8" ht="16" customHeight="1">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -2993,38 +3037,33 @@
           <t>一期标准件下单采购</t>
         </is>
       </c>
-      <c r="D8" s="27" t="n">
-        <v>46259</v>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="29" t="n"/>
-      <c r="K8" s="29" t="n"/>
-      <c r="L8" s="29" t="n"/>
-      <c r="M8" s="29" t="n"/>
-      <c r="N8" s="29" t="n"/>
-      <c r="O8" s="29" t="n"/>
-      <c r="P8" s="29" t="n"/>
-      <c r="Q8" s="29" t="n"/>
-      <c r="R8" s="29" t="n"/>
-      <c r="S8" s="29" t="n"/>
-      <c r="T8" s="29" t="n"/>
-      <c r="U8" s="30" t="n"/>
+      <c r="D8" s="27">
+        <f>IF('时间节点计划表'!E4="","",'时间节点计划表'!E4)</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>IF('时间节点计划表'!F4="","",'时间节点计划表'!F4)</f>
+        <v/>
+      </c>
+      <c r="F8" s="28">
+        <f>IF(OR(D8="",E8=""),"待填",E8-D8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+      <c r="I8" s="24" t="n"/>
+      <c r="J8" s="24" t="n"/>
+      <c r="K8" s="24" t="n"/>
+      <c r="L8" s="24" t="n"/>
+      <c r="M8" s="24" t="n"/>
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="24" t="n"/>
+      <c r="P8" s="24" t="n"/>
+      <c r="Q8" s="24" t="n"/>
+      <c r="R8" s="24" t="n"/>
+      <c r="S8" s="24" t="n"/>
+      <c r="T8" s="24" t="n"/>
+      <c r="U8" s="24" t="n"/>
       <c r="V8" s="24" t="n"/>
       <c r="W8" s="24" t="n"/>
       <c r="X8" s="24" t="n"/>
@@ -3072,7 +3111,7 @@
       <c r="BN8" s="24" t="n"/>
       <c r="BO8" s="24" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -3088,40 +3127,38 @@
           <t>装配线布局完成</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="31" t="n"/>
-      <c r="H9" s="31" t="n"/>
-      <c r="I9" s="31" t="n"/>
-      <c r="J9" s="31" t="n"/>
-      <c r="K9" s="31" t="n"/>
-      <c r="L9" s="31" t="n"/>
-      <c r="M9" s="31" t="n"/>
-      <c r="N9" s="31" t="n"/>
-      <c r="O9" s="31" t="n"/>
-      <c r="P9" s="31" t="n"/>
-      <c r="Q9" s="31" t="n"/>
-      <c r="R9" s="31" t="n"/>
-      <c r="S9" s="31" t="n"/>
-      <c r="T9" s="31" t="n"/>
-      <c r="U9" s="31" t="n"/>
-      <c r="V9" s="31" t="n"/>
-      <c r="W9" s="31" t="n"/>
-      <c r="X9" s="31" t="n"/>
-      <c r="Y9" s="31" t="n"/>
-      <c r="Z9" s="31" t="n"/>
-      <c r="AA9" s="31" t="n"/>
-      <c r="AB9" s="31" t="n"/>
-      <c r="AC9" s="23" t="n">
-        <v>15</v>
-      </c>
+      <c r="D9" s="22">
+        <f>IF('时间节点计划表'!E5="","",'时间节点计划表'!E5)</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>IF('时间节点计划表'!F5="","",'时间节点计划表'!F5)</f>
+        <v/>
+      </c>
+      <c r="F9" s="23" t="inlineStr"/>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
+      <c r="K9" s="24" t="n"/>
+      <c r="L9" s="24" t="n"/>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="24" t="n"/>
+      <c r="O9" s="24" t="n"/>
+      <c r="P9" s="24" t="n"/>
+      <c r="Q9" s="24" t="n"/>
+      <c r="R9" s="24" t="n"/>
+      <c r="S9" s="24" t="n"/>
+      <c r="T9" s="24" t="n"/>
+      <c r="U9" s="24" t="n"/>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="24" t="n"/>
+      <c r="X9" s="24" t="n"/>
+      <c r="Y9" s="24" t="n"/>
+      <c r="Z9" s="24" t="n"/>
+      <c r="AA9" s="24" t="n"/>
+      <c r="AB9" s="24" t="n"/>
+      <c r="AC9" s="24" t="n"/>
       <c r="AD9" s="24" t="n"/>
       <c r="AE9" s="24" t="n"/>
       <c r="AF9" s="24" t="n"/>
@@ -3161,7 +3198,7 @@
       <c r="BN9" s="24" t="n"/>
       <c r="BO9" s="24" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -3177,38 +3214,33 @@
           <t>装配线布局完成</t>
         </is>
       </c>
-      <c r="D10" s="27" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="29" t="n"/>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="29" t="n"/>
-      <c r="P10" s="29" t="n"/>
-      <c r="Q10" s="29" t="n"/>
-      <c r="R10" s="29" t="n"/>
-      <c r="S10" s="29" t="n"/>
-      <c r="T10" s="29" t="n"/>
-      <c r="U10" s="30" t="n"/>
+      <c r="D10" s="27">
+        <f>IF('时间节点计划表'!E5="","",'时间节点计划表'!E5)</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>IF('时间节点计划表'!F5="","",'时间节点计划表'!F5)</f>
+        <v/>
+      </c>
+      <c r="F10" s="28">
+        <f>IF(OR(D10="",E10=""),"待填",E10-D10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="24" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="24" t="n"/>
+      <c r="K10" s="24" t="n"/>
+      <c r="L10" s="24" t="n"/>
+      <c r="M10" s="24" t="n"/>
+      <c r="N10" s="24" t="n"/>
+      <c r="O10" s="24" t="n"/>
+      <c r="P10" s="24" t="n"/>
+      <c r="Q10" s="24" t="n"/>
+      <c r="R10" s="24" t="n"/>
+      <c r="S10" s="24" t="n"/>
+      <c r="T10" s="24" t="n"/>
+      <c r="U10" s="24" t="n"/>
       <c r="V10" s="24" t="n"/>
       <c r="W10" s="24" t="n"/>
       <c r="X10" s="24" t="n"/>
@@ -3256,7 +3288,7 @@
       <c r="BN10" s="24" t="n"/>
       <c r="BO10" s="24" t="n"/>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -3272,35 +3304,33 @@
           <t>装配工具到位</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n">
-        <v>46275</v>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr"/>
-      <c r="G11" s="31" t="n"/>
-      <c r="H11" s="31" t="n"/>
-      <c r="I11" s="31" t="n"/>
-      <c r="J11" s="31" t="n"/>
-      <c r="K11" s="31" t="n"/>
-      <c r="L11" s="31" t="n"/>
-      <c r="M11" s="31" t="n"/>
-      <c r="N11" s="31" t="n"/>
-      <c r="O11" s="31" t="n"/>
-      <c r="P11" s="31" t="n"/>
-      <c r="Q11" s="31" t="n"/>
-      <c r="R11" s="31" t="n"/>
-      <c r="S11" s="31" t="n"/>
-      <c r="T11" s="31" t="n"/>
-      <c r="U11" s="31" t="n"/>
-      <c r="V11" s="31" t="n"/>
-      <c r="W11" s="31" t="n"/>
-      <c r="X11" s="23" t="n">
-        <v>10</v>
-      </c>
+      <c r="D11" s="22">
+        <f>IF('时间节点计划表'!E6="","",'时间节点计划表'!E6)</f>
+        <v/>
+      </c>
+      <c r="E11" s="22">
+        <f>IF('时间节点计划表'!F6="","",'时间节点计划表'!F6)</f>
+        <v/>
+      </c>
+      <c r="F11" s="23" t="inlineStr"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="24" t="n"/>
+      <c r="K11" s="24" t="n"/>
+      <c r="L11" s="24" t="n"/>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="24" t="n"/>
+      <c r="O11" s="24" t="n"/>
+      <c r="P11" s="24" t="n"/>
+      <c r="Q11" s="24" t="n"/>
+      <c r="R11" s="24" t="n"/>
+      <c r="S11" s="24" t="n"/>
+      <c r="T11" s="24" t="n"/>
+      <c r="U11" s="24" t="n"/>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="24" t="n"/>
+      <c r="X11" s="24" t="n"/>
       <c r="Y11" s="24" t="n"/>
       <c r="Z11" s="24" t="n"/>
       <c r="AA11" s="24" t="n"/>
@@ -3345,7 +3375,7 @@
       <c r="BN11" s="24" t="n"/>
       <c r="BO11" s="24" t="n"/>
     </row>
-    <row r="12" ht="16" customHeight="1">
+    <row r="12" ht="18" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -3361,38 +3391,33 @@
           <t>装配工具到位</t>
         </is>
       </c>
-      <c r="D12" s="27" t="n">
-        <v>46275</v>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F12" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="29" t="n"/>
-      <c r="K12" s="29" t="n"/>
-      <c r="L12" s="29" t="n"/>
-      <c r="M12" s="29" t="n"/>
-      <c r="N12" s="29" t="n"/>
-      <c r="O12" s="29" t="n"/>
-      <c r="P12" s="29" t="n"/>
-      <c r="Q12" s="29" t="n"/>
-      <c r="R12" s="29" t="n"/>
-      <c r="S12" s="29" t="n"/>
-      <c r="T12" s="29" t="n"/>
-      <c r="U12" s="30" t="n"/>
+      <c r="D12" s="27">
+        <f>IF('时间节点计划表'!E6="","",'时间节点计划表'!E6)</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>IF('时间节点计划表'!F6="","",'时间节点计划表'!F6)</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>IF(OR(D12="",E12=""),"待填",E12-D12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="24" t="n"/>
+      <c r="K12" s="24" t="n"/>
+      <c r="L12" s="24" t="n"/>
+      <c r="M12" s="24" t="n"/>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="24" t="n"/>
+      <c r="P12" s="24" t="n"/>
+      <c r="Q12" s="24" t="n"/>
+      <c r="R12" s="24" t="n"/>
+      <c r="S12" s="24" t="n"/>
+      <c r="T12" s="24" t="n"/>
+      <c r="U12" s="24" t="n"/>
       <c r="V12" s="24" t="n"/>
       <c r="W12" s="24" t="n"/>
       <c r="X12" s="24" t="n"/>
@@ -3440,7 +3465,7 @@
       <c r="BN12" s="24" t="n"/>
       <c r="BO12" s="24" t="n"/>
     </row>
-    <row r="13" ht="16" customHeight="1">
+    <row r="13" ht="18" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -3456,49 +3481,47 @@
           <t>PAB060·零件到位</t>
         </is>
       </c>
-      <c r="D13" s="22" t="n">
-        <v>46289</v>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="31" t="n"/>
-      <c r="I13" s="31" t="n"/>
-      <c r="J13" s="31" t="n"/>
-      <c r="K13" s="31" t="n"/>
-      <c r="L13" s="31" t="n"/>
-      <c r="M13" s="31" t="n"/>
-      <c r="N13" s="31" t="n"/>
-      <c r="O13" s="31" t="n"/>
-      <c r="P13" s="31" t="n"/>
-      <c r="Q13" s="31" t="n"/>
-      <c r="R13" s="31" t="n"/>
-      <c r="S13" s="31" t="n"/>
-      <c r="T13" s="31" t="n"/>
-      <c r="U13" s="31" t="n"/>
-      <c r="V13" s="31" t="n"/>
-      <c r="W13" s="31" t="n"/>
-      <c r="X13" s="31" t="n"/>
-      <c r="Y13" s="31" t="n"/>
-      <c r="Z13" s="31" t="n"/>
-      <c r="AA13" s="31" t="n"/>
-      <c r="AB13" s="31" t="n"/>
-      <c r="AC13" s="31" t="n"/>
-      <c r="AD13" s="31" t="n"/>
-      <c r="AE13" s="31" t="n"/>
-      <c r="AF13" s="31" t="n"/>
-      <c r="AG13" s="31" t="n"/>
-      <c r="AH13" s="31" t="n"/>
-      <c r="AI13" s="31" t="n"/>
-      <c r="AJ13" s="31" t="n"/>
-      <c r="AK13" s="31" t="n"/>
-      <c r="AL13" s="23" t="n">
-        <v>24</v>
-      </c>
+      <c r="D13" s="22">
+        <f>IF('时间节点计划表'!E7="","",'时间节点计划表'!E7)</f>
+        <v/>
+      </c>
+      <c r="E13" s="22">
+        <f>IF('时间节点计划表'!F7="","",'时间节点计划表'!F7)</f>
+        <v/>
+      </c>
+      <c r="F13" s="23" t="inlineStr"/>
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="24" t="n"/>
+      <c r="I13" s="24" t="n"/>
+      <c r="J13" s="24" t="n"/>
+      <c r="K13" s="24" t="n"/>
+      <c r="L13" s="24" t="n"/>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="24" t="n"/>
+      <c r="O13" s="24" t="n"/>
+      <c r="P13" s="24" t="n"/>
+      <c r="Q13" s="24" t="n"/>
+      <c r="R13" s="24" t="n"/>
+      <c r="S13" s="24" t="n"/>
+      <c r="T13" s="24" t="n"/>
+      <c r="U13" s="24" t="n"/>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="24" t="n"/>
+      <c r="X13" s="24" t="n"/>
+      <c r="Y13" s="24" t="n"/>
+      <c r="Z13" s="24" t="n"/>
+      <c r="AA13" s="24" t="n"/>
+      <c r="AB13" s="24" t="n"/>
+      <c r="AC13" s="24" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="24" t="n"/>
+      <c r="AF13" s="24" t="n"/>
+      <c r="AG13" s="24" t="n"/>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="24" t="n"/>
+      <c r="AJ13" s="24" t="n"/>
+      <c r="AK13" s="24" t="n"/>
+      <c r="AL13" s="24" t="n"/>
       <c r="AM13" s="24" t="n"/>
       <c r="AN13" s="24" t="n"/>
       <c r="AO13" s="24" t="n"/>
@@ -3529,7 +3552,7 @@
       <c r="BN13" s="24" t="n"/>
       <c r="BO13" s="24" t="n"/>
     </row>
-    <row r="14" ht="16" customHeight="1">
+    <row r="14" ht="18" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -3545,38 +3568,33 @@
           <t>PAB060·零件到位</t>
         </is>
       </c>
-      <c r="D14" s="27" t="n">
-        <v>46289</v>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G14" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="n"/>
-      <c r="I14" s="29" t="n"/>
-      <c r="J14" s="29" t="n"/>
-      <c r="K14" s="29" t="n"/>
-      <c r="L14" s="29" t="n"/>
-      <c r="M14" s="29" t="n"/>
-      <c r="N14" s="29" t="n"/>
-      <c r="O14" s="29" t="n"/>
-      <c r="P14" s="29" t="n"/>
-      <c r="Q14" s="29" t="n"/>
-      <c r="R14" s="29" t="n"/>
-      <c r="S14" s="29" t="n"/>
-      <c r="T14" s="29" t="n"/>
-      <c r="U14" s="30" t="n"/>
+      <c r="D14" s="27">
+        <f>IF('时间节点计划表'!E7="","",'时间节点计划表'!E7)</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>IF('时间节点计划表'!F7="","",'时间节点计划表'!F7)</f>
+        <v/>
+      </c>
+      <c r="F14" s="28">
+        <f>IF(OR(D14="",E14=""),"待填",E14-D14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="24" t="n"/>
+      <c r="K14" s="24" t="n"/>
+      <c r="L14" s="24" t="n"/>
+      <c r="M14" s="24" t="n"/>
+      <c r="N14" s="24" t="n"/>
+      <c r="O14" s="24" t="n"/>
+      <c r="P14" s="24" t="n"/>
+      <c r="Q14" s="24" t="n"/>
+      <c r="R14" s="24" t="n"/>
+      <c r="S14" s="24" t="n"/>
+      <c r="T14" s="24" t="n"/>
+      <c r="U14" s="24" t="n"/>
       <c r="V14" s="24" t="n"/>
       <c r="W14" s="24" t="n"/>
       <c r="X14" s="24" t="n"/>
@@ -3624,7 +3642,7 @@
       <c r="BN14" s="24" t="n"/>
       <c r="BO14" s="24" t="n"/>
     </row>
-    <row r="15" ht="16" customHeight="1">
+    <row r="15" ht="18" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -3640,22 +3658,20 @@
           <t>PAB060·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D15" s="22" t="n">
-        <v>46262</v>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="31" t="n"/>
-      <c r="H15" s="31" t="n"/>
-      <c r="I15" s="31" t="n"/>
-      <c r="J15" s="31" t="n"/>
-      <c r="K15" s="23" t="n">
-        <v>28</v>
-      </c>
+      <c r="D15" s="22">
+        <f>IF('时间节点计划表'!E8="","",'时间节点计划表'!E8)</f>
+        <v/>
+      </c>
+      <c r="E15" s="22">
+        <f>IF('时间节点计划表'!F8="","",'时间节点计划表'!F8)</f>
+        <v/>
+      </c>
+      <c r="F15" s="23" t="inlineStr"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
+      <c r="K15" s="24" t="n"/>
       <c r="L15" s="24" t="n"/>
       <c r="M15" s="24" t="n"/>
       <c r="N15" s="24" t="n"/>
@@ -3713,7 +3729,7 @@
       <c r="BN15" s="24" t="n"/>
       <c r="BO15" s="24" t="n"/>
     </row>
-    <row r="16" ht="16" customHeight="1">
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -3729,38 +3745,33 @@
           <t>PAB060·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D16" s="27" t="n">
-        <v>46262</v>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F16" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G16" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H16" s="29" t="n"/>
-      <c r="I16" s="29" t="n"/>
-      <c r="J16" s="29" t="n"/>
-      <c r="K16" s="29" t="n"/>
-      <c r="L16" s="29" t="n"/>
-      <c r="M16" s="29" t="n"/>
-      <c r="N16" s="29" t="n"/>
-      <c r="O16" s="29" t="n"/>
-      <c r="P16" s="29" t="n"/>
-      <c r="Q16" s="29" t="n"/>
-      <c r="R16" s="29" t="n"/>
-      <c r="S16" s="29" t="n"/>
-      <c r="T16" s="29" t="n"/>
-      <c r="U16" s="30" t="n"/>
+      <c r="D16" s="27">
+        <f>IF('时间节点计划表'!E8="","",'时间节点计划表'!E8)</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>IF('时间节点计划表'!F8="","",'时间节点计划表'!F8)</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>IF(OR(D16="",E16=""),"待填",E16-D16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="24" t="n"/>
+      <c r="I16" s="24" t="n"/>
+      <c r="J16" s="24" t="n"/>
+      <c r="K16" s="24" t="n"/>
+      <c r="L16" s="24" t="n"/>
+      <c r="M16" s="24" t="n"/>
+      <c r="N16" s="24" t="n"/>
+      <c r="O16" s="24" t="n"/>
+      <c r="P16" s="24" t="n"/>
+      <c r="Q16" s="24" t="n"/>
+      <c r="R16" s="24" t="n"/>
+      <c r="S16" s="24" t="n"/>
+      <c r="T16" s="24" t="n"/>
+      <c r="U16" s="24" t="n"/>
       <c r="V16" s="24" t="n"/>
       <c r="W16" s="24" t="n"/>
       <c r="X16" s="24" t="n"/>
@@ -3808,7 +3819,7 @@
       <c r="BN16" s="24" t="n"/>
       <c r="BO16" s="24" t="n"/>
     </row>
-    <row r="17" ht="16" customHeight="1">
+    <row r="17" ht="18" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -3824,40 +3835,38 @@
           <t>PAB060·工装实物到位</t>
         </is>
       </c>
-      <c r="D17" s="22" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="31" t="n"/>
-      <c r="I17" s="31" t="n"/>
-      <c r="J17" s="31" t="n"/>
-      <c r="K17" s="31" t="n"/>
-      <c r="L17" s="31" t="n"/>
-      <c r="M17" s="31" t="n"/>
-      <c r="N17" s="31" t="n"/>
-      <c r="O17" s="31" t="n"/>
-      <c r="P17" s="31" t="n"/>
-      <c r="Q17" s="31" t="n"/>
-      <c r="R17" s="31" t="n"/>
-      <c r="S17" s="31" t="n"/>
-      <c r="T17" s="31" t="n"/>
-      <c r="U17" s="31" t="n"/>
-      <c r="V17" s="31" t="n"/>
-      <c r="W17" s="31" t="n"/>
-      <c r="X17" s="31" t="n"/>
-      <c r="Y17" s="31" t="n"/>
-      <c r="Z17" s="31" t="n"/>
-      <c r="AA17" s="31" t="n"/>
-      <c r="AB17" s="31" t="n"/>
-      <c r="AC17" s="23" t="n">
-        <v>15</v>
-      </c>
+      <c r="D17" s="22">
+        <f>IF('时间节点计划表'!E9="","",'时间节点计划表'!E9)</f>
+        <v/>
+      </c>
+      <c r="E17" s="22">
+        <f>IF('时间节点计划表'!F9="","",'时间节点计划表'!F9)</f>
+        <v/>
+      </c>
+      <c r="F17" s="23" t="inlineStr"/>
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="24" t="n"/>
+      <c r="I17" s="24" t="n"/>
+      <c r="J17" s="24" t="n"/>
+      <c r="K17" s="24" t="n"/>
+      <c r="L17" s="24" t="n"/>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="24" t="n"/>
+      <c r="O17" s="24" t="n"/>
+      <c r="P17" s="24" t="n"/>
+      <c r="Q17" s="24" t="n"/>
+      <c r="R17" s="24" t="n"/>
+      <c r="S17" s="24" t="n"/>
+      <c r="T17" s="24" t="n"/>
+      <c r="U17" s="24" t="n"/>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="24" t="n"/>
+      <c r="X17" s="24" t="n"/>
+      <c r="Y17" s="24" t="n"/>
+      <c r="Z17" s="24" t="n"/>
+      <c r="AA17" s="24" t="n"/>
+      <c r="AB17" s="24" t="n"/>
+      <c r="AC17" s="24" t="n"/>
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="24" t="n"/>
       <c r="AF17" s="24" t="n"/>
@@ -3897,7 +3906,7 @@
       <c r="BN17" s="24" t="n"/>
       <c r="BO17" s="24" t="n"/>
     </row>
-    <row r="18" ht="16" customHeight="1">
+    <row r="18" ht="18" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -3913,38 +3922,33 @@
           <t>PAB060·工装实物到位</t>
         </is>
       </c>
-      <c r="D18" s="27" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G18" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H18" s="29" t="n"/>
-      <c r="I18" s="29" t="n"/>
-      <c r="J18" s="29" t="n"/>
-      <c r="K18" s="29" t="n"/>
-      <c r="L18" s="29" t="n"/>
-      <c r="M18" s="29" t="n"/>
-      <c r="N18" s="29" t="n"/>
-      <c r="O18" s="29" t="n"/>
-      <c r="P18" s="29" t="n"/>
-      <c r="Q18" s="29" t="n"/>
-      <c r="R18" s="29" t="n"/>
-      <c r="S18" s="29" t="n"/>
-      <c r="T18" s="29" t="n"/>
-      <c r="U18" s="30" t="n"/>
+      <c r="D18" s="27">
+        <f>IF('时间节点计划表'!E9="","",'时间节点计划表'!E9)</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>IF('时间节点计划表'!F9="","",'时间节点计划表'!F9)</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>IF(OR(D18="",E18=""),"待填",E18-D18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="n"/>
+      <c r="I18" s="24" t="n"/>
+      <c r="J18" s="24" t="n"/>
+      <c r="K18" s="24" t="n"/>
+      <c r="L18" s="24" t="n"/>
+      <c r="M18" s="24" t="n"/>
+      <c r="N18" s="24" t="n"/>
+      <c r="O18" s="24" t="n"/>
+      <c r="P18" s="24" t="n"/>
+      <c r="Q18" s="24" t="n"/>
+      <c r="R18" s="24" t="n"/>
+      <c r="S18" s="24" t="n"/>
+      <c r="T18" s="24" t="n"/>
+      <c r="U18" s="24" t="n"/>
       <c r="V18" s="24" t="n"/>
       <c r="W18" s="24" t="n"/>
       <c r="X18" s="24" t="n"/>
@@ -3992,7 +3996,7 @@
       <c r="BN18" s="24" t="n"/>
       <c r="BO18" s="24" t="n"/>
     </row>
-    <row r="19" ht="16" customHeight="1">
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -4008,49 +4012,47 @@
           <t>PAB060·排针机安装调试</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n">
-        <v>46289</v>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr"/>
-      <c r="G19" s="31" t="n"/>
-      <c r="H19" s="31" t="n"/>
-      <c r="I19" s="31" t="n"/>
-      <c r="J19" s="31" t="n"/>
-      <c r="K19" s="31" t="n"/>
-      <c r="L19" s="31" t="n"/>
-      <c r="M19" s="31" t="n"/>
-      <c r="N19" s="31" t="n"/>
-      <c r="O19" s="31" t="n"/>
-      <c r="P19" s="31" t="n"/>
-      <c r="Q19" s="31" t="n"/>
-      <c r="R19" s="31" t="n"/>
-      <c r="S19" s="31" t="n"/>
-      <c r="T19" s="31" t="n"/>
-      <c r="U19" s="31" t="n"/>
-      <c r="V19" s="31" t="n"/>
-      <c r="W19" s="31" t="n"/>
-      <c r="X19" s="31" t="n"/>
-      <c r="Y19" s="31" t="n"/>
-      <c r="Z19" s="31" t="n"/>
-      <c r="AA19" s="31" t="n"/>
-      <c r="AB19" s="31" t="n"/>
-      <c r="AC19" s="31" t="n"/>
-      <c r="AD19" s="31" t="n"/>
-      <c r="AE19" s="31" t="n"/>
-      <c r="AF19" s="31" t="n"/>
-      <c r="AG19" s="31" t="n"/>
-      <c r="AH19" s="31" t="n"/>
-      <c r="AI19" s="31" t="n"/>
-      <c r="AJ19" s="31" t="n"/>
-      <c r="AK19" s="31" t="n"/>
-      <c r="AL19" s="23" t="n">
-        <v>24</v>
-      </c>
+      <c r="D19" s="22">
+        <f>IF('时间节点计划表'!E10="","",'时间节点计划表'!E10)</f>
+        <v/>
+      </c>
+      <c r="E19" s="22">
+        <f>IF('时间节点计划表'!F10="","",'时间节点计划表'!F10)</f>
+        <v/>
+      </c>
+      <c r="F19" s="23" t="inlineStr"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+      <c r="I19" s="24" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="24" t="n"/>
+      <c r="L19" s="24" t="n"/>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="24" t="n"/>
+      <c r="O19" s="24" t="n"/>
+      <c r="P19" s="24" t="n"/>
+      <c r="Q19" s="24" t="n"/>
+      <c r="R19" s="24" t="n"/>
+      <c r="S19" s="24" t="n"/>
+      <c r="T19" s="24" t="n"/>
+      <c r="U19" s="24" t="n"/>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="24" t="n"/>
+      <c r="X19" s="24" t="n"/>
+      <c r="Y19" s="24" t="n"/>
+      <c r="Z19" s="24" t="n"/>
+      <c r="AA19" s="24" t="n"/>
+      <c r="AB19" s="24" t="n"/>
+      <c r="AC19" s="24" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="24" t="n"/>
+      <c r="AF19" s="24" t="n"/>
+      <c r="AG19" s="24" t="n"/>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="24" t="n"/>
+      <c r="AJ19" s="24" t="n"/>
+      <c r="AK19" s="24" t="n"/>
+      <c r="AL19" s="24" t="n"/>
       <c r="AM19" s="24" t="n"/>
       <c r="AN19" s="24" t="n"/>
       <c r="AO19" s="24" t="n"/>
@@ -4081,7 +4083,7 @@
       <c r="BN19" s="24" t="n"/>
       <c r="BO19" s="24" t="n"/>
     </row>
-    <row r="20" ht="16" customHeight="1">
+    <row r="20" ht="18" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -4097,38 +4099,33 @@
           <t>PAB060·排针机安装调试</t>
         </is>
       </c>
-      <c r="D20" s="27" t="n">
-        <v>46289</v>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G20" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H20" s="29" t="n"/>
-      <c r="I20" s="29" t="n"/>
-      <c r="J20" s="29" t="n"/>
-      <c r="K20" s="29" t="n"/>
-      <c r="L20" s="29" t="n"/>
-      <c r="M20" s="29" t="n"/>
-      <c r="N20" s="29" t="n"/>
-      <c r="O20" s="29" t="n"/>
-      <c r="P20" s="29" t="n"/>
-      <c r="Q20" s="29" t="n"/>
-      <c r="R20" s="29" t="n"/>
-      <c r="S20" s="29" t="n"/>
-      <c r="T20" s="29" t="n"/>
-      <c r="U20" s="30" t="n"/>
+      <c r="D20" s="27">
+        <f>IF('时间节点计划表'!E10="","",'时间节点计划表'!E10)</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>IF('时间节点计划表'!F10="","",'时间节点计划表'!F10)</f>
+        <v/>
+      </c>
+      <c r="F20" s="28">
+        <f>IF(OR(D20="",E20=""),"待填",E20-D20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="24" t="n"/>
+      <c r="H20" s="24" t="n"/>
+      <c r="I20" s="24" t="n"/>
+      <c r="J20" s="24" t="n"/>
+      <c r="K20" s="24" t="n"/>
+      <c r="L20" s="24" t="n"/>
+      <c r="M20" s="24" t="n"/>
+      <c r="N20" s="24" t="n"/>
+      <c r="O20" s="24" t="n"/>
+      <c r="P20" s="24" t="n"/>
+      <c r="Q20" s="24" t="n"/>
+      <c r="R20" s="24" t="n"/>
+      <c r="S20" s="24" t="n"/>
+      <c r="T20" s="24" t="n"/>
+      <c r="U20" s="24" t="n"/>
       <c r="V20" s="24" t="n"/>
       <c r="W20" s="24" t="n"/>
       <c r="X20" s="24" t="n"/>
@@ -4176,7 +4173,7 @@
       <c r="BN20" s="24" t="n"/>
       <c r="BO20" s="24" t="n"/>
     </row>
-    <row r="21" ht="16" customHeight="1">
+    <row r="21" ht="18" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -4192,51 +4189,49 @@
           <t>PAB060·单级样机</t>
         </is>
       </c>
-      <c r="D21" s="22" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="31" t="n"/>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="31" t="n"/>
-      <c r="J21" s="31" t="n"/>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="31" t="n"/>
-      <c r="M21" s="31" t="n"/>
-      <c r="N21" s="31" t="n"/>
-      <c r="O21" s="31" t="n"/>
-      <c r="P21" s="31" t="n"/>
-      <c r="Q21" s="31" t="n"/>
-      <c r="R21" s="31" t="n"/>
-      <c r="S21" s="31" t="n"/>
-      <c r="T21" s="31" t="n"/>
-      <c r="U21" s="31" t="n"/>
-      <c r="V21" s="31" t="n"/>
-      <c r="W21" s="31" t="n"/>
-      <c r="X21" s="31" t="n"/>
-      <c r="Y21" s="31" t="n"/>
-      <c r="Z21" s="31" t="n"/>
-      <c r="AA21" s="31" t="n"/>
-      <c r="AB21" s="31" t="n"/>
-      <c r="AC21" s="31" t="n"/>
-      <c r="AD21" s="31" t="n"/>
-      <c r="AE21" s="31" t="n"/>
-      <c r="AF21" s="31" t="n"/>
-      <c r="AG21" s="31" t="n"/>
-      <c r="AH21" s="31" t="n"/>
-      <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
-      <c r="AK21" s="31" t="n"/>
-      <c r="AL21" s="31" t="n"/>
-      <c r="AM21" s="31" t="n"/>
-      <c r="AN21" s="23" t="n">
-        <v>26</v>
-      </c>
+      <c r="D21" s="22">
+        <f>IF('时间节点计划表'!E11="","",'时间节点计划表'!E11)</f>
+        <v/>
+      </c>
+      <c r="E21" s="22">
+        <f>IF('时间节点计划表'!F11="","",'时间节点计划表'!F11)</f>
+        <v/>
+      </c>
+      <c r="F21" s="23" t="inlineStr"/>
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="n"/>
+      <c r="I21" s="24" t="n"/>
+      <c r="J21" s="24" t="n"/>
+      <c r="K21" s="24" t="n"/>
+      <c r="L21" s="24" t="n"/>
+      <c r="M21" s="24" t="n"/>
+      <c r="N21" s="24" t="n"/>
+      <c r="O21" s="24" t="n"/>
+      <c r="P21" s="24" t="n"/>
+      <c r="Q21" s="24" t="n"/>
+      <c r="R21" s="24" t="n"/>
+      <c r="S21" s="24" t="n"/>
+      <c r="T21" s="24" t="n"/>
+      <c r="U21" s="24" t="n"/>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="24" t="n"/>
+      <c r="X21" s="24" t="n"/>
+      <c r="Y21" s="24" t="n"/>
+      <c r="Z21" s="24" t="n"/>
+      <c r="AA21" s="24" t="n"/>
+      <c r="AB21" s="24" t="n"/>
+      <c r="AC21" s="24" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="24" t="n"/>
+      <c r="AF21" s="24" t="n"/>
+      <c r="AG21" s="24" t="n"/>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="24" t="n"/>
+      <c r="AJ21" s="24" t="n"/>
+      <c r="AK21" s="24" t="n"/>
+      <c r="AL21" s="24" t="n"/>
+      <c r="AM21" s="24" t="n"/>
+      <c r="AN21" s="24" t="n"/>
       <c r="AO21" s="24" t="n"/>
       <c r="AP21" s="24" t="n"/>
       <c r="AQ21" s="24" t="n"/>
@@ -4265,7 +4260,7 @@
       <c r="BN21" s="24" t="n"/>
       <c r="BO21" s="24" t="n"/>
     </row>
-    <row r="22" ht="16" customHeight="1">
+    <row r="22" ht="18" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -4281,38 +4276,33 @@
           <t>PAB060·单级样机</t>
         </is>
       </c>
-      <c r="D22" s="27" t="n">
-        <v>46291</v>
-      </c>
-      <c r="E22" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G22" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H22" s="29" t="n"/>
-      <c r="I22" s="29" t="n"/>
-      <c r="J22" s="29" t="n"/>
-      <c r="K22" s="29" t="n"/>
-      <c r="L22" s="29" t="n"/>
-      <c r="M22" s="29" t="n"/>
-      <c r="N22" s="29" t="n"/>
-      <c r="O22" s="29" t="n"/>
-      <c r="P22" s="29" t="n"/>
-      <c r="Q22" s="29" t="n"/>
-      <c r="R22" s="29" t="n"/>
-      <c r="S22" s="29" t="n"/>
-      <c r="T22" s="29" t="n"/>
-      <c r="U22" s="30" t="n"/>
+      <c r="D22" s="27">
+        <f>IF('时间节点计划表'!E11="","",'时间节点计划表'!E11)</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
+        <f>IF('时间节点计划表'!F11="","",'时间节点计划表'!F11)</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>IF(OR(D22="",E22=""),"待填",E22-D22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
+      <c r="K22" s="24" t="n"/>
+      <c r="L22" s="24" t="n"/>
+      <c r="M22" s="24" t="n"/>
+      <c r="N22" s="24" t="n"/>
+      <c r="O22" s="24" t="n"/>
+      <c r="P22" s="24" t="n"/>
+      <c r="Q22" s="24" t="n"/>
+      <c r="R22" s="24" t="n"/>
+      <c r="S22" s="24" t="n"/>
+      <c r="T22" s="24" t="n"/>
+      <c r="U22" s="24" t="n"/>
       <c r="V22" s="24" t="n"/>
       <c r="W22" s="24" t="n"/>
       <c r="X22" s="24" t="n"/>
@@ -4360,7 +4350,7 @@
       <c r="BN22" s="24" t="n"/>
       <c r="BO22" s="24" t="n"/>
     </row>
-    <row r="23" ht="16" customHeight="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -4376,53 +4366,51 @@
           <t>PAB060·双级样机</t>
         </is>
       </c>
-      <c r="D23" s="22" t="n">
-        <v>46293</v>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="31" t="n"/>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n"/>
-      <c r="N23" s="31" t="n"/>
-      <c r="O23" s="31" t="n"/>
-      <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="31" t="n"/>
-      <c r="R23" s="31" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n"/>
-      <c r="U23" s="31" t="n"/>
-      <c r="V23" s="31" t="n"/>
-      <c r="W23" s="31" t="n"/>
-      <c r="X23" s="31" t="n"/>
-      <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="31" t="n"/>
-      <c r="AA23" s="31" t="n"/>
-      <c r="AB23" s="31" t="n"/>
-      <c r="AC23" s="31" t="n"/>
-      <c r="AD23" s="31" t="n"/>
-      <c r="AE23" s="31" t="n"/>
-      <c r="AF23" s="31" t="n"/>
-      <c r="AG23" s="31" t="n"/>
-      <c r="AH23" s="31" t="n"/>
-      <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
-      <c r="AK23" s="31" t="n"/>
-      <c r="AL23" s="31" t="n"/>
-      <c r="AM23" s="31" t="n"/>
-      <c r="AN23" s="31" t="n"/>
-      <c r="AO23" s="31" t="n"/>
-      <c r="AP23" s="23" t="n">
-        <v>28</v>
-      </c>
+      <c r="D23" s="22">
+        <f>IF('时间节点计划表'!E12="","",'时间节点计划表'!E12)</f>
+        <v/>
+      </c>
+      <c r="E23" s="22">
+        <f>IF('时间节点计划表'!F12="","",'时间节点计划表'!F12)</f>
+        <v/>
+      </c>
+      <c r="F23" s="23" t="inlineStr"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="n"/>
+      <c r="K23" s="24" t="n"/>
+      <c r="L23" s="24" t="n"/>
+      <c r="M23" s="24" t="n"/>
+      <c r="N23" s="24" t="n"/>
+      <c r="O23" s="24" t="n"/>
+      <c r="P23" s="24" t="n"/>
+      <c r="Q23" s="24" t="n"/>
+      <c r="R23" s="24" t="n"/>
+      <c r="S23" s="24" t="n"/>
+      <c r="T23" s="24" t="n"/>
+      <c r="U23" s="24" t="n"/>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="24" t="n"/>
+      <c r="X23" s="24" t="n"/>
+      <c r="Y23" s="24" t="n"/>
+      <c r="Z23" s="24" t="n"/>
+      <c r="AA23" s="24" t="n"/>
+      <c r="AB23" s="24" t="n"/>
+      <c r="AC23" s="24" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="24" t="n"/>
+      <c r="AF23" s="24" t="n"/>
+      <c r="AG23" s="24" t="n"/>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="24" t="n"/>
+      <c r="AJ23" s="24" t="n"/>
+      <c r="AK23" s="24" t="n"/>
+      <c r="AL23" s="24" t="n"/>
+      <c r="AM23" s="24" t="n"/>
+      <c r="AN23" s="24" t="n"/>
+      <c r="AO23" s="24" t="n"/>
+      <c r="AP23" s="24" t="n"/>
       <c r="AQ23" s="24" t="n"/>
       <c r="AR23" s="24" t="n"/>
       <c r="AS23" s="24" t="n"/>
@@ -4449,7 +4437,7 @@
       <c r="BN23" s="24" t="n"/>
       <c r="BO23" s="24" t="n"/>
     </row>
-    <row r="24" ht="16" customHeight="1">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -4465,38 +4453,33 @@
           <t>PAB060·双级样机</t>
         </is>
       </c>
-      <c r="D24" s="27" t="n">
-        <v>46293</v>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G24" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H24" s="29" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="29" t="n"/>
-      <c r="K24" s="29" t="n"/>
-      <c r="L24" s="29" t="n"/>
-      <c r="M24" s="29" t="n"/>
-      <c r="N24" s="29" t="n"/>
-      <c r="O24" s="29" t="n"/>
-      <c r="P24" s="29" t="n"/>
-      <c r="Q24" s="29" t="n"/>
-      <c r="R24" s="29" t="n"/>
-      <c r="S24" s="29" t="n"/>
-      <c r="T24" s="29" t="n"/>
-      <c r="U24" s="30" t="n"/>
+      <c r="D24" s="27">
+        <f>IF('时间节点计划表'!E12="","",'时间节点计划表'!E12)</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>IF('时间节点计划表'!F12="","",'时间节点计划表'!F12)</f>
+        <v/>
+      </c>
+      <c r="F24" s="28">
+        <f>IF(OR(D24="",E24=""),"待填",E24-D24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="n"/>
+      <c r="I24" s="24" t="n"/>
+      <c r="J24" s="24" t="n"/>
+      <c r="K24" s="24" t="n"/>
+      <c r="L24" s="24" t="n"/>
+      <c r="M24" s="24" t="n"/>
+      <c r="N24" s="24" t="n"/>
+      <c r="O24" s="24" t="n"/>
+      <c r="P24" s="24" t="n"/>
+      <c r="Q24" s="24" t="n"/>
+      <c r="R24" s="24" t="n"/>
+      <c r="S24" s="24" t="n"/>
+      <c r="T24" s="24" t="n"/>
+      <c r="U24" s="24" t="n"/>
       <c r="V24" s="24" t="n"/>
       <c r="W24" s="24" t="n"/>
       <c r="X24" s="24" t="n"/>
@@ -4544,7 +4527,7 @@
       <c r="BN24" s="24" t="n"/>
       <c r="BO24" s="24" t="n"/>
     </row>
-    <row r="25" ht="16" customHeight="1">
+    <row r="25" ht="18" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -4560,52 +4543,50 @@
           <t>PAB090·零件到位</t>
         </is>
       </c>
-      <c r="D25" s="22" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
-      <c r="O25" s="31" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-      <c r="U25" s="31" t="n"/>
-      <c r="V25" s="31" t="n"/>
-      <c r="W25" s="31" t="n"/>
-      <c r="X25" s="31" t="n"/>
-      <c r="Y25" s="31" t="n"/>
-      <c r="Z25" s="31" t="n"/>
-      <c r="AA25" s="31" t="n"/>
-      <c r="AB25" s="31" t="n"/>
-      <c r="AC25" s="31" t="n"/>
-      <c r="AD25" s="31" t="n"/>
-      <c r="AE25" s="31" t="n"/>
-      <c r="AF25" s="31" t="n"/>
-      <c r="AG25" s="31" t="n"/>
-      <c r="AH25" s="31" t="n"/>
-      <c r="AI25" s="31" t="n"/>
-      <c r="AJ25" s="31" t="n"/>
-      <c r="AK25" s="31" t="n"/>
-      <c r="AL25" s="31" t="n"/>
-      <c r="AM25" s="31" t="n"/>
-      <c r="AN25" s="31" t="n"/>
-      <c r="AO25" s="23" t="n">
-        <v>27</v>
-      </c>
+      <c r="D25" s="22">
+        <f>IF('时间节点计划表'!E13="","",'时间节点计划表'!E13)</f>
+        <v/>
+      </c>
+      <c r="E25" s="22">
+        <f>IF('时间节点计划表'!F13="","",'时间节点计划表'!F13)</f>
+        <v/>
+      </c>
+      <c r="F25" s="23" t="inlineStr"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
+      <c r="I25" s="24" t="n"/>
+      <c r="J25" s="24" t="n"/>
+      <c r="K25" s="24" t="n"/>
+      <c r="L25" s="24" t="n"/>
+      <c r="M25" s="24" t="n"/>
+      <c r="N25" s="24" t="n"/>
+      <c r="O25" s="24" t="n"/>
+      <c r="P25" s="24" t="n"/>
+      <c r="Q25" s="24" t="n"/>
+      <c r="R25" s="24" t="n"/>
+      <c r="S25" s="24" t="n"/>
+      <c r="T25" s="24" t="n"/>
+      <c r="U25" s="24" t="n"/>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="24" t="n"/>
+      <c r="X25" s="24" t="n"/>
+      <c r="Y25" s="24" t="n"/>
+      <c r="Z25" s="24" t="n"/>
+      <c r="AA25" s="24" t="n"/>
+      <c r="AB25" s="24" t="n"/>
+      <c r="AC25" s="24" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="24" t="n"/>
+      <c r="AF25" s="24" t="n"/>
+      <c r="AG25" s="24" t="n"/>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="24" t="n"/>
+      <c r="AJ25" s="24" t="n"/>
+      <c r="AK25" s="24" t="n"/>
+      <c r="AL25" s="24" t="n"/>
+      <c r="AM25" s="24" t="n"/>
+      <c r="AN25" s="24" t="n"/>
+      <c r="AO25" s="24" t="n"/>
       <c r="AP25" s="24" t="n"/>
       <c r="AQ25" s="24" t="n"/>
       <c r="AR25" s="24" t="n"/>
@@ -4633,7 +4614,7 @@
       <c r="BN25" s="24" t="n"/>
       <c r="BO25" s="24" t="n"/>
     </row>
-    <row r="26" ht="16" customHeight="1">
+    <row r="26" ht="18" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -4649,38 +4630,33 @@
           <t>PAB090·零件到位</t>
         </is>
       </c>
-      <c r="D26" s="27" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F26" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G26" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H26" s="29" t="n"/>
-      <c r="I26" s="29" t="n"/>
-      <c r="J26" s="29" t="n"/>
-      <c r="K26" s="29" t="n"/>
-      <c r="L26" s="29" t="n"/>
-      <c r="M26" s="29" t="n"/>
-      <c r="N26" s="29" t="n"/>
-      <c r="O26" s="29" t="n"/>
-      <c r="P26" s="29" t="n"/>
-      <c r="Q26" s="29" t="n"/>
-      <c r="R26" s="29" t="n"/>
-      <c r="S26" s="29" t="n"/>
-      <c r="T26" s="29" t="n"/>
-      <c r="U26" s="30" t="n"/>
+      <c r="D26" s="27">
+        <f>IF('时间节点计划表'!E13="","",'时间节点计划表'!E13)</f>
+        <v/>
+      </c>
+      <c r="E26" s="27">
+        <f>IF('时间节点计划表'!F13="","",'时间节点计划表'!F13)</f>
+        <v/>
+      </c>
+      <c r="F26" s="28">
+        <f>IF(OR(D26="",E26=""),"待填",E26-D26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+      <c r="I26" s="24" t="n"/>
+      <c r="J26" s="24" t="n"/>
+      <c r="K26" s="24" t="n"/>
+      <c r="L26" s="24" t="n"/>
+      <c r="M26" s="24" t="n"/>
+      <c r="N26" s="24" t="n"/>
+      <c r="O26" s="24" t="n"/>
+      <c r="P26" s="24" t="n"/>
+      <c r="Q26" s="24" t="n"/>
+      <c r="R26" s="24" t="n"/>
+      <c r="S26" s="24" t="n"/>
+      <c r="T26" s="24" t="n"/>
+      <c r="U26" s="24" t="n"/>
       <c r="V26" s="24" t="n"/>
       <c r="W26" s="24" t="n"/>
       <c r="X26" s="24" t="n"/>
@@ -4728,7 +4704,7 @@
       <c r="BN26" s="24" t="n"/>
       <c r="BO26" s="24" t="n"/>
     </row>
-    <row r="27" ht="16" customHeight="1">
+    <row r="27" ht="18" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -4744,26 +4720,24 @@
           <t>PAB090·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D27" s="22" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="31" t="n"/>
-      <c r="J27" s="31" t="n"/>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="31" t="n"/>
-      <c r="M27" s="31" t="n"/>
-      <c r="N27" s="31" t="n"/>
-      <c r="O27" s="23" t="n">
-        <v>1</v>
-      </c>
+      <c r="D27" s="22">
+        <f>IF('时间节点计划表'!E14="","",'时间节点计划表'!E14)</f>
+        <v/>
+      </c>
+      <c r="E27" s="22">
+        <f>IF('时间节点计划表'!F14="","",'时间节点计划表'!F14)</f>
+        <v/>
+      </c>
+      <c r="F27" s="23" t="inlineStr"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
+      <c r="I27" s="24" t="n"/>
+      <c r="J27" s="24" t="n"/>
+      <c r="K27" s="24" t="n"/>
+      <c r="L27" s="24" t="n"/>
+      <c r="M27" s="24" t="n"/>
+      <c r="N27" s="24" t="n"/>
+      <c r="O27" s="24" t="n"/>
       <c r="P27" s="24" t="n"/>
       <c r="Q27" s="24" t="n"/>
       <c r="R27" s="24" t="n"/>
@@ -4817,7 +4791,7 @@
       <c r="BN27" s="24" t="n"/>
       <c r="BO27" s="24" t="n"/>
     </row>
-    <row r="28" ht="16" customHeight="1">
+    <row r="28" ht="18" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -4833,38 +4807,33 @@
           <t>PAB090·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D28" s="27" t="n">
-        <v>46266</v>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H28" s="29" t="n"/>
-      <c r="I28" s="29" t="n"/>
-      <c r="J28" s="29" t="n"/>
-      <c r="K28" s="29" t="n"/>
-      <c r="L28" s="29" t="n"/>
-      <c r="M28" s="29" t="n"/>
-      <c r="N28" s="29" t="n"/>
-      <c r="O28" s="29" t="n"/>
-      <c r="P28" s="29" t="n"/>
-      <c r="Q28" s="29" t="n"/>
-      <c r="R28" s="29" t="n"/>
-      <c r="S28" s="29" t="n"/>
-      <c r="T28" s="29" t="n"/>
-      <c r="U28" s="30" t="n"/>
+      <c r="D28" s="27">
+        <f>IF('时间节点计划表'!E14="","",'时间节点计划表'!E14)</f>
+        <v/>
+      </c>
+      <c r="E28" s="27">
+        <f>IF('时间节点计划表'!F14="","",'时间节点计划表'!F14)</f>
+        <v/>
+      </c>
+      <c r="F28" s="28">
+        <f>IF(OR(D28="",E28=""),"待填",E28-D28)</f>
+        <v/>
+      </c>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
+      <c r="I28" s="24" t="n"/>
+      <c r="J28" s="24" t="n"/>
+      <c r="K28" s="24" t="n"/>
+      <c r="L28" s="24" t="n"/>
+      <c r="M28" s="24" t="n"/>
+      <c r="N28" s="24" t="n"/>
+      <c r="O28" s="24" t="n"/>
+      <c r="P28" s="24" t="n"/>
+      <c r="Q28" s="24" t="n"/>
+      <c r="R28" s="24" t="n"/>
+      <c r="S28" s="24" t="n"/>
+      <c r="T28" s="24" t="n"/>
+      <c r="U28" s="24" t="n"/>
       <c r="V28" s="24" t="n"/>
       <c r="W28" s="24" t="n"/>
       <c r="X28" s="24" t="n"/>
@@ -4912,7 +4881,7 @@
       <c r="BN28" s="24" t="n"/>
       <c r="BO28" s="24" t="n"/>
     </row>
-    <row r="29" ht="16" customHeight="1">
+    <row r="29" ht="18" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -4928,45 +4897,43 @@
           <t>PAB090·工装实物到位</t>
         </is>
       </c>
-      <c r="D29" s="22" t="n">
-        <v>46285</v>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-      <c r="U29" s="31" t="n"/>
-      <c r="V29" s="31" t="n"/>
-      <c r="W29" s="31" t="n"/>
-      <c r="X29" s="31" t="n"/>
-      <c r="Y29" s="31" t="n"/>
-      <c r="Z29" s="31" t="n"/>
-      <c r="AA29" s="31" t="n"/>
-      <c r="AB29" s="31" t="n"/>
-      <c r="AC29" s="31" t="n"/>
-      <c r="AD29" s="31" t="n"/>
-      <c r="AE29" s="31" t="n"/>
-      <c r="AF29" s="31" t="n"/>
-      <c r="AG29" s="31" t="n"/>
-      <c r="AH29" s="23" t="n">
-        <v>20</v>
-      </c>
+      <c r="D29" s="22">
+        <f>IF('时间节点计划表'!E15="","",'时间节点计划表'!E15)</f>
+        <v/>
+      </c>
+      <c r="E29" s="22">
+        <f>IF('时间节点计划表'!F15="","",'时间节点计划表'!F15)</f>
+        <v/>
+      </c>
+      <c r="F29" s="23" t="inlineStr"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="n"/>
+      <c r="K29" s="24" t="n"/>
+      <c r="L29" s="24" t="n"/>
+      <c r="M29" s="24" t="n"/>
+      <c r="N29" s="24" t="n"/>
+      <c r="O29" s="24" t="n"/>
+      <c r="P29" s="24" t="n"/>
+      <c r="Q29" s="24" t="n"/>
+      <c r="R29" s="24" t="n"/>
+      <c r="S29" s="24" t="n"/>
+      <c r="T29" s="24" t="n"/>
+      <c r="U29" s="24" t="n"/>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="24" t="n"/>
+      <c r="X29" s="24" t="n"/>
+      <c r="Y29" s="24" t="n"/>
+      <c r="Z29" s="24" t="n"/>
+      <c r="AA29" s="24" t="n"/>
+      <c r="AB29" s="24" t="n"/>
+      <c r="AC29" s="24" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="24" t="n"/>
+      <c r="AF29" s="24" t="n"/>
+      <c r="AG29" s="24" t="n"/>
+      <c r="AH29" s="24" t="n"/>
       <c r="AI29" s="24" t="n"/>
       <c r="AJ29" s="24" t="n"/>
       <c r="AK29" s="24" t="n"/>
@@ -5001,7 +4968,7 @@
       <c r="BN29" s="24" t="n"/>
       <c r="BO29" s="24" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1">
+    <row r="30" ht="18" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -5017,38 +4984,33 @@
           <t>PAB090·工装实物到位</t>
         </is>
       </c>
-      <c r="D30" s="27" t="n">
-        <v>46285</v>
-      </c>
-      <c r="E30" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H30" s="29" t="n"/>
-      <c r="I30" s="29" t="n"/>
-      <c r="J30" s="29" t="n"/>
-      <c r="K30" s="29" t="n"/>
-      <c r="L30" s="29" t="n"/>
-      <c r="M30" s="29" t="n"/>
-      <c r="N30" s="29" t="n"/>
-      <c r="O30" s="29" t="n"/>
-      <c r="P30" s="29" t="n"/>
-      <c r="Q30" s="29" t="n"/>
-      <c r="R30" s="29" t="n"/>
-      <c r="S30" s="29" t="n"/>
-      <c r="T30" s="29" t="n"/>
-      <c r="U30" s="30" t="n"/>
+      <c r="D30" s="27">
+        <f>IF('时间节点计划表'!E15="","",'时间节点计划表'!E15)</f>
+        <v/>
+      </c>
+      <c r="E30" s="27">
+        <f>IF('时间节点计划表'!F15="","",'时间节点计划表'!F15)</f>
+        <v/>
+      </c>
+      <c r="F30" s="28">
+        <f>IF(OR(D30="",E30=""),"待填",E30-D30)</f>
+        <v/>
+      </c>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
+      <c r="K30" s="24" t="n"/>
+      <c r="L30" s="24" t="n"/>
+      <c r="M30" s="24" t="n"/>
+      <c r="N30" s="24" t="n"/>
+      <c r="O30" s="24" t="n"/>
+      <c r="P30" s="24" t="n"/>
+      <c r="Q30" s="24" t="n"/>
+      <c r="R30" s="24" t="n"/>
+      <c r="S30" s="24" t="n"/>
+      <c r="T30" s="24" t="n"/>
+      <c r="U30" s="24" t="n"/>
       <c r="V30" s="24" t="n"/>
       <c r="W30" s="24" t="n"/>
       <c r="X30" s="24" t="n"/>
@@ -5096,7 +5058,7 @@
       <c r="BN30" s="24" t="n"/>
       <c r="BO30" s="24" t="n"/>
     </row>
-    <row r="31" ht="16" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -5112,52 +5074,50 @@
           <t>PAB090·排针机安装调试</t>
         </is>
       </c>
-      <c r="D31" s="22" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E31" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="31" t="n"/>
-      <c r="R31" s="31" t="n"/>
-      <c r="S31" s="31" t="n"/>
-      <c r="T31" s="31" t="n"/>
-      <c r="U31" s="31" t="n"/>
-      <c r="V31" s="31" t="n"/>
-      <c r="W31" s="31" t="n"/>
-      <c r="X31" s="31" t="n"/>
-      <c r="Y31" s="31" t="n"/>
-      <c r="Z31" s="31" t="n"/>
-      <c r="AA31" s="31" t="n"/>
-      <c r="AB31" s="31" t="n"/>
-      <c r="AC31" s="31" t="n"/>
-      <c r="AD31" s="31" t="n"/>
-      <c r="AE31" s="31" t="n"/>
-      <c r="AF31" s="31" t="n"/>
-      <c r="AG31" s="31" t="n"/>
-      <c r="AH31" s="31" t="n"/>
-      <c r="AI31" s="31" t="n"/>
-      <c r="AJ31" s="31" t="n"/>
-      <c r="AK31" s="31" t="n"/>
-      <c r="AL31" s="31" t="n"/>
-      <c r="AM31" s="31" t="n"/>
-      <c r="AN31" s="31" t="n"/>
-      <c r="AO31" s="23" t="n">
-        <v>27</v>
-      </c>
+      <c r="D31" s="22">
+        <f>IF('时间节点计划表'!E16="","",'时间节点计划表'!E16)</f>
+        <v/>
+      </c>
+      <c r="E31" s="22">
+        <f>IF('时间节点计划表'!F16="","",'时间节点计划表'!F16)</f>
+        <v/>
+      </c>
+      <c r="F31" s="23" t="inlineStr"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="n"/>
+      <c r="K31" s="24" t="n"/>
+      <c r="L31" s="24" t="n"/>
+      <c r="M31" s="24" t="n"/>
+      <c r="N31" s="24" t="n"/>
+      <c r="O31" s="24" t="n"/>
+      <c r="P31" s="24" t="n"/>
+      <c r="Q31" s="24" t="n"/>
+      <c r="R31" s="24" t="n"/>
+      <c r="S31" s="24" t="n"/>
+      <c r="T31" s="24" t="n"/>
+      <c r="U31" s="24" t="n"/>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="24" t="n"/>
+      <c r="X31" s="24" t="n"/>
+      <c r="Y31" s="24" t="n"/>
+      <c r="Z31" s="24" t="n"/>
+      <c r="AA31" s="24" t="n"/>
+      <c r="AB31" s="24" t="n"/>
+      <c r="AC31" s="24" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="24" t="n"/>
+      <c r="AF31" s="24" t="n"/>
+      <c r="AG31" s="24" t="n"/>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="24" t="n"/>
+      <c r="AJ31" s="24" t="n"/>
+      <c r="AK31" s="24" t="n"/>
+      <c r="AL31" s="24" t="n"/>
+      <c r="AM31" s="24" t="n"/>
+      <c r="AN31" s="24" t="n"/>
+      <c r="AO31" s="24" t="n"/>
       <c r="AP31" s="24" t="n"/>
       <c r="AQ31" s="24" t="n"/>
       <c r="AR31" s="24" t="n"/>
@@ -5185,7 +5145,7 @@
       <c r="BN31" s="24" t="n"/>
       <c r="BO31" s="24" t="n"/>
     </row>
-    <row r="32" ht="16" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -5201,38 +5161,33 @@
           <t>PAB090·排针机安装调试</t>
         </is>
       </c>
-      <c r="D32" s="27" t="n">
-        <v>46292</v>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G32" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H32" s="29" t="n"/>
-      <c r="I32" s="29" t="n"/>
-      <c r="J32" s="29" t="n"/>
-      <c r="K32" s="29" t="n"/>
-      <c r="L32" s="29" t="n"/>
-      <c r="M32" s="29" t="n"/>
-      <c r="N32" s="29" t="n"/>
-      <c r="O32" s="29" t="n"/>
-      <c r="P32" s="29" t="n"/>
-      <c r="Q32" s="29" t="n"/>
-      <c r="R32" s="29" t="n"/>
-      <c r="S32" s="29" t="n"/>
-      <c r="T32" s="29" t="n"/>
-      <c r="U32" s="30" t="n"/>
+      <c r="D32" s="27">
+        <f>IF('时间节点计划表'!E16="","",'时间节点计划表'!E16)</f>
+        <v/>
+      </c>
+      <c r="E32" s="27">
+        <f>IF('时间节点计划表'!F16="","",'时间节点计划表'!F16)</f>
+        <v/>
+      </c>
+      <c r="F32" s="28">
+        <f>IF(OR(D32="",E32=""),"待填",E32-D32)</f>
+        <v/>
+      </c>
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="n"/>
+      <c r="I32" s="24" t="n"/>
+      <c r="J32" s="24" t="n"/>
+      <c r="K32" s="24" t="n"/>
+      <c r="L32" s="24" t="n"/>
+      <c r="M32" s="24" t="n"/>
+      <c r="N32" s="24" t="n"/>
+      <c r="O32" s="24" t="n"/>
+      <c r="P32" s="24" t="n"/>
+      <c r="Q32" s="24" t="n"/>
+      <c r="R32" s="24" t="n"/>
+      <c r="S32" s="24" t="n"/>
+      <c r="T32" s="24" t="n"/>
+      <c r="U32" s="24" t="n"/>
       <c r="V32" s="24" t="n"/>
       <c r="W32" s="24" t="n"/>
       <c r="X32" s="24" t="n"/>
@@ -5280,7 +5235,7 @@
       <c r="BN32" s="24" t="n"/>
       <c r="BO32" s="24" t="n"/>
     </row>
-    <row r="33" ht="16" customHeight="1">
+    <row r="33" ht="18" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -5296,54 +5251,52 @@
           <t>PAB090·单级样机</t>
         </is>
       </c>
-      <c r="D33" s="22" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F33" s="20" t="inlineStr"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n"/>
-      <c r="N33" s="31" t="n"/>
-      <c r="O33" s="31" t="n"/>
-      <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="31" t="n"/>
-      <c r="R33" s="31" t="n"/>
-      <c r="S33" s="31" t="n"/>
-      <c r="T33" s="31" t="n"/>
-      <c r="U33" s="31" t="n"/>
-      <c r="V33" s="31" t="n"/>
-      <c r="W33" s="31" t="n"/>
-      <c r="X33" s="31" t="n"/>
-      <c r="Y33" s="31" t="n"/>
-      <c r="Z33" s="31" t="n"/>
-      <c r="AA33" s="31" t="n"/>
-      <c r="AB33" s="31" t="n"/>
-      <c r="AC33" s="31" t="n"/>
-      <c r="AD33" s="31" t="n"/>
-      <c r="AE33" s="31" t="n"/>
-      <c r="AF33" s="31" t="n"/>
-      <c r="AG33" s="31" t="n"/>
-      <c r="AH33" s="31" t="n"/>
-      <c r="AI33" s="31" t="n"/>
-      <c r="AJ33" s="31" t="n"/>
-      <c r="AK33" s="31" t="n"/>
-      <c r="AL33" s="31" t="n"/>
-      <c r="AM33" s="31" t="n"/>
-      <c r="AN33" s="31" t="n"/>
-      <c r="AO33" s="31" t="n"/>
-      <c r="AP33" s="31" t="n"/>
-      <c r="AQ33" s="23" t="n">
-        <v>29</v>
-      </c>
+      <c r="D33" s="22">
+        <f>IF('时间节点计划表'!E17="","",'时间节点计划表'!E17)</f>
+        <v/>
+      </c>
+      <c r="E33" s="22">
+        <f>IF('时间节点计划表'!F17="","",'时间节点计划表'!F17)</f>
+        <v/>
+      </c>
+      <c r="F33" s="23" t="inlineStr"/>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="24" t="n"/>
+      <c r="K33" s="24" t="n"/>
+      <c r="L33" s="24" t="n"/>
+      <c r="M33" s="24" t="n"/>
+      <c r="N33" s="24" t="n"/>
+      <c r="O33" s="24" t="n"/>
+      <c r="P33" s="24" t="n"/>
+      <c r="Q33" s="24" t="n"/>
+      <c r="R33" s="24" t="n"/>
+      <c r="S33" s="24" t="n"/>
+      <c r="T33" s="24" t="n"/>
+      <c r="U33" s="24" t="n"/>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="24" t="n"/>
+      <c r="X33" s="24" t="n"/>
+      <c r="Y33" s="24" t="n"/>
+      <c r="Z33" s="24" t="n"/>
+      <c r="AA33" s="24" t="n"/>
+      <c r="AB33" s="24" t="n"/>
+      <c r="AC33" s="24" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="24" t="n"/>
+      <c r="AF33" s="24" t="n"/>
+      <c r="AG33" s="24" t="n"/>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="24" t="n"/>
+      <c r="AJ33" s="24" t="n"/>
+      <c r="AK33" s="24" t="n"/>
+      <c r="AL33" s="24" t="n"/>
+      <c r="AM33" s="24" t="n"/>
+      <c r="AN33" s="24" t="n"/>
+      <c r="AO33" s="24" t="n"/>
+      <c r="AP33" s="24" t="n"/>
+      <c r="AQ33" s="24" t="n"/>
       <c r="AR33" s="24" t="n"/>
       <c r="AS33" s="24" t="n"/>
       <c r="AT33" s="24" t="n"/>
@@ -5369,7 +5322,7 @@
       <c r="BN33" s="24" t="n"/>
       <c r="BO33" s="24" t="n"/>
     </row>
-    <row r="34" ht="16" customHeight="1">
+    <row r="34" ht="18" customHeight="1">
       <c r="A34" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -5385,38 +5338,33 @@
           <t>PAB090·单级样机</t>
         </is>
       </c>
-      <c r="D34" s="27" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G34" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="29" t="n"/>
-      <c r="K34" s="29" t="n"/>
-      <c r="L34" s="29" t="n"/>
-      <c r="M34" s="29" t="n"/>
-      <c r="N34" s="29" t="n"/>
-      <c r="O34" s="29" t="n"/>
-      <c r="P34" s="29" t="n"/>
-      <c r="Q34" s="29" t="n"/>
-      <c r="R34" s="29" t="n"/>
-      <c r="S34" s="29" t="n"/>
-      <c r="T34" s="29" t="n"/>
-      <c r="U34" s="30" t="n"/>
+      <c r="D34" s="27">
+        <f>IF('时间节点计划表'!E17="","",'时间节点计划表'!E17)</f>
+        <v/>
+      </c>
+      <c r="E34" s="27">
+        <f>IF('时间节点计划表'!F17="","",'时间节点计划表'!F17)</f>
+        <v/>
+      </c>
+      <c r="F34" s="28">
+        <f>IF(OR(D34="",E34=""),"待填",E34-D34)</f>
+        <v/>
+      </c>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="24" t="n"/>
+      <c r="K34" s="24" t="n"/>
+      <c r="L34" s="24" t="n"/>
+      <c r="M34" s="24" t="n"/>
+      <c r="N34" s="24" t="n"/>
+      <c r="O34" s="24" t="n"/>
+      <c r="P34" s="24" t="n"/>
+      <c r="Q34" s="24" t="n"/>
+      <c r="R34" s="24" t="n"/>
+      <c r="S34" s="24" t="n"/>
+      <c r="T34" s="24" t="n"/>
+      <c r="U34" s="24" t="n"/>
       <c r="V34" s="24" t="n"/>
       <c r="W34" s="24" t="n"/>
       <c r="X34" s="24" t="n"/>
@@ -5464,7 +5412,7 @@
       <c r="BN34" s="24" t="n"/>
       <c r="BO34" s="24" t="n"/>
     </row>
-    <row r="35" ht="16" customHeight="1">
+    <row r="35" ht="18" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -5480,55 +5428,53 @@
           <t>PAB090·双级样机</t>
         </is>
       </c>
-      <c r="D35" s="22" t="n">
-        <v>46295</v>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-      <c r="V35" s="31" t="n"/>
-      <c r="W35" s="31" t="n"/>
-      <c r="X35" s="31" t="n"/>
-      <c r="Y35" s="31" t="n"/>
-      <c r="Z35" s="31" t="n"/>
-      <c r="AA35" s="31" t="n"/>
-      <c r="AB35" s="31" t="n"/>
-      <c r="AC35" s="31" t="n"/>
-      <c r="AD35" s="31" t="n"/>
-      <c r="AE35" s="31" t="n"/>
-      <c r="AF35" s="31" t="n"/>
-      <c r="AG35" s="31" t="n"/>
-      <c r="AH35" s="31" t="n"/>
-      <c r="AI35" s="31" t="n"/>
-      <c r="AJ35" s="31" t="n"/>
-      <c r="AK35" s="31" t="n"/>
-      <c r="AL35" s="31" t="n"/>
-      <c r="AM35" s="31" t="n"/>
-      <c r="AN35" s="31" t="n"/>
-      <c r="AO35" s="31" t="n"/>
-      <c r="AP35" s="31" t="n"/>
-      <c r="AQ35" s="31" t="n"/>
-      <c r="AR35" s="23" t="n">
-        <v>30</v>
-      </c>
+      <c r="D35" s="22">
+        <f>IF('时间节点计划表'!E18="","",'时间节点计划表'!E18)</f>
+        <v/>
+      </c>
+      <c r="E35" s="22">
+        <f>IF('时间节点计划表'!F18="","",'时间节点计划表'!F18)</f>
+        <v/>
+      </c>
+      <c r="F35" s="23" t="inlineStr"/>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="n"/>
+      <c r="I35" s="24" t="n"/>
+      <c r="J35" s="24" t="n"/>
+      <c r="K35" s="24" t="n"/>
+      <c r="L35" s="24" t="n"/>
+      <c r="M35" s="24" t="n"/>
+      <c r="N35" s="24" t="n"/>
+      <c r="O35" s="24" t="n"/>
+      <c r="P35" s="24" t="n"/>
+      <c r="Q35" s="24" t="n"/>
+      <c r="R35" s="24" t="n"/>
+      <c r="S35" s="24" t="n"/>
+      <c r="T35" s="24" t="n"/>
+      <c r="U35" s="24" t="n"/>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="24" t="n"/>
+      <c r="X35" s="24" t="n"/>
+      <c r="Y35" s="24" t="n"/>
+      <c r="Z35" s="24" t="n"/>
+      <c r="AA35" s="24" t="n"/>
+      <c r="AB35" s="24" t="n"/>
+      <c r="AC35" s="24" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="24" t="n"/>
+      <c r="AF35" s="24" t="n"/>
+      <c r="AG35" s="24" t="n"/>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="24" t="n"/>
+      <c r="AJ35" s="24" t="n"/>
+      <c r="AK35" s="24" t="n"/>
+      <c r="AL35" s="24" t="n"/>
+      <c r="AM35" s="24" t="n"/>
+      <c r="AN35" s="24" t="n"/>
+      <c r="AO35" s="24" t="n"/>
+      <c r="AP35" s="24" t="n"/>
+      <c r="AQ35" s="24" t="n"/>
+      <c r="AR35" s="24" t="n"/>
       <c r="AS35" s="24" t="n"/>
       <c r="AT35" s="24" t="n"/>
       <c r="AU35" s="24" t="n"/>
@@ -5553,7 +5499,7 @@
       <c r="BN35" s="24" t="n"/>
       <c r="BO35" s="24" t="n"/>
     </row>
-    <row r="36" ht="16" customHeight="1">
+    <row r="36" ht="18" customHeight="1">
       <c r="A36" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -5569,38 +5515,33 @@
           <t>PAB090·双级样机</t>
         </is>
       </c>
-      <c r="D36" s="27" t="n">
-        <v>46295</v>
-      </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F36" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G36" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H36" s="29" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="29" t="n"/>
-      <c r="K36" s="29" t="n"/>
-      <c r="L36" s="29" t="n"/>
-      <c r="M36" s="29" t="n"/>
-      <c r="N36" s="29" t="n"/>
-      <c r="O36" s="29" t="n"/>
-      <c r="P36" s="29" t="n"/>
-      <c r="Q36" s="29" t="n"/>
-      <c r="R36" s="29" t="n"/>
-      <c r="S36" s="29" t="n"/>
-      <c r="T36" s="29" t="n"/>
-      <c r="U36" s="30" t="n"/>
+      <c r="D36" s="27">
+        <f>IF('时间节点计划表'!E18="","",'时间节点计划表'!E18)</f>
+        <v/>
+      </c>
+      <c r="E36" s="27">
+        <f>IF('时间节点计划表'!F18="","",'时间节点计划表'!F18)</f>
+        <v/>
+      </c>
+      <c r="F36" s="28">
+        <f>IF(OR(D36="",E36=""),"待填",E36-D36)</f>
+        <v/>
+      </c>
+      <c r="G36" s="24" t="n"/>
+      <c r="H36" s="24" t="n"/>
+      <c r="I36" s="24" t="n"/>
+      <c r="J36" s="24" t="n"/>
+      <c r="K36" s="24" t="n"/>
+      <c r="L36" s="24" t="n"/>
+      <c r="M36" s="24" t="n"/>
+      <c r="N36" s="24" t="n"/>
+      <c r="O36" s="24" t="n"/>
+      <c r="P36" s="24" t="n"/>
+      <c r="Q36" s="24" t="n"/>
+      <c r="R36" s="24" t="n"/>
+      <c r="S36" s="24" t="n"/>
+      <c r="T36" s="24" t="n"/>
+      <c r="U36" s="24" t="n"/>
       <c r="V36" s="24" t="n"/>
       <c r="W36" s="24" t="n"/>
       <c r="X36" s="24" t="n"/>
@@ -5648,7 +5589,7 @@
       <c r="BN36" s="24" t="n"/>
       <c r="BO36" s="24" t="n"/>
     </row>
-    <row r="37" ht="16" customHeight="1">
+    <row r="37" ht="18" customHeight="1">
       <c r="A37" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -5664,63 +5605,61 @@
           <t>PAB115·零件到位</t>
         </is>
       </c>
-      <c r="D37" s="22" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F37" s="20" t="inlineStr"/>
-      <c r="G37" s="31" t="n"/>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="31" t="n"/>
-      <c r="J37" s="31" t="n"/>
-      <c r="K37" s="31" t="n"/>
-      <c r="L37" s="31" t="n"/>
-      <c r="M37" s="31" t="n"/>
-      <c r="N37" s="31" t="n"/>
-      <c r="O37" s="31" t="n"/>
-      <c r="P37" s="31" t="n"/>
-      <c r="Q37" s="31" t="n"/>
-      <c r="R37" s="31" t="n"/>
-      <c r="S37" s="31" t="n"/>
-      <c r="T37" s="31" t="n"/>
-      <c r="U37" s="31" t="n"/>
-      <c r="V37" s="31" t="n"/>
-      <c r="W37" s="31" t="n"/>
-      <c r="X37" s="31" t="n"/>
-      <c r="Y37" s="31" t="n"/>
-      <c r="Z37" s="31" t="n"/>
-      <c r="AA37" s="31" t="n"/>
-      <c r="AB37" s="31" t="n"/>
-      <c r="AC37" s="31" t="n"/>
-      <c r="AD37" s="31" t="n"/>
-      <c r="AE37" s="31" t="n"/>
-      <c r="AF37" s="31" t="n"/>
-      <c r="AG37" s="31" t="n"/>
-      <c r="AH37" s="31" t="n"/>
-      <c r="AI37" s="31" t="n"/>
-      <c r="AJ37" s="31" t="n"/>
-      <c r="AK37" s="31" t="n"/>
-      <c r="AL37" s="31" t="n"/>
-      <c r="AM37" s="31" t="n"/>
-      <c r="AN37" s="31" t="n"/>
-      <c r="AO37" s="31" t="n"/>
-      <c r="AP37" s="31" t="n"/>
-      <c r="AQ37" s="31" t="n"/>
-      <c r="AR37" s="31" t="n"/>
-      <c r="AS37" s="31" t="n"/>
-      <c r="AT37" s="31" t="n"/>
-      <c r="AU37" s="31" t="n"/>
-      <c r="AV37" s="31" t="n"/>
-      <c r="AW37" s="31" t="n"/>
-      <c r="AX37" s="31" t="n"/>
-      <c r="AY37" s="31" t="n"/>
-      <c r="AZ37" s="23" t="n">
-        <v>8</v>
-      </c>
+      <c r="D37" s="22">
+        <f>IF('时间节点计划表'!E19="","",'时间节点计划表'!E19)</f>
+        <v/>
+      </c>
+      <c r="E37" s="22">
+        <f>IF('时间节点计划表'!F19="","",'时间节点计划表'!F19)</f>
+        <v/>
+      </c>
+      <c r="F37" s="23" t="inlineStr"/>
+      <c r="G37" s="24" t="n"/>
+      <c r="H37" s="24" t="n"/>
+      <c r="I37" s="24" t="n"/>
+      <c r="J37" s="24" t="n"/>
+      <c r="K37" s="24" t="n"/>
+      <c r="L37" s="24" t="n"/>
+      <c r="M37" s="24" t="n"/>
+      <c r="N37" s="24" t="n"/>
+      <c r="O37" s="24" t="n"/>
+      <c r="P37" s="24" t="n"/>
+      <c r="Q37" s="24" t="n"/>
+      <c r="R37" s="24" t="n"/>
+      <c r="S37" s="24" t="n"/>
+      <c r="T37" s="24" t="n"/>
+      <c r="U37" s="24" t="n"/>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="24" t="n"/>
+      <c r="X37" s="24" t="n"/>
+      <c r="Y37" s="24" t="n"/>
+      <c r="Z37" s="24" t="n"/>
+      <c r="AA37" s="24" t="n"/>
+      <c r="AB37" s="24" t="n"/>
+      <c r="AC37" s="24" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="24" t="n"/>
+      <c r="AF37" s="24" t="n"/>
+      <c r="AG37" s="24" t="n"/>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="24" t="n"/>
+      <c r="AJ37" s="24" t="n"/>
+      <c r="AK37" s="24" t="n"/>
+      <c r="AL37" s="24" t="n"/>
+      <c r="AM37" s="24" t="n"/>
+      <c r="AN37" s="24" t="n"/>
+      <c r="AO37" s="24" t="n"/>
+      <c r="AP37" s="24" t="n"/>
+      <c r="AQ37" s="24" t="n"/>
+      <c r="AR37" s="24" t="n"/>
+      <c r="AS37" s="24" t="n"/>
+      <c r="AT37" s="24" t="n"/>
+      <c r="AU37" s="24" t="n"/>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="n"/>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="n"/>
       <c r="BA37" s="24" t="n"/>
       <c r="BB37" s="24" t="n"/>
       <c r="BC37" s="24" t="n"/>
@@ -5737,7 +5676,7 @@
       <c r="BN37" s="24" t="n"/>
       <c r="BO37" s="24" t="n"/>
     </row>
-    <row r="38" ht="16" customHeight="1">
+    <row r="38" ht="18" customHeight="1">
       <c r="A38" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -5753,38 +5692,33 @@
           <t>PAB115·零件到位</t>
         </is>
       </c>
-      <c r="D38" s="27" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E38" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F38" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G38" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H38" s="29" t="n"/>
-      <c r="I38" s="29" t="n"/>
-      <c r="J38" s="29" t="n"/>
-      <c r="K38" s="29" t="n"/>
-      <c r="L38" s="29" t="n"/>
-      <c r="M38" s="29" t="n"/>
-      <c r="N38" s="29" t="n"/>
-      <c r="O38" s="29" t="n"/>
-      <c r="P38" s="29" t="n"/>
-      <c r="Q38" s="29" t="n"/>
-      <c r="R38" s="29" t="n"/>
-      <c r="S38" s="29" t="n"/>
-      <c r="T38" s="29" t="n"/>
-      <c r="U38" s="30" t="n"/>
+      <c r="D38" s="27">
+        <f>IF('时间节点计划表'!E19="","",'时间节点计划表'!E19)</f>
+        <v/>
+      </c>
+      <c r="E38" s="27">
+        <f>IF('时间节点计划表'!F19="","",'时间节点计划表'!F19)</f>
+        <v/>
+      </c>
+      <c r="F38" s="28">
+        <f>IF(OR(D38="",E38=""),"待填",E38-D38)</f>
+        <v/>
+      </c>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="24" t="n"/>
+      <c r="I38" s="24" t="n"/>
+      <c r="J38" s="24" t="n"/>
+      <c r="K38" s="24" t="n"/>
+      <c r="L38" s="24" t="n"/>
+      <c r="M38" s="24" t="n"/>
+      <c r="N38" s="24" t="n"/>
+      <c r="O38" s="24" t="n"/>
+      <c r="P38" s="24" t="n"/>
+      <c r="Q38" s="24" t="n"/>
+      <c r="R38" s="24" t="n"/>
+      <c r="S38" s="24" t="n"/>
+      <c r="T38" s="24" t="n"/>
+      <c r="U38" s="24" t="n"/>
       <c r="V38" s="24" t="n"/>
       <c r="W38" s="24" t="n"/>
       <c r="X38" s="24" t="n"/>
@@ -5832,7 +5766,7 @@
       <c r="BN38" s="24" t="n"/>
       <c r="BO38" s="24" t="n"/>
     </row>
-    <row r="39" ht="16" customHeight="1">
+    <row r="39" ht="18" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -5848,29 +5782,27 @@
           <t>PAB115·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D39" s="22" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E39" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F39" s="20" t="inlineStr"/>
-      <c r="G39" s="31" t="n"/>
-      <c r="H39" s="31" t="n"/>
-      <c r="I39" s="31" t="n"/>
-      <c r="J39" s="31" t="n"/>
-      <c r="K39" s="31" t="n"/>
-      <c r="L39" s="31" t="n"/>
-      <c r="M39" s="31" t="n"/>
-      <c r="N39" s="31" t="n"/>
-      <c r="O39" s="31" t="n"/>
-      <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="31" t="n"/>
-      <c r="R39" s="23" t="n">
-        <v>4</v>
-      </c>
+      <c r="D39" s="22">
+        <f>IF('时间节点计划表'!E20="","",'时间节点计划表'!E20)</f>
+        <v/>
+      </c>
+      <c r="E39" s="22">
+        <f>IF('时间节点计划表'!F20="","",'时间节点计划表'!F20)</f>
+        <v/>
+      </c>
+      <c r="F39" s="23" t="inlineStr"/>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="24" t="n"/>
+      <c r="J39" s="24" t="n"/>
+      <c r="K39" s="24" t="n"/>
+      <c r="L39" s="24" t="n"/>
+      <c r="M39" s="24" t="n"/>
+      <c r="N39" s="24" t="n"/>
+      <c r="O39" s="24" t="n"/>
+      <c r="P39" s="24" t="n"/>
+      <c r="Q39" s="24" t="n"/>
+      <c r="R39" s="24" t="n"/>
       <c r="S39" s="24" t="n"/>
       <c r="T39" s="24" t="n"/>
       <c r="U39" s="24" t="n"/>
@@ -5921,7 +5853,7 @@
       <c r="BN39" s="24" t="n"/>
       <c r="BO39" s="24" t="n"/>
     </row>
-    <row r="40" ht="16" customHeight="1">
+    <row r="40" ht="18" customHeight="1">
       <c r="A40" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -5937,38 +5869,33 @@
           <t>PAB115·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D40" s="27" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E40" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F40" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G40" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H40" s="29" t="n"/>
-      <c r="I40" s="29" t="n"/>
-      <c r="J40" s="29" t="n"/>
-      <c r="K40" s="29" t="n"/>
-      <c r="L40" s="29" t="n"/>
-      <c r="M40" s="29" t="n"/>
-      <c r="N40" s="29" t="n"/>
-      <c r="O40" s="29" t="n"/>
-      <c r="P40" s="29" t="n"/>
-      <c r="Q40" s="29" t="n"/>
-      <c r="R40" s="29" t="n"/>
-      <c r="S40" s="29" t="n"/>
-      <c r="T40" s="29" t="n"/>
-      <c r="U40" s="30" t="n"/>
+      <c r="D40" s="27">
+        <f>IF('时间节点计划表'!E20="","",'时间节点计划表'!E20)</f>
+        <v/>
+      </c>
+      <c r="E40" s="27">
+        <f>IF('时间节点计划表'!F20="","",'时间节点计划表'!F20)</f>
+        <v/>
+      </c>
+      <c r="F40" s="28">
+        <f>IF(OR(D40="",E40=""),"待填",E40-D40)</f>
+        <v/>
+      </c>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="24" t="n"/>
+      <c r="J40" s="24" t="n"/>
+      <c r="K40" s="24" t="n"/>
+      <c r="L40" s="24" t="n"/>
+      <c r="M40" s="24" t="n"/>
+      <c r="N40" s="24" t="n"/>
+      <c r="O40" s="24" t="n"/>
+      <c r="P40" s="24" t="n"/>
+      <c r="Q40" s="24" t="n"/>
+      <c r="R40" s="24" t="n"/>
+      <c r="S40" s="24" t="n"/>
+      <c r="T40" s="24" t="n"/>
+      <c r="U40" s="24" t="n"/>
       <c r="V40" s="24" t="n"/>
       <c r="W40" s="24" t="n"/>
       <c r="X40" s="24" t="n"/>
@@ -6016,7 +5943,7 @@
       <c r="BN40" s="24" t="n"/>
       <c r="BO40" s="24" t="n"/>
     </row>
-    <row r="41" ht="16" customHeight="1">
+    <row r="41" ht="18" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -6032,50 +5959,48 @@
           <t>PAB115·工装实物到位</t>
         </is>
       </c>
-      <c r="D41" s="22" t="n">
-        <v>46290</v>
-      </c>
-      <c r="E41" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="inlineStr"/>
-      <c r="G41" s="31" t="n"/>
-      <c r="H41" s="31" t="n"/>
-      <c r="I41" s="31" t="n"/>
-      <c r="J41" s="31" t="n"/>
-      <c r="K41" s="31" t="n"/>
-      <c r="L41" s="31" t="n"/>
-      <c r="M41" s="31" t="n"/>
-      <c r="N41" s="31" t="n"/>
-      <c r="O41" s="31" t="n"/>
-      <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="31" t="n"/>
-      <c r="R41" s="31" t="n"/>
-      <c r="S41" s="31" t="n"/>
-      <c r="T41" s="31" t="n"/>
-      <c r="U41" s="31" t="n"/>
-      <c r="V41" s="31" t="n"/>
-      <c r="W41" s="31" t="n"/>
-      <c r="X41" s="31" t="n"/>
-      <c r="Y41" s="31" t="n"/>
-      <c r="Z41" s="31" t="n"/>
-      <c r="AA41" s="31" t="n"/>
-      <c r="AB41" s="31" t="n"/>
-      <c r="AC41" s="31" t="n"/>
-      <c r="AD41" s="31" t="n"/>
-      <c r="AE41" s="31" t="n"/>
-      <c r="AF41" s="31" t="n"/>
-      <c r="AG41" s="31" t="n"/>
-      <c r="AH41" s="31" t="n"/>
-      <c r="AI41" s="31" t="n"/>
-      <c r="AJ41" s="31" t="n"/>
-      <c r="AK41" s="31" t="n"/>
-      <c r="AL41" s="31" t="n"/>
-      <c r="AM41" s="23" t="n">
-        <v>25</v>
-      </c>
+      <c r="D41" s="22">
+        <f>IF('时间节点计划表'!E21="","",'时间节点计划表'!E21)</f>
+        <v/>
+      </c>
+      <c r="E41" s="22">
+        <f>IF('时间节点计划表'!F21="","",'时间节点计划表'!F21)</f>
+        <v/>
+      </c>
+      <c r="F41" s="23" t="inlineStr"/>
+      <c r="G41" s="24" t="n"/>
+      <c r="H41" s="24" t="n"/>
+      <c r="I41" s="24" t="n"/>
+      <c r="J41" s="24" t="n"/>
+      <c r="K41" s="24" t="n"/>
+      <c r="L41" s="24" t="n"/>
+      <c r="M41" s="24" t="n"/>
+      <c r="N41" s="24" t="n"/>
+      <c r="O41" s="24" t="n"/>
+      <c r="P41" s="24" t="n"/>
+      <c r="Q41" s="24" t="n"/>
+      <c r="R41" s="24" t="n"/>
+      <c r="S41" s="24" t="n"/>
+      <c r="T41" s="24" t="n"/>
+      <c r="U41" s="24" t="n"/>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="24" t="n"/>
+      <c r="X41" s="24" t="n"/>
+      <c r="Y41" s="24" t="n"/>
+      <c r="Z41" s="24" t="n"/>
+      <c r="AA41" s="24" t="n"/>
+      <c r="AB41" s="24" t="n"/>
+      <c r="AC41" s="24" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="24" t="n"/>
+      <c r="AF41" s="24" t="n"/>
+      <c r="AG41" s="24" t="n"/>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="24" t="n"/>
+      <c r="AJ41" s="24" t="n"/>
+      <c r="AK41" s="24" t="n"/>
+      <c r="AL41" s="24" t="n"/>
+      <c r="AM41" s="24" t="n"/>
       <c r="AN41" s="24" t="n"/>
       <c r="AO41" s="24" t="n"/>
       <c r="AP41" s="24" t="n"/>
@@ -6105,7 +6030,7 @@
       <c r="BN41" s="24" t="n"/>
       <c r="BO41" s="24" t="n"/>
     </row>
-    <row r="42" ht="16" customHeight="1">
+    <row r="42" ht="18" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -6121,38 +6046,33 @@
           <t>PAB115·工装实物到位</t>
         </is>
       </c>
-      <c r="D42" s="27" t="n">
-        <v>46290</v>
-      </c>
-      <c r="E42" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G42" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H42" s="29" t="n"/>
-      <c r="I42" s="29" t="n"/>
-      <c r="J42" s="29" t="n"/>
-      <c r="K42" s="29" t="n"/>
-      <c r="L42" s="29" t="n"/>
-      <c r="M42" s="29" t="n"/>
-      <c r="N42" s="29" t="n"/>
-      <c r="O42" s="29" t="n"/>
-      <c r="P42" s="29" t="n"/>
-      <c r="Q42" s="29" t="n"/>
-      <c r="R42" s="29" t="n"/>
-      <c r="S42" s="29" t="n"/>
-      <c r="T42" s="29" t="n"/>
-      <c r="U42" s="30" t="n"/>
+      <c r="D42" s="27">
+        <f>IF('时间节点计划表'!E21="","",'时间节点计划表'!E21)</f>
+        <v/>
+      </c>
+      <c r="E42" s="27">
+        <f>IF('时间节点计划表'!F21="","",'时间节点计划表'!F21)</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>IF(OR(D42="",E42=""),"待填",E42-D42)</f>
+        <v/>
+      </c>
+      <c r="G42" s="24" t="n"/>
+      <c r="H42" s="24" t="n"/>
+      <c r="I42" s="24" t="n"/>
+      <c r="J42" s="24" t="n"/>
+      <c r="K42" s="24" t="n"/>
+      <c r="L42" s="24" t="n"/>
+      <c r="M42" s="24" t="n"/>
+      <c r="N42" s="24" t="n"/>
+      <c r="O42" s="24" t="n"/>
+      <c r="P42" s="24" t="n"/>
+      <c r="Q42" s="24" t="n"/>
+      <c r="R42" s="24" t="n"/>
+      <c r="S42" s="24" t="n"/>
+      <c r="T42" s="24" t="n"/>
+      <c r="U42" s="24" t="n"/>
       <c r="V42" s="24" t="n"/>
       <c r="W42" s="24" t="n"/>
       <c r="X42" s="24" t="n"/>
@@ -6200,7 +6120,7 @@
       <c r="BN42" s="24" t="n"/>
       <c r="BO42" s="24" t="n"/>
     </row>
-    <row r="43" ht="16" customHeight="1">
+    <row r="43" ht="18" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -6216,63 +6136,61 @@
           <t>PAB115·排针机安装调试</t>
         </is>
       </c>
-      <c r="D43" s="22" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E43" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="inlineStr"/>
-      <c r="G43" s="31" t="n"/>
-      <c r="H43" s="31" t="n"/>
-      <c r="I43" s="31" t="n"/>
-      <c r="J43" s="31" t="n"/>
-      <c r="K43" s="31" t="n"/>
-      <c r="L43" s="31" t="n"/>
-      <c r="M43" s="31" t="n"/>
-      <c r="N43" s="31" t="n"/>
-      <c r="O43" s="31" t="n"/>
-      <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="31" t="n"/>
-      <c r="R43" s="31" t="n"/>
-      <c r="S43" s="31" t="n"/>
-      <c r="T43" s="31" t="n"/>
-      <c r="U43" s="31" t="n"/>
-      <c r="V43" s="31" t="n"/>
-      <c r="W43" s="31" t="n"/>
-      <c r="X43" s="31" t="n"/>
-      <c r="Y43" s="31" t="n"/>
-      <c r="Z43" s="31" t="n"/>
-      <c r="AA43" s="31" t="n"/>
-      <c r="AB43" s="31" t="n"/>
-      <c r="AC43" s="31" t="n"/>
-      <c r="AD43" s="31" t="n"/>
-      <c r="AE43" s="31" t="n"/>
-      <c r="AF43" s="31" t="n"/>
-      <c r="AG43" s="31" t="n"/>
-      <c r="AH43" s="31" t="n"/>
-      <c r="AI43" s="31" t="n"/>
-      <c r="AJ43" s="31" t="n"/>
-      <c r="AK43" s="31" t="n"/>
-      <c r="AL43" s="31" t="n"/>
-      <c r="AM43" s="31" t="n"/>
-      <c r="AN43" s="31" t="n"/>
-      <c r="AO43" s="31" t="n"/>
-      <c r="AP43" s="31" t="n"/>
-      <c r="AQ43" s="31" t="n"/>
-      <c r="AR43" s="31" t="n"/>
-      <c r="AS43" s="31" t="n"/>
-      <c r="AT43" s="31" t="n"/>
-      <c r="AU43" s="31" t="n"/>
-      <c r="AV43" s="31" t="n"/>
-      <c r="AW43" s="31" t="n"/>
-      <c r="AX43" s="31" t="n"/>
-      <c r="AY43" s="31" t="n"/>
-      <c r="AZ43" s="23" t="n">
-        <v>8</v>
-      </c>
+      <c r="D43" s="22">
+        <f>IF('时间节点计划表'!E22="","",'时间节点计划表'!E22)</f>
+        <v/>
+      </c>
+      <c r="E43" s="22">
+        <f>IF('时间节点计划表'!F22="","",'时间节点计划表'!F22)</f>
+        <v/>
+      </c>
+      <c r="F43" s="23" t="inlineStr"/>
+      <c r="G43" s="24" t="n"/>
+      <c r="H43" s="24" t="n"/>
+      <c r="I43" s="24" t="n"/>
+      <c r="J43" s="24" t="n"/>
+      <c r="K43" s="24" t="n"/>
+      <c r="L43" s="24" t="n"/>
+      <c r="M43" s="24" t="n"/>
+      <c r="N43" s="24" t="n"/>
+      <c r="O43" s="24" t="n"/>
+      <c r="P43" s="24" t="n"/>
+      <c r="Q43" s="24" t="n"/>
+      <c r="R43" s="24" t="n"/>
+      <c r="S43" s="24" t="n"/>
+      <c r="T43" s="24" t="n"/>
+      <c r="U43" s="24" t="n"/>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="24" t="n"/>
+      <c r="X43" s="24" t="n"/>
+      <c r="Y43" s="24" t="n"/>
+      <c r="Z43" s="24" t="n"/>
+      <c r="AA43" s="24" t="n"/>
+      <c r="AB43" s="24" t="n"/>
+      <c r="AC43" s="24" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="24" t="n"/>
+      <c r="AF43" s="24" t="n"/>
+      <c r="AG43" s="24" t="n"/>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="24" t="n"/>
+      <c r="AJ43" s="24" t="n"/>
+      <c r="AK43" s="24" t="n"/>
+      <c r="AL43" s="24" t="n"/>
+      <c r="AM43" s="24" t="n"/>
+      <c r="AN43" s="24" t="n"/>
+      <c r="AO43" s="24" t="n"/>
+      <c r="AP43" s="24" t="n"/>
+      <c r="AQ43" s="24" t="n"/>
+      <c r="AR43" s="24" t="n"/>
+      <c r="AS43" s="24" t="n"/>
+      <c r="AT43" s="24" t="n"/>
+      <c r="AU43" s="24" t="n"/>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="n"/>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="n"/>
       <c r="BA43" s="24" t="n"/>
       <c r="BB43" s="24" t="n"/>
       <c r="BC43" s="24" t="n"/>
@@ -6289,7 +6207,7 @@
       <c r="BN43" s="24" t="n"/>
       <c r="BO43" s="24" t="n"/>
     </row>
-    <row r="44" ht="16" customHeight="1">
+    <row r="44" ht="18" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -6305,38 +6223,33 @@
           <t>PAB115·排针机安装调试</t>
         </is>
       </c>
-      <c r="D44" s="27" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E44" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F44" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G44" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H44" s="29" t="n"/>
-      <c r="I44" s="29" t="n"/>
-      <c r="J44" s="29" t="n"/>
-      <c r="K44" s="29" t="n"/>
-      <c r="L44" s="29" t="n"/>
-      <c r="M44" s="29" t="n"/>
-      <c r="N44" s="29" t="n"/>
-      <c r="O44" s="29" t="n"/>
-      <c r="P44" s="29" t="n"/>
-      <c r="Q44" s="29" t="n"/>
-      <c r="R44" s="29" t="n"/>
-      <c r="S44" s="29" t="n"/>
-      <c r="T44" s="29" t="n"/>
-      <c r="U44" s="30" t="n"/>
+      <c r="D44" s="27">
+        <f>IF('时间节点计划表'!E22="","",'时间节点计划表'!E22)</f>
+        <v/>
+      </c>
+      <c r="E44" s="27">
+        <f>IF('时间节点计划表'!F22="","",'时间节点计划表'!F22)</f>
+        <v/>
+      </c>
+      <c r="F44" s="28">
+        <f>IF(OR(D44="",E44=""),"待填",E44-D44)</f>
+        <v/>
+      </c>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="n"/>
+      <c r="I44" s="24" t="n"/>
+      <c r="J44" s="24" t="n"/>
+      <c r="K44" s="24" t="n"/>
+      <c r="L44" s="24" t="n"/>
+      <c r="M44" s="24" t="n"/>
+      <c r="N44" s="24" t="n"/>
+      <c r="O44" s="24" t="n"/>
+      <c r="P44" s="24" t="n"/>
+      <c r="Q44" s="24" t="n"/>
+      <c r="R44" s="24" t="n"/>
+      <c r="S44" s="24" t="n"/>
+      <c r="T44" s="24" t="n"/>
+      <c r="U44" s="24" t="n"/>
       <c r="V44" s="24" t="n"/>
       <c r="W44" s="24" t="n"/>
       <c r="X44" s="24" t="n"/>
@@ -6384,7 +6297,7 @@
       <c r="BN44" s="24" t="n"/>
       <c r="BO44" s="24" t="n"/>
     </row>
-    <row r="45" ht="16" customHeight="1">
+    <row r="45" ht="18" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -6400,64 +6313,62 @@
           <t>PAB115·单级样机</t>
         </is>
       </c>
-      <c r="D45" s="22" t="n">
-        <v>46304</v>
-      </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr"/>
-      <c r="G45" s="31" t="n"/>
-      <c r="H45" s="31" t="n"/>
-      <c r="I45" s="31" t="n"/>
-      <c r="J45" s="31" t="n"/>
-      <c r="K45" s="31" t="n"/>
-      <c r="L45" s="31" t="n"/>
-      <c r="M45" s="31" t="n"/>
-      <c r="N45" s="31" t="n"/>
-      <c r="O45" s="31" t="n"/>
-      <c r="P45" s="31" t="n"/>
-      <c r="Q45" s="31" t="n"/>
-      <c r="R45" s="31" t="n"/>
-      <c r="S45" s="31" t="n"/>
-      <c r="T45" s="31" t="n"/>
-      <c r="U45" s="31" t="n"/>
-      <c r="V45" s="31" t="n"/>
-      <c r="W45" s="31" t="n"/>
-      <c r="X45" s="31" t="n"/>
-      <c r="Y45" s="31" t="n"/>
-      <c r="Z45" s="31" t="n"/>
-      <c r="AA45" s="31" t="n"/>
-      <c r="AB45" s="31" t="n"/>
-      <c r="AC45" s="31" t="n"/>
-      <c r="AD45" s="31" t="n"/>
-      <c r="AE45" s="31" t="n"/>
-      <c r="AF45" s="31" t="n"/>
-      <c r="AG45" s="31" t="n"/>
-      <c r="AH45" s="31" t="n"/>
-      <c r="AI45" s="31" t="n"/>
-      <c r="AJ45" s="31" t="n"/>
-      <c r="AK45" s="31" t="n"/>
-      <c r="AL45" s="31" t="n"/>
-      <c r="AM45" s="31" t="n"/>
-      <c r="AN45" s="31" t="n"/>
-      <c r="AO45" s="31" t="n"/>
-      <c r="AP45" s="31" t="n"/>
-      <c r="AQ45" s="31" t="n"/>
-      <c r="AR45" s="31" t="n"/>
-      <c r="AS45" s="31" t="n"/>
-      <c r="AT45" s="31" t="n"/>
-      <c r="AU45" s="31" t="n"/>
-      <c r="AV45" s="31" t="n"/>
-      <c r="AW45" s="31" t="n"/>
-      <c r="AX45" s="31" t="n"/>
-      <c r="AY45" s="31" t="n"/>
-      <c r="AZ45" s="31" t="n"/>
-      <c r="BA45" s="23" t="n">
-        <v>9</v>
-      </c>
+      <c r="D45" s="22">
+        <f>IF('时间节点计划表'!E23="","",'时间节点计划表'!E23)</f>
+        <v/>
+      </c>
+      <c r="E45" s="22">
+        <f>IF('时间节点计划表'!F23="","",'时间节点计划表'!F23)</f>
+        <v/>
+      </c>
+      <c r="F45" s="23" t="inlineStr"/>
+      <c r="G45" s="24" t="n"/>
+      <c r="H45" s="24" t="n"/>
+      <c r="I45" s="24" t="n"/>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="24" t="n"/>
+      <c r="L45" s="24" t="n"/>
+      <c r="M45" s="24" t="n"/>
+      <c r="N45" s="24" t="n"/>
+      <c r="O45" s="24" t="n"/>
+      <c r="P45" s="24" t="n"/>
+      <c r="Q45" s="24" t="n"/>
+      <c r="R45" s="24" t="n"/>
+      <c r="S45" s="24" t="n"/>
+      <c r="T45" s="24" t="n"/>
+      <c r="U45" s="24" t="n"/>
+      <c r="V45" s="24" t="n"/>
+      <c r="W45" s="24" t="n"/>
+      <c r="X45" s="24" t="n"/>
+      <c r="Y45" s="24" t="n"/>
+      <c r="Z45" s="24" t="n"/>
+      <c r="AA45" s="24" t="n"/>
+      <c r="AB45" s="24" t="n"/>
+      <c r="AC45" s="24" t="n"/>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="24" t="n"/>
+      <c r="AF45" s="24" t="n"/>
+      <c r="AG45" s="24" t="n"/>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="24" t="n"/>
+      <c r="AJ45" s="24" t="n"/>
+      <c r="AK45" s="24" t="n"/>
+      <c r="AL45" s="24" t="n"/>
+      <c r="AM45" s="24" t="n"/>
+      <c r="AN45" s="24" t="n"/>
+      <c r="AO45" s="24" t="n"/>
+      <c r="AP45" s="24" t="n"/>
+      <c r="AQ45" s="24" t="n"/>
+      <c r="AR45" s="24" t="n"/>
+      <c r="AS45" s="24" t="n"/>
+      <c r="AT45" s="24" t="n"/>
+      <c r="AU45" s="24" t="n"/>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="n"/>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="n"/>
+      <c r="BA45" s="24" t="n"/>
       <c r="BB45" s="24" t="n"/>
       <c r="BC45" s="24" t="n"/>
       <c r="BD45" s="24" t="n"/>
@@ -6473,7 +6384,7 @@
       <c r="BN45" s="24" t="n"/>
       <c r="BO45" s="24" t="n"/>
     </row>
-    <row r="46" ht="16" customHeight="1">
+    <row r="46" ht="18" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -6489,38 +6400,33 @@
           <t>PAB115·单级样机</t>
         </is>
       </c>
-      <c r="D46" s="27" t="n">
-        <v>46304</v>
-      </c>
-      <c r="E46" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F46" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G46" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H46" s="29" t="n"/>
-      <c r="I46" s="29" t="n"/>
-      <c r="J46" s="29" t="n"/>
-      <c r="K46" s="29" t="n"/>
-      <c r="L46" s="29" t="n"/>
-      <c r="M46" s="29" t="n"/>
-      <c r="N46" s="29" t="n"/>
-      <c r="O46" s="29" t="n"/>
-      <c r="P46" s="29" t="n"/>
-      <c r="Q46" s="29" t="n"/>
-      <c r="R46" s="29" t="n"/>
-      <c r="S46" s="29" t="n"/>
-      <c r="T46" s="29" t="n"/>
-      <c r="U46" s="30" t="n"/>
+      <c r="D46" s="27">
+        <f>IF('时间节点计划表'!E23="","",'时间节点计划表'!E23)</f>
+        <v/>
+      </c>
+      <c r="E46" s="27">
+        <f>IF('时间节点计划表'!F23="","",'时间节点计划表'!F23)</f>
+        <v/>
+      </c>
+      <c r="F46" s="28">
+        <f>IF(OR(D46="",E46=""),"待填",E46-D46)</f>
+        <v/>
+      </c>
+      <c r="G46" s="24" t="n"/>
+      <c r="H46" s="24" t="n"/>
+      <c r="I46" s="24" t="n"/>
+      <c r="J46" s="24" t="n"/>
+      <c r="K46" s="24" t="n"/>
+      <c r="L46" s="24" t="n"/>
+      <c r="M46" s="24" t="n"/>
+      <c r="N46" s="24" t="n"/>
+      <c r="O46" s="24" t="n"/>
+      <c r="P46" s="24" t="n"/>
+      <c r="Q46" s="24" t="n"/>
+      <c r="R46" s="24" t="n"/>
+      <c r="S46" s="24" t="n"/>
+      <c r="T46" s="24" t="n"/>
+      <c r="U46" s="24" t="n"/>
       <c r="V46" s="24" t="n"/>
       <c r="W46" s="24" t="n"/>
       <c r="X46" s="24" t="n"/>
@@ -6568,7 +6474,7 @@
       <c r="BN46" s="24" t="n"/>
       <c r="BO46" s="24" t="n"/>
     </row>
-    <row r="47" ht="16" customHeight="1">
+    <row r="47" ht="18" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -6584,66 +6490,64 @@
           <t>PAB115·双级样机</t>
         </is>
       </c>
-      <c r="D47" s="22" t="n">
-        <v>46306</v>
-      </c>
-      <c r="E47" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F47" s="20" t="inlineStr"/>
-      <c r="G47" s="31" t="n"/>
-      <c r="H47" s="31" t="n"/>
-      <c r="I47" s="31" t="n"/>
-      <c r="J47" s="31" t="n"/>
-      <c r="K47" s="31" t="n"/>
-      <c r="L47" s="31" t="n"/>
-      <c r="M47" s="31" t="n"/>
-      <c r="N47" s="31" t="n"/>
-      <c r="O47" s="31" t="n"/>
-      <c r="P47" s="31" t="n"/>
-      <c r="Q47" s="31" t="n"/>
-      <c r="R47" s="31" t="n"/>
-      <c r="S47" s="31" t="n"/>
-      <c r="T47" s="31" t="n"/>
-      <c r="U47" s="31" t="n"/>
-      <c r="V47" s="31" t="n"/>
-      <c r="W47" s="31" t="n"/>
-      <c r="X47" s="31" t="n"/>
-      <c r="Y47" s="31" t="n"/>
-      <c r="Z47" s="31" t="n"/>
-      <c r="AA47" s="31" t="n"/>
-      <c r="AB47" s="31" t="n"/>
-      <c r="AC47" s="31" t="n"/>
-      <c r="AD47" s="31" t="n"/>
-      <c r="AE47" s="31" t="n"/>
-      <c r="AF47" s="31" t="n"/>
-      <c r="AG47" s="31" t="n"/>
-      <c r="AH47" s="31" t="n"/>
-      <c r="AI47" s="31" t="n"/>
-      <c r="AJ47" s="31" t="n"/>
-      <c r="AK47" s="31" t="n"/>
-      <c r="AL47" s="31" t="n"/>
-      <c r="AM47" s="31" t="n"/>
-      <c r="AN47" s="31" t="n"/>
-      <c r="AO47" s="31" t="n"/>
-      <c r="AP47" s="31" t="n"/>
-      <c r="AQ47" s="31" t="n"/>
-      <c r="AR47" s="31" t="n"/>
-      <c r="AS47" s="31" t="n"/>
-      <c r="AT47" s="31" t="n"/>
-      <c r="AU47" s="31" t="n"/>
-      <c r="AV47" s="31" t="n"/>
-      <c r="AW47" s="31" t="n"/>
-      <c r="AX47" s="31" t="n"/>
-      <c r="AY47" s="31" t="n"/>
-      <c r="AZ47" s="31" t="n"/>
-      <c r="BA47" s="31" t="n"/>
-      <c r="BB47" s="31" t="n"/>
-      <c r="BC47" s="23" t="n">
-        <v>11</v>
-      </c>
+      <c r="D47" s="22">
+        <f>IF('时间节点计划表'!E24="","",'时间节点计划表'!E24)</f>
+        <v/>
+      </c>
+      <c r="E47" s="22">
+        <f>IF('时间节点计划表'!F24="","",'时间节点计划表'!F24)</f>
+        <v/>
+      </c>
+      <c r="F47" s="23" t="inlineStr"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+      <c r="I47" s="24" t="n"/>
+      <c r="J47" s="24" t="n"/>
+      <c r="K47" s="24" t="n"/>
+      <c r="L47" s="24" t="n"/>
+      <c r="M47" s="24" t="n"/>
+      <c r="N47" s="24" t="n"/>
+      <c r="O47" s="24" t="n"/>
+      <c r="P47" s="24" t="n"/>
+      <c r="Q47" s="24" t="n"/>
+      <c r="R47" s="24" t="n"/>
+      <c r="S47" s="24" t="n"/>
+      <c r="T47" s="24" t="n"/>
+      <c r="U47" s="24" t="n"/>
+      <c r="V47" s="24" t="n"/>
+      <c r="W47" s="24" t="n"/>
+      <c r="X47" s="24" t="n"/>
+      <c r="Y47" s="24" t="n"/>
+      <c r="Z47" s="24" t="n"/>
+      <c r="AA47" s="24" t="n"/>
+      <c r="AB47" s="24" t="n"/>
+      <c r="AC47" s="24" t="n"/>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="24" t="n"/>
+      <c r="AF47" s="24" t="n"/>
+      <c r="AG47" s="24" t="n"/>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="24" t="n"/>
+      <c r="AJ47" s="24" t="n"/>
+      <c r="AK47" s="24" t="n"/>
+      <c r="AL47" s="24" t="n"/>
+      <c r="AM47" s="24" t="n"/>
+      <c r="AN47" s="24" t="n"/>
+      <c r="AO47" s="24" t="n"/>
+      <c r="AP47" s="24" t="n"/>
+      <c r="AQ47" s="24" t="n"/>
+      <c r="AR47" s="24" t="n"/>
+      <c r="AS47" s="24" t="n"/>
+      <c r="AT47" s="24" t="n"/>
+      <c r="AU47" s="24" t="n"/>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="n"/>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="n"/>
+      <c r="BA47" s="24" t="n"/>
+      <c r="BB47" s="24" t="n"/>
+      <c r="BC47" s="24" t="n"/>
       <c r="BD47" s="24" t="n"/>
       <c r="BE47" s="24" t="n"/>
       <c r="BF47" s="24" t="n"/>
@@ -6657,7 +6561,7 @@
       <c r="BN47" s="24" t="n"/>
       <c r="BO47" s="24" t="n"/>
     </row>
-    <row r="48" ht="16" customHeight="1">
+    <row r="48" ht="18" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -6673,38 +6577,33 @@
           <t>PAB115·双级样机</t>
         </is>
       </c>
-      <c r="D48" s="27" t="n">
-        <v>46306</v>
-      </c>
-      <c r="E48" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F48" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G48" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H48" s="29" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="29" t="n"/>
-      <c r="K48" s="29" t="n"/>
-      <c r="L48" s="29" t="n"/>
-      <c r="M48" s="29" t="n"/>
-      <c r="N48" s="29" t="n"/>
-      <c r="O48" s="29" t="n"/>
-      <c r="P48" s="29" t="n"/>
-      <c r="Q48" s="29" t="n"/>
-      <c r="R48" s="29" t="n"/>
-      <c r="S48" s="29" t="n"/>
-      <c r="T48" s="29" t="n"/>
-      <c r="U48" s="30" t="n"/>
+      <c r="D48" s="27">
+        <f>IF('时间节点计划表'!E24="","",'时间节点计划表'!E24)</f>
+        <v/>
+      </c>
+      <c r="E48" s="27">
+        <f>IF('时间节点计划表'!F24="","",'时间节点计划表'!F24)</f>
+        <v/>
+      </c>
+      <c r="F48" s="28">
+        <f>IF(OR(D48="",E48=""),"待填",E48-D48)</f>
+        <v/>
+      </c>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
+      <c r="K48" s="24" t="n"/>
+      <c r="L48" s="24" t="n"/>
+      <c r="M48" s="24" t="n"/>
+      <c r="N48" s="24" t="n"/>
+      <c r="O48" s="24" t="n"/>
+      <c r="P48" s="24" t="n"/>
+      <c r="Q48" s="24" t="n"/>
+      <c r="R48" s="24" t="n"/>
+      <c r="S48" s="24" t="n"/>
+      <c r="T48" s="24" t="n"/>
+      <c r="U48" s="24" t="n"/>
       <c r="V48" s="24" t="n"/>
       <c r="W48" s="24" t="n"/>
       <c r="X48" s="24" t="n"/>
@@ -6752,7 +6651,7 @@
       <c r="BN48" s="24" t="n"/>
       <c r="BO48" s="24" t="n"/>
     </row>
-    <row r="49" ht="16" customHeight="1">
+    <row r="49" ht="18" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -6768,67 +6667,65 @@
           <t>PAB142·零件到位</t>
         </is>
       </c>
-      <c r="D49" s="22" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr"/>
-      <c r="G49" s="31" t="n"/>
-      <c r="H49" s="31" t="n"/>
-      <c r="I49" s="31" t="n"/>
-      <c r="J49" s="31" t="n"/>
-      <c r="K49" s="31" t="n"/>
-      <c r="L49" s="31" t="n"/>
-      <c r="M49" s="31" t="n"/>
-      <c r="N49" s="31" t="n"/>
-      <c r="O49" s="31" t="n"/>
-      <c r="P49" s="31" t="n"/>
-      <c r="Q49" s="31" t="n"/>
-      <c r="R49" s="31" t="n"/>
-      <c r="S49" s="31" t="n"/>
-      <c r="T49" s="31" t="n"/>
-      <c r="U49" s="31" t="n"/>
-      <c r="V49" s="31" t="n"/>
-      <c r="W49" s="31" t="n"/>
-      <c r="X49" s="31" t="n"/>
-      <c r="Y49" s="31" t="n"/>
-      <c r="Z49" s="31" t="n"/>
-      <c r="AA49" s="31" t="n"/>
-      <c r="AB49" s="31" t="n"/>
-      <c r="AC49" s="31" t="n"/>
-      <c r="AD49" s="31" t="n"/>
-      <c r="AE49" s="31" t="n"/>
-      <c r="AF49" s="31" t="n"/>
-      <c r="AG49" s="31" t="n"/>
-      <c r="AH49" s="31" t="n"/>
-      <c r="AI49" s="31" t="n"/>
-      <c r="AJ49" s="31" t="n"/>
-      <c r="AK49" s="31" t="n"/>
-      <c r="AL49" s="31" t="n"/>
-      <c r="AM49" s="31" t="n"/>
-      <c r="AN49" s="31" t="n"/>
-      <c r="AO49" s="31" t="n"/>
-      <c r="AP49" s="31" t="n"/>
-      <c r="AQ49" s="31" t="n"/>
-      <c r="AR49" s="31" t="n"/>
-      <c r="AS49" s="31" t="n"/>
-      <c r="AT49" s="31" t="n"/>
-      <c r="AU49" s="31" t="n"/>
-      <c r="AV49" s="31" t="n"/>
-      <c r="AW49" s="31" t="n"/>
-      <c r="AX49" s="31" t="n"/>
-      <c r="AY49" s="31" t="n"/>
-      <c r="AZ49" s="31" t="n"/>
-      <c r="BA49" s="31" t="n"/>
-      <c r="BB49" s="31" t="n"/>
-      <c r="BC49" s="31" t="n"/>
-      <c r="BD49" s="23" t="n">
-        <v>12</v>
-      </c>
+      <c r="D49" s="22">
+        <f>IF('时间节点计划表'!E25="","",'时间节点计划表'!E25)</f>
+        <v/>
+      </c>
+      <c r="E49" s="22">
+        <f>IF('时间节点计划表'!F25="","",'时间节点计划表'!F25)</f>
+        <v/>
+      </c>
+      <c r="F49" s="23" t="inlineStr"/>
+      <c r="G49" s="24" t="n"/>
+      <c r="H49" s="24" t="n"/>
+      <c r="I49" s="24" t="n"/>
+      <c r="J49" s="24" t="n"/>
+      <c r="K49" s="24" t="n"/>
+      <c r="L49" s="24" t="n"/>
+      <c r="M49" s="24" t="n"/>
+      <c r="N49" s="24" t="n"/>
+      <c r="O49" s="24" t="n"/>
+      <c r="P49" s="24" t="n"/>
+      <c r="Q49" s="24" t="n"/>
+      <c r="R49" s="24" t="n"/>
+      <c r="S49" s="24" t="n"/>
+      <c r="T49" s="24" t="n"/>
+      <c r="U49" s="24" t="n"/>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="24" t="n"/>
+      <c r="X49" s="24" t="n"/>
+      <c r="Y49" s="24" t="n"/>
+      <c r="Z49" s="24" t="n"/>
+      <c r="AA49" s="24" t="n"/>
+      <c r="AB49" s="24" t="n"/>
+      <c r="AC49" s="24" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="24" t="n"/>
+      <c r="AF49" s="24" t="n"/>
+      <c r="AG49" s="24" t="n"/>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="24" t="n"/>
+      <c r="AJ49" s="24" t="n"/>
+      <c r="AK49" s="24" t="n"/>
+      <c r="AL49" s="24" t="n"/>
+      <c r="AM49" s="24" t="n"/>
+      <c r="AN49" s="24" t="n"/>
+      <c r="AO49" s="24" t="n"/>
+      <c r="AP49" s="24" t="n"/>
+      <c r="AQ49" s="24" t="n"/>
+      <c r="AR49" s="24" t="n"/>
+      <c r="AS49" s="24" t="n"/>
+      <c r="AT49" s="24" t="n"/>
+      <c r="AU49" s="24" t="n"/>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="n"/>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="n"/>
+      <c r="BA49" s="24" t="n"/>
+      <c r="BB49" s="24" t="n"/>
+      <c r="BC49" s="24" t="n"/>
+      <c r="BD49" s="24" t="n"/>
       <c r="BE49" s="24" t="n"/>
       <c r="BF49" s="24" t="n"/>
       <c r="BG49" s="24" t="n"/>
@@ -6841,7 +6738,7 @@
       <c r="BN49" s="24" t="n"/>
       <c r="BO49" s="24" t="n"/>
     </row>
-    <row r="50" ht="16" customHeight="1">
+    <row r="50" ht="18" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -6857,38 +6754,33 @@
           <t>PAB142·零件到位</t>
         </is>
       </c>
-      <c r="D50" s="27" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E50" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F50" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G50" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H50" s="29" t="n"/>
-      <c r="I50" s="29" t="n"/>
-      <c r="J50" s="29" t="n"/>
-      <c r="K50" s="29" t="n"/>
-      <c r="L50" s="29" t="n"/>
-      <c r="M50" s="29" t="n"/>
-      <c r="N50" s="29" t="n"/>
-      <c r="O50" s="29" t="n"/>
-      <c r="P50" s="29" t="n"/>
-      <c r="Q50" s="29" t="n"/>
-      <c r="R50" s="29" t="n"/>
-      <c r="S50" s="29" t="n"/>
-      <c r="T50" s="29" t="n"/>
-      <c r="U50" s="30" t="n"/>
+      <c r="D50" s="27">
+        <f>IF('时间节点计划表'!E25="","",'时间节点计划表'!E25)</f>
+        <v/>
+      </c>
+      <c r="E50" s="27">
+        <f>IF('时间节点计划表'!F25="","",'时间节点计划表'!F25)</f>
+        <v/>
+      </c>
+      <c r="F50" s="28">
+        <f>IF(OR(D50="",E50=""),"待填",E50-D50)</f>
+        <v/>
+      </c>
+      <c r="G50" s="24" t="n"/>
+      <c r="H50" s="24" t="n"/>
+      <c r="I50" s="24" t="n"/>
+      <c r="J50" s="24" t="n"/>
+      <c r="K50" s="24" t="n"/>
+      <c r="L50" s="24" t="n"/>
+      <c r="M50" s="24" t="n"/>
+      <c r="N50" s="24" t="n"/>
+      <c r="O50" s="24" t="n"/>
+      <c r="P50" s="24" t="n"/>
+      <c r="Q50" s="24" t="n"/>
+      <c r="R50" s="24" t="n"/>
+      <c r="S50" s="24" t="n"/>
+      <c r="T50" s="24" t="n"/>
+      <c r="U50" s="24" t="n"/>
       <c r="V50" s="24" t="n"/>
       <c r="W50" s="24" t="n"/>
       <c r="X50" s="24" t="n"/>
@@ -6936,7 +6828,7 @@
       <c r="BN50" s="24" t="n"/>
       <c r="BO50" s="24" t="n"/>
     </row>
-    <row r="51" ht="16" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -6952,29 +6844,27 @@
           <t>PAB142·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D51" s="22" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E51" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F51" s="20" t="inlineStr"/>
-      <c r="G51" s="31" t="n"/>
-      <c r="H51" s="31" t="n"/>
-      <c r="I51" s="31" t="n"/>
-      <c r="J51" s="31" t="n"/>
-      <c r="K51" s="31" t="n"/>
-      <c r="L51" s="31" t="n"/>
-      <c r="M51" s="31" t="n"/>
-      <c r="N51" s="31" t="n"/>
-      <c r="O51" s="31" t="n"/>
-      <c r="P51" s="31" t="n"/>
-      <c r="Q51" s="31" t="n"/>
-      <c r="R51" s="23" t="n">
-        <v>4</v>
-      </c>
+      <c r="D51" s="22">
+        <f>IF('时间节点计划表'!E26="","",'时间节点计划表'!E26)</f>
+        <v/>
+      </c>
+      <c r="E51" s="22">
+        <f>IF('时间节点计划表'!F26="","",'时间节点计划表'!F26)</f>
+        <v/>
+      </c>
+      <c r="F51" s="23" t="inlineStr"/>
+      <c r="G51" s="24" t="n"/>
+      <c r="H51" s="24" t="n"/>
+      <c r="I51" s="24" t="n"/>
+      <c r="J51" s="24" t="n"/>
+      <c r="K51" s="24" t="n"/>
+      <c r="L51" s="24" t="n"/>
+      <c r="M51" s="24" t="n"/>
+      <c r="N51" s="24" t="n"/>
+      <c r="O51" s="24" t="n"/>
+      <c r="P51" s="24" t="n"/>
+      <c r="Q51" s="24" t="n"/>
+      <c r="R51" s="24" t="n"/>
       <c r="S51" s="24" t="n"/>
       <c r="T51" s="24" t="n"/>
       <c r="U51" s="24" t="n"/>
@@ -7025,7 +6915,7 @@
       <c r="BN51" s="24" t="n"/>
       <c r="BO51" s="24" t="n"/>
     </row>
-    <row r="52" ht="16" customHeight="1">
+    <row r="52" ht="18" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -7041,38 +6931,33 @@
           <t>PAB142·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D52" s="27" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E52" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F52" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G52" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H52" s="29" t="n"/>
-      <c r="I52" s="29" t="n"/>
-      <c r="J52" s="29" t="n"/>
-      <c r="K52" s="29" t="n"/>
-      <c r="L52" s="29" t="n"/>
-      <c r="M52" s="29" t="n"/>
-      <c r="N52" s="29" t="n"/>
-      <c r="O52" s="29" t="n"/>
-      <c r="P52" s="29" t="n"/>
-      <c r="Q52" s="29" t="n"/>
-      <c r="R52" s="29" t="n"/>
-      <c r="S52" s="29" t="n"/>
-      <c r="T52" s="29" t="n"/>
-      <c r="U52" s="30" t="n"/>
+      <c r="D52" s="27">
+        <f>IF('时间节点计划表'!E26="","",'时间节点计划表'!E26)</f>
+        <v/>
+      </c>
+      <c r="E52" s="27">
+        <f>IF('时间节点计划表'!F26="","",'时间节点计划表'!F26)</f>
+        <v/>
+      </c>
+      <c r="F52" s="28">
+        <f>IF(OR(D52="",E52=""),"待填",E52-D52)</f>
+        <v/>
+      </c>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+      <c r="I52" s="24" t="n"/>
+      <c r="J52" s="24" t="n"/>
+      <c r="K52" s="24" t="n"/>
+      <c r="L52" s="24" t="n"/>
+      <c r="M52" s="24" t="n"/>
+      <c r="N52" s="24" t="n"/>
+      <c r="O52" s="24" t="n"/>
+      <c r="P52" s="24" t="n"/>
+      <c r="Q52" s="24" t="n"/>
+      <c r="R52" s="24" t="n"/>
+      <c r="S52" s="24" t="n"/>
+      <c r="T52" s="24" t="n"/>
+      <c r="U52" s="24" t="n"/>
       <c r="V52" s="24" t="n"/>
       <c r="W52" s="24" t="n"/>
       <c r="X52" s="24" t="n"/>
@@ -7120,7 +7005,7 @@
       <c r="BN52" s="24" t="n"/>
       <c r="BO52" s="24" t="n"/>
     </row>
-    <row r="53" ht="16" customHeight="1">
+    <row r="53" ht="18" customHeight="1">
       <c r="A53" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -7136,54 +7021,52 @@
           <t>PAB142·工装实物到位</t>
         </is>
       </c>
-      <c r="D53" s="22" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E53" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="inlineStr"/>
-      <c r="G53" s="31" t="n"/>
-      <c r="H53" s="31" t="n"/>
-      <c r="I53" s="31" t="n"/>
-      <c r="J53" s="31" t="n"/>
-      <c r="K53" s="31" t="n"/>
-      <c r="L53" s="31" t="n"/>
-      <c r="M53" s="31" t="n"/>
-      <c r="N53" s="31" t="n"/>
-      <c r="O53" s="31" t="n"/>
-      <c r="P53" s="31" t="n"/>
-      <c r="Q53" s="31" t="n"/>
-      <c r="R53" s="31" t="n"/>
-      <c r="S53" s="31" t="n"/>
-      <c r="T53" s="31" t="n"/>
-      <c r="U53" s="31" t="n"/>
-      <c r="V53" s="31" t="n"/>
-      <c r="W53" s="31" t="n"/>
-      <c r="X53" s="31" t="n"/>
-      <c r="Y53" s="31" t="n"/>
-      <c r="Z53" s="31" t="n"/>
-      <c r="AA53" s="31" t="n"/>
-      <c r="AB53" s="31" t="n"/>
-      <c r="AC53" s="31" t="n"/>
-      <c r="AD53" s="31" t="n"/>
-      <c r="AE53" s="31" t="n"/>
-      <c r="AF53" s="31" t="n"/>
-      <c r="AG53" s="31" t="n"/>
-      <c r="AH53" s="31" t="n"/>
-      <c r="AI53" s="31" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
-      <c r="AK53" s="31" t="n"/>
-      <c r="AL53" s="31" t="n"/>
-      <c r="AM53" s="31" t="n"/>
-      <c r="AN53" s="31" t="n"/>
-      <c r="AO53" s="31" t="n"/>
-      <c r="AP53" s="31" t="n"/>
-      <c r="AQ53" s="23" t="n">
-        <v>29</v>
-      </c>
+      <c r="D53" s="22">
+        <f>IF('时间节点计划表'!E27="","",'时间节点计划表'!E27)</f>
+        <v/>
+      </c>
+      <c r="E53" s="22">
+        <f>IF('时间节点计划表'!F27="","",'时间节点计划表'!F27)</f>
+        <v/>
+      </c>
+      <c r="F53" s="23" t="inlineStr"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="24" t="n"/>
+      <c r="J53" s="24" t="n"/>
+      <c r="K53" s="24" t="n"/>
+      <c r="L53" s="24" t="n"/>
+      <c r="M53" s="24" t="n"/>
+      <c r="N53" s="24" t="n"/>
+      <c r="O53" s="24" t="n"/>
+      <c r="P53" s="24" t="n"/>
+      <c r="Q53" s="24" t="n"/>
+      <c r="R53" s="24" t="n"/>
+      <c r="S53" s="24" t="n"/>
+      <c r="T53" s="24" t="n"/>
+      <c r="U53" s="24" t="n"/>
+      <c r="V53" s="24" t="n"/>
+      <c r="W53" s="24" t="n"/>
+      <c r="X53" s="24" t="n"/>
+      <c r="Y53" s="24" t="n"/>
+      <c r="Z53" s="24" t="n"/>
+      <c r="AA53" s="24" t="n"/>
+      <c r="AB53" s="24" t="n"/>
+      <c r="AC53" s="24" t="n"/>
+      <c r="AD53" s="24" t="n"/>
+      <c r="AE53" s="24" t="n"/>
+      <c r="AF53" s="24" t="n"/>
+      <c r="AG53" s="24" t="n"/>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="24" t="n"/>
+      <c r="AJ53" s="24" t="n"/>
+      <c r="AK53" s="24" t="n"/>
+      <c r="AL53" s="24" t="n"/>
+      <c r="AM53" s="24" t="n"/>
+      <c r="AN53" s="24" t="n"/>
+      <c r="AO53" s="24" t="n"/>
+      <c r="AP53" s="24" t="n"/>
+      <c r="AQ53" s="24" t="n"/>
       <c r="AR53" s="24" t="n"/>
       <c r="AS53" s="24" t="n"/>
       <c r="AT53" s="24" t="n"/>
@@ -7209,7 +7092,7 @@
       <c r="BN53" s="24" t="n"/>
       <c r="BO53" s="24" t="n"/>
     </row>
-    <row r="54" ht="16" customHeight="1">
+    <row r="54" ht="18" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -7225,38 +7108,33 @@
           <t>PAB142·工装实物到位</t>
         </is>
       </c>
-      <c r="D54" s="27" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E54" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F54" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G54" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H54" s="29" t="n"/>
-      <c r="I54" s="29" t="n"/>
-      <c r="J54" s="29" t="n"/>
-      <c r="K54" s="29" t="n"/>
-      <c r="L54" s="29" t="n"/>
-      <c r="M54" s="29" t="n"/>
-      <c r="N54" s="29" t="n"/>
-      <c r="O54" s="29" t="n"/>
-      <c r="P54" s="29" t="n"/>
-      <c r="Q54" s="29" t="n"/>
-      <c r="R54" s="29" t="n"/>
-      <c r="S54" s="29" t="n"/>
-      <c r="T54" s="29" t="n"/>
-      <c r="U54" s="30" t="n"/>
+      <c r="D54" s="27">
+        <f>IF('时间节点计划表'!E27="","",'时间节点计划表'!E27)</f>
+        <v/>
+      </c>
+      <c r="E54" s="27">
+        <f>IF('时间节点计划表'!F27="","",'时间节点计划表'!F27)</f>
+        <v/>
+      </c>
+      <c r="F54" s="28">
+        <f>IF(OR(D54="",E54=""),"待填",E54-D54)</f>
+        <v/>
+      </c>
+      <c r="G54" s="24" t="n"/>
+      <c r="H54" s="24" t="n"/>
+      <c r="I54" s="24" t="n"/>
+      <c r="J54" s="24" t="n"/>
+      <c r="K54" s="24" t="n"/>
+      <c r="L54" s="24" t="n"/>
+      <c r="M54" s="24" t="n"/>
+      <c r="N54" s="24" t="n"/>
+      <c r="O54" s="24" t="n"/>
+      <c r="P54" s="24" t="n"/>
+      <c r="Q54" s="24" t="n"/>
+      <c r="R54" s="24" t="n"/>
+      <c r="S54" s="24" t="n"/>
+      <c r="T54" s="24" t="n"/>
+      <c r="U54" s="24" t="n"/>
       <c r="V54" s="24" t="n"/>
       <c r="W54" s="24" t="n"/>
       <c r="X54" s="24" t="n"/>
@@ -7304,7 +7182,7 @@
       <c r="BN54" s="24" t="n"/>
       <c r="BO54" s="24" t="n"/>
     </row>
-    <row r="55" ht="16" customHeight="1">
+    <row r="55" ht="18" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -7320,67 +7198,65 @@
           <t>PAB142·排针机安装调试</t>
         </is>
       </c>
-      <c r="D55" s="22" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E55" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr"/>
-      <c r="G55" s="31" t="n"/>
-      <c r="H55" s="31" t="n"/>
-      <c r="I55" s="31" t="n"/>
-      <c r="J55" s="31" t="n"/>
-      <c r="K55" s="31" t="n"/>
-      <c r="L55" s="31" t="n"/>
-      <c r="M55" s="31" t="n"/>
-      <c r="N55" s="31" t="n"/>
-      <c r="O55" s="31" t="n"/>
-      <c r="P55" s="31" t="n"/>
-      <c r="Q55" s="31" t="n"/>
-      <c r="R55" s="31" t="n"/>
-      <c r="S55" s="31" t="n"/>
-      <c r="T55" s="31" t="n"/>
-      <c r="U55" s="31" t="n"/>
-      <c r="V55" s="31" t="n"/>
-      <c r="W55" s="31" t="n"/>
-      <c r="X55" s="31" t="n"/>
-      <c r="Y55" s="31" t="n"/>
-      <c r="Z55" s="31" t="n"/>
-      <c r="AA55" s="31" t="n"/>
-      <c r="AB55" s="31" t="n"/>
-      <c r="AC55" s="31" t="n"/>
-      <c r="AD55" s="31" t="n"/>
-      <c r="AE55" s="31" t="n"/>
-      <c r="AF55" s="31" t="n"/>
-      <c r="AG55" s="31" t="n"/>
-      <c r="AH55" s="31" t="n"/>
-      <c r="AI55" s="31" t="n"/>
-      <c r="AJ55" s="31" t="n"/>
-      <c r="AK55" s="31" t="n"/>
-      <c r="AL55" s="31" t="n"/>
-      <c r="AM55" s="31" t="n"/>
-      <c r="AN55" s="31" t="n"/>
-      <c r="AO55" s="31" t="n"/>
-      <c r="AP55" s="31" t="n"/>
-      <c r="AQ55" s="31" t="n"/>
-      <c r="AR55" s="31" t="n"/>
-      <c r="AS55" s="31" t="n"/>
-      <c r="AT55" s="31" t="n"/>
-      <c r="AU55" s="31" t="n"/>
-      <c r="AV55" s="31" t="n"/>
-      <c r="AW55" s="31" t="n"/>
-      <c r="AX55" s="31" t="n"/>
-      <c r="AY55" s="31" t="n"/>
-      <c r="AZ55" s="31" t="n"/>
-      <c r="BA55" s="31" t="n"/>
-      <c r="BB55" s="31" t="n"/>
-      <c r="BC55" s="31" t="n"/>
-      <c r="BD55" s="23" t="n">
-        <v>12</v>
-      </c>
+      <c r="D55" s="22">
+        <f>IF('时间节点计划表'!E28="","",'时间节点计划表'!E28)</f>
+        <v/>
+      </c>
+      <c r="E55" s="22">
+        <f>IF('时间节点计划表'!F28="","",'时间节点计划表'!F28)</f>
+        <v/>
+      </c>
+      <c r="F55" s="23" t="inlineStr"/>
+      <c r="G55" s="24" t="n"/>
+      <c r="H55" s="24" t="n"/>
+      <c r="I55" s="24" t="n"/>
+      <c r="J55" s="24" t="n"/>
+      <c r="K55" s="24" t="n"/>
+      <c r="L55" s="24" t="n"/>
+      <c r="M55" s="24" t="n"/>
+      <c r="N55" s="24" t="n"/>
+      <c r="O55" s="24" t="n"/>
+      <c r="P55" s="24" t="n"/>
+      <c r="Q55" s="24" t="n"/>
+      <c r="R55" s="24" t="n"/>
+      <c r="S55" s="24" t="n"/>
+      <c r="T55" s="24" t="n"/>
+      <c r="U55" s="24" t="n"/>
+      <c r="V55" s="24" t="n"/>
+      <c r="W55" s="24" t="n"/>
+      <c r="X55" s="24" t="n"/>
+      <c r="Y55" s="24" t="n"/>
+      <c r="Z55" s="24" t="n"/>
+      <c r="AA55" s="24" t="n"/>
+      <c r="AB55" s="24" t="n"/>
+      <c r="AC55" s="24" t="n"/>
+      <c r="AD55" s="24" t="n"/>
+      <c r="AE55" s="24" t="n"/>
+      <c r="AF55" s="24" t="n"/>
+      <c r="AG55" s="24" t="n"/>
+      <c r="AH55" s="24" t="n"/>
+      <c r="AI55" s="24" t="n"/>
+      <c r="AJ55" s="24" t="n"/>
+      <c r="AK55" s="24" t="n"/>
+      <c r="AL55" s="24" t="n"/>
+      <c r="AM55" s="24" t="n"/>
+      <c r="AN55" s="24" t="n"/>
+      <c r="AO55" s="24" t="n"/>
+      <c r="AP55" s="24" t="n"/>
+      <c r="AQ55" s="24" t="n"/>
+      <c r="AR55" s="24" t="n"/>
+      <c r="AS55" s="24" t="n"/>
+      <c r="AT55" s="24" t="n"/>
+      <c r="AU55" s="24" t="n"/>
+      <c r="AV55" s="24" t="n"/>
+      <c r="AW55" s="24" t="n"/>
+      <c r="AX55" s="24" t="n"/>
+      <c r="AY55" s="24" t="n"/>
+      <c r="AZ55" s="24" t="n"/>
+      <c r="BA55" s="24" t="n"/>
+      <c r="BB55" s="24" t="n"/>
+      <c r="BC55" s="24" t="n"/>
+      <c r="BD55" s="24" t="n"/>
       <c r="BE55" s="24" t="n"/>
       <c r="BF55" s="24" t="n"/>
       <c r="BG55" s="24" t="n"/>
@@ -7393,7 +7269,7 @@
       <c r="BN55" s="24" t="n"/>
       <c r="BO55" s="24" t="n"/>
     </row>
-    <row r="56" ht="16" customHeight="1">
+    <row r="56" ht="18" customHeight="1">
       <c r="A56" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -7409,38 +7285,33 @@
           <t>PAB142·排针机安装调试</t>
         </is>
       </c>
-      <c r="D56" s="27" t="n">
-        <v>46307</v>
-      </c>
-      <c r="E56" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F56" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G56" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H56" s="29" t="n"/>
-      <c r="I56" s="29" t="n"/>
-      <c r="J56" s="29" t="n"/>
-      <c r="K56" s="29" t="n"/>
-      <c r="L56" s="29" t="n"/>
-      <c r="M56" s="29" t="n"/>
-      <c r="N56" s="29" t="n"/>
-      <c r="O56" s="29" t="n"/>
-      <c r="P56" s="29" t="n"/>
-      <c r="Q56" s="29" t="n"/>
-      <c r="R56" s="29" t="n"/>
-      <c r="S56" s="29" t="n"/>
-      <c r="T56" s="29" t="n"/>
-      <c r="U56" s="30" t="n"/>
+      <c r="D56" s="27">
+        <f>IF('时间节点计划表'!E28="","",'时间节点计划表'!E28)</f>
+        <v/>
+      </c>
+      <c r="E56" s="27">
+        <f>IF('时间节点计划表'!F28="","",'时间节点计划表'!F28)</f>
+        <v/>
+      </c>
+      <c r="F56" s="28">
+        <f>IF(OR(D56="",E56=""),"待填",E56-D56)</f>
+        <v/>
+      </c>
+      <c r="G56" s="24" t="n"/>
+      <c r="H56" s="24" t="n"/>
+      <c r="I56" s="24" t="n"/>
+      <c r="J56" s="24" t="n"/>
+      <c r="K56" s="24" t="n"/>
+      <c r="L56" s="24" t="n"/>
+      <c r="M56" s="24" t="n"/>
+      <c r="N56" s="24" t="n"/>
+      <c r="O56" s="24" t="n"/>
+      <c r="P56" s="24" t="n"/>
+      <c r="Q56" s="24" t="n"/>
+      <c r="R56" s="24" t="n"/>
+      <c r="S56" s="24" t="n"/>
+      <c r="T56" s="24" t="n"/>
+      <c r="U56" s="24" t="n"/>
       <c r="V56" s="24" t="n"/>
       <c r="W56" s="24" t="n"/>
       <c r="X56" s="24" t="n"/>
@@ -7488,7 +7359,7 @@
       <c r="BN56" s="24" t="n"/>
       <c r="BO56" s="24" t="n"/>
     </row>
-    <row r="57" ht="16" customHeight="1">
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -7504,68 +7375,66 @@
           <t>PAB142·单级样机</t>
         </is>
       </c>
-      <c r="D57" s="22" t="n">
-        <v>46308</v>
-      </c>
-      <c r="E57" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="inlineStr"/>
-      <c r="G57" s="31" t="n"/>
-      <c r="H57" s="31" t="n"/>
-      <c r="I57" s="31" t="n"/>
-      <c r="J57" s="31" t="n"/>
-      <c r="K57" s="31" t="n"/>
-      <c r="L57" s="31" t="n"/>
-      <c r="M57" s="31" t="n"/>
-      <c r="N57" s="31" t="n"/>
-      <c r="O57" s="31" t="n"/>
-      <c r="P57" s="31" t="n"/>
-      <c r="Q57" s="31" t="n"/>
-      <c r="R57" s="31" t="n"/>
-      <c r="S57" s="31" t="n"/>
-      <c r="T57" s="31" t="n"/>
-      <c r="U57" s="31" t="n"/>
-      <c r="V57" s="31" t="n"/>
-      <c r="W57" s="31" t="n"/>
-      <c r="X57" s="31" t="n"/>
-      <c r="Y57" s="31" t="n"/>
-      <c r="Z57" s="31" t="n"/>
-      <c r="AA57" s="31" t="n"/>
-      <c r="AB57" s="31" t="n"/>
-      <c r="AC57" s="31" t="n"/>
-      <c r="AD57" s="31" t="n"/>
-      <c r="AE57" s="31" t="n"/>
-      <c r="AF57" s="31" t="n"/>
-      <c r="AG57" s="31" t="n"/>
-      <c r="AH57" s="31" t="n"/>
-      <c r="AI57" s="31" t="n"/>
-      <c r="AJ57" s="31" t="n"/>
-      <c r="AK57" s="31" t="n"/>
-      <c r="AL57" s="31" t="n"/>
-      <c r="AM57" s="31" t="n"/>
-      <c r="AN57" s="31" t="n"/>
-      <c r="AO57" s="31" t="n"/>
-      <c r="AP57" s="31" t="n"/>
-      <c r="AQ57" s="31" t="n"/>
-      <c r="AR57" s="31" t="n"/>
-      <c r="AS57" s="31" t="n"/>
-      <c r="AT57" s="31" t="n"/>
-      <c r="AU57" s="31" t="n"/>
-      <c r="AV57" s="31" t="n"/>
-      <c r="AW57" s="31" t="n"/>
-      <c r="AX57" s="31" t="n"/>
-      <c r="AY57" s="31" t="n"/>
-      <c r="AZ57" s="31" t="n"/>
-      <c r="BA57" s="31" t="n"/>
-      <c r="BB57" s="31" t="n"/>
-      <c r="BC57" s="31" t="n"/>
-      <c r="BD57" s="31" t="n"/>
-      <c r="BE57" s="23" t="n">
-        <v>13</v>
-      </c>
+      <c r="D57" s="22">
+        <f>IF('时间节点计划表'!E29="","",'时间节点计划表'!E29)</f>
+        <v/>
+      </c>
+      <c r="E57" s="22">
+        <f>IF('时间节点计划表'!F29="","",'时间节点计划表'!F29)</f>
+        <v/>
+      </c>
+      <c r="F57" s="23" t="inlineStr"/>
+      <c r="G57" s="24" t="n"/>
+      <c r="H57" s="24" t="n"/>
+      <c r="I57" s="24" t="n"/>
+      <c r="J57" s="24" t="n"/>
+      <c r="K57" s="24" t="n"/>
+      <c r="L57" s="24" t="n"/>
+      <c r="M57" s="24" t="n"/>
+      <c r="N57" s="24" t="n"/>
+      <c r="O57" s="24" t="n"/>
+      <c r="P57" s="24" t="n"/>
+      <c r="Q57" s="24" t="n"/>
+      <c r="R57" s="24" t="n"/>
+      <c r="S57" s="24" t="n"/>
+      <c r="T57" s="24" t="n"/>
+      <c r="U57" s="24" t="n"/>
+      <c r="V57" s="24" t="n"/>
+      <c r="W57" s="24" t="n"/>
+      <c r="X57" s="24" t="n"/>
+      <c r="Y57" s="24" t="n"/>
+      <c r="Z57" s="24" t="n"/>
+      <c r="AA57" s="24" t="n"/>
+      <c r="AB57" s="24" t="n"/>
+      <c r="AC57" s="24" t="n"/>
+      <c r="AD57" s="24" t="n"/>
+      <c r="AE57" s="24" t="n"/>
+      <c r="AF57" s="24" t="n"/>
+      <c r="AG57" s="24" t="n"/>
+      <c r="AH57" s="24" t="n"/>
+      <c r="AI57" s="24" t="n"/>
+      <c r="AJ57" s="24" t="n"/>
+      <c r="AK57" s="24" t="n"/>
+      <c r="AL57" s="24" t="n"/>
+      <c r="AM57" s="24" t="n"/>
+      <c r="AN57" s="24" t="n"/>
+      <c r="AO57" s="24" t="n"/>
+      <c r="AP57" s="24" t="n"/>
+      <c r="AQ57" s="24" t="n"/>
+      <c r="AR57" s="24" t="n"/>
+      <c r="AS57" s="24" t="n"/>
+      <c r="AT57" s="24" t="n"/>
+      <c r="AU57" s="24" t="n"/>
+      <c r="AV57" s="24" t="n"/>
+      <c r="AW57" s="24" t="n"/>
+      <c r="AX57" s="24" t="n"/>
+      <c r="AY57" s="24" t="n"/>
+      <c r="AZ57" s="24" t="n"/>
+      <c r="BA57" s="24" t="n"/>
+      <c r="BB57" s="24" t="n"/>
+      <c r="BC57" s="24" t="n"/>
+      <c r="BD57" s="24" t="n"/>
+      <c r="BE57" s="24" t="n"/>
       <c r="BF57" s="24" t="n"/>
       <c r="BG57" s="24" t="n"/>
       <c r="BH57" s="24" t="n"/>
@@ -7577,7 +7446,7 @@
       <c r="BN57" s="24" t="n"/>
       <c r="BO57" s="24" t="n"/>
     </row>
-    <row r="58" ht="16" customHeight="1">
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -7593,38 +7462,33 @@
           <t>PAB142·单级样机</t>
         </is>
       </c>
-      <c r="D58" s="27" t="n">
-        <v>46308</v>
-      </c>
-      <c r="E58" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F58" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G58" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H58" s="29" t="n"/>
-      <c r="I58" s="29" t="n"/>
-      <c r="J58" s="29" t="n"/>
-      <c r="K58" s="29" t="n"/>
-      <c r="L58" s="29" t="n"/>
-      <c r="M58" s="29" t="n"/>
-      <c r="N58" s="29" t="n"/>
-      <c r="O58" s="29" t="n"/>
-      <c r="P58" s="29" t="n"/>
-      <c r="Q58" s="29" t="n"/>
-      <c r="R58" s="29" t="n"/>
-      <c r="S58" s="29" t="n"/>
-      <c r="T58" s="29" t="n"/>
-      <c r="U58" s="30" t="n"/>
+      <c r="D58" s="27">
+        <f>IF('时间节点计划表'!E29="","",'时间节点计划表'!E29)</f>
+        <v/>
+      </c>
+      <c r="E58" s="27">
+        <f>IF('时间节点计划表'!F29="","",'时间节点计划表'!F29)</f>
+        <v/>
+      </c>
+      <c r="F58" s="28">
+        <f>IF(OR(D58="",E58=""),"待填",E58-D58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="24" t="n"/>
+      <c r="H58" s="24" t="n"/>
+      <c r="I58" s="24" t="n"/>
+      <c r="J58" s="24" t="n"/>
+      <c r="K58" s="24" t="n"/>
+      <c r="L58" s="24" t="n"/>
+      <c r="M58" s="24" t="n"/>
+      <c r="N58" s="24" t="n"/>
+      <c r="O58" s="24" t="n"/>
+      <c r="P58" s="24" t="n"/>
+      <c r="Q58" s="24" t="n"/>
+      <c r="R58" s="24" t="n"/>
+      <c r="S58" s="24" t="n"/>
+      <c r="T58" s="24" t="n"/>
+      <c r="U58" s="24" t="n"/>
       <c r="V58" s="24" t="n"/>
       <c r="W58" s="24" t="n"/>
       <c r="X58" s="24" t="n"/>
@@ -7672,7 +7536,7 @@
       <c r="BN58" s="24" t="n"/>
       <c r="BO58" s="24" t="n"/>
     </row>
-    <row r="59" ht="16" customHeight="1">
+    <row r="59" ht="18" customHeight="1">
       <c r="A59" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -7688,70 +7552,68 @@
           <t>PAB142·双级样机</t>
         </is>
       </c>
-      <c r="D59" s="22" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E59" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="inlineStr"/>
-      <c r="G59" s="31" t="n"/>
-      <c r="H59" s="31" t="n"/>
-      <c r="I59" s="31" t="n"/>
-      <c r="J59" s="31" t="n"/>
-      <c r="K59" s="31" t="n"/>
-      <c r="L59" s="31" t="n"/>
-      <c r="M59" s="31" t="n"/>
-      <c r="N59" s="31" t="n"/>
-      <c r="O59" s="31" t="n"/>
-      <c r="P59" s="31" t="n"/>
-      <c r="Q59" s="31" t="n"/>
-      <c r="R59" s="31" t="n"/>
-      <c r="S59" s="31" t="n"/>
-      <c r="T59" s="31" t="n"/>
-      <c r="U59" s="31" t="n"/>
-      <c r="V59" s="31" t="n"/>
-      <c r="W59" s="31" t="n"/>
-      <c r="X59" s="31" t="n"/>
-      <c r="Y59" s="31" t="n"/>
-      <c r="Z59" s="31" t="n"/>
-      <c r="AA59" s="31" t="n"/>
-      <c r="AB59" s="31" t="n"/>
-      <c r="AC59" s="31" t="n"/>
-      <c r="AD59" s="31" t="n"/>
-      <c r="AE59" s="31" t="n"/>
-      <c r="AF59" s="31" t="n"/>
-      <c r="AG59" s="31" t="n"/>
-      <c r="AH59" s="31" t="n"/>
-      <c r="AI59" s="31" t="n"/>
-      <c r="AJ59" s="31" t="n"/>
-      <c r="AK59" s="31" t="n"/>
-      <c r="AL59" s="31" t="n"/>
-      <c r="AM59" s="31" t="n"/>
-      <c r="AN59" s="31" t="n"/>
-      <c r="AO59" s="31" t="n"/>
-      <c r="AP59" s="31" t="n"/>
-      <c r="AQ59" s="31" t="n"/>
-      <c r="AR59" s="31" t="n"/>
-      <c r="AS59" s="31" t="n"/>
-      <c r="AT59" s="31" t="n"/>
-      <c r="AU59" s="31" t="n"/>
-      <c r="AV59" s="31" t="n"/>
-      <c r="AW59" s="31" t="n"/>
-      <c r="AX59" s="31" t="n"/>
-      <c r="AY59" s="31" t="n"/>
-      <c r="AZ59" s="31" t="n"/>
-      <c r="BA59" s="31" t="n"/>
-      <c r="BB59" s="31" t="n"/>
-      <c r="BC59" s="31" t="n"/>
-      <c r="BD59" s="31" t="n"/>
-      <c r="BE59" s="31" t="n"/>
-      <c r="BF59" s="31" t="n"/>
-      <c r="BG59" s="23" t="n">
-        <v>15</v>
-      </c>
+      <c r="D59" s="22">
+        <f>IF('时间节点计划表'!E30="","",'时间节点计划表'!E30)</f>
+        <v/>
+      </c>
+      <c r="E59" s="22">
+        <f>IF('时间节点计划表'!F30="","",'时间节点计划表'!F30)</f>
+        <v/>
+      </c>
+      <c r="F59" s="23" t="inlineStr"/>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="24" t="n"/>
+      <c r="I59" s="24" t="n"/>
+      <c r="J59" s="24" t="n"/>
+      <c r="K59" s="24" t="n"/>
+      <c r="L59" s="24" t="n"/>
+      <c r="M59" s="24" t="n"/>
+      <c r="N59" s="24" t="n"/>
+      <c r="O59" s="24" t="n"/>
+      <c r="P59" s="24" t="n"/>
+      <c r="Q59" s="24" t="n"/>
+      <c r="R59" s="24" t="n"/>
+      <c r="S59" s="24" t="n"/>
+      <c r="T59" s="24" t="n"/>
+      <c r="U59" s="24" t="n"/>
+      <c r="V59" s="24" t="n"/>
+      <c r="W59" s="24" t="n"/>
+      <c r="X59" s="24" t="n"/>
+      <c r="Y59" s="24" t="n"/>
+      <c r="Z59" s="24" t="n"/>
+      <c r="AA59" s="24" t="n"/>
+      <c r="AB59" s="24" t="n"/>
+      <c r="AC59" s="24" t="n"/>
+      <c r="AD59" s="24" t="n"/>
+      <c r="AE59" s="24" t="n"/>
+      <c r="AF59" s="24" t="n"/>
+      <c r="AG59" s="24" t="n"/>
+      <c r="AH59" s="24" t="n"/>
+      <c r="AI59" s="24" t="n"/>
+      <c r="AJ59" s="24" t="n"/>
+      <c r="AK59" s="24" t="n"/>
+      <c r="AL59" s="24" t="n"/>
+      <c r="AM59" s="24" t="n"/>
+      <c r="AN59" s="24" t="n"/>
+      <c r="AO59" s="24" t="n"/>
+      <c r="AP59" s="24" t="n"/>
+      <c r="AQ59" s="24" t="n"/>
+      <c r="AR59" s="24" t="n"/>
+      <c r="AS59" s="24" t="n"/>
+      <c r="AT59" s="24" t="n"/>
+      <c r="AU59" s="24" t="n"/>
+      <c r="AV59" s="24" t="n"/>
+      <c r="AW59" s="24" t="n"/>
+      <c r="AX59" s="24" t="n"/>
+      <c r="AY59" s="24" t="n"/>
+      <c r="AZ59" s="24" t="n"/>
+      <c r="BA59" s="24" t="n"/>
+      <c r="BB59" s="24" t="n"/>
+      <c r="BC59" s="24" t="n"/>
+      <c r="BD59" s="24" t="n"/>
+      <c r="BE59" s="24" t="n"/>
+      <c r="BF59" s="24" t="n"/>
+      <c r="BG59" s="24" t="n"/>
       <c r="BH59" s="24" t="n"/>
       <c r="BI59" s="24" t="n"/>
       <c r="BJ59" s="24" t="n"/>
@@ -7761,7 +7623,7 @@
       <c r="BN59" s="24" t="n"/>
       <c r="BO59" s="24" t="n"/>
     </row>
-    <row r="60" ht="16" customHeight="1">
+    <row r="60" ht="18" customHeight="1">
       <c r="A60" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -7777,38 +7639,33 @@
           <t>PAB142·双级样机</t>
         </is>
       </c>
-      <c r="D60" s="27" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E60" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F60" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G60" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H60" s="29" t="n"/>
-      <c r="I60" s="29" t="n"/>
-      <c r="J60" s="29" t="n"/>
-      <c r="K60" s="29" t="n"/>
-      <c r="L60" s="29" t="n"/>
-      <c r="M60" s="29" t="n"/>
-      <c r="N60" s="29" t="n"/>
-      <c r="O60" s="29" t="n"/>
-      <c r="P60" s="29" t="n"/>
-      <c r="Q60" s="29" t="n"/>
-      <c r="R60" s="29" t="n"/>
-      <c r="S60" s="29" t="n"/>
-      <c r="T60" s="29" t="n"/>
-      <c r="U60" s="30" t="n"/>
+      <c r="D60" s="27">
+        <f>IF('时间节点计划表'!E30="","",'时间节点计划表'!E30)</f>
+        <v/>
+      </c>
+      <c r="E60" s="27">
+        <f>IF('时间节点计划表'!F30="","",'时间节点计划表'!F30)</f>
+        <v/>
+      </c>
+      <c r="F60" s="28">
+        <f>IF(OR(D60="",E60=""),"待填",E60-D60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="24" t="n"/>
+      <c r="H60" s="24" t="n"/>
+      <c r="I60" s="24" t="n"/>
+      <c r="J60" s="24" t="n"/>
+      <c r="K60" s="24" t="n"/>
+      <c r="L60" s="24" t="n"/>
+      <c r="M60" s="24" t="n"/>
+      <c r="N60" s="24" t="n"/>
+      <c r="O60" s="24" t="n"/>
+      <c r="P60" s="24" t="n"/>
+      <c r="Q60" s="24" t="n"/>
+      <c r="R60" s="24" t="n"/>
+      <c r="S60" s="24" t="n"/>
+      <c r="T60" s="24" t="n"/>
+      <c r="U60" s="24" t="n"/>
       <c r="V60" s="24" t="n"/>
       <c r="W60" s="24" t="n"/>
       <c r="X60" s="24" t="n"/>
@@ -7856,7 +7713,7 @@
       <c r="BN60" s="24" t="n"/>
       <c r="BO60" s="24" t="n"/>
     </row>
-    <row r="61" ht="16" customHeight="1">
+    <row r="61" ht="18" customHeight="1">
       <c r="A61" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -7872,32 +7729,30 @@
           <t>二期零件图纸整理归档</t>
         </is>
       </c>
-      <c r="D61" s="22" t="n">
-        <v>46272</v>
-      </c>
-      <c r="E61" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F61" s="20" t="inlineStr"/>
-      <c r="G61" s="31" t="n"/>
-      <c r="H61" s="31" t="n"/>
-      <c r="I61" s="31" t="n"/>
-      <c r="J61" s="31" t="n"/>
-      <c r="K61" s="31" t="n"/>
-      <c r="L61" s="31" t="n"/>
-      <c r="M61" s="31" t="n"/>
-      <c r="N61" s="31" t="n"/>
-      <c r="O61" s="31" t="n"/>
-      <c r="P61" s="31" t="n"/>
-      <c r="Q61" s="31" t="n"/>
-      <c r="R61" s="31" t="n"/>
-      <c r="S61" s="31" t="n"/>
-      <c r="T61" s="31" t="n"/>
-      <c r="U61" s="23" t="n">
-        <v>7</v>
-      </c>
+      <c r="D61" s="22">
+        <f>IF('时间节点计划表'!E31="","",'时间节点计划表'!E31)</f>
+        <v/>
+      </c>
+      <c r="E61" s="22">
+        <f>IF('时间节点计划表'!F31="","",'时间节点计划表'!F31)</f>
+        <v/>
+      </c>
+      <c r="F61" s="23" t="inlineStr"/>
+      <c r="G61" s="24" t="n"/>
+      <c r="H61" s="24" t="n"/>
+      <c r="I61" s="24" t="n"/>
+      <c r="J61" s="24" t="n"/>
+      <c r="K61" s="24" t="n"/>
+      <c r="L61" s="24" t="n"/>
+      <c r="M61" s="24" t="n"/>
+      <c r="N61" s="24" t="n"/>
+      <c r="O61" s="24" t="n"/>
+      <c r="P61" s="24" t="n"/>
+      <c r="Q61" s="24" t="n"/>
+      <c r="R61" s="24" t="n"/>
+      <c r="S61" s="24" t="n"/>
+      <c r="T61" s="24" t="n"/>
+      <c r="U61" s="24" t="n"/>
       <c r="V61" s="24" t="n"/>
       <c r="W61" s="24" t="n"/>
       <c r="X61" s="24" t="n"/>
@@ -7945,7 +7800,7 @@
       <c r="BN61" s="24" t="n"/>
       <c r="BO61" s="24" t="n"/>
     </row>
-    <row r="62" ht="16" customHeight="1">
+    <row r="62" ht="18" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -7961,38 +7816,33 @@
           <t>二期零件图纸整理归档</t>
         </is>
       </c>
-      <c r="D62" s="27" t="n">
-        <v>46272</v>
-      </c>
-      <c r="E62" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F62" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G62" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H62" s="29" t="n"/>
-      <c r="I62" s="29" t="n"/>
-      <c r="J62" s="29" t="n"/>
-      <c r="K62" s="29" t="n"/>
-      <c r="L62" s="29" t="n"/>
-      <c r="M62" s="29" t="n"/>
-      <c r="N62" s="29" t="n"/>
-      <c r="O62" s="29" t="n"/>
-      <c r="P62" s="29" t="n"/>
-      <c r="Q62" s="29" t="n"/>
-      <c r="R62" s="29" t="n"/>
-      <c r="S62" s="29" t="n"/>
-      <c r="T62" s="29" t="n"/>
-      <c r="U62" s="30" t="n"/>
+      <c r="D62" s="27">
+        <f>IF('时间节点计划表'!E31="","",'时间节点计划表'!E31)</f>
+        <v/>
+      </c>
+      <c r="E62" s="27">
+        <f>IF('时间节点计划表'!F31="","",'时间节点计划表'!F31)</f>
+        <v/>
+      </c>
+      <c r="F62" s="28">
+        <f>IF(OR(D62="",E62=""),"待填",E62-D62)</f>
+        <v/>
+      </c>
+      <c r="G62" s="24" t="n"/>
+      <c r="H62" s="24" t="n"/>
+      <c r="I62" s="24" t="n"/>
+      <c r="J62" s="24" t="n"/>
+      <c r="K62" s="24" t="n"/>
+      <c r="L62" s="24" t="n"/>
+      <c r="M62" s="24" t="n"/>
+      <c r="N62" s="24" t="n"/>
+      <c r="O62" s="24" t="n"/>
+      <c r="P62" s="24" t="n"/>
+      <c r="Q62" s="24" t="n"/>
+      <c r="R62" s="24" t="n"/>
+      <c r="S62" s="24" t="n"/>
+      <c r="T62" s="24" t="n"/>
+      <c r="U62" s="24" t="n"/>
       <c r="V62" s="24" t="n"/>
       <c r="W62" s="24" t="n"/>
       <c r="X62" s="24" t="n"/>
@@ -8040,7 +7890,7 @@
       <c r="BN62" s="24" t="n"/>
       <c r="BO62" s="24" t="n"/>
     </row>
-    <row r="63" ht="16" customHeight="1">
+    <row r="63" ht="18" customHeight="1">
       <c r="A63" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -8056,35 +7906,33 @@
           <t>二期零件下单采购</t>
         </is>
       </c>
-      <c r="D63" s="22" t="n">
-        <v>46275</v>
-      </c>
-      <c r="E63" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="inlineStr"/>
-      <c r="G63" s="31" t="n"/>
-      <c r="H63" s="31" t="n"/>
-      <c r="I63" s="31" t="n"/>
-      <c r="J63" s="31" t="n"/>
-      <c r="K63" s="31" t="n"/>
-      <c r="L63" s="31" t="n"/>
-      <c r="M63" s="31" t="n"/>
-      <c r="N63" s="31" t="n"/>
-      <c r="O63" s="31" t="n"/>
-      <c r="P63" s="31" t="n"/>
-      <c r="Q63" s="31" t="n"/>
-      <c r="R63" s="31" t="n"/>
-      <c r="S63" s="31" t="n"/>
-      <c r="T63" s="31" t="n"/>
-      <c r="U63" s="31" t="n"/>
-      <c r="V63" s="31" t="n"/>
-      <c r="W63" s="31" t="n"/>
-      <c r="X63" s="23" t="n">
-        <v>10</v>
-      </c>
+      <c r="D63" s="22">
+        <f>IF('时间节点计划表'!E32="","",'时间节点计划表'!E32)</f>
+        <v/>
+      </c>
+      <c r="E63" s="22">
+        <f>IF('时间节点计划表'!F32="","",'时间节点计划表'!F32)</f>
+        <v/>
+      </c>
+      <c r="F63" s="23" t="inlineStr"/>
+      <c r="G63" s="24" t="n"/>
+      <c r="H63" s="24" t="n"/>
+      <c r="I63" s="24" t="n"/>
+      <c r="J63" s="24" t="n"/>
+      <c r="K63" s="24" t="n"/>
+      <c r="L63" s="24" t="n"/>
+      <c r="M63" s="24" t="n"/>
+      <c r="N63" s="24" t="n"/>
+      <c r="O63" s="24" t="n"/>
+      <c r="P63" s="24" t="n"/>
+      <c r="Q63" s="24" t="n"/>
+      <c r="R63" s="24" t="n"/>
+      <c r="S63" s="24" t="n"/>
+      <c r="T63" s="24" t="n"/>
+      <c r="U63" s="24" t="n"/>
+      <c r="V63" s="24" t="n"/>
+      <c r="W63" s="24" t="n"/>
+      <c r="X63" s="24" t="n"/>
       <c r="Y63" s="24" t="n"/>
       <c r="Z63" s="24" t="n"/>
       <c r="AA63" s="24" t="n"/>
@@ -8129,7 +7977,7 @@
       <c r="BN63" s="24" t="n"/>
       <c r="BO63" s="24" t="n"/>
     </row>
-    <row r="64" ht="16" customHeight="1">
+    <row r="64" ht="18" customHeight="1">
       <c r="A64" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -8145,38 +7993,33 @@
           <t>二期零件下单采购</t>
         </is>
       </c>
-      <c r="D64" s="27" t="n">
-        <v>46275</v>
-      </c>
-      <c r="E64" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F64" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G64" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H64" s="29" t="n"/>
-      <c r="I64" s="29" t="n"/>
-      <c r="J64" s="29" t="n"/>
-      <c r="K64" s="29" t="n"/>
-      <c r="L64" s="29" t="n"/>
-      <c r="M64" s="29" t="n"/>
-      <c r="N64" s="29" t="n"/>
-      <c r="O64" s="29" t="n"/>
-      <c r="P64" s="29" t="n"/>
-      <c r="Q64" s="29" t="n"/>
-      <c r="R64" s="29" t="n"/>
-      <c r="S64" s="29" t="n"/>
-      <c r="T64" s="29" t="n"/>
-      <c r="U64" s="30" t="n"/>
+      <c r="D64" s="27">
+        <f>IF('时间节点计划表'!E32="","",'时间节点计划表'!E32)</f>
+        <v/>
+      </c>
+      <c r="E64" s="27">
+        <f>IF('时间节点计划表'!F32="","",'时间节点计划表'!F32)</f>
+        <v/>
+      </c>
+      <c r="F64" s="28">
+        <f>IF(OR(D64="",E64=""),"待填",E64-D64)</f>
+        <v/>
+      </c>
+      <c r="G64" s="24" t="n"/>
+      <c r="H64" s="24" t="n"/>
+      <c r="I64" s="24" t="n"/>
+      <c r="J64" s="24" t="n"/>
+      <c r="K64" s="24" t="n"/>
+      <c r="L64" s="24" t="n"/>
+      <c r="M64" s="24" t="n"/>
+      <c r="N64" s="24" t="n"/>
+      <c r="O64" s="24" t="n"/>
+      <c r="P64" s="24" t="n"/>
+      <c r="Q64" s="24" t="n"/>
+      <c r="R64" s="24" t="n"/>
+      <c r="S64" s="24" t="n"/>
+      <c r="T64" s="24" t="n"/>
+      <c r="U64" s="24" t="n"/>
       <c r="V64" s="24" t="n"/>
       <c r="W64" s="24" t="n"/>
       <c r="X64" s="24" t="n"/>
@@ -8224,7 +8067,7 @@
       <c r="BN64" s="24" t="n"/>
       <c r="BO64" s="24" t="n"/>
     </row>
-    <row r="65" ht="16" customHeight="1">
+    <row r="65" ht="18" customHeight="1">
       <c r="A65" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -8240,35 +8083,33 @@
           <t>二期标准件下单采购</t>
         </is>
       </c>
-      <c r="D65" s="22" t="n">
-        <v>46275</v>
-      </c>
-      <c r="E65" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F65" s="20" t="inlineStr"/>
-      <c r="G65" s="31" t="n"/>
-      <c r="H65" s="31" t="n"/>
-      <c r="I65" s="31" t="n"/>
-      <c r="J65" s="31" t="n"/>
-      <c r="K65" s="31" t="n"/>
-      <c r="L65" s="31" t="n"/>
-      <c r="M65" s="31" t="n"/>
-      <c r="N65" s="31" t="n"/>
-      <c r="O65" s="31" t="n"/>
-      <c r="P65" s="31" t="n"/>
-      <c r="Q65" s="31" t="n"/>
-      <c r="R65" s="31" t="n"/>
-      <c r="S65" s="31" t="n"/>
-      <c r="T65" s="31" t="n"/>
-      <c r="U65" s="31" t="n"/>
-      <c r="V65" s="31" t="n"/>
-      <c r="W65" s="31" t="n"/>
-      <c r="X65" s="23" t="n">
-        <v>10</v>
-      </c>
+      <c r="D65" s="22">
+        <f>IF('时间节点计划表'!E33="","",'时间节点计划表'!E33)</f>
+        <v/>
+      </c>
+      <c r="E65" s="22">
+        <f>IF('时间节点计划表'!F33="","",'时间节点计划表'!F33)</f>
+        <v/>
+      </c>
+      <c r="F65" s="23" t="inlineStr"/>
+      <c r="G65" s="24" t="n"/>
+      <c r="H65" s="24" t="n"/>
+      <c r="I65" s="24" t="n"/>
+      <c r="J65" s="24" t="n"/>
+      <c r="K65" s="24" t="n"/>
+      <c r="L65" s="24" t="n"/>
+      <c r="M65" s="24" t="n"/>
+      <c r="N65" s="24" t="n"/>
+      <c r="O65" s="24" t="n"/>
+      <c r="P65" s="24" t="n"/>
+      <c r="Q65" s="24" t="n"/>
+      <c r="R65" s="24" t="n"/>
+      <c r="S65" s="24" t="n"/>
+      <c r="T65" s="24" t="n"/>
+      <c r="U65" s="24" t="n"/>
+      <c r="V65" s="24" t="n"/>
+      <c r="W65" s="24" t="n"/>
+      <c r="X65" s="24" t="n"/>
       <c r="Y65" s="24" t="n"/>
       <c r="Z65" s="24" t="n"/>
       <c r="AA65" s="24" t="n"/>
@@ -8313,7 +8154,7 @@
       <c r="BN65" s="24" t="n"/>
       <c r="BO65" s="24" t="n"/>
     </row>
-    <row r="66" ht="16" customHeight="1">
+    <row r="66" ht="18" customHeight="1">
       <c r="A66" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -8329,38 +8170,33 @@
           <t>二期标准件下单采购</t>
         </is>
       </c>
-      <c r="D66" s="27" t="n">
-        <v>46275</v>
-      </c>
-      <c r="E66" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F66" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G66" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H66" s="29" t="n"/>
-      <c r="I66" s="29" t="n"/>
-      <c r="J66" s="29" t="n"/>
-      <c r="K66" s="29" t="n"/>
-      <c r="L66" s="29" t="n"/>
-      <c r="M66" s="29" t="n"/>
-      <c r="N66" s="29" t="n"/>
-      <c r="O66" s="29" t="n"/>
-      <c r="P66" s="29" t="n"/>
-      <c r="Q66" s="29" t="n"/>
-      <c r="R66" s="29" t="n"/>
-      <c r="S66" s="29" t="n"/>
-      <c r="T66" s="29" t="n"/>
-      <c r="U66" s="30" t="n"/>
+      <c r="D66" s="27">
+        <f>IF('时间节点计划表'!E33="","",'时间节点计划表'!E33)</f>
+        <v/>
+      </c>
+      <c r="E66" s="27">
+        <f>IF('时间节点计划表'!F33="","",'时间节点计划表'!F33)</f>
+        <v/>
+      </c>
+      <c r="F66" s="28">
+        <f>IF(OR(D66="",E66=""),"待填",E66-D66)</f>
+        <v/>
+      </c>
+      <c r="G66" s="24" t="n"/>
+      <c r="H66" s="24" t="n"/>
+      <c r="I66" s="24" t="n"/>
+      <c r="J66" s="24" t="n"/>
+      <c r="K66" s="24" t="n"/>
+      <c r="L66" s="24" t="n"/>
+      <c r="M66" s="24" t="n"/>
+      <c r="N66" s="24" t="n"/>
+      <c r="O66" s="24" t="n"/>
+      <c r="P66" s="24" t="n"/>
+      <c r="Q66" s="24" t="n"/>
+      <c r="R66" s="24" t="n"/>
+      <c r="S66" s="24" t="n"/>
+      <c r="T66" s="24" t="n"/>
+      <c r="U66" s="24" t="n"/>
       <c r="V66" s="24" t="n"/>
       <c r="W66" s="24" t="n"/>
       <c r="X66" s="24" t="n"/>
@@ -8408,7 +8244,7 @@
       <c r="BN66" s="24" t="n"/>
       <c r="BO66" s="24" t="n"/>
     </row>
-    <row r="67" ht="16" customHeight="1">
+    <row r="67" ht="18" customHeight="1">
       <c r="A67" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -8424,70 +8260,68 @@
           <t>PAB180·零件到位</t>
         </is>
       </c>
-      <c r="D67" s="22" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E67" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F67" s="20" t="inlineStr"/>
-      <c r="G67" s="31" t="n"/>
-      <c r="H67" s="31" t="n"/>
-      <c r="I67" s="31" t="n"/>
-      <c r="J67" s="31" t="n"/>
-      <c r="K67" s="31" t="n"/>
-      <c r="L67" s="31" t="n"/>
-      <c r="M67" s="31" t="n"/>
-      <c r="N67" s="31" t="n"/>
-      <c r="O67" s="31" t="n"/>
-      <c r="P67" s="31" t="n"/>
-      <c r="Q67" s="31" t="n"/>
-      <c r="R67" s="31" t="n"/>
-      <c r="S67" s="31" t="n"/>
-      <c r="T67" s="31" t="n"/>
-      <c r="U67" s="31" t="n"/>
-      <c r="V67" s="31" t="n"/>
-      <c r="W67" s="31" t="n"/>
-      <c r="X67" s="31" t="n"/>
-      <c r="Y67" s="31" t="n"/>
-      <c r="Z67" s="31" t="n"/>
-      <c r="AA67" s="31" t="n"/>
-      <c r="AB67" s="31" t="n"/>
-      <c r="AC67" s="31" t="n"/>
-      <c r="AD67" s="31" t="n"/>
-      <c r="AE67" s="31" t="n"/>
-      <c r="AF67" s="31" t="n"/>
-      <c r="AG67" s="31" t="n"/>
-      <c r="AH67" s="31" t="n"/>
-      <c r="AI67" s="31" t="n"/>
-      <c r="AJ67" s="31" t="n"/>
-      <c r="AK67" s="31" t="n"/>
-      <c r="AL67" s="31" t="n"/>
-      <c r="AM67" s="31" t="n"/>
-      <c r="AN67" s="31" t="n"/>
-      <c r="AO67" s="31" t="n"/>
-      <c r="AP67" s="31" t="n"/>
-      <c r="AQ67" s="31" t="n"/>
-      <c r="AR67" s="31" t="n"/>
-      <c r="AS67" s="31" t="n"/>
-      <c r="AT67" s="31" t="n"/>
-      <c r="AU67" s="31" t="n"/>
-      <c r="AV67" s="31" t="n"/>
-      <c r="AW67" s="31" t="n"/>
-      <c r="AX67" s="31" t="n"/>
-      <c r="AY67" s="31" t="n"/>
-      <c r="AZ67" s="31" t="n"/>
-      <c r="BA67" s="31" t="n"/>
-      <c r="BB67" s="31" t="n"/>
-      <c r="BC67" s="31" t="n"/>
-      <c r="BD67" s="31" t="n"/>
-      <c r="BE67" s="31" t="n"/>
-      <c r="BF67" s="31" t="n"/>
-      <c r="BG67" s="23" t="n">
-        <v>15</v>
-      </c>
+      <c r="D67" s="22">
+        <f>IF('时间节点计划表'!E34="","",'时间节点计划表'!E34)</f>
+        <v/>
+      </c>
+      <c r="E67" s="22">
+        <f>IF('时间节点计划表'!F34="","",'时间节点计划表'!F34)</f>
+        <v/>
+      </c>
+      <c r="F67" s="23" t="inlineStr"/>
+      <c r="G67" s="24" t="n"/>
+      <c r="H67" s="24" t="n"/>
+      <c r="I67" s="24" t="n"/>
+      <c r="J67" s="24" t="n"/>
+      <c r="K67" s="24" t="n"/>
+      <c r="L67" s="24" t="n"/>
+      <c r="M67" s="24" t="n"/>
+      <c r="N67" s="24" t="n"/>
+      <c r="O67" s="24" t="n"/>
+      <c r="P67" s="24" t="n"/>
+      <c r="Q67" s="24" t="n"/>
+      <c r="R67" s="24" t="n"/>
+      <c r="S67" s="24" t="n"/>
+      <c r="T67" s="24" t="n"/>
+      <c r="U67" s="24" t="n"/>
+      <c r="V67" s="24" t="n"/>
+      <c r="W67" s="24" t="n"/>
+      <c r="X67" s="24" t="n"/>
+      <c r="Y67" s="24" t="n"/>
+      <c r="Z67" s="24" t="n"/>
+      <c r="AA67" s="24" t="n"/>
+      <c r="AB67" s="24" t="n"/>
+      <c r="AC67" s="24" t="n"/>
+      <c r="AD67" s="24" t="n"/>
+      <c r="AE67" s="24" t="n"/>
+      <c r="AF67" s="24" t="n"/>
+      <c r="AG67" s="24" t="n"/>
+      <c r="AH67" s="24" t="n"/>
+      <c r="AI67" s="24" t="n"/>
+      <c r="AJ67" s="24" t="n"/>
+      <c r="AK67" s="24" t="n"/>
+      <c r="AL67" s="24" t="n"/>
+      <c r="AM67" s="24" t="n"/>
+      <c r="AN67" s="24" t="n"/>
+      <c r="AO67" s="24" t="n"/>
+      <c r="AP67" s="24" t="n"/>
+      <c r="AQ67" s="24" t="n"/>
+      <c r="AR67" s="24" t="n"/>
+      <c r="AS67" s="24" t="n"/>
+      <c r="AT67" s="24" t="n"/>
+      <c r="AU67" s="24" t="n"/>
+      <c r="AV67" s="24" t="n"/>
+      <c r="AW67" s="24" t="n"/>
+      <c r="AX67" s="24" t="n"/>
+      <c r="AY67" s="24" t="n"/>
+      <c r="AZ67" s="24" t="n"/>
+      <c r="BA67" s="24" t="n"/>
+      <c r="BB67" s="24" t="n"/>
+      <c r="BC67" s="24" t="n"/>
+      <c r="BD67" s="24" t="n"/>
+      <c r="BE67" s="24" t="n"/>
+      <c r="BF67" s="24" t="n"/>
+      <c r="BG67" s="24" t="n"/>
       <c r="BH67" s="24" t="n"/>
       <c r="BI67" s="24" t="n"/>
       <c r="BJ67" s="24" t="n"/>
@@ -8497,7 +8331,7 @@
       <c r="BN67" s="24" t="n"/>
       <c r="BO67" s="24" t="n"/>
     </row>
-    <row r="68" ht="16" customHeight="1">
+    <row r="68" ht="18" customHeight="1">
       <c r="A68" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -8513,38 +8347,33 @@
           <t>PAB180·零件到位</t>
         </is>
       </c>
-      <c r="D68" s="27" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E68" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F68" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G68" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H68" s="29" t="n"/>
-      <c r="I68" s="29" t="n"/>
-      <c r="J68" s="29" t="n"/>
-      <c r="K68" s="29" t="n"/>
-      <c r="L68" s="29" t="n"/>
-      <c r="M68" s="29" t="n"/>
-      <c r="N68" s="29" t="n"/>
-      <c r="O68" s="29" t="n"/>
-      <c r="P68" s="29" t="n"/>
-      <c r="Q68" s="29" t="n"/>
-      <c r="R68" s="29" t="n"/>
-      <c r="S68" s="29" t="n"/>
-      <c r="T68" s="29" t="n"/>
-      <c r="U68" s="30" t="n"/>
+      <c r="D68" s="27">
+        <f>IF('时间节点计划表'!E34="","",'时间节点计划表'!E34)</f>
+        <v/>
+      </c>
+      <c r="E68" s="27">
+        <f>IF('时间节点计划表'!F34="","",'时间节点计划表'!F34)</f>
+        <v/>
+      </c>
+      <c r="F68" s="28">
+        <f>IF(OR(D68="",E68=""),"待填",E68-D68)</f>
+        <v/>
+      </c>
+      <c r="G68" s="24" t="n"/>
+      <c r="H68" s="24" t="n"/>
+      <c r="I68" s="24" t="n"/>
+      <c r="J68" s="24" t="n"/>
+      <c r="K68" s="24" t="n"/>
+      <c r="L68" s="24" t="n"/>
+      <c r="M68" s="24" t="n"/>
+      <c r="N68" s="24" t="n"/>
+      <c r="O68" s="24" t="n"/>
+      <c r="P68" s="24" t="n"/>
+      <c r="Q68" s="24" t="n"/>
+      <c r="R68" s="24" t="n"/>
+      <c r="S68" s="24" t="n"/>
+      <c r="T68" s="24" t="n"/>
+      <c r="U68" s="24" t="n"/>
       <c r="V68" s="24" t="n"/>
       <c r="W68" s="24" t="n"/>
       <c r="X68" s="24" t="n"/>
@@ -8592,7 +8421,7 @@
       <c r="BN68" s="24" t="n"/>
       <c r="BO68" s="24" t="n"/>
     </row>
-    <row r="69" ht="16" customHeight="1">
+    <row r="69" ht="18" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -8608,36 +8437,34 @@
           <t>PAB180·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D69" s="22" t="n">
-        <v>46276</v>
-      </c>
-      <c r="E69" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F69" s="20" t="inlineStr"/>
-      <c r="G69" s="31" t="n"/>
-      <c r="H69" s="31" t="n"/>
-      <c r="I69" s="31" t="n"/>
-      <c r="J69" s="31" t="n"/>
-      <c r="K69" s="31" t="n"/>
-      <c r="L69" s="31" t="n"/>
-      <c r="M69" s="31" t="n"/>
-      <c r="N69" s="31" t="n"/>
-      <c r="O69" s="31" t="n"/>
-      <c r="P69" s="31" t="n"/>
-      <c r="Q69" s="31" t="n"/>
-      <c r="R69" s="31" t="n"/>
-      <c r="S69" s="31" t="n"/>
-      <c r="T69" s="31" t="n"/>
-      <c r="U69" s="31" t="n"/>
-      <c r="V69" s="31" t="n"/>
-      <c r="W69" s="31" t="n"/>
-      <c r="X69" s="31" t="n"/>
-      <c r="Y69" s="23" t="n">
-        <v>11</v>
-      </c>
+      <c r="D69" s="22">
+        <f>IF('时间节点计划表'!E35="","",'时间节点计划表'!E35)</f>
+        <v/>
+      </c>
+      <c r="E69" s="22">
+        <f>IF('时间节点计划表'!F35="","",'时间节点计划表'!F35)</f>
+        <v/>
+      </c>
+      <c r="F69" s="23" t="inlineStr"/>
+      <c r="G69" s="24" t="n"/>
+      <c r="H69" s="24" t="n"/>
+      <c r="I69" s="24" t="n"/>
+      <c r="J69" s="24" t="n"/>
+      <c r="K69" s="24" t="n"/>
+      <c r="L69" s="24" t="n"/>
+      <c r="M69" s="24" t="n"/>
+      <c r="N69" s="24" t="n"/>
+      <c r="O69" s="24" t="n"/>
+      <c r="P69" s="24" t="n"/>
+      <c r="Q69" s="24" t="n"/>
+      <c r="R69" s="24" t="n"/>
+      <c r="S69" s="24" t="n"/>
+      <c r="T69" s="24" t="n"/>
+      <c r="U69" s="24" t="n"/>
+      <c r="V69" s="24" t="n"/>
+      <c r="W69" s="24" t="n"/>
+      <c r="X69" s="24" t="n"/>
+      <c r="Y69" s="24" t="n"/>
       <c r="Z69" s="24" t="n"/>
       <c r="AA69" s="24" t="n"/>
       <c r="AB69" s="24" t="n"/>
@@ -8681,7 +8508,7 @@
       <c r="BN69" s="24" t="n"/>
       <c r="BO69" s="24" t="n"/>
     </row>
-    <row r="70" ht="16" customHeight="1">
+    <row r="70" ht="18" customHeight="1">
       <c r="A70" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -8697,38 +8524,33 @@
           <t>PAB180·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D70" s="27" t="n">
-        <v>46276</v>
-      </c>
-      <c r="E70" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F70" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G70" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="n"/>
-      <c r="I70" s="29" t="n"/>
-      <c r="J70" s="29" t="n"/>
-      <c r="K70" s="29" t="n"/>
-      <c r="L70" s="29" t="n"/>
-      <c r="M70" s="29" t="n"/>
-      <c r="N70" s="29" t="n"/>
-      <c r="O70" s="29" t="n"/>
-      <c r="P70" s="29" t="n"/>
-      <c r="Q70" s="29" t="n"/>
-      <c r="R70" s="29" t="n"/>
-      <c r="S70" s="29" t="n"/>
-      <c r="T70" s="29" t="n"/>
-      <c r="U70" s="30" t="n"/>
+      <c r="D70" s="27">
+        <f>IF('时间节点计划表'!E35="","",'时间节点计划表'!E35)</f>
+        <v/>
+      </c>
+      <c r="E70" s="27">
+        <f>IF('时间节点计划表'!F35="","",'时间节点计划表'!F35)</f>
+        <v/>
+      </c>
+      <c r="F70" s="28">
+        <f>IF(OR(D70="",E70=""),"待填",E70-D70)</f>
+        <v/>
+      </c>
+      <c r="G70" s="24" t="n"/>
+      <c r="H70" s="24" t="n"/>
+      <c r="I70" s="24" t="n"/>
+      <c r="J70" s="24" t="n"/>
+      <c r="K70" s="24" t="n"/>
+      <c r="L70" s="24" t="n"/>
+      <c r="M70" s="24" t="n"/>
+      <c r="N70" s="24" t="n"/>
+      <c r="O70" s="24" t="n"/>
+      <c r="P70" s="24" t="n"/>
+      <c r="Q70" s="24" t="n"/>
+      <c r="R70" s="24" t="n"/>
+      <c r="S70" s="24" t="n"/>
+      <c r="T70" s="24" t="n"/>
+      <c r="U70" s="24" t="n"/>
       <c r="V70" s="24" t="n"/>
       <c r="W70" s="24" t="n"/>
       <c r="X70" s="24" t="n"/>
@@ -8776,7 +8598,7 @@
       <c r="BN70" s="24" t="n"/>
       <c r="BO70" s="24" t="n"/>
     </row>
-    <row r="71" ht="16" customHeight="1">
+    <row r="71" ht="18" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -8792,63 +8614,61 @@
           <t>PAB180·工装实物到位</t>
         </is>
       </c>
-      <c r="D71" s="22" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E71" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F71" s="20" t="inlineStr"/>
-      <c r="G71" s="31" t="n"/>
-      <c r="H71" s="31" t="n"/>
-      <c r="I71" s="31" t="n"/>
-      <c r="J71" s="31" t="n"/>
-      <c r="K71" s="31" t="n"/>
-      <c r="L71" s="31" t="n"/>
-      <c r="M71" s="31" t="n"/>
-      <c r="N71" s="31" t="n"/>
-      <c r="O71" s="31" t="n"/>
-      <c r="P71" s="31" t="n"/>
-      <c r="Q71" s="31" t="n"/>
-      <c r="R71" s="31" t="n"/>
-      <c r="S71" s="31" t="n"/>
-      <c r="T71" s="31" t="n"/>
-      <c r="U71" s="31" t="n"/>
-      <c r="V71" s="31" t="n"/>
-      <c r="W71" s="31" t="n"/>
-      <c r="X71" s="31" t="n"/>
-      <c r="Y71" s="31" t="n"/>
-      <c r="Z71" s="31" t="n"/>
-      <c r="AA71" s="31" t="n"/>
-      <c r="AB71" s="31" t="n"/>
-      <c r="AC71" s="31" t="n"/>
-      <c r="AD71" s="31" t="n"/>
-      <c r="AE71" s="31" t="n"/>
-      <c r="AF71" s="31" t="n"/>
-      <c r="AG71" s="31" t="n"/>
-      <c r="AH71" s="31" t="n"/>
-      <c r="AI71" s="31" t="n"/>
-      <c r="AJ71" s="31" t="n"/>
-      <c r="AK71" s="31" t="n"/>
-      <c r="AL71" s="31" t="n"/>
-      <c r="AM71" s="31" t="n"/>
-      <c r="AN71" s="31" t="n"/>
-      <c r="AO71" s="31" t="n"/>
-      <c r="AP71" s="31" t="n"/>
-      <c r="AQ71" s="31" t="n"/>
-      <c r="AR71" s="31" t="n"/>
-      <c r="AS71" s="31" t="n"/>
-      <c r="AT71" s="31" t="n"/>
-      <c r="AU71" s="31" t="n"/>
-      <c r="AV71" s="31" t="n"/>
-      <c r="AW71" s="31" t="n"/>
-      <c r="AX71" s="31" t="n"/>
-      <c r="AY71" s="31" t="n"/>
-      <c r="AZ71" s="23" t="n">
-        <v>8</v>
-      </c>
+      <c r="D71" s="22">
+        <f>IF('时间节点计划表'!E36="","",'时间节点计划表'!E36)</f>
+        <v/>
+      </c>
+      <c r="E71" s="22">
+        <f>IF('时间节点计划表'!F36="","",'时间节点计划表'!F36)</f>
+        <v/>
+      </c>
+      <c r="F71" s="23" t="inlineStr"/>
+      <c r="G71" s="24" t="n"/>
+      <c r="H71" s="24" t="n"/>
+      <c r="I71" s="24" t="n"/>
+      <c r="J71" s="24" t="n"/>
+      <c r="K71" s="24" t="n"/>
+      <c r="L71" s="24" t="n"/>
+      <c r="M71" s="24" t="n"/>
+      <c r="N71" s="24" t="n"/>
+      <c r="O71" s="24" t="n"/>
+      <c r="P71" s="24" t="n"/>
+      <c r="Q71" s="24" t="n"/>
+      <c r="R71" s="24" t="n"/>
+      <c r="S71" s="24" t="n"/>
+      <c r="T71" s="24" t="n"/>
+      <c r="U71" s="24" t="n"/>
+      <c r="V71" s="24" t="n"/>
+      <c r="W71" s="24" t="n"/>
+      <c r="X71" s="24" t="n"/>
+      <c r="Y71" s="24" t="n"/>
+      <c r="Z71" s="24" t="n"/>
+      <c r="AA71" s="24" t="n"/>
+      <c r="AB71" s="24" t="n"/>
+      <c r="AC71" s="24" t="n"/>
+      <c r="AD71" s="24" t="n"/>
+      <c r="AE71" s="24" t="n"/>
+      <c r="AF71" s="24" t="n"/>
+      <c r="AG71" s="24" t="n"/>
+      <c r="AH71" s="24" t="n"/>
+      <c r="AI71" s="24" t="n"/>
+      <c r="AJ71" s="24" t="n"/>
+      <c r="AK71" s="24" t="n"/>
+      <c r="AL71" s="24" t="n"/>
+      <c r="AM71" s="24" t="n"/>
+      <c r="AN71" s="24" t="n"/>
+      <c r="AO71" s="24" t="n"/>
+      <c r="AP71" s="24" t="n"/>
+      <c r="AQ71" s="24" t="n"/>
+      <c r="AR71" s="24" t="n"/>
+      <c r="AS71" s="24" t="n"/>
+      <c r="AT71" s="24" t="n"/>
+      <c r="AU71" s="24" t="n"/>
+      <c r="AV71" s="24" t="n"/>
+      <c r="AW71" s="24" t="n"/>
+      <c r="AX71" s="24" t="n"/>
+      <c r="AY71" s="24" t="n"/>
+      <c r="AZ71" s="24" t="n"/>
       <c r="BA71" s="24" t="n"/>
       <c r="BB71" s="24" t="n"/>
       <c r="BC71" s="24" t="n"/>
@@ -8865,7 +8685,7 @@
       <c r="BN71" s="24" t="n"/>
       <c r="BO71" s="24" t="n"/>
     </row>
-    <row r="72" ht="16" customHeight="1">
+    <row r="72" ht="18" customHeight="1">
       <c r="A72" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -8881,38 +8701,33 @@
           <t>PAB180·工装实物到位</t>
         </is>
       </c>
-      <c r="D72" s="27" t="n">
-        <v>46303</v>
-      </c>
-      <c r="E72" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F72" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G72" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H72" s="29" t="n"/>
-      <c r="I72" s="29" t="n"/>
-      <c r="J72" s="29" t="n"/>
-      <c r="K72" s="29" t="n"/>
-      <c r="L72" s="29" t="n"/>
-      <c r="M72" s="29" t="n"/>
-      <c r="N72" s="29" t="n"/>
-      <c r="O72" s="29" t="n"/>
-      <c r="P72" s="29" t="n"/>
-      <c r="Q72" s="29" t="n"/>
-      <c r="R72" s="29" t="n"/>
-      <c r="S72" s="29" t="n"/>
-      <c r="T72" s="29" t="n"/>
-      <c r="U72" s="30" t="n"/>
+      <c r="D72" s="27">
+        <f>IF('时间节点计划表'!E36="","",'时间节点计划表'!E36)</f>
+        <v/>
+      </c>
+      <c r="E72" s="27">
+        <f>IF('时间节点计划表'!F36="","",'时间节点计划表'!F36)</f>
+        <v/>
+      </c>
+      <c r="F72" s="28">
+        <f>IF(OR(D72="",E72=""),"待填",E72-D72)</f>
+        <v/>
+      </c>
+      <c r="G72" s="24" t="n"/>
+      <c r="H72" s="24" t="n"/>
+      <c r="I72" s="24" t="n"/>
+      <c r="J72" s="24" t="n"/>
+      <c r="K72" s="24" t="n"/>
+      <c r="L72" s="24" t="n"/>
+      <c r="M72" s="24" t="n"/>
+      <c r="N72" s="24" t="n"/>
+      <c r="O72" s="24" t="n"/>
+      <c r="P72" s="24" t="n"/>
+      <c r="Q72" s="24" t="n"/>
+      <c r="R72" s="24" t="n"/>
+      <c r="S72" s="24" t="n"/>
+      <c r="T72" s="24" t="n"/>
+      <c r="U72" s="24" t="n"/>
       <c r="V72" s="24" t="n"/>
       <c r="W72" s="24" t="n"/>
       <c r="X72" s="24" t="n"/>
@@ -8960,7 +8775,7 @@
       <c r="BN72" s="24" t="n"/>
       <c r="BO72" s="24" t="n"/>
     </row>
-    <row r="73" ht="16" customHeight="1">
+    <row r="73" ht="18" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -8976,70 +8791,68 @@
           <t>PAB180·排针机安装调试</t>
         </is>
       </c>
-      <c r="D73" s="22" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E73" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F73" s="20" t="inlineStr"/>
-      <c r="G73" s="31" t="n"/>
-      <c r="H73" s="31" t="n"/>
-      <c r="I73" s="31" t="n"/>
-      <c r="J73" s="31" t="n"/>
-      <c r="K73" s="31" t="n"/>
-      <c r="L73" s="31" t="n"/>
-      <c r="M73" s="31" t="n"/>
-      <c r="N73" s="31" t="n"/>
-      <c r="O73" s="31" t="n"/>
-      <c r="P73" s="31" t="n"/>
-      <c r="Q73" s="31" t="n"/>
-      <c r="R73" s="31" t="n"/>
-      <c r="S73" s="31" t="n"/>
-      <c r="T73" s="31" t="n"/>
-      <c r="U73" s="31" t="n"/>
-      <c r="V73" s="31" t="n"/>
-      <c r="W73" s="31" t="n"/>
-      <c r="X73" s="31" t="n"/>
-      <c r="Y73" s="31" t="n"/>
-      <c r="Z73" s="31" t="n"/>
-      <c r="AA73" s="31" t="n"/>
-      <c r="AB73" s="31" t="n"/>
-      <c r="AC73" s="31" t="n"/>
-      <c r="AD73" s="31" t="n"/>
-      <c r="AE73" s="31" t="n"/>
-      <c r="AF73" s="31" t="n"/>
-      <c r="AG73" s="31" t="n"/>
-      <c r="AH73" s="31" t="n"/>
-      <c r="AI73" s="31" t="n"/>
-      <c r="AJ73" s="31" t="n"/>
-      <c r="AK73" s="31" t="n"/>
-      <c r="AL73" s="31" t="n"/>
-      <c r="AM73" s="31" t="n"/>
-      <c r="AN73" s="31" t="n"/>
-      <c r="AO73" s="31" t="n"/>
-      <c r="AP73" s="31" t="n"/>
-      <c r="AQ73" s="31" t="n"/>
-      <c r="AR73" s="31" t="n"/>
-      <c r="AS73" s="31" t="n"/>
-      <c r="AT73" s="31" t="n"/>
-      <c r="AU73" s="31" t="n"/>
-      <c r="AV73" s="31" t="n"/>
-      <c r="AW73" s="31" t="n"/>
-      <c r="AX73" s="31" t="n"/>
-      <c r="AY73" s="31" t="n"/>
-      <c r="AZ73" s="31" t="n"/>
-      <c r="BA73" s="31" t="n"/>
-      <c r="BB73" s="31" t="n"/>
-      <c r="BC73" s="31" t="n"/>
-      <c r="BD73" s="31" t="n"/>
-      <c r="BE73" s="31" t="n"/>
-      <c r="BF73" s="31" t="n"/>
-      <c r="BG73" s="23" t="n">
-        <v>15</v>
-      </c>
+      <c r="D73" s="22">
+        <f>IF('时间节点计划表'!E37="","",'时间节点计划表'!E37)</f>
+        <v/>
+      </c>
+      <c r="E73" s="22">
+        <f>IF('时间节点计划表'!F37="","",'时间节点计划表'!F37)</f>
+        <v/>
+      </c>
+      <c r="F73" s="23" t="inlineStr"/>
+      <c r="G73" s="24" t="n"/>
+      <c r="H73" s="24" t="n"/>
+      <c r="I73" s="24" t="n"/>
+      <c r="J73" s="24" t="n"/>
+      <c r="K73" s="24" t="n"/>
+      <c r="L73" s="24" t="n"/>
+      <c r="M73" s="24" t="n"/>
+      <c r="N73" s="24" t="n"/>
+      <c r="O73" s="24" t="n"/>
+      <c r="P73" s="24" t="n"/>
+      <c r="Q73" s="24" t="n"/>
+      <c r="R73" s="24" t="n"/>
+      <c r="S73" s="24" t="n"/>
+      <c r="T73" s="24" t="n"/>
+      <c r="U73" s="24" t="n"/>
+      <c r="V73" s="24" t="n"/>
+      <c r="W73" s="24" t="n"/>
+      <c r="X73" s="24" t="n"/>
+      <c r="Y73" s="24" t="n"/>
+      <c r="Z73" s="24" t="n"/>
+      <c r="AA73" s="24" t="n"/>
+      <c r="AB73" s="24" t="n"/>
+      <c r="AC73" s="24" t="n"/>
+      <c r="AD73" s="24" t="n"/>
+      <c r="AE73" s="24" t="n"/>
+      <c r="AF73" s="24" t="n"/>
+      <c r="AG73" s="24" t="n"/>
+      <c r="AH73" s="24" t="n"/>
+      <c r="AI73" s="24" t="n"/>
+      <c r="AJ73" s="24" t="n"/>
+      <c r="AK73" s="24" t="n"/>
+      <c r="AL73" s="24" t="n"/>
+      <c r="AM73" s="24" t="n"/>
+      <c r="AN73" s="24" t="n"/>
+      <c r="AO73" s="24" t="n"/>
+      <c r="AP73" s="24" t="n"/>
+      <c r="AQ73" s="24" t="n"/>
+      <c r="AR73" s="24" t="n"/>
+      <c r="AS73" s="24" t="n"/>
+      <c r="AT73" s="24" t="n"/>
+      <c r="AU73" s="24" t="n"/>
+      <c r="AV73" s="24" t="n"/>
+      <c r="AW73" s="24" t="n"/>
+      <c r="AX73" s="24" t="n"/>
+      <c r="AY73" s="24" t="n"/>
+      <c r="AZ73" s="24" t="n"/>
+      <c r="BA73" s="24" t="n"/>
+      <c r="BB73" s="24" t="n"/>
+      <c r="BC73" s="24" t="n"/>
+      <c r="BD73" s="24" t="n"/>
+      <c r="BE73" s="24" t="n"/>
+      <c r="BF73" s="24" t="n"/>
+      <c r="BG73" s="24" t="n"/>
       <c r="BH73" s="24" t="n"/>
       <c r="BI73" s="24" t="n"/>
       <c r="BJ73" s="24" t="n"/>
@@ -9049,7 +8862,7 @@
       <c r="BN73" s="24" t="n"/>
       <c r="BO73" s="24" t="n"/>
     </row>
-    <row r="74" ht="16" customHeight="1">
+    <row r="74" ht="18" customHeight="1">
       <c r="A74" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -9065,38 +8878,33 @@
           <t>PAB180·排针机安装调试</t>
         </is>
       </c>
-      <c r="D74" s="27" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E74" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F74" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G74" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H74" s="29" t="n"/>
-      <c r="I74" s="29" t="n"/>
-      <c r="J74" s="29" t="n"/>
-      <c r="K74" s="29" t="n"/>
-      <c r="L74" s="29" t="n"/>
-      <c r="M74" s="29" t="n"/>
-      <c r="N74" s="29" t="n"/>
-      <c r="O74" s="29" t="n"/>
-      <c r="P74" s="29" t="n"/>
-      <c r="Q74" s="29" t="n"/>
-      <c r="R74" s="29" t="n"/>
-      <c r="S74" s="29" t="n"/>
-      <c r="T74" s="29" t="n"/>
-      <c r="U74" s="30" t="n"/>
+      <c r="D74" s="27">
+        <f>IF('时间节点计划表'!E37="","",'时间节点计划表'!E37)</f>
+        <v/>
+      </c>
+      <c r="E74" s="27">
+        <f>IF('时间节点计划表'!F37="","",'时间节点计划表'!F37)</f>
+        <v/>
+      </c>
+      <c r="F74" s="28">
+        <f>IF(OR(D74="",E74=""),"待填",E74-D74)</f>
+        <v/>
+      </c>
+      <c r="G74" s="24" t="n"/>
+      <c r="H74" s="24" t="n"/>
+      <c r="I74" s="24" t="n"/>
+      <c r="J74" s="24" t="n"/>
+      <c r="K74" s="24" t="n"/>
+      <c r="L74" s="24" t="n"/>
+      <c r="M74" s="24" t="n"/>
+      <c r="N74" s="24" t="n"/>
+      <c r="O74" s="24" t="n"/>
+      <c r="P74" s="24" t="n"/>
+      <c r="Q74" s="24" t="n"/>
+      <c r="R74" s="24" t="n"/>
+      <c r="S74" s="24" t="n"/>
+      <c r="T74" s="24" t="n"/>
+      <c r="U74" s="24" t="n"/>
       <c r="V74" s="24" t="n"/>
       <c r="W74" s="24" t="n"/>
       <c r="X74" s="24" t="n"/>
@@ -9144,7 +8952,7 @@
       <c r="BN74" s="24" t="n"/>
       <c r="BO74" s="24" t="n"/>
     </row>
-    <row r="75" ht="16" customHeight="1">
+    <row r="75" ht="18" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -9160,71 +8968,69 @@
           <t>PAB180·单级样机</t>
         </is>
       </c>
-      <c r="D75" s="22" t="n">
-        <v>46311</v>
-      </c>
-      <c r="E75" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F75" s="20" t="inlineStr"/>
-      <c r="G75" s="31" t="n"/>
-      <c r="H75" s="31" t="n"/>
-      <c r="I75" s="31" t="n"/>
-      <c r="J75" s="31" t="n"/>
-      <c r="K75" s="31" t="n"/>
-      <c r="L75" s="31" t="n"/>
-      <c r="M75" s="31" t="n"/>
-      <c r="N75" s="31" t="n"/>
-      <c r="O75" s="31" t="n"/>
-      <c r="P75" s="31" t="n"/>
-      <c r="Q75" s="31" t="n"/>
-      <c r="R75" s="31" t="n"/>
-      <c r="S75" s="31" t="n"/>
-      <c r="T75" s="31" t="n"/>
-      <c r="U75" s="31" t="n"/>
-      <c r="V75" s="31" t="n"/>
-      <c r="W75" s="31" t="n"/>
-      <c r="X75" s="31" t="n"/>
-      <c r="Y75" s="31" t="n"/>
-      <c r="Z75" s="31" t="n"/>
-      <c r="AA75" s="31" t="n"/>
-      <c r="AB75" s="31" t="n"/>
-      <c r="AC75" s="31" t="n"/>
-      <c r="AD75" s="31" t="n"/>
-      <c r="AE75" s="31" t="n"/>
-      <c r="AF75" s="31" t="n"/>
-      <c r="AG75" s="31" t="n"/>
-      <c r="AH75" s="31" t="n"/>
-      <c r="AI75" s="31" t="n"/>
-      <c r="AJ75" s="31" t="n"/>
-      <c r="AK75" s="31" t="n"/>
-      <c r="AL75" s="31" t="n"/>
-      <c r="AM75" s="31" t="n"/>
-      <c r="AN75" s="31" t="n"/>
-      <c r="AO75" s="31" t="n"/>
-      <c r="AP75" s="31" t="n"/>
-      <c r="AQ75" s="31" t="n"/>
-      <c r="AR75" s="31" t="n"/>
-      <c r="AS75" s="31" t="n"/>
-      <c r="AT75" s="31" t="n"/>
-      <c r="AU75" s="31" t="n"/>
-      <c r="AV75" s="31" t="n"/>
-      <c r="AW75" s="31" t="n"/>
-      <c r="AX75" s="31" t="n"/>
-      <c r="AY75" s="31" t="n"/>
-      <c r="AZ75" s="31" t="n"/>
-      <c r="BA75" s="31" t="n"/>
-      <c r="BB75" s="31" t="n"/>
-      <c r="BC75" s="31" t="n"/>
-      <c r="BD75" s="31" t="n"/>
-      <c r="BE75" s="31" t="n"/>
-      <c r="BF75" s="31" t="n"/>
-      <c r="BG75" s="31" t="n"/>
-      <c r="BH75" s="23" t="n">
-        <v>16</v>
-      </c>
+      <c r="D75" s="22">
+        <f>IF('时间节点计划表'!E38="","",'时间节点计划表'!E38)</f>
+        <v/>
+      </c>
+      <c r="E75" s="22">
+        <f>IF('时间节点计划表'!F38="","",'时间节点计划表'!F38)</f>
+        <v/>
+      </c>
+      <c r="F75" s="23" t="inlineStr"/>
+      <c r="G75" s="24" t="n"/>
+      <c r="H75" s="24" t="n"/>
+      <c r="I75" s="24" t="n"/>
+      <c r="J75" s="24" t="n"/>
+      <c r="K75" s="24" t="n"/>
+      <c r="L75" s="24" t="n"/>
+      <c r="M75" s="24" t="n"/>
+      <c r="N75" s="24" t="n"/>
+      <c r="O75" s="24" t="n"/>
+      <c r="P75" s="24" t="n"/>
+      <c r="Q75" s="24" t="n"/>
+      <c r="R75" s="24" t="n"/>
+      <c r="S75" s="24" t="n"/>
+      <c r="T75" s="24" t="n"/>
+      <c r="U75" s="24" t="n"/>
+      <c r="V75" s="24" t="n"/>
+      <c r="W75" s="24" t="n"/>
+      <c r="X75" s="24" t="n"/>
+      <c r="Y75" s="24" t="n"/>
+      <c r="Z75" s="24" t="n"/>
+      <c r="AA75" s="24" t="n"/>
+      <c r="AB75" s="24" t="n"/>
+      <c r="AC75" s="24" t="n"/>
+      <c r="AD75" s="24" t="n"/>
+      <c r="AE75" s="24" t="n"/>
+      <c r="AF75" s="24" t="n"/>
+      <c r="AG75" s="24" t="n"/>
+      <c r="AH75" s="24" t="n"/>
+      <c r="AI75" s="24" t="n"/>
+      <c r="AJ75" s="24" t="n"/>
+      <c r="AK75" s="24" t="n"/>
+      <c r="AL75" s="24" t="n"/>
+      <c r="AM75" s="24" t="n"/>
+      <c r="AN75" s="24" t="n"/>
+      <c r="AO75" s="24" t="n"/>
+      <c r="AP75" s="24" t="n"/>
+      <c r="AQ75" s="24" t="n"/>
+      <c r="AR75" s="24" t="n"/>
+      <c r="AS75" s="24" t="n"/>
+      <c r="AT75" s="24" t="n"/>
+      <c r="AU75" s="24" t="n"/>
+      <c r="AV75" s="24" t="n"/>
+      <c r="AW75" s="24" t="n"/>
+      <c r="AX75" s="24" t="n"/>
+      <c r="AY75" s="24" t="n"/>
+      <c r="AZ75" s="24" t="n"/>
+      <c r="BA75" s="24" t="n"/>
+      <c r="BB75" s="24" t="n"/>
+      <c r="BC75" s="24" t="n"/>
+      <c r="BD75" s="24" t="n"/>
+      <c r="BE75" s="24" t="n"/>
+      <c r="BF75" s="24" t="n"/>
+      <c r="BG75" s="24" t="n"/>
+      <c r="BH75" s="24" t="n"/>
       <c r="BI75" s="24" t="n"/>
       <c r="BJ75" s="24" t="n"/>
       <c r="BK75" s="24" t="n"/>
@@ -9233,7 +9039,7 @@
       <c r="BN75" s="24" t="n"/>
       <c r="BO75" s="24" t="n"/>
     </row>
-    <row r="76" ht="16" customHeight="1">
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -9249,38 +9055,33 @@
           <t>PAB180·单级样机</t>
         </is>
       </c>
-      <c r="D76" s="27" t="n">
-        <v>46311</v>
-      </c>
-      <c r="E76" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F76" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G76" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H76" s="29" t="n"/>
-      <c r="I76" s="29" t="n"/>
-      <c r="J76" s="29" t="n"/>
-      <c r="K76" s="29" t="n"/>
-      <c r="L76" s="29" t="n"/>
-      <c r="M76" s="29" t="n"/>
-      <c r="N76" s="29" t="n"/>
-      <c r="O76" s="29" t="n"/>
-      <c r="P76" s="29" t="n"/>
-      <c r="Q76" s="29" t="n"/>
-      <c r="R76" s="29" t="n"/>
-      <c r="S76" s="29" t="n"/>
-      <c r="T76" s="29" t="n"/>
-      <c r="U76" s="30" t="n"/>
+      <c r="D76" s="27">
+        <f>IF('时间节点计划表'!E38="","",'时间节点计划表'!E38)</f>
+        <v/>
+      </c>
+      <c r="E76" s="27">
+        <f>IF('时间节点计划表'!F38="","",'时间节点计划表'!F38)</f>
+        <v/>
+      </c>
+      <c r="F76" s="28">
+        <f>IF(OR(D76="",E76=""),"待填",E76-D76)</f>
+        <v/>
+      </c>
+      <c r="G76" s="24" t="n"/>
+      <c r="H76" s="24" t="n"/>
+      <c r="I76" s="24" t="n"/>
+      <c r="J76" s="24" t="n"/>
+      <c r="K76" s="24" t="n"/>
+      <c r="L76" s="24" t="n"/>
+      <c r="M76" s="24" t="n"/>
+      <c r="N76" s="24" t="n"/>
+      <c r="O76" s="24" t="n"/>
+      <c r="P76" s="24" t="n"/>
+      <c r="Q76" s="24" t="n"/>
+      <c r="R76" s="24" t="n"/>
+      <c r="S76" s="24" t="n"/>
+      <c r="T76" s="24" t="n"/>
+      <c r="U76" s="24" t="n"/>
       <c r="V76" s="24" t="n"/>
       <c r="W76" s="24" t="n"/>
       <c r="X76" s="24" t="n"/>
@@ -9328,7 +9129,7 @@
       <c r="BN76" s="24" t="n"/>
       <c r="BO76" s="24" t="n"/>
     </row>
-    <row r="77" ht="16" customHeight="1">
+    <row r="77" ht="18" customHeight="1">
       <c r="A77" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -9344,80 +9145,78 @@
           <t>PAB180·双级样机</t>
         </is>
       </c>
-      <c r="D77" s="22" t="n">
-        <v>46314</v>
-      </c>
-      <c r="E77" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F77" s="20" t="inlineStr"/>
-      <c r="G77" s="31" t="n"/>
-      <c r="H77" s="31" t="n"/>
-      <c r="I77" s="31" t="n"/>
-      <c r="J77" s="31" t="n"/>
-      <c r="K77" s="31" t="n"/>
-      <c r="L77" s="31" t="n"/>
-      <c r="M77" s="31" t="n"/>
-      <c r="N77" s="31" t="n"/>
-      <c r="O77" s="31" t="n"/>
-      <c r="P77" s="31" t="n"/>
-      <c r="Q77" s="31" t="n"/>
-      <c r="R77" s="31" t="n"/>
-      <c r="S77" s="31" t="n"/>
-      <c r="T77" s="31" t="n"/>
-      <c r="U77" s="31" t="n"/>
-      <c r="V77" s="31" t="n"/>
-      <c r="W77" s="31" t="n"/>
-      <c r="X77" s="31" t="n"/>
-      <c r="Y77" s="31" t="n"/>
-      <c r="Z77" s="31" t="n"/>
-      <c r="AA77" s="31" t="n"/>
-      <c r="AB77" s="31" t="n"/>
-      <c r="AC77" s="31" t="n"/>
-      <c r="AD77" s="31" t="n"/>
-      <c r="AE77" s="31" t="n"/>
-      <c r="AF77" s="31" t="n"/>
-      <c r="AG77" s="31" t="n"/>
-      <c r="AH77" s="31" t="n"/>
-      <c r="AI77" s="31" t="n"/>
-      <c r="AJ77" s="31" t="n"/>
-      <c r="AK77" s="31" t="n"/>
-      <c r="AL77" s="31" t="n"/>
-      <c r="AM77" s="31" t="n"/>
-      <c r="AN77" s="31" t="n"/>
-      <c r="AO77" s="31" t="n"/>
-      <c r="AP77" s="31" t="n"/>
-      <c r="AQ77" s="31" t="n"/>
-      <c r="AR77" s="31" t="n"/>
-      <c r="AS77" s="31" t="n"/>
-      <c r="AT77" s="31" t="n"/>
-      <c r="AU77" s="31" t="n"/>
-      <c r="AV77" s="31" t="n"/>
-      <c r="AW77" s="31" t="n"/>
-      <c r="AX77" s="31" t="n"/>
-      <c r="AY77" s="31" t="n"/>
-      <c r="AZ77" s="31" t="n"/>
-      <c r="BA77" s="31" t="n"/>
-      <c r="BB77" s="31" t="n"/>
-      <c r="BC77" s="31" t="n"/>
-      <c r="BD77" s="31" t="n"/>
-      <c r="BE77" s="31" t="n"/>
-      <c r="BF77" s="31" t="n"/>
-      <c r="BG77" s="31" t="n"/>
-      <c r="BH77" s="31" t="n"/>
-      <c r="BI77" s="31" t="n"/>
-      <c r="BJ77" s="31" t="n"/>
-      <c r="BK77" s="23" t="n">
-        <v>19</v>
-      </c>
+      <c r="D77" s="22">
+        <f>IF('时间节点计划表'!E39="","",'时间节点计划表'!E39)</f>
+        <v/>
+      </c>
+      <c r="E77" s="22">
+        <f>IF('时间节点计划表'!F39="","",'时间节点计划表'!F39)</f>
+        <v/>
+      </c>
+      <c r="F77" s="23" t="inlineStr"/>
+      <c r="G77" s="24" t="n"/>
+      <c r="H77" s="24" t="n"/>
+      <c r="I77" s="24" t="n"/>
+      <c r="J77" s="24" t="n"/>
+      <c r="K77" s="24" t="n"/>
+      <c r="L77" s="24" t="n"/>
+      <c r="M77" s="24" t="n"/>
+      <c r="N77" s="24" t="n"/>
+      <c r="O77" s="24" t="n"/>
+      <c r="P77" s="24" t="n"/>
+      <c r="Q77" s="24" t="n"/>
+      <c r="R77" s="24" t="n"/>
+      <c r="S77" s="24" t="n"/>
+      <c r="T77" s="24" t="n"/>
+      <c r="U77" s="24" t="n"/>
+      <c r="V77" s="24" t="n"/>
+      <c r="W77" s="24" t="n"/>
+      <c r="X77" s="24" t="n"/>
+      <c r="Y77" s="24" t="n"/>
+      <c r="Z77" s="24" t="n"/>
+      <c r="AA77" s="24" t="n"/>
+      <c r="AB77" s="24" t="n"/>
+      <c r="AC77" s="24" t="n"/>
+      <c r="AD77" s="24" t="n"/>
+      <c r="AE77" s="24" t="n"/>
+      <c r="AF77" s="24" t="n"/>
+      <c r="AG77" s="24" t="n"/>
+      <c r="AH77" s="24" t="n"/>
+      <c r="AI77" s="24" t="n"/>
+      <c r="AJ77" s="24" t="n"/>
+      <c r="AK77" s="24" t="n"/>
+      <c r="AL77" s="24" t="n"/>
+      <c r="AM77" s="24" t="n"/>
+      <c r="AN77" s="24" t="n"/>
+      <c r="AO77" s="24" t="n"/>
+      <c r="AP77" s="24" t="n"/>
+      <c r="AQ77" s="24" t="n"/>
+      <c r="AR77" s="24" t="n"/>
+      <c r="AS77" s="24" t="n"/>
+      <c r="AT77" s="24" t="n"/>
+      <c r="AU77" s="24" t="n"/>
+      <c r="AV77" s="24" t="n"/>
+      <c r="AW77" s="24" t="n"/>
+      <c r="AX77" s="24" t="n"/>
+      <c r="AY77" s="24" t="n"/>
+      <c r="AZ77" s="24" t="n"/>
+      <c r="BA77" s="24" t="n"/>
+      <c r="BB77" s="24" t="n"/>
+      <c r="BC77" s="24" t="n"/>
+      <c r="BD77" s="24" t="n"/>
+      <c r="BE77" s="24" t="n"/>
+      <c r="BF77" s="24" t="n"/>
+      <c r="BG77" s="24" t="n"/>
+      <c r="BH77" s="24" t="n"/>
+      <c r="BI77" s="24" t="n"/>
+      <c r="BJ77" s="24" t="n"/>
+      <c r="BK77" s="24" t="n"/>
       <c r="BL77" s="24" t="n"/>
       <c r="BM77" s="24" t="n"/>
       <c r="BN77" s="24" t="n"/>
       <c r="BO77" s="24" t="n"/>
     </row>
-    <row r="78" ht="16" customHeight="1">
+    <row r="78" ht="18" customHeight="1">
       <c r="A78" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -9433,38 +9232,33 @@
           <t>PAB180·双级样机</t>
         </is>
       </c>
-      <c r="D78" s="27" t="n">
-        <v>46314</v>
-      </c>
-      <c r="E78" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F78" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G78" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="n"/>
-      <c r="I78" s="29" t="n"/>
-      <c r="J78" s="29" t="n"/>
-      <c r="K78" s="29" t="n"/>
-      <c r="L78" s="29" t="n"/>
-      <c r="M78" s="29" t="n"/>
-      <c r="N78" s="29" t="n"/>
-      <c r="O78" s="29" t="n"/>
-      <c r="P78" s="29" t="n"/>
-      <c r="Q78" s="29" t="n"/>
-      <c r="R78" s="29" t="n"/>
-      <c r="S78" s="29" t="n"/>
-      <c r="T78" s="29" t="n"/>
-      <c r="U78" s="30" t="n"/>
+      <c r="D78" s="27">
+        <f>IF('时间节点计划表'!E39="","",'时间节点计划表'!E39)</f>
+        <v/>
+      </c>
+      <c r="E78" s="27">
+        <f>IF('时间节点计划表'!F39="","",'时间节点计划表'!F39)</f>
+        <v/>
+      </c>
+      <c r="F78" s="28">
+        <f>IF(OR(D78="",E78=""),"待填",E78-D78)</f>
+        <v/>
+      </c>
+      <c r="G78" s="24" t="n"/>
+      <c r="H78" s="24" t="n"/>
+      <c r="I78" s="24" t="n"/>
+      <c r="J78" s="24" t="n"/>
+      <c r="K78" s="24" t="n"/>
+      <c r="L78" s="24" t="n"/>
+      <c r="M78" s="24" t="n"/>
+      <c r="N78" s="24" t="n"/>
+      <c r="O78" s="24" t="n"/>
+      <c r="P78" s="24" t="n"/>
+      <c r="Q78" s="24" t="n"/>
+      <c r="R78" s="24" t="n"/>
+      <c r="S78" s="24" t="n"/>
+      <c r="T78" s="24" t="n"/>
+      <c r="U78" s="24" t="n"/>
       <c r="V78" s="24" t="n"/>
       <c r="W78" s="24" t="n"/>
       <c r="X78" s="24" t="n"/>
@@ -9512,7 +9306,7 @@
       <c r="BN78" s="24" t="n"/>
       <c r="BO78" s="24" t="n"/>
     </row>
-    <row r="79" ht="16" customHeight="1">
+    <row r="79" ht="18" customHeight="1">
       <c r="A79" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -9528,80 +9322,78 @@
           <t>PAB220·零件到位</t>
         </is>
       </c>
-      <c r="D79" s="22" t="n">
-        <v>46315</v>
-      </c>
-      <c r="E79" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F79" s="20" t="inlineStr"/>
-      <c r="G79" s="31" t="n"/>
-      <c r="H79" s="31" t="n"/>
-      <c r="I79" s="31" t="n"/>
-      <c r="J79" s="31" t="n"/>
-      <c r="K79" s="31" t="n"/>
-      <c r="L79" s="31" t="n"/>
-      <c r="M79" s="31" t="n"/>
-      <c r="N79" s="31" t="n"/>
-      <c r="O79" s="31" t="n"/>
-      <c r="P79" s="31" t="n"/>
-      <c r="Q79" s="31" t="n"/>
-      <c r="R79" s="31" t="n"/>
-      <c r="S79" s="31" t="n"/>
-      <c r="T79" s="31" t="n"/>
-      <c r="U79" s="31" t="n"/>
-      <c r="V79" s="31" t="n"/>
-      <c r="W79" s="31" t="n"/>
-      <c r="X79" s="31" t="n"/>
-      <c r="Y79" s="31" t="n"/>
-      <c r="Z79" s="31" t="n"/>
-      <c r="AA79" s="31" t="n"/>
-      <c r="AB79" s="31" t="n"/>
-      <c r="AC79" s="31" t="n"/>
-      <c r="AD79" s="31" t="n"/>
-      <c r="AE79" s="31" t="n"/>
-      <c r="AF79" s="31" t="n"/>
-      <c r="AG79" s="31" t="n"/>
-      <c r="AH79" s="31" t="n"/>
-      <c r="AI79" s="31" t="n"/>
-      <c r="AJ79" s="31" t="n"/>
-      <c r="AK79" s="31" t="n"/>
-      <c r="AL79" s="31" t="n"/>
-      <c r="AM79" s="31" t="n"/>
-      <c r="AN79" s="31" t="n"/>
-      <c r="AO79" s="31" t="n"/>
-      <c r="AP79" s="31" t="n"/>
-      <c r="AQ79" s="31" t="n"/>
-      <c r="AR79" s="31" t="n"/>
-      <c r="AS79" s="31" t="n"/>
-      <c r="AT79" s="31" t="n"/>
-      <c r="AU79" s="31" t="n"/>
-      <c r="AV79" s="31" t="n"/>
-      <c r="AW79" s="31" t="n"/>
-      <c r="AX79" s="31" t="n"/>
-      <c r="AY79" s="31" t="n"/>
-      <c r="AZ79" s="31" t="n"/>
-      <c r="BA79" s="31" t="n"/>
-      <c r="BB79" s="31" t="n"/>
-      <c r="BC79" s="31" t="n"/>
-      <c r="BD79" s="31" t="n"/>
-      <c r="BE79" s="31" t="n"/>
-      <c r="BF79" s="31" t="n"/>
-      <c r="BG79" s="31" t="n"/>
-      <c r="BH79" s="31" t="n"/>
-      <c r="BI79" s="31" t="n"/>
-      <c r="BJ79" s="31" t="n"/>
-      <c r="BK79" s="31" t="n"/>
-      <c r="BL79" s="23" t="n">
-        <v>20</v>
-      </c>
+      <c r="D79" s="22">
+        <f>IF('时间节点计划表'!E40="","",'时间节点计划表'!E40)</f>
+        <v/>
+      </c>
+      <c r="E79" s="22">
+        <f>IF('时间节点计划表'!F40="","",'时间节点计划表'!F40)</f>
+        <v/>
+      </c>
+      <c r="F79" s="23" t="inlineStr"/>
+      <c r="G79" s="24" t="n"/>
+      <c r="H79" s="24" t="n"/>
+      <c r="I79" s="24" t="n"/>
+      <c r="J79" s="24" t="n"/>
+      <c r="K79" s="24" t="n"/>
+      <c r="L79" s="24" t="n"/>
+      <c r="M79" s="24" t="n"/>
+      <c r="N79" s="24" t="n"/>
+      <c r="O79" s="24" t="n"/>
+      <c r="P79" s="24" t="n"/>
+      <c r="Q79" s="24" t="n"/>
+      <c r="R79" s="24" t="n"/>
+      <c r="S79" s="24" t="n"/>
+      <c r="T79" s="24" t="n"/>
+      <c r="U79" s="24" t="n"/>
+      <c r="V79" s="24" t="n"/>
+      <c r="W79" s="24" t="n"/>
+      <c r="X79" s="24" t="n"/>
+      <c r="Y79" s="24" t="n"/>
+      <c r="Z79" s="24" t="n"/>
+      <c r="AA79" s="24" t="n"/>
+      <c r="AB79" s="24" t="n"/>
+      <c r="AC79" s="24" t="n"/>
+      <c r="AD79" s="24" t="n"/>
+      <c r="AE79" s="24" t="n"/>
+      <c r="AF79" s="24" t="n"/>
+      <c r="AG79" s="24" t="n"/>
+      <c r="AH79" s="24" t="n"/>
+      <c r="AI79" s="24" t="n"/>
+      <c r="AJ79" s="24" t="n"/>
+      <c r="AK79" s="24" t="n"/>
+      <c r="AL79" s="24" t="n"/>
+      <c r="AM79" s="24" t="n"/>
+      <c r="AN79" s="24" t="n"/>
+      <c r="AO79" s="24" t="n"/>
+      <c r="AP79" s="24" t="n"/>
+      <c r="AQ79" s="24" t="n"/>
+      <c r="AR79" s="24" t="n"/>
+      <c r="AS79" s="24" t="n"/>
+      <c r="AT79" s="24" t="n"/>
+      <c r="AU79" s="24" t="n"/>
+      <c r="AV79" s="24" t="n"/>
+      <c r="AW79" s="24" t="n"/>
+      <c r="AX79" s="24" t="n"/>
+      <c r="AY79" s="24" t="n"/>
+      <c r="AZ79" s="24" t="n"/>
+      <c r="BA79" s="24" t="n"/>
+      <c r="BB79" s="24" t="n"/>
+      <c r="BC79" s="24" t="n"/>
+      <c r="BD79" s="24" t="n"/>
+      <c r="BE79" s="24" t="n"/>
+      <c r="BF79" s="24" t="n"/>
+      <c r="BG79" s="24" t="n"/>
+      <c r="BH79" s="24" t="n"/>
+      <c r="BI79" s="24" t="n"/>
+      <c r="BJ79" s="24" t="n"/>
+      <c r="BK79" s="24" t="n"/>
+      <c r="BL79" s="24" t="n"/>
       <c r="BM79" s="24" t="n"/>
       <c r="BN79" s="24" t="n"/>
       <c r="BO79" s="24" t="n"/>
     </row>
-    <row r="80" ht="16" customHeight="1">
+    <row r="80" ht="18" customHeight="1">
       <c r="A80" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -9617,38 +9409,33 @@
           <t>PAB220·零件到位</t>
         </is>
       </c>
-      <c r="D80" s="27" t="n">
-        <v>46315</v>
-      </c>
-      <c r="E80" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F80" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G80" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H80" s="29" t="n"/>
-      <c r="I80" s="29" t="n"/>
-      <c r="J80" s="29" t="n"/>
-      <c r="K80" s="29" t="n"/>
-      <c r="L80" s="29" t="n"/>
-      <c r="M80" s="29" t="n"/>
-      <c r="N80" s="29" t="n"/>
-      <c r="O80" s="29" t="n"/>
-      <c r="P80" s="29" t="n"/>
-      <c r="Q80" s="29" t="n"/>
-      <c r="R80" s="29" t="n"/>
-      <c r="S80" s="29" t="n"/>
-      <c r="T80" s="29" t="n"/>
-      <c r="U80" s="30" t="n"/>
+      <c r="D80" s="27">
+        <f>IF('时间节点计划表'!E40="","",'时间节点计划表'!E40)</f>
+        <v/>
+      </c>
+      <c r="E80" s="27">
+        <f>IF('时间节点计划表'!F40="","",'时间节点计划表'!F40)</f>
+        <v/>
+      </c>
+      <c r="F80" s="28">
+        <f>IF(OR(D80="",E80=""),"待填",E80-D80)</f>
+        <v/>
+      </c>
+      <c r="G80" s="24" t="n"/>
+      <c r="H80" s="24" t="n"/>
+      <c r="I80" s="24" t="n"/>
+      <c r="J80" s="24" t="n"/>
+      <c r="K80" s="24" t="n"/>
+      <c r="L80" s="24" t="n"/>
+      <c r="M80" s="24" t="n"/>
+      <c r="N80" s="24" t="n"/>
+      <c r="O80" s="24" t="n"/>
+      <c r="P80" s="24" t="n"/>
+      <c r="Q80" s="24" t="n"/>
+      <c r="R80" s="24" t="n"/>
+      <c r="S80" s="24" t="n"/>
+      <c r="T80" s="24" t="n"/>
+      <c r="U80" s="24" t="n"/>
       <c r="V80" s="24" t="n"/>
       <c r="W80" s="24" t="n"/>
       <c r="X80" s="24" t="n"/>
@@ -9696,7 +9483,7 @@
       <c r="BN80" s="24" t="n"/>
       <c r="BO80" s="24" t="n"/>
     </row>
-    <row r="81" ht="16" customHeight="1">
+    <row r="81" ht="18" customHeight="1">
       <c r="A81" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -9712,39 +9499,37 @@
           <t>PAB220·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D81" s="22" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E81" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F81" s="20" t="inlineStr"/>
-      <c r="G81" s="31" t="n"/>
-      <c r="H81" s="31" t="n"/>
-      <c r="I81" s="31" t="n"/>
-      <c r="J81" s="31" t="n"/>
-      <c r="K81" s="31" t="n"/>
-      <c r="L81" s="31" t="n"/>
-      <c r="M81" s="31" t="n"/>
-      <c r="N81" s="31" t="n"/>
-      <c r="O81" s="31" t="n"/>
-      <c r="P81" s="31" t="n"/>
-      <c r="Q81" s="31" t="n"/>
-      <c r="R81" s="31" t="n"/>
-      <c r="S81" s="31" t="n"/>
-      <c r="T81" s="31" t="n"/>
-      <c r="U81" s="31" t="n"/>
-      <c r="V81" s="31" t="n"/>
-      <c r="W81" s="31" t="n"/>
-      <c r="X81" s="31" t="n"/>
-      <c r="Y81" s="31" t="n"/>
-      <c r="Z81" s="31" t="n"/>
-      <c r="AA81" s="31" t="n"/>
-      <c r="AB81" s="23" t="n">
-        <v>14</v>
-      </c>
+      <c r="D81" s="22">
+        <f>IF('时间节点计划表'!E41="","",'时间节点计划表'!E41)</f>
+        <v/>
+      </c>
+      <c r="E81" s="22">
+        <f>IF('时间节点计划表'!F41="","",'时间节点计划表'!F41)</f>
+        <v/>
+      </c>
+      <c r="F81" s="23" t="inlineStr"/>
+      <c r="G81" s="24" t="n"/>
+      <c r="H81" s="24" t="n"/>
+      <c r="I81" s="24" t="n"/>
+      <c r="J81" s="24" t="n"/>
+      <c r="K81" s="24" t="n"/>
+      <c r="L81" s="24" t="n"/>
+      <c r="M81" s="24" t="n"/>
+      <c r="N81" s="24" t="n"/>
+      <c r="O81" s="24" t="n"/>
+      <c r="P81" s="24" t="n"/>
+      <c r="Q81" s="24" t="n"/>
+      <c r="R81" s="24" t="n"/>
+      <c r="S81" s="24" t="n"/>
+      <c r="T81" s="24" t="n"/>
+      <c r="U81" s="24" t="n"/>
+      <c r="V81" s="24" t="n"/>
+      <c r="W81" s="24" t="n"/>
+      <c r="X81" s="24" t="n"/>
+      <c r="Y81" s="24" t="n"/>
+      <c r="Z81" s="24" t="n"/>
+      <c r="AA81" s="24" t="n"/>
+      <c r="AB81" s="24" t="n"/>
       <c r="AC81" s="24" t="n"/>
       <c r="AD81" s="24" t="n"/>
       <c r="AE81" s="24" t="n"/>
@@ -9785,7 +9570,7 @@
       <c r="BN81" s="24" t="n"/>
       <c r="BO81" s="24" t="n"/>
     </row>
-    <row r="82" ht="16" customHeight="1">
+    <row r="82" ht="18" customHeight="1">
       <c r="A82" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -9801,38 +9586,33 @@
           <t>PAB220·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D82" s="27" t="n">
-        <v>46279</v>
-      </c>
-      <c r="E82" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F82" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G82" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H82" s="29" t="n"/>
-      <c r="I82" s="29" t="n"/>
-      <c r="J82" s="29" t="n"/>
-      <c r="K82" s="29" t="n"/>
-      <c r="L82" s="29" t="n"/>
-      <c r="M82" s="29" t="n"/>
-      <c r="N82" s="29" t="n"/>
-      <c r="O82" s="29" t="n"/>
-      <c r="P82" s="29" t="n"/>
-      <c r="Q82" s="29" t="n"/>
-      <c r="R82" s="29" t="n"/>
-      <c r="S82" s="29" t="n"/>
-      <c r="T82" s="29" t="n"/>
-      <c r="U82" s="30" t="n"/>
+      <c r="D82" s="27">
+        <f>IF('时间节点计划表'!E41="","",'时间节点计划表'!E41)</f>
+        <v/>
+      </c>
+      <c r="E82" s="27">
+        <f>IF('时间节点计划表'!F41="","",'时间节点计划表'!F41)</f>
+        <v/>
+      </c>
+      <c r="F82" s="28">
+        <f>IF(OR(D82="",E82=""),"待填",E82-D82)</f>
+        <v/>
+      </c>
+      <c r="G82" s="24" t="n"/>
+      <c r="H82" s="24" t="n"/>
+      <c r="I82" s="24" t="n"/>
+      <c r="J82" s="24" t="n"/>
+      <c r="K82" s="24" t="n"/>
+      <c r="L82" s="24" t="n"/>
+      <c r="M82" s="24" t="n"/>
+      <c r="N82" s="24" t="n"/>
+      <c r="O82" s="24" t="n"/>
+      <c r="P82" s="24" t="n"/>
+      <c r="Q82" s="24" t="n"/>
+      <c r="R82" s="24" t="n"/>
+      <c r="S82" s="24" t="n"/>
+      <c r="T82" s="24" t="n"/>
+      <c r="U82" s="24" t="n"/>
       <c r="V82" s="24" t="n"/>
       <c r="W82" s="24" t="n"/>
       <c r="X82" s="24" t="n"/>
@@ -9880,7 +9660,7 @@
       <c r="BN82" s="24" t="n"/>
       <c r="BO82" s="24" t="n"/>
     </row>
-    <row r="83" ht="16" customHeight="1">
+    <row r="83" ht="18" customHeight="1">
       <c r="A83" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -9896,65 +9676,63 @@
           <t>PAB220·工装实物到位</t>
         </is>
       </c>
-      <c r="D83" s="22" t="n">
-        <v>46305</v>
-      </c>
-      <c r="E83" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F83" s="20" t="inlineStr"/>
-      <c r="G83" s="31" t="n"/>
-      <c r="H83" s="31" t="n"/>
-      <c r="I83" s="31" t="n"/>
-      <c r="J83" s="31" t="n"/>
-      <c r="K83" s="31" t="n"/>
-      <c r="L83" s="31" t="n"/>
-      <c r="M83" s="31" t="n"/>
-      <c r="N83" s="31" t="n"/>
-      <c r="O83" s="31" t="n"/>
-      <c r="P83" s="31" t="n"/>
-      <c r="Q83" s="31" t="n"/>
-      <c r="R83" s="31" t="n"/>
-      <c r="S83" s="31" t="n"/>
-      <c r="T83" s="31" t="n"/>
-      <c r="U83" s="31" t="n"/>
-      <c r="V83" s="31" t="n"/>
-      <c r="W83" s="31" t="n"/>
-      <c r="X83" s="31" t="n"/>
-      <c r="Y83" s="31" t="n"/>
-      <c r="Z83" s="31" t="n"/>
-      <c r="AA83" s="31" t="n"/>
-      <c r="AB83" s="31" t="n"/>
-      <c r="AC83" s="31" t="n"/>
-      <c r="AD83" s="31" t="n"/>
-      <c r="AE83" s="31" t="n"/>
-      <c r="AF83" s="31" t="n"/>
-      <c r="AG83" s="31" t="n"/>
-      <c r="AH83" s="31" t="n"/>
-      <c r="AI83" s="31" t="n"/>
-      <c r="AJ83" s="31" t="n"/>
-      <c r="AK83" s="31" t="n"/>
-      <c r="AL83" s="31" t="n"/>
-      <c r="AM83" s="31" t="n"/>
-      <c r="AN83" s="31" t="n"/>
-      <c r="AO83" s="31" t="n"/>
-      <c r="AP83" s="31" t="n"/>
-      <c r="AQ83" s="31" t="n"/>
-      <c r="AR83" s="31" t="n"/>
-      <c r="AS83" s="31" t="n"/>
-      <c r="AT83" s="31" t="n"/>
-      <c r="AU83" s="31" t="n"/>
-      <c r="AV83" s="31" t="n"/>
-      <c r="AW83" s="31" t="n"/>
-      <c r="AX83" s="31" t="n"/>
-      <c r="AY83" s="31" t="n"/>
-      <c r="AZ83" s="31" t="n"/>
-      <c r="BA83" s="31" t="n"/>
-      <c r="BB83" s="23" t="n">
-        <v>10</v>
-      </c>
+      <c r="D83" s="22">
+        <f>IF('时间节点计划表'!E42="","",'时间节点计划表'!E42)</f>
+        <v/>
+      </c>
+      <c r="E83" s="22">
+        <f>IF('时间节点计划表'!F42="","",'时间节点计划表'!F42)</f>
+        <v/>
+      </c>
+      <c r="F83" s="23" t="inlineStr"/>
+      <c r="G83" s="24" t="n"/>
+      <c r="H83" s="24" t="n"/>
+      <c r="I83" s="24" t="n"/>
+      <c r="J83" s="24" t="n"/>
+      <c r="K83" s="24" t="n"/>
+      <c r="L83" s="24" t="n"/>
+      <c r="M83" s="24" t="n"/>
+      <c r="N83" s="24" t="n"/>
+      <c r="O83" s="24" t="n"/>
+      <c r="P83" s="24" t="n"/>
+      <c r="Q83" s="24" t="n"/>
+      <c r="R83" s="24" t="n"/>
+      <c r="S83" s="24" t="n"/>
+      <c r="T83" s="24" t="n"/>
+      <c r="U83" s="24" t="n"/>
+      <c r="V83" s="24" t="n"/>
+      <c r="W83" s="24" t="n"/>
+      <c r="X83" s="24" t="n"/>
+      <c r="Y83" s="24" t="n"/>
+      <c r="Z83" s="24" t="n"/>
+      <c r="AA83" s="24" t="n"/>
+      <c r="AB83" s="24" t="n"/>
+      <c r="AC83" s="24" t="n"/>
+      <c r="AD83" s="24" t="n"/>
+      <c r="AE83" s="24" t="n"/>
+      <c r="AF83" s="24" t="n"/>
+      <c r="AG83" s="24" t="n"/>
+      <c r="AH83" s="24" t="n"/>
+      <c r="AI83" s="24" t="n"/>
+      <c r="AJ83" s="24" t="n"/>
+      <c r="AK83" s="24" t="n"/>
+      <c r="AL83" s="24" t="n"/>
+      <c r="AM83" s="24" t="n"/>
+      <c r="AN83" s="24" t="n"/>
+      <c r="AO83" s="24" t="n"/>
+      <c r="AP83" s="24" t="n"/>
+      <c r="AQ83" s="24" t="n"/>
+      <c r="AR83" s="24" t="n"/>
+      <c r="AS83" s="24" t="n"/>
+      <c r="AT83" s="24" t="n"/>
+      <c r="AU83" s="24" t="n"/>
+      <c r="AV83" s="24" t="n"/>
+      <c r="AW83" s="24" t="n"/>
+      <c r="AX83" s="24" t="n"/>
+      <c r="AY83" s="24" t="n"/>
+      <c r="AZ83" s="24" t="n"/>
+      <c r="BA83" s="24" t="n"/>
+      <c r="BB83" s="24" t="n"/>
       <c r="BC83" s="24" t="n"/>
       <c r="BD83" s="24" t="n"/>
       <c r="BE83" s="24" t="n"/>
@@ -9969,7 +9747,7 @@
       <c r="BN83" s="24" t="n"/>
       <c r="BO83" s="24" t="n"/>
     </row>
-    <row r="84" ht="16" customHeight="1">
+    <row r="84" ht="18" customHeight="1">
       <c r="A84" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -9985,38 +9763,33 @@
           <t>PAB220·工装实物到位</t>
         </is>
       </c>
-      <c r="D84" s="27" t="n">
-        <v>46305</v>
-      </c>
-      <c r="E84" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F84" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G84" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H84" s="29" t="n"/>
-      <c r="I84" s="29" t="n"/>
-      <c r="J84" s="29" t="n"/>
-      <c r="K84" s="29" t="n"/>
-      <c r="L84" s="29" t="n"/>
-      <c r="M84" s="29" t="n"/>
-      <c r="N84" s="29" t="n"/>
-      <c r="O84" s="29" t="n"/>
-      <c r="P84" s="29" t="n"/>
-      <c r="Q84" s="29" t="n"/>
-      <c r="R84" s="29" t="n"/>
-      <c r="S84" s="29" t="n"/>
-      <c r="T84" s="29" t="n"/>
-      <c r="U84" s="30" t="n"/>
+      <c r="D84" s="27">
+        <f>IF('时间节点计划表'!E42="","",'时间节点计划表'!E42)</f>
+        <v/>
+      </c>
+      <c r="E84" s="27">
+        <f>IF('时间节点计划表'!F42="","",'时间节点计划表'!F42)</f>
+        <v/>
+      </c>
+      <c r="F84" s="28">
+        <f>IF(OR(D84="",E84=""),"待填",E84-D84)</f>
+        <v/>
+      </c>
+      <c r="G84" s="24" t="n"/>
+      <c r="H84" s="24" t="n"/>
+      <c r="I84" s="24" t="n"/>
+      <c r="J84" s="24" t="n"/>
+      <c r="K84" s="24" t="n"/>
+      <c r="L84" s="24" t="n"/>
+      <c r="M84" s="24" t="n"/>
+      <c r="N84" s="24" t="n"/>
+      <c r="O84" s="24" t="n"/>
+      <c r="P84" s="24" t="n"/>
+      <c r="Q84" s="24" t="n"/>
+      <c r="R84" s="24" t="n"/>
+      <c r="S84" s="24" t="n"/>
+      <c r="T84" s="24" t="n"/>
+      <c r="U84" s="24" t="n"/>
       <c r="V84" s="24" t="n"/>
       <c r="W84" s="24" t="n"/>
       <c r="X84" s="24" t="n"/>
@@ -10064,7 +9837,7 @@
       <c r="BN84" s="24" t="n"/>
       <c r="BO84" s="24" t="n"/>
     </row>
-    <row r="85" ht="16" customHeight="1">
+    <row r="85" ht="18" customHeight="1">
       <c r="A85" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -10080,80 +9853,78 @@
           <t>PAB220·排针机安装调试</t>
         </is>
       </c>
-      <c r="D85" s="22" t="n">
-        <v>46315</v>
-      </c>
-      <c r="E85" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F85" s="20" t="inlineStr"/>
-      <c r="G85" s="31" t="n"/>
-      <c r="H85" s="31" t="n"/>
-      <c r="I85" s="31" t="n"/>
-      <c r="J85" s="31" t="n"/>
-      <c r="K85" s="31" t="n"/>
-      <c r="L85" s="31" t="n"/>
-      <c r="M85" s="31" t="n"/>
-      <c r="N85" s="31" t="n"/>
-      <c r="O85" s="31" t="n"/>
-      <c r="P85" s="31" t="n"/>
-      <c r="Q85" s="31" t="n"/>
-      <c r="R85" s="31" t="n"/>
-      <c r="S85" s="31" t="n"/>
-      <c r="T85" s="31" t="n"/>
-      <c r="U85" s="31" t="n"/>
-      <c r="V85" s="31" t="n"/>
-      <c r="W85" s="31" t="n"/>
-      <c r="X85" s="31" t="n"/>
-      <c r="Y85" s="31" t="n"/>
-      <c r="Z85" s="31" t="n"/>
-      <c r="AA85" s="31" t="n"/>
-      <c r="AB85" s="31" t="n"/>
-      <c r="AC85" s="31" t="n"/>
-      <c r="AD85" s="31" t="n"/>
-      <c r="AE85" s="31" t="n"/>
-      <c r="AF85" s="31" t="n"/>
-      <c r="AG85" s="31" t="n"/>
-      <c r="AH85" s="31" t="n"/>
-      <c r="AI85" s="31" t="n"/>
-      <c r="AJ85" s="31" t="n"/>
-      <c r="AK85" s="31" t="n"/>
-      <c r="AL85" s="31" t="n"/>
-      <c r="AM85" s="31" t="n"/>
-      <c r="AN85" s="31" t="n"/>
-      <c r="AO85" s="31" t="n"/>
-      <c r="AP85" s="31" t="n"/>
-      <c r="AQ85" s="31" t="n"/>
-      <c r="AR85" s="31" t="n"/>
-      <c r="AS85" s="31" t="n"/>
-      <c r="AT85" s="31" t="n"/>
-      <c r="AU85" s="31" t="n"/>
-      <c r="AV85" s="31" t="n"/>
-      <c r="AW85" s="31" t="n"/>
-      <c r="AX85" s="31" t="n"/>
-      <c r="AY85" s="31" t="n"/>
-      <c r="AZ85" s="31" t="n"/>
-      <c r="BA85" s="31" t="n"/>
-      <c r="BB85" s="31" t="n"/>
-      <c r="BC85" s="31" t="n"/>
-      <c r="BD85" s="31" t="n"/>
-      <c r="BE85" s="31" t="n"/>
-      <c r="BF85" s="31" t="n"/>
-      <c r="BG85" s="31" t="n"/>
-      <c r="BH85" s="31" t="n"/>
-      <c r="BI85" s="31" t="n"/>
-      <c r="BJ85" s="31" t="n"/>
-      <c r="BK85" s="31" t="n"/>
-      <c r="BL85" s="23" t="n">
-        <v>20</v>
-      </c>
+      <c r="D85" s="22">
+        <f>IF('时间节点计划表'!E43="","",'时间节点计划表'!E43)</f>
+        <v/>
+      </c>
+      <c r="E85" s="22">
+        <f>IF('时间节点计划表'!F43="","",'时间节点计划表'!F43)</f>
+        <v/>
+      </c>
+      <c r="F85" s="23" t="inlineStr"/>
+      <c r="G85" s="24" t="n"/>
+      <c r="H85" s="24" t="n"/>
+      <c r="I85" s="24" t="n"/>
+      <c r="J85" s="24" t="n"/>
+      <c r="K85" s="24" t="n"/>
+      <c r="L85" s="24" t="n"/>
+      <c r="M85" s="24" t="n"/>
+      <c r="N85" s="24" t="n"/>
+      <c r="O85" s="24" t="n"/>
+      <c r="P85" s="24" t="n"/>
+      <c r="Q85" s="24" t="n"/>
+      <c r="R85" s="24" t="n"/>
+      <c r="S85" s="24" t="n"/>
+      <c r="T85" s="24" t="n"/>
+      <c r="U85" s="24" t="n"/>
+      <c r="V85" s="24" t="n"/>
+      <c r="W85" s="24" t="n"/>
+      <c r="X85" s="24" t="n"/>
+      <c r="Y85" s="24" t="n"/>
+      <c r="Z85" s="24" t="n"/>
+      <c r="AA85" s="24" t="n"/>
+      <c r="AB85" s="24" t="n"/>
+      <c r="AC85" s="24" t="n"/>
+      <c r="AD85" s="24" t="n"/>
+      <c r="AE85" s="24" t="n"/>
+      <c r="AF85" s="24" t="n"/>
+      <c r="AG85" s="24" t="n"/>
+      <c r="AH85" s="24" t="n"/>
+      <c r="AI85" s="24" t="n"/>
+      <c r="AJ85" s="24" t="n"/>
+      <c r="AK85" s="24" t="n"/>
+      <c r="AL85" s="24" t="n"/>
+      <c r="AM85" s="24" t="n"/>
+      <c r="AN85" s="24" t="n"/>
+      <c r="AO85" s="24" t="n"/>
+      <c r="AP85" s="24" t="n"/>
+      <c r="AQ85" s="24" t="n"/>
+      <c r="AR85" s="24" t="n"/>
+      <c r="AS85" s="24" t="n"/>
+      <c r="AT85" s="24" t="n"/>
+      <c r="AU85" s="24" t="n"/>
+      <c r="AV85" s="24" t="n"/>
+      <c r="AW85" s="24" t="n"/>
+      <c r="AX85" s="24" t="n"/>
+      <c r="AY85" s="24" t="n"/>
+      <c r="AZ85" s="24" t="n"/>
+      <c r="BA85" s="24" t="n"/>
+      <c r="BB85" s="24" t="n"/>
+      <c r="BC85" s="24" t="n"/>
+      <c r="BD85" s="24" t="n"/>
+      <c r="BE85" s="24" t="n"/>
+      <c r="BF85" s="24" t="n"/>
+      <c r="BG85" s="24" t="n"/>
+      <c r="BH85" s="24" t="n"/>
+      <c r="BI85" s="24" t="n"/>
+      <c r="BJ85" s="24" t="n"/>
+      <c r="BK85" s="24" t="n"/>
+      <c r="BL85" s="24" t="n"/>
       <c r="BM85" s="24" t="n"/>
       <c r="BN85" s="24" t="n"/>
       <c r="BO85" s="24" t="n"/>
     </row>
-    <row r="86" ht="16" customHeight="1">
+    <row r="86" ht="18" customHeight="1">
       <c r="A86" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -10169,38 +9940,33 @@
           <t>PAB220·排针机安装调试</t>
         </is>
       </c>
-      <c r="D86" s="27" t="n">
-        <v>46315</v>
-      </c>
-      <c r="E86" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F86" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G86" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H86" s="29" t="n"/>
-      <c r="I86" s="29" t="n"/>
-      <c r="J86" s="29" t="n"/>
-      <c r="K86" s="29" t="n"/>
-      <c r="L86" s="29" t="n"/>
-      <c r="M86" s="29" t="n"/>
-      <c r="N86" s="29" t="n"/>
-      <c r="O86" s="29" t="n"/>
-      <c r="P86" s="29" t="n"/>
-      <c r="Q86" s="29" t="n"/>
-      <c r="R86" s="29" t="n"/>
-      <c r="S86" s="29" t="n"/>
-      <c r="T86" s="29" t="n"/>
-      <c r="U86" s="30" t="n"/>
+      <c r="D86" s="27">
+        <f>IF('时间节点计划表'!E43="","",'时间节点计划表'!E43)</f>
+        <v/>
+      </c>
+      <c r="E86" s="27">
+        <f>IF('时间节点计划表'!F43="","",'时间节点计划表'!F43)</f>
+        <v/>
+      </c>
+      <c r="F86" s="28">
+        <f>IF(OR(D86="",E86=""),"待填",E86-D86)</f>
+        <v/>
+      </c>
+      <c r="G86" s="24" t="n"/>
+      <c r="H86" s="24" t="n"/>
+      <c r="I86" s="24" t="n"/>
+      <c r="J86" s="24" t="n"/>
+      <c r="K86" s="24" t="n"/>
+      <c r="L86" s="24" t="n"/>
+      <c r="M86" s="24" t="n"/>
+      <c r="N86" s="24" t="n"/>
+      <c r="O86" s="24" t="n"/>
+      <c r="P86" s="24" t="n"/>
+      <c r="Q86" s="24" t="n"/>
+      <c r="R86" s="24" t="n"/>
+      <c r="S86" s="24" t="n"/>
+      <c r="T86" s="24" t="n"/>
+      <c r="U86" s="24" t="n"/>
       <c r="V86" s="24" t="n"/>
       <c r="W86" s="24" t="n"/>
       <c r="X86" s="24" t="n"/>
@@ -10248,7 +10014,7 @@
       <c r="BN86" s="24" t="n"/>
       <c r="BO86" s="24" t="n"/>
     </row>
-    <row r="87" ht="16" customHeight="1">
+    <row r="87" ht="18" customHeight="1">
       <c r="A87" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -10264,80 +10030,78 @@
           <t>PAB220·单级样机</t>
         </is>
       </c>
-      <c r="D87" s="22" t="n">
-        <v>46316</v>
-      </c>
-      <c r="E87" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F87" s="20" t="inlineStr"/>
-      <c r="G87" s="31" t="n"/>
-      <c r="H87" s="31" t="n"/>
-      <c r="I87" s="31" t="n"/>
-      <c r="J87" s="31" t="n"/>
-      <c r="K87" s="31" t="n"/>
-      <c r="L87" s="31" t="n"/>
-      <c r="M87" s="31" t="n"/>
-      <c r="N87" s="31" t="n"/>
-      <c r="O87" s="31" t="n"/>
-      <c r="P87" s="31" t="n"/>
-      <c r="Q87" s="31" t="n"/>
-      <c r="R87" s="31" t="n"/>
-      <c r="S87" s="31" t="n"/>
-      <c r="T87" s="31" t="n"/>
-      <c r="U87" s="31" t="n"/>
-      <c r="V87" s="31" t="n"/>
-      <c r="W87" s="31" t="n"/>
-      <c r="X87" s="31" t="n"/>
-      <c r="Y87" s="31" t="n"/>
-      <c r="Z87" s="31" t="n"/>
-      <c r="AA87" s="31" t="n"/>
-      <c r="AB87" s="31" t="n"/>
-      <c r="AC87" s="31" t="n"/>
-      <c r="AD87" s="31" t="n"/>
-      <c r="AE87" s="31" t="n"/>
-      <c r="AF87" s="31" t="n"/>
-      <c r="AG87" s="31" t="n"/>
-      <c r="AH87" s="31" t="n"/>
-      <c r="AI87" s="31" t="n"/>
-      <c r="AJ87" s="31" t="n"/>
-      <c r="AK87" s="31" t="n"/>
-      <c r="AL87" s="31" t="n"/>
-      <c r="AM87" s="31" t="n"/>
-      <c r="AN87" s="31" t="n"/>
-      <c r="AO87" s="31" t="n"/>
-      <c r="AP87" s="31" t="n"/>
-      <c r="AQ87" s="31" t="n"/>
-      <c r="AR87" s="31" t="n"/>
-      <c r="AS87" s="31" t="n"/>
-      <c r="AT87" s="31" t="n"/>
-      <c r="AU87" s="31" t="n"/>
-      <c r="AV87" s="31" t="n"/>
-      <c r="AW87" s="31" t="n"/>
-      <c r="AX87" s="31" t="n"/>
-      <c r="AY87" s="31" t="n"/>
-      <c r="AZ87" s="31" t="n"/>
-      <c r="BA87" s="31" t="n"/>
-      <c r="BB87" s="31" t="n"/>
-      <c r="BC87" s="31" t="n"/>
-      <c r="BD87" s="31" t="n"/>
-      <c r="BE87" s="31" t="n"/>
-      <c r="BF87" s="31" t="n"/>
-      <c r="BG87" s="31" t="n"/>
-      <c r="BH87" s="31" t="n"/>
-      <c r="BI87" s="31" t="n"/>
-      <c r="BJ87" s="31" t="n"/>
-      <c r="BK87" s="31" t="n"/>
-      <c r="BL87" s="31" t="n"/>
-      <c r="BM87" s="23" t="n">
-        <v>21</v>
-      </c>
+      <c r="D87" s="22">
+        <f>IF('时间节点计划表'!E44="","",'时间节点计划表'!E44)</f>
+        <v/>
+      </c>
+      <c r="E87" s="22">
+        <f>IF('时间节点计划表'!F44="","",'时间节点计划表'!F44)</f>
+        <v/>
+      </c>
+      <c r="F87" s="23" t="inlineStr"/>
+      <c r="G87" s="24" t="n"/>
+      <c r="H87" s="24" t="n"/>
+      <c r="I87" s="24" t="n"/>
+      <c r="J87" s="24" t="n"/>
+      <c r="K87" s="24" t="n"/>
+      <c r="L87" s="24" t="n"/>
+      <c r="M87" s="24" t="n"/>
+      <c r="N87" s="24" t="n"/>
+      <c r="O87" s="24" t="n"/>
+      <c r="P87" s="24" t="n"/>
+      <c r="Q87" s="24" t="n"/>
+      <c r="R87" s="24" t="n"/>
+      <c r="S87" s="24" t="n"/>
+      <c r="T87" s="24" t="n"/>
+      <c r="U87" s="24" t="n"/>
+      <c r="V87" s="24" t="n"/>
+      <c r="W87" s="24" t="n"/>
+      <c r="X87" s="24" t="n"/>
+      <c r="Y87" s="24" t="n"/>
+      <c r="Z87" s="24" t="n"/>
+      <c r="AA87" s="24" t="n"/>
+      <c r="AB87" s="24" t="n"/>
+      <c r="AC87" s="24" t="n"/>
+      <c r="AD87" s="24" t="n"/>
+      <c r="AE87" s="24" t="n"/>
+      <c r="AF87" s="24" t="n"/>
+      <c r="AG87" s="24" t="n"/>
+      <c r="AH87" s="24" t="n"/>
+      <c r="AI87" s="24" t="n"/>
+      <c r="AJ87" s="24" t="n"/>
+      <c r="AK87" s="24" t="n"/>
+      <c r="AL87" s="24" t="n"/>
+      <c r="AM87" s="24" t="n"/>
+      <c r="AN87" s="24" t="n"/>
+      <c r="AO87" s="24" t="n"/>
+      <c r="AP87" s="24" t="n"/>
+      <c r="AQ87" s="24" t="n"/>
+      <c r="AR87" s="24" t="n"/>
+      <c r="AS87" s="24" t="n"/>
+      <c r="AT87" s="24" t="n"/>
+      <c r="AU87" s="24" t="n"/>
+      <c r="AV87" s="24" t="n"/>
+      <c r="AW87" s="24" t="n"/>
+      <c r="AX87" s="24" t="n"/>
+      <c r="AY87" s="24" t="n"/>
+      <c r="AZ87" s="24" t="n"/>
+      <c r="BA87" s="24" t="n"/>
+      <c r="BB87" s="24" t="n"/>
+      <c r="BC87" s="24" t="n"/>
+      <c r="BD87" s="24" t="n"/>
+      <c r="BE87" s="24" t="n"/>
+      <c r="BF87" s="24" t="n"/>
+      <c r="BG87" s="24" t="n"/>
+      <c r="BH87" s="24" t="n"/>
+      <c r="BI87" s="24" t="n"/>
+      <c r="BJ87" s="24" t="n"/>
+      <c r="BK87" s="24" t="n"/>
+      <c r="BL87" s="24" t="n"/>
+      <c r="BM87" s="24" t="n"/>
       <c r="BN87" s="24" t="n"/>
       <c r="BO87" s="24" t="n"/>
     </row>
-    <row r="88" ht="16" customHeight="1">
+    <row r="88" ht="18" customHeight="1">
       <c r="A88" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -10353,38 +10117,33 @@
           <t>PAB220·单级样机</t>
         </is>
       </c>
-      <c r="D88" s="27" t="n">
-        <v>46316</v>
-      </c>
-      <c r="E88" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F88" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G88" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H88" s="29" t="n"/>
-      <c r="I88" s="29" t="n"/>
-      <c r="J88" s="29" t="n"/>
-      <c r="K88" s="29" t="n"/>
-      <c r="L88" s="29" t="n"/>
-      <c r="M88" s="29" t="n"/>
-      <c r="N88" s="29" t="n"/>
-      <c r="O88" s="29" t="n"/>
-      <c r="P88" s="29" t="n"/>
-      <c r="Q88" s="29" t="n"/>
-      <c r="R88" s="29" t="n"/>
-      <c r="S88" s="29" t="n"/>
-      <c r="T88" s="29" t="n"/>
-      <c r="U88" s="30" t="n"/>
+      <c r="D88" s="27">
+        <f>IF('时间节点计划表'!E44="","",'时间节点计划表'!E44)</f>
+        <v/>
+      </c>
+      <c r="E88" s="27">
+        <f>IF('时间节点计划表'!F44="","",'时间节点计划表'!F44)</f>
+        <v/>
+      </c>
+      <c r="F88" s="28">
+        <f>IF(OR(D88="",E88=""),"待填",E88-D88)</f>
+        <v/>
+      </c>
+      <c r="G88" s="24" t="n"/>
+      <c r="H88" s="24" t="n"/>
+      <c r="I88" s="24" t="n"/>
+      <c r="J88" s="24" t="n"/>
+      <c r="K88" s="24" t="n"/>
+      <c r="L88" s="24" t="n"/>
+      <c r="M88" s="24" t="n"/>
+      <c r="N88" s="24" t="n"/>
+      <c r="O88" s="24" t="n"/>
+      <c r="P88" s="24" t="n"/>
+      <c r="Q88" s="24" t="n"/>
+      <c r="R88" s="24" t="n"/>
+      <c r="S88" s="24" t="n"/>
+      <c r="T88" s="24" t="n"/>
+      <c r="U88" s="24" t="n"/>
       <c r="V88" s="24" t="n"/>
       <c r="W88" s="24" t="n"/>
       <c r="X88" s="24" t="n"/>
@@ -10432,7 +10191,7 @@
       <c r="BN88" s="24" t="n"/>
       <c r="BO88" s="24" t="n"/>
     </row>
-    <row r="89" ht="16" customHeight="1">
+    <row r="89" ht="18" customHeight="1">
       <c r="A89" s="20" t="inlineStr">
         <is>
           <t>预估</t>
@@ -10448,80 +10207,78 @@
           <t>PAB220·双级样机</t>
         </is>
       </c>
-      <c r="D89" s="22" t="n">
-        <v>46318</v>
-      </c>
-      <c r="E89" s="20" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F89" s="20" t="inlineStr"/>
-      <c r="G89" s="31" t="n"/>
-      <c r="H89" s="31" t="n"/>
-      <c r="I89" s="31" t="n"/>
-      <c r="J89" s="31" t="n"/>
-      <c r="K89" s="31" t="n"/>
-      <c r="L89" s="31" t="n"/>
-      <c r="M89" s="31" t="n"/>
-      <c r="N89" s="31" t="n"/>
-      <c r="O89" s="31" t="n"/>
-      <c r="P89" s="31" t="n"/>
-      <c r="Q89" s="31" t="n"/>
-      <c r="R89" s="31" t="n"/>
-      <c r="S89" s="31" t="n"/>
-      <c r="T89" s="31" t="n"/>
-      <c r="U89" s="31" t="n"/>
-      <c r="V89" s="31" t="n"/>
-      <c r="W89" s="31" t="n"/>
-      <c r="X89" s="31" t="n"/>
-      <c r="Y89" s="31" t="n"/>
-      <c r="Z89" s="31" t="n"/>
-      <c r="AA89" s="31" t="n"/>
-      <c r="AB89" s="31" t="n"/>
-      <c r="AC89" s="31" t="n"/>
-      <c r="AD89" s="31" t="n"/>
-      <c r="AE89" s="31" t="n"/>
-      <c r="AF89" s="31" t="n"/>
-      <c r="AG89" s="31" t="n"/>
-      <c r="AH89" s="31" t="n"/>
-      <c r="AI89" s="31" t="n"/>
-      <c r="AJ89" s="31" t="n"/>
-      <c r="AK89" s="31" t="n"/>
-      <c r="AL89" s="31" t="n"/>
-      <c r="AM89" s="31" t="n"/>
-      <c r="AN89" s="31" t="n"/>
-      <c r="AO89" s="31" t="n"/>
-      <c r="AP89" s="31" t="n"/>
-      <c r="AQ89" s="31" t="n"/>
-      <c r="AR89" s="31" t="n"/>
-      <c r="AS89" s="31" t="n"/>
-      <c r="AT89" s="31" t="n"/>
-      <c r="AU89" s="31" t="n"/>
-      <c r="AV89" s="31" t="n"/>
-      <c r="AW89" s="31" t="n"/>
-      <c r="AX89" s="31" t="n"/>
-      <c r="AY89" s="31" t="n"/>
-      <c r="AZ89" s="31" t="n"/>
-      <c r="BA89" s="31" t="n"/>
-      <c r="BB89" s="31" t="n"/>
-      <c r="BC89" s="31" t="n"/>
-      <c r="BD89" s="31" t="n"/>
-      <c r="BE89" s="31" t="n"/>
-      <c r="BF89" s="31" t="n"/>
-      <c r="BG89" s="31" t="n"/>
-      <c r="BH89" s="31" t="n"/>
-      <c r="BI89" s="31" t="n"/>
-      <c r="BJ89" s="31" t="n"/>
-      <c r="BK89" s="31" t="n"/>
-      <c r="BL89" s="31" t="n"/>
-      <c r="BM89" s="31" t="n"/>
-      <c r="BN89" s="31" t="n"/>
-      <c r="BO89" s="23" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
+      <c r="D89" s="22">
+        <f>IF('时间节点计划表'!E45="","",'时间节点计划表'!E45)</f>
+        <v/>
+      </c>
+      <c r="E89" s="22">
+        <f>IF('时间节点计划表'!F45="","",'时间节点计划表'!F45)</f>
+        <v/>
+      </c>
+      <c r="F89" s="23" t="inlineStr"/>
+      <c r="G89" s="24" t="n"/>
+      <c r="H89" s="24" t="n"/>
+      <c r="I89" s="24" t="n"/>
+      <c r="J89" s="24" t="n"/>
+      <c r="K89" s="24" t="n"/>
+      <c r="L89" s="24" t="n"/>
+      <c r="M89" s="24" t="n"/>
+      <c r="N89" s="24" t="n"/>
+      <c r="O89" s="24" t="n"/>
+      <c r="P89" s="24" t="n"/>
+      <c r="Q89" s="24" t="n"/>
+      <c r="R89" s="24" t="n"/>
+      <c r="S89" s="24" t="n"/>
+      <c r="T89" s="24" t="n"/>
+      <c r="U89" s="24" t="n"/>
+      <c r="V89" s="24" t="n"/>
+      <c r="W89" s="24" t="n"/>
+      <c r="X89" s="24" t="n"/>
+      <c r="Y89" s="24" t="n"/>
+      <c r="Z89" s="24" t="n"/>
+      <c r="AA89" s="24" t="n"/>
+      <c r="AB89" s="24" t="n"/>
+      <c r="AC89" s="24" t="n"/>
+      <c r="AD89" s="24" t="n"/>
+      <c r="AE89" s="24" t="n"/>
+      <c r="AF89" s="24" t="n"/>
+      <c r="AG89" s="24" t="n"/>
+      <c r="AH89" s="24" t="n"/>
+      <c r="AI89" s="24" t="n"/>
+      <c r="AJ89" s="24" t="n"/>
+      <c r="AK89" s="24" t="n"/>
+      <c r="AL89" s="24" t="n"/>
+      <c r="AM89" s="24" t="n"/>
+      <c r="AN89" s="24" t="n"/>
+      <c r="AO89" s="24" t="n"/>
+      <c r="AP89" s="24" t="n"/>
+      <c r="AQ89" s="24" t="n"/>
+      <c r="AR89" s="24" t="n"/>
+      <c r="AS89" s="24" t="n"/>
+      <c r="AT89" s="24" t="n"/>
+      <c r="AU89" s="24" t="n"/>
+      <c r="AV89" s="24" t="n"/>
+      <c r="AW89" s="24" t="n"/>
+      <c r="AX89" s="24" t="n"/>
+      <c r="AY89" s="24" t="n"/>
+      <c r="AZ89" s="24" t="n"/>
+      <c r="BA89" s="24" t="n"/>
+      <c r="BB89" s="24" t="n"/>
+      <c r="BC89" s="24" t="n"/>
+      <c r="BD89" s="24" t="n"/>
+      <c r="BE89" s="24" t="n"/>
+      <c r="BF89" s="24" t="n"/>
+      <c r="BG89" s="24" t="n"/>
+      <c r="BH89" s="24" t="n"/>
+      <c r="BI89" s="24" t="n"/>
+      <c r="BJ89" s="24" t="n"/>
+      <c r="BK89" s="24" t="n"/>
+      <c r="BL89" s="24" t="n"/>
+      <c r="BM89" s="24" t="n"/>
+      <c r="BN89" s="24" t="n"/>
+      <c r="BO89" s="24" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
       <c r="A90" s="25" t="inlineStr">
         <is>
           <t>实际</t>
@@ -10537,38 +10294,33 @@
           <t>PAB220·双级样机</t>
         </is>
       </c>
-      <c r="D90" s="27" t="n">
-        <v>46318</v>
-      </c>
-      <c r="E90" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="F90" s="25" t="inlineStr">
-        <is>
-          <t>待填</t>
-        </is>
-      </c>
-      <c r="G90" s="28" t="inlineStr">
-        <is>
-          <t>待填（尚无实际完成日期）</t>
-        </is>
-      </c>
-      <c r="H90" s="29" t="n"/>
-      <c r="I90" s="29" t="n"/>
-      <c r="J90" s="29" t="n"/>
-      <c r="K90" s="29" t="n"/>
-      <c r="L90" s="29" t="n"/>
-      <c r="M90" s="29" t="n"/>
-      <c r="N90" s="29" t="n"/>
-      <c r="O90" s="29" t="n"/>
-      <c r="P90" s="29" t="n"/>
-      <c r="Q90" s="29" t="n"/>
-      <c r="R90" s="29" t="n"/>
-      <c r="S90" s="29" t="n"/>
-      <c r="T90" s="29" t="n"/>
-      <c r="U90" s="30" t="n"/>
+      <c r="D90" s="27">
+        <f>IF('时间节点计划表'!E45="","",'时间节点计划表'!E45)</f>
+        <v/>
+      </c>
+      <c r="E90" s="27">
+        <f>IF('时间节点计划表'!F45="","",'时间节点计划表'!F45)</f>
+        <v/>
+      </c>
+      <c r="F90" s="28">
+        <f>IF(OR(D90="",E90=""),"待填",E90-D90)</f>
+        <v/>
+      </c>
+      <c r="G90" s="24" t="n"/>
+      <c r="H90" s="24" t="n"/>
+      <c r="I90" s="24" t="n"/>
+      <c r="J90" s="24" t="n"/>
+      <c r="K90" s="24" t="n"/>
+      <c r="L90" s="24" t="n"/>
+      <c r="M90" s="24" t="n"/>
+      <c r="N90" s="24" t="n"/>
+      <c r="O90" s="24" t="n"/>
+      <c r="P90" s="24" t="n"/>
+      <c r="Q90" s="24" t="n"/>
+      <c r="R90" s="24" t="n"/>
+      <c r="S90" s="24" t="n"/>
+      <c r="T90" s="24" t="n"/>
+      <c r="U90" s="24" t="n"/>
       <c r="V90" s="24" t="n"/>
       <c r="W90" s="24" t="n"/>
       <c r="X90" s="24" t="n"/>
@@ -10616,85 +10368,93 @@
       <c r="BN90" s="24" t="n"/>
       <c r="BO90" s="24" t="n"/>
     </row>
-    <row r="92" ht="32" customHeight="1">
+    <row r="92" ht="36" customHeight="1">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>图例：蓝条=预估（从项目首日铺到预估完成日，格数=日历天数）；橙/红/绿=实际（准时/延期/提前）。未填实际完成节点时显示「待填」。深色列为周末。</t>
-        </is>
-      </c>
-      <c r="G92" s="32" t="inlineStr">
+          <t>用法：在主表填写日期即可，本表色条自动变长/变色，不要手工涂格子。蓝条=预估（项目首日→预估完成日）；橙/红/绿=实际（准时/延期/提前）。实际未填时无色条。</t>
+        </is>
+      </c>
+      <c r="G92" s="29" t="inlineStr">
         <is>
           <t>预估</t>
         </is>
       </c>
-      <c r="K92" s="33" t="inlineStr">
+      <c r="K92" s="30" t="inlineStr">
         <is>
           <t>实际·准时</t>
         </is>
       </c>
-      <c r="O92" s="34" t="inlineStr">
+      <c r="O92" s="31" t="inlineStr">
         <is>
           <t>实际·延期</t>
         </is>
       </c>
-      <c r="S92" s="35" t="inlineStr">
+      <c r="S92" s="32" t="inlineStr">
         <is>
           <t>实际·提前</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="G82:U82"/>
-    <mergeCell ref="G38:U38"/>
-    <mergeCell ref="G10:U10"/>
-    <mergeCell ref="G28:U28"/>
-    <mergeCell ref="G66:U66"/>
-    <mergeCell ref="G6:U6"/>
-    <mergeCell ref="G62:U62"/>
-    <mergeCell ref="O1:AR1"/>
-    <mergeCell ref="G18:U18"/>
-    <mergeCell ref="G34:U34"/>
-    <mergeCell ref="G78:U78"/>
-    <mergeCell ref="G74:U74"/>
+  <mergeCells count="5">
     <mergeCell ref="AS1:BO1"/>
-    <mergeCell ref="G30:U30"/>
-    <mergeCell ref="G68:U68"/>
-    <mergeCell ref="G24:U24"/>
-    <mergeCell ref="G58:U58"/>
-    <mergeCell ref="G14:U14"/>
-    <mergeCell ref="G80:U80"/>
-    <mergeCell ref="G4:U4"/>
-    <mergeCell ref="G88:U88"/>
-    <mergeCell ref="G26:U26"/>
-    <mergeCell ref="G20:U20"/>
-    <mergeCell ref="G64:U64"/>
-    <mergeCell ref="G76:U76"/>
-    <mergeCell ref="G16:U16"/>
-    <mergeCell ref="G54:U54"/>
-    <mergeCell ref="G32:U32"/>
-    <mergeCell ref="G50:U50"/>
-    <mergeCell ref="G44:U44"/>
-    <mergeCell ref="G46:U46"/>
-    <mergeCell ref="G22:U22"/>
-    <mergeCell ref="G60:U60"/>
-    <mergeCell ref="G84:U84"/>
-    <mergeCell ref="G90:U90"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="G40:U40"/>
-    <mergeCell ref="G12:U12"/>
-    <mergeCell ref="G56:U56"/>
-    <mergeCell ref="G72:U72"/>
-    <mergeCell ref="G52:U52"/>
-    <mergeCell ref="G86:U86"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:N1"/>
-    <mergeCell ref="G36:U36"/>
-    <mergeCell ref="G42:U42"/>
-    <mergeCell ref="G70:U70"/>
-    <mergeCell ref="G8:U8"/>
-    <mergeCell ref="G48:U48"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="O1:AR1"/>
   </mergeCells>
+  <conditionalFormatting sqref="G3:BO90">
+    <cfRule type="expression" priority="1" dxfId="4">
+      <formula>AND($A3="预估",ISNUMBER($D3),G$2&gt;=$G$2,G$2&lt;=$D3)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="5">
+      <formula>AND($A3="实际",ISNUMBER($E3),G$2&gt;=$G$2,G$2&lt;=$E3,$E3=$D3)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="6">
+      <formula>AND($A3="实际",ISNUMBER($E3),G$2&gt;=$G$2,G$2&lt;=$E3,$E3&gt;$D3)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="7">
+      <formula>AND($A3="实际",ISNUMBER($E3),G$2&gt;=$G$2,G$2&lt;=$E3,$E3&lt;$D3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A90">
+    <cfRule type="expression" priority="5" dxfId="8">
+      <formula>AND($A3="预估",ISNUMBER($D3))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="9">
+      <formula>AND($A3="实际",ISNUMBER($E3),$E3&gt;$D3)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="10">
+      <formula>AND($A3="实际",ISNUMBER($E3),$E3&lt;$D3)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="11">
+      <formula>AND($A3="实际",ISNUMBER($E3),$E3=$D3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D90">
+    <cfRule type="expression" priority="9" dxfId="8">
+      <formula>ISNUMBER(D3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E90">
+    <cfRule type="expression" priority="10" dxfId="9">
+      <formula>AND(ISNUMBER(E3),E3&gt;D3)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="10">
+      <formula>AND(ISNUMBER(E3),E3&lt;D3)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="11">
+      <formula>AND(ISNUMBER(E3),E3=D3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F90">
+    <cfRule type="expression" priority="13" dxfId="9">
+      <formula>AND(ISNUMBER(F3),F3&gt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="12">
+      <formula>AND(ISNUMBER(F3),F3&lt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8"/>
 </worksheet>

--- a/PAB产品计划表.xlsx
+++ b/PAB产品计划表.xlsx
@@ -325,7 +325,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="微软雅黑"/>
@@ -413,59 +413,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFA9D08E"/>
           <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <color rgb="001F2937"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD6EAF8"/>
-          <bgColor rgb="FFD6EAF8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <b val="1"/>
-        <color rgb="00991B1B"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFECACA"/>
-          <bgColor rgb="FFFECACA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <color rgb="0014532D"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBBF7D0"/>
-          <bgColor rgb="FFBBF7D0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <color rgb="001F2937"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFDE68A"/>
-          <bgColor rgb="FFFDE68A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3222,11 +3169,11 @@
         </is>
       </c>
       <c r="D3" s="23">
-        <f>IF('时间节点计划表'!E2="","",'时间节点计划表'!E2)</f>
+        <f>'时间节点计划表'!E2</f>
         <v/>
       </c>
       <c r="E3" s="23">
-        <f>IF('时间节点计划表'!F2="","",'时间节点计划表'!F2)</f>
+        <f>IF(COUNT('时间节点计划表'!F2),'时间节点计划表'!F2,"")</f>
         <v/>
       </c>
       <c r="F3" s="24" t="inlineStr"/>
@@ -3492,11 +3439,11 @@
         </is>
       </c>
       <c r="D4" s="28">
-        <f>IF('时间节点计划表'!E2="","",'时间节点计划表'!E2)</f>
+        <f>'时间节点计划表'!E2</f>
         <v/>
       </c>
       <c r="E4" s="28">
-        <f>IF('时间节点计划表'!F2="","",'时间节点计划表'!F2)</f>
+        <f>IF(COUNT('时间节点计划表'!F2),'时间节点计划表'!F2,"")</f>
         <v/>
       </c>
       <c r="F4" s="29">
@@ -3765,11 +3712,11 @@
         </is>
       </c>
       <c r="D5" s="23">
-        <f>IF('时间节点计划表'!E3="","",'时间节点计划表'!E3)</f>
+        <f>'时间节点计划表'!E3</f>
         <v/>
       </c>
       <c r="E5" s="23">
-        <f>IF('时间节点计划表'!F3="","",'时间节点计划表'!F3)</f>
+        <f>IF(COUNT('时间节点计划表'!F3),'时间节点计划表'!F3,"")</f>
         <v/>
       </c>
       <c r="F5" s="24" t="inlineStr"/>
@@ -4035,11 +3982,11 @@
         </is>
       </c>
       <c r="D6" s="28">
-        <f>IF('时间节点计划表'!E3="","",'时间节点计划表'!E3)</f>
+        <f>'时间节点计划表'!E3</f>
         <v/>
       </c>
       <c r="E6" s="28">
-        <f>IF('时间节点计划表'!F3="","",'时间节点计划表'!F3)</f>
+        <f>IF(COUNT('时间节点计划表'!F3),'时间节点计划表'!F3,"")</f>
         <v/>
       </c>
       <c r="F6" s="29">
@@ -4308,11 +4255,11 @@
         </is>
       </c>
       <c r="D7" s="23">
-        <f>IF('时间节点计划表'!E4="","",'时间节点计划表'!E4)</f>
+        <f>'时间节点计划表'!E4</f>
         <v/>
       </c>
       <c r="E7" s="23">
-        <f>IF('时间节点计划表'!F4="","",'时间节点计划表'!F4)</f>
+        <f>IF(COUNT('时间节点计划表'!F4),'时间节点计划表'!F4,"")</f>
         <v/>
       </c>
       <c r="F7" s="24" t="inlineStr"/>
@@ -4578,11 +4525,11 @@
         </is>
       </c>
       <c r="D8" s="28">
-        <f>IF('时间节点计划表'!E4="","",'时间节点计划表'!E4)</f>
+        <f>'时间节点计划表'!E4</f>
         <v/>
       </c>
       <c r="E8" s="28">
-        <f>IF('时间节点计划表'!F4="","",'时间节点计划表'!F4)</f>
+        <f>IF(COUNT('时间节点计划表'!F4),'时间节点计划表'!F4,"")</f>
         <v/>
       </c>
       <c r="F8" s="29">
@@ -4851,11 +4798,11 @@
         </is>
       </c>
       <c r="D9" s="23">
-        <f>IF('时间节点计划表'!E5="","",'时间节点计划表'!E5)</f>
+        <f>'时间节点计划表'!E5</f>
         <v/>
       </c>
       <c r="E9" s="23">
-        <f>IF('时间节点计划表'!F5="","",'时间节点计划表'!F5)</f>
+        <f>IF(COUNT('时间节点计划表'!F5),'时间节点计划表'!F5,"")</f>
         <v/>
       </c>
       <c r="F9" s="24" t="inlineStr"/>
@@ -5121,11 +5068,11 @@
         </is>
       </c>
       <c r="D10" s="28">
-        <f>IF('时间节点计划表'!E5="","",'时间节点计划表'!E5)</f>
+        <f>'时间节点计划表'!E5</f>
         <v/>
       </c>
       <c r="E10" s="28">
-        <f>IF('时间节点计划表'!F5="","",'时间节点计划表'!F5)</f>
+        <f>IF(COUNT('时间节点计划表'!F5),'时间节点计划表'!F5,"")</f>
         <v/>
       </c>
       <c r="F10" s="29">
@@ -5394,11 +5341,11 @@
         </is>
       </c>
       <c r="D11" s="23">
-        <f>IF('时间节点计划表'!E6="","",'时间节点计划表'!E6)</f>
+        <f>'时间节点计划表'!E6</f>
         <v/>
       </c>
       <c r="E11" s="23">
-        <f>IF('时间节点计划表'!F6="","",'时间节点计划表'!F6)</f>
+        <f>IF(COUNT('时间节点计划表'!F6),'时间节点计划表'!F6,"")</f>
         <v/>
       </c>
       <c r="F11" s="24" t="inlineStr"/>
@@ -5664,11 +5611,11 @@
         </is>
       </c>
       <c r="D12" s="28">
-        <f>IF('时间节点计划表'!E6="","",'时间节点计划表'!E6)</f>
+        <f>'时间节点计划表'!E6</f>
         <v/>
       </c>
       <c r="E12" s="28">
-        <f>IF('时间节点计划表'!F6="","",'时间节点计划表'!F6)</f>
+        <f>IF(COUNT('时间节点计划表'!F6),'时间节点计划表'!F6,"")</f>
         <v/>
       </c>
       <c r="F12" s="29">
@@ -5937,11 +5884,11 @@
         </is>
       </c>
       <c r="D13" s="23">
-        <f>IF('时间节点计划表'!E7="","",'时间节点计划表'!E7)</f>
+        <f>'时间节点计划表'!E7</f>
         <v/>
       </c>
       <c r="E13" s="23">
-        <f>IF('时间节点计划表'!F7="","",'时间节点计划表'!F7)</f>
+        <f>IF(COUNT('时间节点计划表'!F7),'时间节点计划表'!F7,"")</f>
         <v/>
       </c>
       <c r="F13" s="24" t="inlineStr"/>
@@ -6207,11 +6154,11 @@
         </is>
       </c>
       <c r="D14" s="28">
-        <f>IF('时间节点计划表'!E7="","",'时间节点计划表'!E7)</f>
+        <f>'时间节点计划表'!E7</f>
         <v/>
       </c>
       <c r="E14" s="28">
-        <f>IF('时间节点计划表'!F7="","",'时间节点计划表'!F7)</f>
+        <f>IF(COUNT('时间节点计划表'!F7),'时间节点计划表'!F7,"")</f>
         <v/>
       </c>
       <c r="F14" s="29">
@@ -6480,11 +6427,11 @@
         </is>
       </c>
       <c r="D15" s="23">
-        <f>IF('时间节点计划表'!E8="","",'时间节点计划表'!E8)</f>
+        <f>'时间节点计划表'!E8</f>
         <v/>
       </c>
       <c r="E15" s="23">
-        <f>IF('时间节点计划表'!F8="","",'时间节点计划表'!F8)</f>
+        <f>IF(COUNT('时间节点计划表'!F8),'时间节点计划表'!F8,"")</f>
         <v/>
       </c>
       <c r="F15" s="24" t="inlineStr"/>
@@ -6750,11 +6697,11 @@
         </is>
       </c>
       <c r="D16" s="28">
-        <f>IF('时间节点计划表'!E8="","",'时间节点计划表'!E8)</f>
+        <f>'时间节点计划表'!E8</f>
         <v/>
       </c>
       <c r="E16" s="28">
-        <f>IF('时间节点计划表'!F8="","",'时间节点计划表'!F8)</f>
+        <f>IF(COUNT('时间节点计划表'!F8),'时间节点计划表'!F8,"")</f>
         <v/>
       </c>
       <c r="F16" s="29">
@@ -7023,11 +6970,11 @@
         </is>
       </c>
       <c r="D17" s="23">
-        <f>IF('时间节点计划表'!E9="","",'时间节点计划表'!E9)</f>
+        <f>'时间节点计划表'!E9</f>
         <v/>
       </c>
       <c r="E17" s="23">
-        <f>IF('时间节点计划表'!F9="","",'时间节点计划表'!F9)</f>
+        <f>IF(COUNT('时间节点计划表'!F9),'时间节点计划表'!F9,"")</f>
         <v/>
       </c>
       <c r="F17" s="24" t="inlineStr"/>
@@ -7293,11 +7240,11 @@
         </is>
       </c>
       <c r="D18" s="28">
-        <f>IF('时间节点计划表'!E9="","",'时间节点计划表'!E9)</f>
+        <f>'时间节点计划表'!E9</f>
         <v/>
       </c>
       <c r="E18" s="28">
-        <f>IF('时间节点计划表'!F9="","",'时间节点计划表'!F9)</f>
+        <f>IF(COUNT('时间节点计划表'!F9),'时间节点计划表'!F9,"")</f>
         <v/>
       </c>
       <c r="F18" s="29">
@@ -7566,11 +7513,11 @@
         </is>
       </c>
       <c r="D19" s="23">
-        <f>IF('时间节点计划表'!E10="","",'时间节点计划表'!E10)</f>
+        <f>'时间节点计划表'!E10</f>
         <v/>
       </c>
       <c r="E19" s="23">
-        <f>IF('时间节点计划表'!F10="","",'时间节点计划表'!F10)</f>
+        <f>IF(COUNT('时间节点计划表'!F10),'时间节点计划表'!F10,"")</f>
         <v/>
       </c>
       <c r="F19" s="24" t="inlineStr"/>
@@ -7836,11 +7783,11 @@
         </is>
       </c>
       <c r="D20" s="28">
-        <f>IF('时间节点计划表'!E10="","",'时间节点计划表'!E10)</f>
+        <f>'时间节点计划表'!E10</f>
         <v/>
       </c>
       <c r="E20" s="28">
-        <f>IF('时间节点计划表'!F10="","",'时间节点计划表'!F10)</f>
+        <f>IF(COUNT('时间节点计划表'!F10),'时间节点计划表'!F10,"")</f>
         <v/>
       </c>
       <c r="F20" s="29">
@@ -8109,11 +8056,11 @@
         </is>
       </c>
       <c r="D21" s="23">
-        <f>IF('时间节点计划表'!E11="","",'时间节点计划表'!E11)</f>
+        <f>'时间节点计划表'!E11</f>
         <v/>
       </c>
       <c r="E21" s="23">
-        <f>IF('时间节点计划表'!F11="","",'时间节点计划表'!F11)</f>
+        <f>IF(COUNT('时间节点计划表'!F11),'时间节点计划表'!F11,"")</f>
         <v/>
       </c>
       <c r="F21" s="24" t="inlineStr"/>
@@ -8379,11 +8326,11 @@
         </is>
       </c>
       <c r="D22" s="28">
-        <f>IF('时间节点计划表'!E11="","",'时间节点计划表'!E11)</f>
+        <f>'时间节点计划表'!E11</f>
         <v/>
       </c>
       <c r="E22" s="28">
-        <f>IF('时间节点计划表'!F11="","",'时间节点计划表'!F11)</f>
+        <f>IF(COUNT('时间节点计划表'!F11),'时间节点计划表'!F11,"")</f>
         <v/>
       </c>
       <c r="F22" s="29">
@@ -8652,11 +8599,11 @@
         </is>
       </c>
       <c r="D23" s="23">
-        <f>IF('时间节点计划表'!E12="","",'时间节点计划表'!E12)</f>
+        <f>'时间节点计划表'!E12</f>
         <v/>
       </c>
       <c r="E23" s="23">
-        <f>IF('时间节点计划表'!F12="","",'时间节点计划表'!F12)</f>
+        <f>IF(COUNT('时间节点计划表'!F12),'时间节点计划表'!F12,"")</f>
         <v/>
       </c>
       <c r="F23" s="24" t="inlineStr"/>
@@ -8922,11 +8869,11 @@
         </is>
       </c>
       <c r="D24" s="28">
-        <f>IF('时间节点计划表'!E12="","",'时间节点计划表'!E12)</f>
+        <f>'时间节点计划表'!E12</f>
         <v/>
       </c>
       <c r="E24" s="28">
-        <f>IF('时间节点计划表'!F12="","",'时间节点计划表'!F12)</f>
+        <f>IF(COUNT('时间节点计划表'!F12),'时间节点计划表'!F12,"")</f>
         <v/>
       </c>
       <c r="F24" s="29">
@@ -9195,11 +9142,11 @@
         </is>
       </c>
       <c r="D25" s="23">
-        <f>IF('时间节点计划表'!E13="","",'时间节点计划表'!E13)</f>
+        <f>'时间节点计划表'!E13</f>
         <v/>
       </c>
       <c r="E25" s="23">
-        <f>IF('时间节点计划表'!F13="","",'时间节点计划表'!F13)</f>
+        <f>IF(COUNT('时间节点计划表'!F13),'时间节点计划表'!F13,"")</f>
         <v/>
       </c>
       <c r="F25" s="24" t="inlineStr"/>
@@ -9465,11 +9412,11 @@
         </is>
       </c>
       <c r="D26" s="28">
-        <f>IF('时间节点计划表'!E13="","",'时间节点计划表'!E13)</f>
+        <f>'时间节点计划表'!E13</f>
         <v/>
       </c>
       <c r="E26" s="28">
-        <f>IF('时间节点计划表'!F13="","",'时间节点计划表'!F13)</f>
+        <f>IF(COUNT('时间节点计划表'!F13),'时间节点计划表'!F13,"")</f>
         <v/>
       </c>
       <c r="F26" s="29">
@@ -9738,11 +9685,11 @@
         </is>
       </c>
       <c r="D27" s="23">
-        <f>IF('时间节点计划表'!E14="","",'时间节点计划表'!E14)</f>
+        <f>'时间节点计划表'!E14</f>
         <v/>
       </c>
       <c r="E27" s="23">
-        <f>IF('时间节点计划表'!F14="","",'时间节点计划表'!F14)</f>
+        <f>IF(COUNT('时间节点计划表'!F14),'时间节点计划表'!F14,"")</f>
         <v/>
       </c>
       <c r="F27" s="24" t="inlineStr"/>
@@ -10008,11 +9955,11 @@
         </is>
       </c>
       <c r="D28" s="28">
-        <f>IF('时间节点计划表'!E14="","",'时间节点计划表'!E14)</f>
+        <f>'时间节点计划表'!E14</f>
         <v/>
       </c>
       <c r="E28" s="28">
-        <f>IF('时间节点计划表'!F14="","",'时间节点计划表'!F14)</f>
+        <f>IF(COUNT('时间节点计划表'!F14),'时间节点计划表'!F14,"")</f>
         <v/>
       </c>
       <c r="F28" s="29">
@@ -10281,11 +10228,11 @@
         </is>
       </c>
       <c r="D29" s="23">
-        <f>IF('时间节点计划表'!E15="","",'时间节点计划表'!E15)</f>
+        <f>'时间节点计划表'!E15</f>
         <v/>
       </c>
       <c r="E29" s="23">
-        <f>IF('时间节点计划表'!F15="","",'时间节点计划表'!F15)</f>
+        <f>IF(COUNT('时间节点计划表'!F15),'时间节点计划表'!F15,"")</f>
         <v/>
       </c>
       <c r="F29" s="24" t="inlineStr"/>
@@ -10551,11 +10498,11 @@
         </is>
       </c>
       <c r="D30" s="28">
-        <f>IF('时间节点计划表'!E15="","",'时间节点计划表'!E15)</f>
+        <f>'时间节点计划表'!E15</f>
         <v/>
       </c>
       <c r="E30" s="28">
-        <f>IF('时间节点计划表'!F15="","",'时间节点计划表'!F15)</f>
+        <f>IF(COUNT('时间节点计划表'!F15),'时间节点计划表'!F15,"")</f>
         <v/>
       </c>
       <c r="F30" s="29">
@@ -10824,11 +10771,11 @@
         </is>
       </c>
       <c r="D31" s="23">
-        <f>IF('时间节点计划表'!E16="","",'时间节点计划表'!E16)</f>
+        <f>'时间节点计划表'!E16</f>
         <v/>
       </c>
       <c r="E31" s="23">
-        <f>IF('时间节点计划表'!F16="","",'时间节点计划表'!F16)</f>
+        <f>IF(COUNT('时间节点计划表'!F16),'时间节点计划表'!F16,"")</f>
         <v/>
       </c>
       <c r="F31" s="24" t="inlineStr"/>
@@ -11094,11 +11041,11 @@
         </is>
       </c>
       <c r="D32" s="28">
-        <f>IF('时间节点计划表'!E16="","",'时间节点计划表'!E16)</f>
+        <f>'时间节点计划表'!E16</f>
         <v/>
       </c>
       <c r="E32" s="28">
-        <f>IF('时间节点计划表'!F16="","",'时间节点计划表'!F16)</f>
+        <f>IF(COUNT('时间节点计划表'!F16),'时间节点计划表'!F16,"")</f>
         <v/>
       </c>
       <c r="F32" s="29">
@@ -11367,11 +11314,11 @@
         </is>
       </c>
       <c r="D33" s="23">
-        <f>IF('时间节点计划表'!E17="","",'时间节点计划表'!E17)</f>
+        <f>'时间节点计划表'!E17</f>
         <v/>
       </c>
       <c r="E33" s="23">
-        <f>IF('时间节点计划表'!F17="","",'时间节点计划表'!F17)</f>
+        <f>IF(COUNT('时间节点计划表'!F17),'时间节点计划表'!F17,"")</f>
         <v/>
       </c>
       <c r="F33" s="24" t="inlineStr"/>
@@ -11637,11 +11584,11 @@
         </is>
       </c>
       <c r="D34" s="28">
-        <f>IF('时间节点计划表'!E17="","",'时间节点计划表'!E17)</f>
+        <f>'时间节点计划表'!E17</f>
         <v/>
       </c>
       <c r="E34" s="28">
-        <f>IF('时间节点计划表'!F17="","",'时间节点计划表'!F17)</f>
+        <f>IF(COUNT('时间节点计划表'!F17),'时间节点计划表'!F17,"")</f>
         <v/>
       </c>
       <c r="F34" s="29">
@@ -11910,11 +11857,11 @@
         </is>
       </c>
       <c r="D35" s="23">
-        <f>IF('时间节点计划表'!E18="","",'时间节点计划表'!E18)</f>
+        <f>'时间节点计划表'!E18</f>
         <v/>
       </c>
       <c r="E35" s="23">
-        <f>IF('时间节点计划表'!F18="","",'时间节点计划表'!F18)</f>
+        <f>IF(COUNT('时间节点计划表'!F18),'时间节点计划表'!F18,"")</f>
         <v/>
       </c>
       <c r="F35" s="24" t="inlineStr"/>
@@ -12180,11 +12127,11 @@
         </is>
       </c>
       <c r="D36" s="28">
-        <f>IF('时间节点计划表'!E18="","",'时间节点计划表'!E18)</f>
+        <f>'时间节点计划表'!E18</f>
         <v/>
       </c>
       <c r="E36" s="28">
-        <f>IF('时间节点计划表'!F18="","",'时间节点计划表'!F18)</f>
+        <f>IF(COUNT('时间节点计划表'!F18),'时间节点计划表'!F18,"")</f>
         <v/>
       </c>
       <c r="F36" s="29">
@@ -12453,11 +12400,11 @@
         </is>
       </c>
       <c r="D37" s="23">
-        <f>IF('时间节点计划表'!E19="","",'时间节点计划表'!E19)</f>
+        <f>'时间节点计划表'!E19</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>IF('时间节点计划表'!F19="","",'时间节点计划表'!F19)</f>
+        <f>IF(COUNT('时间节点计划表'!F19),'时间节点计划表'!F19,"")</f>
         <v/>
       </c>
       <c r="F37" s="24" t="inlineStr"/>
@@ -12723,11 +12670,11 @@
         </is>
       </c>
       <c r="D38" s="28">
-        <f>IF('时间节点计划表'!E19="","",'时间节点计划表'!E19)</f>
+        <f>'时间节点计划表'!E19</f>
         <v/>
       </c>
       <c r="E38" s="28">
-        <f>IF('时间节点计划表'!F19="","",'时间节点计划表'!F19)</f>
+        <f>IF(COUNT('时间节点计划表'!F19),'时间节点计划表'!F19,"")</f>
         <v/>
       </c>
       <c r="F38" s="29">
@@ -12996,11 +12943,11 @@
         </is>
       </c>
       <c r="D39" s="23">
-        <f>IF('时间节点计划表'!E20="","",'时间节点计划表'!E20)</f>
+        <f>'时间节点计划表'!E20</f>
         <v/>
       </c>
       <c r="E39" s="23">
-        <f>IF('时间节点计划表'!F20="","",'时间节点计划表'!F20)</f>
+        <f>IF(COUNT('时间节点计划表'!F20),'时间节点计划表'!F20,"")</f>
         <v/>
       </c>
       <c r="F39" s="24" t="inlineStr"/>
@@ -13266,11 +13213,11 @@
         </is>
       </c>
       <c r="D40" s="28">
-        <f>IF('时间节点计划表'!E20="","",'时间节点计划表'!E20)</f>
+        <f>'时间节点计划表'!E20</f>
         <v/>
       </c>
       <c r="E40" s="28">
-        <f>IF('时间节点计划表'!F20="","",'时间节点计划表'!F20)</f>
+        <f>IF(COUNT('时间节点计划表'!F20),'时间节点计划表'!F20,"")</f>
         <v/>
       </c>
       <c r="F40" s="29">
@@ -13539,11 +13486,11 @@
         </is>
       </c>
       <c r="D41" s="23">
-        <f>IF('时间节点计划表'!E21="","",'时间节点计划表'!E21)</f>
+        <f>'时间节点计划表'!E21</f>
         <v/>
       </c>
       <c r="E41" s="23">
-        <f>IF('时间节点计划表'!F21="","",'时间节点计划表'!F21)</f>
+        <f>IF(COUNT('时间节点计划表'!F21),'时间节点计划表'!F21,"")</f>
         <v/>
       </c>
       <c r="F41" s="24" t="inlineStr"/>
@@ -13809,11 +13756,11 @@
         </is>
       </c>
       <c r="D42" s="28">
-        <f>IF('时间节点计划表'!E21="","",'时间节点计划表'!E21)</f>
+        <f>'时间节点计划表'!E21</f>
         <v/>
       </c>
       <c r="E42" s="28">
-        <f>IF('时间节点计划表'!F21="","",'时间节点计划表'!F21)</f>
+        <f>IF(COUNT('时间节点计划表'!F21),'时间节点计划表'!F21,"")</f>
         <v/>
       </c>
       <c r="F42" s="29">
@@ -14082,11 +14029,11 @@
         </is>
       </c>
       <c r="D43" s="23">
-        <f>IF('时间节点计划表'!E22="","",'时间节点计划表'!E22)</f>
+        <f>'时间节点计划表'!E22</f>
         <v/>
       </c>
       <c r="E43" s="23">
-        <f>IF('时间节点计划表'!F22="","",'时间节点计划表'!F22)</f>
+        <f>IF(COUNT('时间节点计划表'!F22),'时间节点计划表'!F22,"")</f>
         <v/>
       </c>
       <c r="F43" s="24" t="inlineStr"/>
@@ -14352,11 +14299,11 @@
         </is>
       </c>
       <c r="D44" s="28">
-        <f>IF('时间节点计划表'!E22="","",'时间节点计划表'!E22)</f>
+        <f>'时间节点计划表'!E22</f>
         <v/>
       </c>
       <c r="E44" s="28">
-        <f>IF('时间节点计划表'!F22="","",'时间节点计划表'!F22)</f>
+        <f>IF(COUNT('时间节点计划表'!F22),'时间节点计划表'!F22,"")</f>
         <v/>
       </c>
       <c r="F44" s="29">
@@ -14625,11 +14572,11 @@
         </is>
       </c>
       <c r="D45" s="23">
-        <f>IF('时间节点计划表'!E23="","",'时间节点计划表'!E23)</f>
+        <f>'时间节点计划表'!E23</f>
         <v/>
       </c>
       <c r="E45" s="23">
-        <f>IF('时间节点计划表'!F23="","",'时间节点计划表'!F23)</f>
+        <f>IF(COUNT('时间节点计划表'!F23),'时间节点计划表'!F23,"")</f>
         <v/>
       </c>
       <c r="F45" s="24" t="inlineStr"/>
@@ -14895,11 +14842,11 @@
         </is>
       </c>
       <c r="D46" s="28">
-        <f>IF('时间节点计划表'!E23="","",'时间节点计划表'!E23)</f>
+        <f>'时间节点计划表'!E23</f>
         <v/>
       </c>
       <c r="E46" s="28">
-        <f>IF('时间节点计划表'!F23="","",'时间节点计划表'!F23)</f>
+        <f>IF(COUNT('时间节点计划表'!F23),'时间节点计划表'!F23,"")</f>
         <v/>
       </c>
       <c r="F46" s="29">
@@ -15168,11 +15115,11 @@
         </is>
       </c>
       <c r="D47" s="23">
-        <f>IF('时间节点计划表'!E24="","",'时间节点计划表'!E24)</f>
+        <f>'时间节点计划表'!E24</f>
         <v/>
       </c>
       <c r="E47" s="23">
-        <f>IF('时间节点计划表'!F24="","",'时间节点计划表'!F24)</f>
+        <f>IF(COUNT('时间节点计划表'!F24),'时间节点计划表'!F24,"")</f>
         <v/>
       </c>
       <c r="F47" s="24" t="inlineStr"/>
@@ -15438,11 +15385,11 @@
         </is>
       </c>
       <c r="D48" s="28">
-        <f>IF('时间节点计划表'!E24="","",'时间节点计划表'!E24)</f>
+        <f>'时间节点计划表'!E24</f>
         <v/>
       </c>
       <c r="E48" s="28">
-        <f>IF('时间节点计划表'!F24="","",'时间节点计划表'!F24)</f>
+        <f>IF(COUNT('时间节点计划表'!F24),'时间节点计划表'!F24,"")</f>
         <v/>
       </c>
       <c r="F48" s="29">
@@ -15711,11 +15658,11 @@
         </is>
       </c>
       <c r="D49" s="23">
-        <f>IF('时间节点计划表'!E25="","",'时间节点计划表'!E25)</f>
+        <f>'时间节点计划表'!E25</f>
         <v/>
       </c>
       <c r="E49" s="23">
-        <f>IF('时间节点计划表'!F25="","",'时间节点计划表'!F25)</f>
+        <f>IF(COUNT('时间节点计划表'!F25),'时间节点计划表'!F25,"")</f>
         <v/>
       </c>
       <c r="F49" s="24" t="inlineStr"/>
@@ -15981,11 +15928,11 @@
         </is>
       </c>
       <c r="D50" s="28">
-        <f>IF('时间节点计划表'!E25="","",'时间节点计划表'!E25)</f>
+        <f>'时间节点计划表'!E25</f>
         <v/>
       </c>
       <c r="E50" s="28">
-        <f>IF('时间节点计划表'!F25="","",'时间节点计划表'!F25)</f>
+        <f>IF(COUNT('时间节点计划表'!F25),'时间节点计划表'!F25,"")</f>
         <v/>
       </c>
       <c r="F50" s="29">
@@ -16254,11 +16201,11 @@
         </is>
       </c>
       <c r="D51" s="23">
-        <f>IF('时间节点计划表'!E26="","",'时间节点计划表'!E26)</f>
+        <f>'时间节点计划表'!E26</f>
         <v/>
       </c>
       <c r="E51" s="23">
-        <f>IF('时间节点计划表'!F26="","",'时间节点计划表'!F26)</f>
+        <f>IF(COUNT('时间节点计划表'!F26),'时间节点计划表'!F26,"")</f>
         <v/>
       </c>
       <c r="F51" s="24" t="inlineStr"/>
@@ -16524,11 +16471,11 @@
         </is>
       </c>
       <c r="D52" s="28">
-        <f>IF('时间节点计划表'!E26="","",'时间节点计划表'!E26)</f>
+        <f>'时间节点计划表'!E26</f>
         <v/>
       </c>
       <c r="E52" s="28">
-        <f>IF('时间节点计划表'!F26="","",'时间节点计划表'!F26)</f>
+        <f>IF(COUNT('时间节点计划表'!F26),'时间节点计划表'!F26,"")</f>
         <v/>
       </c>
       <c r="F52" s="29">
@@ -16797,11 +16744,11 @@
         </is>
       </c>
       <c r="D53" s="23">
-        <f>IF('时间节点计划表'!E27="","",'时间节点计划表'!E27)</f>
+        <f>'时间节点计划表'!E27</f>
         <v/>
       </c>
       <c r="E53" s="23">
-        <f>IF('时间节点计划表'!F27="","",'时间节点计划表'!F27)</f>
+        <f>IF(COUNT('时间节点计划表'!F27),'时间节点计划表'!F27,"")</f>
         <v/>
       </c>
       <c r="F53" s="24" t="inlineStr"/>
@@ -17067,11 +17014,11 @@
         </is>
       </c>
       <c r="D54" s="28">
-        <f>IF('时间节点计划表'!E27="","",'时间节点计划表'!E27)</f>
+        <f>'时间节点计划表'!E27</f>
         <v/>
       </c>
       <c r="E54" s="28">
-        <f>IF('时间节点计划表'!F27="","",'时间节点计划表'!F27)</f>
+        <f>IF(COUNT('时间节点计划表'!F27),'时间节点计划表'!F27,"")</f>
         <v/>
       </c>
       <c r="F54" s="29">
@@ -17340,11 +17287,11 @@
         </is>
       </c>
       <c r="D55" s="23">
-        <f>IF('时间节点计划表'!E28="","",'时间节点计划表'!E28)</f>
+        <f>'时间节点计划表'!E28</f>
         <v/>
       </c>
       <c r="E55" s="23">
-        <f>IF('时间节点计划表'!F28="","",'时间节点计划表'!F28)</f>
+        <f>IF(COUNT('时间节点计划表'!F28),'时间节点计划表'!F28,"")</f>
         <v/>
       </c>
       <c r="F55" s="24" t="inlineStr"/>
@@ -17610,11 +17557,11 @@
         </is>
       </c>
       <c r="D56" s="28">
-        <f>IF('时间节点计划表'!E28="","",'时间节点计划表'!E28)</f>
+        <f>'时间节点计划表'!E28</f>
         <v/>
       </c>
       <c r="E56" s="28">
-        <f>IF('时间节点计划表'!F28="","",'时间节点计划表'!F28)</f>
+        <f>IF(COUNT('时间节点计划表'!F28),'时间节点计划表'!F28,"")</f>
         <v/>
       </c>
       <c r="F56" s="29">
@@ -17883,11 +17830,11 @@
         </is>
       </c>
       <c r="D57" s="23">
-        <f>IF('时间节点计划表'!E29="","",'时间节点计划表'!E29)</f>
+        <f>'时间节点计划表'!E29</f>
         <v/>
       </c>
       <c r="E57" s="23">
-        <f>IF('时间节点计划表'!F29="","",'时间节点计划表'!F29)</f>
+        <f>IF(COUNT('时间节点计划表'!F29),'时间节点计划表'!F29,"")</f>
         <v/>
       </c>
       <c r="F57" s="24" t="inlineStr"/>
@@ -18153,11 +18100,11 @@
         </is>
       </c>
       <c r="D58" s="28">
-        <f>IF('时间节点计划表'!E29="","",'时间节点计划表'!E29)</f>
+        <f>'时间节点计划表'!E29</f>
         <v/>
       </c>
       <c r="E58" s="28">
-        <f>IF('时间节点计划表'!F29="","",'时间节点计划表'!F29)</f>
+        <f>IF(COUNT('时间节点计划表'!F29),'时间节点计划表'!F29,"")</f>
         <v/>
       </c>
       <c r="F58" s="29">
@@ -18426,11 +18373,11 @@
         </is>
       </c>
       <c r="D59" s="23">
-        <f>IF('时间节点计划表'!E30="","",'时间节点计划表'!E30)</f>
+        <f>'时间节点计划表'!E30</f>
         <v/>
       </c>
       <c r="E59" s="23">
-        <f>IF('时间节点计划表'!F30="","",'时间节点计划表'!F30)</f>
+        <f>IF(COUNT('时间节点计划表'!F30),'时间节点计划表'!F30,"")</f>
         <v/>
       </c>
       <c r="F59" s="24" t="inlineStr"/>
@@ -18696,11 +18643,11 @@
         </is>
       </c>
       <c r="D60" s="28">
-        <f>IF('时间节点计划表'!E30="","",'时间节点计划表'!E30)</f>
+        <f>'时间节点计划表'!E30</f>
         <v/>
       </c>
       <c r="E60" s="28">
-        <f>IF('时间节点计划表'!F30="","",'时间节点计划表'!F30)</f>
+        <f>IF(COUNT('时间节点计划表'!F30),'时间节点计划表'!F30,"")</f>
         <v/>
       </c>
       <c r="F60" s="29">
@@ -18969,11 +18916,11 @@
         </is>
       </c>
       <c r="D61" s="23">
-        <f>IF('时间节点计划表'!E31="","",'时间节点计划表'!E31)</f>
+        <f>'时间节点计划表'!E31</f>
         <v/>
       </c>
       <c r="E61" s="23">
-        <f>IF('时间节点计划表'!F31="","",'时间节点计划表'!F31)</f>
+        <f>IF(COUNT('时间节点计划表'!F31),'时间节点计划表'!F31,"")</f>
         <v/>
       </c>
       <c r="F61" s="24" t="inlineStr"/>
@@ -19239,11 +19186,11 @@
         </is>
       </c>
       <c r="D62" s="28">
-        <f>IF('时间节点计划表'!E31="","",'时间节点计划表'!E31)</f>
+        <f>'时间节点计划表'!E31</f>
         <v/>
       </c>
       <c r="E62" s="28">
-        <f>IF('时间节点计划表'!F31="","",'时间节点计划表'!F31)</f>
+        <f>IF(COUNT('时间节点计划表'!F31),'时间节点计划表'!F31,"")</f>
         <v/>
       </c>
       <c r="F62" s="29">
@@ -19512,11 +19459,11 @@
         </is>
       </c>
       <c r="D63" s="23">
-        <f>IF('时间节点计划表'!E32="","",'时间节点计划表'!E32)</f>
+        <f>'时间节点计划表'!E32</f>
         <v/>
       </c>
       <c r="E63" s="23">
-        <f>IF('时间节点计划表'!F32="","",'时间节点计划表'!F32)</f>
+        <f>IF(COUNT('时间节点计划表'!F32),'时间节点计划表'!F32,"")</f>
         <v/>
       </c>
       <c r="F63" s="24" t="inlineStr"/>
@@ -19782,11 +19729,11 @@
         </is>
       </c>
       <c r="D64" s="28">
-        <f>IF('时间节点计划表'!E32="","",'时间节点计划表'!E32)</f>
+        <f>'时间节点计划表'!E32</f>
         <v/>
       </c>
       <c r="E64" s="28">
-        <f>IF('时间节点计划表'!F32="","",'时间节点计划表'!F32)</f>
+        <f>IF(COUNT('时间节点计划表'!F32),'时间节点计划表'!F32,"")</f>
         <v/>
       </c>
       <c r="F64" s="29">
@@ -20055,11 +20002,11 @@
         </is>
       </c>
       <c r="D65" s="23">
-        <f>IF('时间节点计划表'!E33="","",'时间节点计划表'!E33)</f>
+        <f>'时间节点计划表'!E33</f>
         <v/>
       </c>
       <c r="E65" s="23">
-        <f>IF('时间节点计划表'!F33="","",'时间节点计划表'!F33)</f>
+        <f>IF(COUNT('时间节点计划表'!F33),'时间节点计划表'!F33,"")</f>
         <v/>
       </c>
       <c r="F65" s="24" t="inlineStr"/>
@@ -20325,11 +20272,11 @@
         </is>
       </c>
       <c r="D66" s="28">
-        <f>IF('时间节点计划表'!E33="","",'时间节点计划表'!E33)</f>
+        <f>'时间节点计划表'!E33</f>
         <v/>
       </c>
       <c r="E66" s="28">
-        <f>IF('时间节点计划表'!F33="","",'时间节点计划表'!F33)</f>
+        <f>IF(COUNT('时间节点计划表'!F33),'时间节点计划表'!F33,"")</f>
         <v/>
       </c>
       <c r="F66" s="29">
@@ -20598,11 +20545,11 @@
         </is>
       </c>
       <c r="D67" s="23">
-        <f>IF('时间节点计划表'!E34="","",'时间节点计划表'!E34)</f>
+        <f>'时间节点计划表'!E34</f>
         <v/>
       </c>
       <c r="E67" s="23">
-        <f>IF('时间节点计划表'!F34="","",'时间节点计划表'!F34)</f>
+        <f>IF(COUNT('时间节点计划表'!F34),'时间节点计划表'!F34,"")</f>
         <v/>
       </c>
       <c r="F67" s="24" t="inlineStr"/>
@@ -20868,11 +20815,11 @@
         </is>
       </c>
       <c r="D68" s="28">
-        <f>IF('时间节点计划表'!E34="","",'时间节点计划表'!E34)</f>
+        <f>'时间节点计划表'!E34</f>
         <v/>
       </c>
       <c r="E68" s="28">
-        <f>IF('时间节点计划表'!F34="","",'时间节点计划表'!F34)</f>
+        <f>IF(COUNT('时间节点计划表'!F34),'时间节点计划表'!F34,"")</f>
         <v/>
       </c>
       <c r="F68" s="29">
@@ -21141,11 +21088,11 @@
         </is>
       </c>
       <c r="D69" s="23">
-        <f>IF('时间节点计划表'!E35="","",'时间节点计划表'!E35)</f>
+        <f>'时间节点计划表'!E35</f>
         <v/>
       </c>
       <c r="E69" s="23">
-        <f>IF('时间节点计划表'!F35="","",'时间节点计划表'!F35)</f>
+        <f>IF(COUNT('时间节点计划表'!F35),'时间节点计划表'!F35,"")</f>
         <v/>
       </c>
       <c r="F69" s="24" t="inlineStr"/>
@@ -21411,11 +21358,11 @@
         </is>
       </c>
       <c r="D70" s="28">
-        <f>IF('时间节点计划表'!E35="","",'时间节点计划表'!E35)</f>
+        <f>'时间节点计划表'!E35</f>
         <v/>
       </c>
       <c r="E70" s="28">
-        <f>IF('时间节点计划表'!F35="","",'时间节点计划表'!F35)</f>
+        <f>IF(COUNT('时间节点计划表'!F35),'时间节点计划表'!F35,"")</f>
         <v/>
       </c>
       <c r="F70" s="29">
@@ -21684,11 +21631,11 @@
         </is>
       </c>
       <c r="D71" s="23">
-        <f>IF('时间节点计划表'!E36="","",'时间节点计划表'!E36)</f>
+        <f>'时间节点计划表'!E36</f>
         <v/>
       </c>
       <c r="E71" s="23">
-        <f>IF('时间节点计划表'!F36="","",'时间节点计划表'!F36)</f>
+        <f>IF(COUNT('时间节点计划表'!F36),'时间节点计划表'!F36,"")</f>
         <v/>
       </c>
       <c r="F71" s="24" t="inlineStr"/>
@@ -21954,11 +21901,11 @@
         </is>
       </c>
       <c r="D72" s="28">
-        <f>IF('时间节点计划表'!E36="","",'时间节点计划表'!E36)</f>
+        <f>'时间节点计划表'!E36</f>
         <v/>
       </c>
       <c r="E72" s="28">
-        <f>IF('时间节点计划表'!F36="","",'时间节点计划表'!F36)</f>
+        <f>IF(COUNT('时间节点计划表'!F36),'时间节点计划表'!F36,"")</f>
         <v/>
       </c>
       <c r="F72" s="29">
@@ -22227,11 +22174,11 @@
         </is>
       </c>
       <c r="D73" s="23">
-        <f>IF('时间节点计划表'!E37="","",'时间节点计划表'!E37)</f>
+        <f>'时间节点计划表'!E37</f>
         <v/>
       </c>
       <c r="E73" s="23">
-        <f>IF('时间节点计划表'!F37="","",'时间节点计划表'!F37)</f>
+        <f>IF(COUNT('时间节点计划表'!F37),'时间节点计划表'!F37,"")</f>
         <v/>
       </c>
       <c r="F73" s="24" t="inlineStr"/>
@@ -22497,11 +22444,11 @@
         </is>
       </c>
       <c r="D74" s="28">
-        <f>IF('时间节点计划表'!E37="","",'时间节点计划表'!E37)</f>
+        <f>'时间节点计划表'!E37</f>
         <v/>
       </c>
       <c r="E74" s="28">
-        <f>IF('时间节点计划表'!F37="","",'时间节点计划表'!F37)</f>
+        <f>IF(COUNT('时间节点计划表'!F37),'时间节点计划表'!F37,"")</f>
         <v/>
       </c>
       <c r="F74" s="29">
@@ -22770,11 +22717,11 @@
         </is>
       </c>
       <c r="D75" s="23">
-        <f>IF('时间节点计划表'!E38="","",'时间节点计划表'!E38)</f>
+        <f>'时间节点计划表'!E38</f>
         <v/>
       </c>
       <c r="E75" s="23">
-        <f>IF('时间节点计划表'!F38="","",'时间节点计划表'!F38)</f>
+        <f>IF(COUNT('时间节点计划表'!F38),'时间节点计划表'!F38,"")</f>
         <v/>
       </c>
       <c r="F75" s="24" t="inlineStr"/>
@@ -23040,11 +22987,11 @@
         </is>
       </c>
       <c r="D76" s="28">
-        <f>IF('时间节点计划表'!E38="","",'时间节点计划表'!E38)</f>
+        <f>'时间节点计划表'!E38</f>
         <v/>
       </c>
       <c r="E76" s="28">
-        <f>IF('时间节点计划表'!F38="","",'时间节点计划表'!F38)</f>
+        <f>IF(COUNT('时间节点计划表'!F38),'时间节点计划表'!F38,"")</f>
         <v/>
       </c>
       <c r="F76" s="29">
@@ -23313,11 +23260,11 @@
         </is>
       </c>
       <c r="D77" s="23">
-        <f>IF('时间节点计划表'!E39="","",'时间节点计划表'!E39)</f>
+        <f>'时间节点计划表'!E39</f>
         <v/>
       </c>
       <c r="E77" s="23">
-        <f>IF('时间节点计划表'!F39="","",'时间节点计划表'!F39)</f>
+        <f>IF(COUNT('时间节点计划表'!F39),'时间节点计划表'!F39,"")</f>
         <v/>
       </c>
       <c r="F77" s="24" t="inlineStr"/>
@@ -23583,11 +23530,11 @@
         </is>
       </c>
       <c r="D78" s="28">
-        <f>IF('时间节点计划表'!E39="","",'时间节点计划表'!E39)</f>
+        <f>'时间节点计划表'!E39</f>
         <v/>
       </c>
       <c r="E78" s="28">
-        <f>IF('时间节点计划表'!F39="","",'时间节点计划表'!F39)</f>
+        <f>IF(COUNT('时间节点计划表'!F39),'时间节点计划表'!F39,"")</f>
         <v/>
       </c>
       <c r="F78" s="29">
@@ -23856,11 +23803,11 @@
         </is>
       </c>
       <c r="D79" s="23">
-        <f>IF('时间节点计划表'!E40="","",'时间节点计划表'!E40)</f>
+        <f>'时间节点计划表'!E40</f>
         <v/>
       </c>
       <c r="E79" s="23">
-        <f>IF('时间节点计划表'!F40="","",'时间节点计划表'!F40)</f>
+        <f>IF(COUNT('时间节点计划表'!F40),'时间节点计划表'!F40,"")</f>
         <v/>
       </c>
       <c r="F79" s="24" t="inlineStr"/>
@@ -24126,11 +24073,11 @@
         </is>
       </c>
       <c r="D80" s="28">
-        <f>IF('时间节点计划表'!E40="","",'时间节点计划表'!E40)</f>
+        <f>'时间节点计划表'!E40</f>
         <v/>
       </c>
       <c r="E80" s="28">
-        <f>IF('时间节点计划表'!F40="","",'时间节点计划表'!F40)</f>
+        <f>IF(COUNT('时间节点计划表'!F40),'时间节点计划表'!F40,"")</f>
         <v/>
       </c>
       <c r="F80" s="29">
@@ -24399,11 +24346,11 @@
         </is>
       </c>
       <c r="D81" s="23">
-        <f>IF('时间节点计划表'!E41="","",'时间节点计划表'!E41)</f>
+        <f>'时间节点计划表'!E41</f>
         <v/>
       </c>
       <c r="E81" s="23">
-        <f>IF('时间节点计划表'!F41="","",'时间节点计划表'!F41)</f>
+        <f>IF(COUNT('时间节点计划表'!F41),'时间节点计划表'!F41,"")</f>
         <v/>
       </c>
       <c r="F81" s="24" t="inlineStr"/>
@@ -24669,11 +24616,11 @@
         </is>
       </c>
       <c r="D82" s="28">
-        <f>IF('时间节点计划表'!E41="","",'时间节点计划表'!E41)</f>
+        <f>'时间节点计划表'!E41</f>
         <v/>
       </c>
       <c r="E82" s="28">
-        <f>IF('时间节点计划表'!F41="","",'时间节点计划表'!F41)</f>
+        <f>IF(COUNT('时间节点计划表'!F41),'时间节点计划表'!F41,"")</f>
         <v/>
       </c>
       <c r="F82" s="29">
@@ -24942,11 +24889,11 @@
         </is>
       </c>
       <c r="D83" s="23">
-        <f>IF('时间节点计划表'!E42="","",'时间节点计划表'!E42)</f>
+        <f>'时间节点计划表'!E42</f>
         <v/>
       </c>
       <c r="E83" s="23">
-        <f>IF('时间节点计划表'!F42="","",'时间节点计划表'!F42)</f>
+        <f>IF(COUNT('时间节点计划表'!F42),'时间节点计划表'!F42,"")</f>
         <v/>
       </c>
       <c r="F83" s="24" t="inlineStr"/>
@@ -25212,11 +25159,11 @@
         </is>
       </c>
       <c r="D84" s="28">
-        <f>IF('时间节点计划表'!E42="","",'时间节点计划表'!E42)</f>
+        <f>'时间节点计划表'!E42</f>
         <v/>
       </c>
       <c r="E84" s="28">
-        <f>IF('时间节点计划表'!F42="","",'时间节点计划表'!F42)</f>
+        <f>IF(COUNT('时间节点计划表'!F42),'时间节点计划表'!F42,"")</f>
         <v/>
       </c>
       <c r="F84" s="29">
@@ -25485,11 +25432,11 @@
         </is>
       </c>
       <c r="D85" s="23">
-        <f>IF('时间节点计划表'!E43="","",'时间节点计划表'!E43)</f>
+        <f>'时间节点计划表'!E43</f>
         <v/>
       </c>
       <c r="E85" s="23">
-        <f>IF('时间节点计划表'!F43="","",'时间节点计划表'!F43)</f>
+        <f>IF(COUNT('时间节点计划表'!F43),'时间节点计划表'!F43,"")</f>
         <v/>
       </c>
       <c r="F85" s="24" t="inlineStr"/>
@@ -25755,11 +25702,11 @@
         </is>
       </c>
       <c r="D86" s="28">
-        <f>IF('时间节点计划表'!E43="","",'时间节点计划表'!E43)</f>
+        <f>'时间节点计划表'!E43</f>
         <v/>
       </c>
       <c r="E86" s="28">
-        <f>IF('时间节点计划表'!F43="","",'时间节点计划表'!F43)</f>
+        <f>IF(COUNT('时间节点计划表'!F43),'时间节点计划表'!F43,"")</f>
         <v/>
       </c>
       <c r="F86" s="29">
@@ -26028,11 +25975,11 @@
         </is>
       </c>
       <c r="D87" s="23">
-        <f>IF('时间节点计划表'!E44="","",'时间节点计划表'!E44)</f>
+        <f>'时间节点计划表'!E44</f>
         <v/>
       </c>
       <c r="E87" s="23">
-        <f>IF('时间节点计划表'!F44="","",'时间节点计划表'!F44)</f>
+        <f>IF(COUNT('时间节点计划表'!F44),'时间节点计划表'!F44,"")</f>
         <v/>
       </c>
       <c r="F87" s="24" t="inlineStr"/>
@@ -26298,11 +26245,11 @@
         </is>
       </c>
       <c r="D88" s="28">
-        <f>IF('时间节点计划表'!E44="","",'时间节点计划表'!E44)</f>
+        <f>'时间节点计划表'!E44</f>
         <v/>
       </c>
       <c r="E88" s="28">
-        <f>IF('时间节点计划表'!F44="","",'时间节点计划表'!F44)</f>
+        <f>IF(COUNT('时间节点计划表'!F44),'时间节点计划表'!F44,"")</f>
         <v/>
       </c>
       <c r="F88" s="29">
@@ -26571,11 +26518,11 @@
         </is>
       </c>
       <c r="D89" s="23">
-        <f>IF('时间节点计划表'!E45="","",'时间节点计划表'!E45)</f>
+        <f>'时间节点计划表'!E45</f>
         <v/>
       </c>
       <c r="E89" s="23">
-        <f>IF('时间节点计划表'!F45="","",'时间节点计划表'!F45)</f>
+        <f>IF(COUNT('时间节点计划表'!F45),'时间节点计划表'!F45,"")</f>
         <v/>
       </c>
       <c r="F89" s="24" t="inlineStr"/>
@@ -26841,11 +26788,11 @@
         </is>
       </c>
       <c r="D90" s="28">
-        <f>IF('时间节点计划表'!E45="","",'时间节点计划表'!E45)</f>
+        <f>'时间节点计划表'!E45</f>
         <v/>
       </c>
       <c r="E90" s="28">
-        <f>IF('时间节点计划表'!F45="","",'时间节点计划表'!F45)</f>
+        <f>IF(COUNT('时间节点计划表'!F45),'时间节点计划表'!F45,"")</f>
         <v/>
       </c>
       <c r="F90" s="29">
@@ -27146,44 +27093,6 @@
       <formula>AND($A3="实际",ISNUMBER(G3),$E3&lt;$D3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A90">
-    <cfRule type="expression" priority="5" dxfId="7">
-      <formula>AND($A3="预估",ISNUMBER($D3))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="8">
-      <formula>AND($A3="实际",ISNUMBER($E3),$E3&gt;$D3)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="9">
-      <formula>AND($A3="实际",ISNUMBER($E3),$E3&lt;$D3)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="10">
-      <formula>AND($A3="实际",ISNUMBER($E3),$E3=$D3)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D90">
-    <cfRule type="expression" priority="9" dxfId="7">
-      <formula>ISNUMBER(D3)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E90">
-    <cfRule type="expression" priority="10" dxfId="8">
-      <formula>AND(ISNUMBER(E3),E3&gt;D3)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="9">
-      <formula>AND(ISNUMBER(E3),E3&lt;D3)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="12" dxfId="10">
-      <formula>AND(ISNUMBER(E3),E3=D3)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F90">
-    <cfRule type="expression" priority="13" dxfId="8">
-      <formula>AND(ISNUMBER(F3),F3&gt;0)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="9">
-      <formula>AND(ISNUMBER(F3),F3&lt;0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8"/>
 </worksheet>

--- a/PAB产品计划表.xlsx
+++ b/PAB产品计划表.xlsx
@@ -243,9 +243,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00B7C9D6"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="00B7C9D6"/>
       </top>
@@ -256,7 +254,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00B7C9D6"/>
+      </right>
       <top style="thin">
         <color rgb="00B7C9D6"/>
       </top>
@@ -342,6 +342,8 @@
     <xf numFmtId="164" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -355,8 +357,6 @@
     <xf numFmtId="1" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2833,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:BO92"/>
+  <dimension ref="A1:BS92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2903,12 +2903,16 @@
     <col width="11" customWidth="1" min="65" max="65"/>
     <col width="11" customWidth="1" min="66" max="66"/>
     <col width="11" customWidth="1" min="67" max="67"/>
+    <col width="11" customWidth="1" min="68" max="68"/>
+    <col width="11" customWidth="1" min="69" max="69"/>
+    <col width="11" customWidth="1" min="70" max="70"/>
+    <col width="11" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>PAB 甘特图（2026-08-24 → 2026-10-23，每格 1 天）。每行从首日合并到完成日（预估）；填写实际日期后自动生成实际色条。请在「时间节点计划表」填写日期。</t>
+          <t>PAB 甘特图（2026-08-20 → 2026-10-23，每格 1 天）。每行从首日合并到完成日（预估）；填写实际日期后自动生成实际色条。请在「时间节点计划表」填写日期。</t>
         </is>
       </c>
       <c r="G1" s="16" t="inlineStr">
@@ -2923,15 +2927,15 @@
       <c r="L1" s="17" t="n"/>
       <c r="M1" s="17" t="n"/>
       <c r="N1" s="17" t="n"/>
-      <c r="O1" s="16" t="inlineStr">
-        <is>
-          <t>2026年9月</t>
-        </is>
-      </c>
+      <c r="O1" s="17" t="n"/>
       <c r="P1" s="17" t="n"/>
       <c r="Q1" s="17" t="n"/>
       <c r="R1" s="17" t="n"/>
-      <c r="S1" s="17" t="n"/>
+      <c r="S1" s="16" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
       <c r="T1" s="17" t="n"/>
       <c r="U1" s="17" t="n"/>
       <c r="V1" s="17" t="n"/>
@@ -2957,15 +2961,15 @@
       <c r="AP1" s="17" t="n"/>
       <c r="AQ1" s="17" t="n"/>
       <c r="AR1" s="17" t="n"/>
-      <c r="AS1" s="16" t="inlineStr">
-        <is>
-          <t>2026年10月</t>
-        </is>
-      </c>
+      <c r="AS1" s="17" t="n"/>
       <c r="AT1" s="17" t="n"/>
       <c r="AU1" s="17" t="n"/>
       <c r="AV1" s="17" t="n"/>
-      <c r="AW1" s="17" t="n"/>
+      <c r="AW1" s="16" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
       <c r="AX1" s="17" t="n"/>
       <c r="AY1" s="17" t="n"/>
       <c r="AZ1" s="17" t="n"/>
@@ -2984,6 +2988,10 @@
       <c r="BM1" s="17" t="n"/>
       <c r="BN1" s="17" t="n"/>
       <c r="BO1" s="17" t="n"/>
+      <c r="BP1" s="17" t="n"/>
+      <c r="BQ1" s="17" t="n"/>
+      <c r="BR1" s="17" t="n"/>
+      <c r="BS1" s="17" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="18" t="inlineStr">
@@ -3017,186 +3025,198 @@
         </is>
       </c>
       <c r="G2" s="19" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>46255</v>
+      </c>
+      <c r="I2" s="20" t="n">
+        <v>46256</v>
+      </c>
+      <c r="J2" s="20" t="n">
+        <v>46257</v>
+      </c>
+      <c r="K2" s="19" t="n">
         <v>46258</v>
       </c>
-      <c r="H2" s="19" t="n">
+      <c r="L2" s="19" t="n">
         <v>46259</v>
       </c>
-      <c r="I2" s="19" t="n">
+      <c r="M2" s="19" t="n">
         <v>46260</v>
       </c>
-      <c r="J2" s="19" t="n">
+      <c r="N2" s="19" t="n">
         <v>46261</v>
       </c>
-      <c r="K2" s="19" t="n">
+      <c r="O2" s="19" t="n">
         <v>46262</v>
       </c>
-      <c r="L2" s="20" t="n">
+      <c r="P2" s="20" t="n">
         <v>46263</v>
       </c>
-      <c r="M2" s="20" t="n">
+      <c r="Q2" s="20" t="n">
         <v>46264</v>
       </c>
-      <c r="N2" s="19" t="n">
+      <c r="R2" s="19" t="n">
         <v>46265</v>
       </c>
-      <c r="O2" s="19" t="n">
+      <c r="S2" s="19" t="n">
         <v>46266</v>
       </c>
-      <c r="P2" s="19" t="n">
+      <c r="T2" s="19" t="n">
         <v>46267</v>
       </c>
-      <c r="Q2" s="19" t="n">
+      <c r="U2" s="19" t="n">
         <v>46268</v>
       </c>
-      <c r="R2" s="19" t="n">
+      <c r="V2" s="19" t="n">
         <v>46269</v>
       </c>
-      <c r="S2" s="20" t="n">
+      <c r="W2" s="20" t="n">
         <v>46270</v>
       </c>
-      <c r="T2" s="20" t="n">
+      <c r="X2" s="20" t="n">
         <v>46271</v>
       </c>
-      <c r="U2" s="19" t="n">
+      <c r="Y2" s="19" t="n">
         <v>46272</v>
       </c>
-      <c r="V2" s="19" t="n">
+      <c r="Z2" s="19" t="n">
         <v>46273</v>
       </c>
-      <c r="W2" s="19" t="n">
+      <c r="AA2" s="19" t="n">
         <v>46274</v>
       </c>
-      <c r="X2" s="19" t="n">
+      <c r="AB2" s="19" t="n">
         <v>46275</v>
       </c>
-      <c r="Y2" s="19" t="n">
+      <c r="AC2" s="19" t="n">
         <v>46276</v>
       </c>
-      <c r="Z2" s="20" t="n">
+      <c r="AD2" s="20" t="n">
         <v>46277</v>
       </c>
-      <c r="AA2" s="20" t="n">
+      <c r="AE2" s="20" t="n">
         <v>46278</v>
       </c>
-      <c r="AB2" s="19" t="n">
+      <c r="AF2" s="19" t="n">
         <v>46279</v>
       </c>
-      <c r="AC2" s="19" t="n">
+      <c r="AG2" s="19" t="n">
         <v>46280</v>
       </c>
-      <c r="AD2" s="19" t="n">
+      <c r="AH2" s="19" t="n">
         <v>46281</v>
       </c>
-      <c r="AE2" s="19" t="n">
+      <c r="AI2" s="19" t="n">
         <v>46282</v>
       </c>
-      <c r="AF2" s="19" t="n">
+      <c r="AJ2" s="19" t="n">
         <v>46283</v>
       </c>
-      <c r="AG2" s="20" t="n">
+      <c r="AK2" s="20" t="n">
         <v>46284</v>
       </c>
-      <c r="AH2" s="20" t="n">
+      <c r="AL2" s="20" t="n">
         <v>46285</v>
       </c>
-      <c r="AI2" s="19" t="n">
+      <c r="AM2" s="19" t="n">
         <v>46286</v>
       </c>
-      <c r="AJ2" s="19" t="n">
+      <c r="AN2" s="19" t="n">
         <v>46287</v>
       </c>
-      <c r="AK2" s="19" t="n">
+      <c r="AO2" s="19" t="n">
         <v>46288</v>
       </c>
-      <c r="AL2" s="19" t="n">
+      <c r="AP2" s="19" t="n">
         <v>46289</v>
       </c>
-      <c r="AM2" s="19" t="n">
+      <c r="AQ2" s="19" t="n">
         <v>46290</v>
       </c>
-      <c r="AN2" s="20" t="n">
+      <c r="AR2" s="20" t="n">
         <v>46291</v>
       </c>
-      <c r="AO2" s="20" t="n">
+      <c r="AS2" s="20" t="n">
         <v>46292</v>
       </c>
-      <c r="AP2" s="19" t="n">
+      <c r="AT2" s="19" t="n">
         <v>46293</v>
       </c>
-      <c r="AQ2" s="19" t="n">
+      <c r="AU2" s="19" t="n">
         <v>46294</v>
       </c>
-      <c r="AR2" s="19" t="n">
+      <c r="AV2" s="19" t="n">
         <v>46295</v>
       </c>
-      <c r="AS2" s="19" t="n">
+      <c r="AW2" s="19" t="n">
         <v>46296</v>
       </c>
-      <c r="AT2" s="19" t="n">
+      <c r="AX2" s="19" t="n">
         <v>46297</v>
       </c>
-      <c r="AU2" s="20" t="n">
+      <c r="AY2" s="20" t="n">
         <v>46298</v>
       </c>
-      <c r="AV2" s="20" t="n">
+      <c r="AZ2" s="20" t="n">
         <v>46299</v>
       </c>
-      <c r="AW2" s="19" t="n">
+      <c r="BA2" s="19" t="n">
         <v>46300</v>
       </c>
-      <c r="AX2" s="19" t="n">
+      <c r="BB2" s="19" t="n">
         <v>46301</v>
       </c>
-      <c r="AY2" s="19" t="n">
+      <c r="BC2" s="19" t="n">
         <v>46302</v>
       </c>
-      <c r="AZ2" s="19" t="n">
+      <c r="BD2" s="19" t="n">
         <v>46303</v>
       </c>
-      <c r="BA2" s="19" t="n">
+      <c r="BE2" s="19" t="n">
         <v>46304</v>
       </c>
-      <c r="BB2" s="20" t="n">
+      <c r="BF2" s="20" t="n">
         <v>46305</v>
       </c>
-      <c r="BC2" s="20" t="n">
+      <c r="BG2" s="20" t="n">
         <v>46306</v>
       </c>
-      <c r="BD2" s="19" t="n">
+      <c r="BH2" s="19" t="n">
         <v>46307</v>
       </c>
-      <c r="BE2" s="19" t="n">
+      <c r="BI2" s="19" t="n">
         <v>46308</v>
       </c>
-      <c r="BF2" s="19" t="n">
+      <c r="BJ2" s="19" t="n">
         <v>46309</v>
       </c>
-      <c r="BG2" s="19" t="n">
+      <c r="BK2" s="19" t="n">
         <v>46310</v>
       </c>
-      <c r="BH2" s="19" t="n">
+      <c r="BL2" s="19" t="n">
         <v>46311</v>
       </c>
-      <c r="BI2" s="20" t="n">
+      <c r="BM2" s="20" t="n">
         <v>46312</v>
       </c>
-      <c r="BJ2" s="20" t="n">
+      <c r="BN2" s="20" t="n">
         <v>46313</v>
       </c>
-      <c r="BK2" s="19" t="n">
+      <c r="BO2" s="19" t="n">
         <v>46314</v>
       </c>
-      <c r="BL2" s="19" t="n">
+      <c r="BP2" s="19" t="n">
         <v>46315</v>
       </c>
-      <c r="BM2" s="19" t="n">
+      <c r="BQ2" s="19" t="n">
         <v>46316</v>
       </c>
-      <c r="BN2" s="19" t="n">
+      <c r="BR2" s="19" t="n">
         <v>46317</v>
       </c>
-      <c r="BO2" s="19" t="n">
+      <c r="BS2" s="19" t="n">
         <v>46318</v>
       </c>
     </row>
@@ -3232,89 +3252,93 @@
       <c r="H3" s="26" t="n"/>
       <c r="I3" s="26" t="n"/>
       <c r="J3" s="26" t="n"/>
-      <c r="K3" s="26" t="n"/>
-      <c r="L3" s="26" t="n"/>
-      <c r="M3" s="26" t="n"/>
-      <c r="N3" s="26" t="n"/>
-      <c r="O3" s="26" t="n"/>
-      <c r="P3" s="26" t="n"/>
-      <c r="Q3" s="26" t="n"/>
-      <c r="R3" s="26" t="n"/>
-      <c r="S3" s="26" t="n"/>
-      <c r="T3" s="26" t="n"/>
-      <c r="U3" s="26" t="n"/>
-      <c r="V3" s="26" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
-      <c r="Y3" s="26" t="n"/>
-      <c r="Z3" s="26" t="n"/>
-      <c r="AA3" s="26" t="n"/>
-      <c r="AB3" s="26" t="n"/>
-      <c r="AC3" s="26" t="n"/>
-      <c r="AD3" s="26" t="n"/>
-      <c r="AE3" s="26" t="n"/>
-      <c r="AF3" s="26" t="n"/>
-      <c r="AG3" s="26" t="n"/>
-      <c r="AH3" s="26" t="n"/>
-      <c r="AI3" s="26" t="n"/>
-      <c r="AJ3" s="26" t="n"/>
-      <c r="AK3" s="26" t="n"/>
-      <c r="AL3" s="26" t="n"/>
-      <c r="AM3" s="26" t="n"/>
-      <c r="AN3" s="26" t="n"/>
-      <c r="AO3" s="26" t="n"/>
-      <c r="AP3" s="26" t="n"/>
-      <c r="AQ3" s="26" t="n"/>
-      <c r="AR3" s="26" t="n"/>
-      <c r="AS3" s="26" t="n"/>
-      <c r="AT3" s="26" t="n"/>
-      <c r="AU3" s="26" t="n"/>
-      <c r="AV3" s="26" t="n"/>
-      <c r="AW3" s="26" t="n"/>
-      <c r="AX3" s="26" t="n"/>
-      <c r="AY3" s="26" t="n"/>
-      <c r="AZ3" s="26" t="n"/>
-      <c r="BA3" s="26" t="n"/>
-      <c r="BB3" s="26" t="n"/>
-      <c r="BC3" s="26" t="n"/>
-      <c r="BD3" s="26" t="n"/>
-      <c r="BE3" s="26" t="n"/>
-      <c r="BF3" s="26" t="n"/>
-      <c r="BG3" s="26" t="n"/>
-      <c r="BH3" s="26" t="n"/>
-      <c r="BI3" s="26" t="n"/>
-      <c r="BJ3" s="26" t="n"/>
-      <c r="BK3" s="26" t="n"/>
-      <c r="BL3" s="26" t="n"/>
-      <c r="BM3" s="26" t="n"/>
-      <c r="BN3" s="26" t="n"/>
-      <c r="BO3" s="26" t="n"/>
+      <c r="K3" s="27" t="n"/>
+      <c r="L3" s="28" t="n"/>
+      <c r="M3" s="28" t="n"/>
+      <c r="N3" s="28" t="n"/>
+      <c r="O3" s="28" t="n"/>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n"/>
+      <c r="R3" s="28" t="n"/>
+      <c r="S3" s="28" t="n"/>
+      <c r="T3" s="28" t="n"/>
+      <c r="U3" s="28" t="n"/>
+      <c r="V3" s="28" t="n"/>
+      <c r="W3" s="28" t="n"/>
+      <c r="X3" s="28" t="n"/>
+      <c r="Y3" s="28" t="n"/>
+      <c r="Z3" s="28" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="28" t="n"/>
+      <c r="AD3" s="28" t="n"/>
+      <c r="AE3" s="28" t="n"/>
+      <c r="AF3" s="28" t="n"/>
+      <c r="AG3" s="28" t="n"/>
+      <c r="AH3" s="28" t="n"/>
+      <c r="AI3" s="28" t="n"/>
+      <c r="AJ3" s="28" t="n"/>
+      <c r="AK3" s="28" t="n"/>
+      <c r="AL3" s="28" t="n"/>
+      <c r="AM3" s="28" t="n"/>
+      <c r="AN3" s="28" t="n"/>
+      <c r="AO3" s="28" t="n"/>
+      <c r="AP3" s="28" t="n"/>
+      <c r="AQ3" s="28" t="n"/>
+      <c r="AR3" s="28" t="n"/>
+      <c r="AS3" s="28" t="n"/>
+      <c r="AT3" s="28" t="n"/>
+      <c r="AU3" s="28" t="n"/>
+      <c r="AV3" s="28" t="n"/>
+      <c r="AW3" s="28" t="n"/>
+      <c r="AX3" s="28" t="n"/>
+      <c r="AY3" s="28" t="n"/>
+      <c r="AZ3" s="28" t="n"/>
+      <c r="BA3" s="28" t="n"/>
+      <c r="BB3" s="28" t="n"/>
+      <c r="BC3" s="28" t="n"/>
+      <c r="BD3" s="28" t="n"/>
+      <c r="BE3" s="28" t="n"/>
+      <c r="BF3" s="28" t="n"/>
+      <c r="BG3" s="28" t="n"/>
+      <c r="BH3" s="28" t="n"/>
+      <c r="BI3" s="28" t="n"/>
+      <c r="BJ3" s="28" t="n"/>
+      <c r="BK3" s="28" t="n"/>
+      <c r="BL3" s="28" t="n"/>
+      <c r="BM3" s="28" t="n"/>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="28" t="n"/>
+      <c r="BQ3" s="28" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>一期零件图纸整理归档</t>
         </is>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="31">
         <f>'时间节点计划表'!E2</f>
         <v/>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="31">
         <f>IF(COUNT('时间节点计划表'!F2),'时间节点计划表'!F2,"")</f>
         <v/>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="32">
         <f>IF(OR(D4="",E4=""),"待填",E4-D4)</f>
         <v/>
       </c>
@@ -3560,6 +3584,22 @@
       </c>
       <c r="BO4" s="23">
         <f>IF(AND(COUNT($E4),N(BO$2)=N($E4)),$E4,IF(AND(COUNT($E4),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E4))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP4" s="23">
+        <f>IF(AND(COUNT($E4),N(BP$2)=N($E4)),$E4,IF(AND(COUNT($E4),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E4))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ4" s="23">
+        <f>IF(AND(COUNT($E4),N(BQ$2)=N($E4)),$E4,IF(AND(COUNT($E4),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E4))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR4" s="23">
+        <f>IF(AND(COUNT($E4),N(BR$2)=N($E4)),$E4,IF(AND(COUNT($E4),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E4))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS4" s="23">
+        <f>IF(AND(COUNT($E4),N(BS$2)=N($E4)),$E4,IF(AND(COUNT($E4),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E4))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -3592,92 +3632,96 @@
         <f>D5</f>
         <v/>
       </c>
-      <c r="H5" s="31" t="n"/>
+      <c r="H5" s="26" t="n"/>
       <c r="I5" s="26" t="n"/>
       <c r="J5" s="26" t="n"/>
       <c r="K5" s="26" t="n"/>
-      <c r="L5" s="26" t="n"/>
-      <c r="M5" s="26" t="n"/>
-      <c r="N5" s="26" t="n"/>
-      <c r="O5" s="26" t="n"/>
-      <c r="P5" s="26" t="n"/>
-      <c r="Q5" s="26" t="n"/>
-      <c r="R5" s="26" t="n"/>
-      <c r="S5" s="26" t="n"/>
-      <c r="T5" s="26" t="n"/>
-      <c r="U5" s="26" t="n"/>
-      <c r="V5" s="26" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
-      <c r="Y5" s="26" t="n"/>
-      <c r="Z5" s="26" t="n"/>
-      <c r="AA5" s="26" t="n"/>
-      <c r="AB5" s="26" t="n"/>
-      <c r="AC5" s="26" t="n"/>
-      <c r="AD5" s="26" t="n"/>
-      <c r="AE5" s="26" t="n"/>
-      <c r="AF5" s="26" t="n"/>
-      <c r="AG5" s="26" t="n"/>
-      <c r="AH5" s="26" t="n"/>
-      <c r="AI5" s="26" t="n"/>
-      <c r="AJ5" s="26" t="n"/>
-      <c r="AK5" s="26" t="n"/>
-      <c r="AL5" s="26" t="n"/>
-      <c r="AM5" s="26" t="n"/>
-      <c r="AN5" s="26" t="n"/>
-      <c r="AO5" s="26" t="n"/>
-      <c r="AP5" s="26" t="n"/>
-      <c r="AQ5" s="26" t="n"/>
-      <c r="AR5" s="26" t="n"/>
-      <c r="AS5" s="26" t="n"/>
-      <c r="AT5" s="26" t="n"/>
-      <c r="AU5" s="26" t="n"/>
-      <c r="AV5" s="26" t="n"/>
-      <c r="AW5" s="26" t="n"/>
-      <c r="AX5" s="26" t="n"/>
-      <c r="AY5" s="26" t="n"/>
-      <c r="AZ5" s="26" t="n"/>
-      <c r="BA5" s="26" t="n"/>
-      <c r="BB5" s="26" t="n"/>
-      <c r="BC5" s="26" t="n"/>
-      <c r="BD5" s="26" t="n"/>
-      <c r="BE5" s="26" t="n"/>
-      <c r="BF5" s="26" t="n"/>
-      <c r="BG5" s="26" t="n"/>
-      <c r="BH5" s="26" t="n"/>
-      <c r="BI5" s="26" t="n"/>
-      <c r="BJ5" s="26" t="n"/>
-      <c r="BK5" s="26" t="n"/>
-      <c r="BL5" s="26" t="n"/>
-      <c r="BM5" s="26" t="n"/>
-      <c r="BN5" s="26" t="n"/>
-      <c r="BO5" s="26" t="n"/>
+      <c r="L5" s="27" t="n"/>
+      <c r="M5" s="28" t="n"/>
+      <c r="N5" s="28" t="n"/>
+      <c r="O5" s="28" t="n"/>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n"/>
+      <c r="R5" s="28" t="n"/>
+      <c r="S5" s="28" t="n"/>
+      <c r="T5" s="28" t="n"/>
+      <c r="U5" s="28" t="n"/>
+      <c r="V5" s="28" t="n"/>
+      <c r="W5" s="28" t="n"/>
+      <c r="X5" s="28" t="n"/>
+      <c r="Y5" s="28" t="n"/>
+      <c r="Z5" s="28" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="28" t="n"/>
+      <c r="AD5" s="28" t="n"/>
+      <c r="AE5" s="28" t="n"/>
+      <c r="AF5" s="28" t="n"/>
+      <c r="AG5" s="28" t="n"/>
+      <c r="AH5" s="28" t="n"/>
+      <c r="AI5" s="28" t="n"/>
+      <c r="AJ5" s="28" t="n"/>
+      <c r="AK5" s="28" t="n"/>
+      <c r="AL5" s="28" t="n"/>
+      <c r="AM5" s="28" t="n"/>
+      <c r="AN5" s="28" t="n"/>
+      <c r="AO5" s="28" t="n"/>
+      <c r="AP5" s="28" t="n"/>
+      <c r="AQ5" s="28" t="n"/>
+      <c r="AR5" s="28" t="n"/>
+      <c r="AS5" s="28" t="n"/>
+      <c r="AT5" s="28" t="n"/>
+      <c r="AU5" s="28" t="n"/>
+      <c r="AV5" s="28" t="n"/>
+      <c r="AW5" s="28" t="n"/>
+      <c r="AX5" s="28" t="n"/>
+      <c r="AY5" s="28" t="n"/>
+      <c r="AZ5" s="28" t="n"/>
+      <c r="BA5" s="28" t="n"/>
+      <c r="BB5" s="28" t="n"/>
+      <c r="BC5" s="28" t="n"/>
+      <c r="BD5" s="28" t="n"/>
+      <c r="BE5" s="28" t="n"/>
+      <c r="BF5" s="28" t="n"/>
+      <c r="BG5" s="28" t="n"/>
+      <c r="BH5" s="28" t="n"/>
+      <c r="BI5" s="28" t="n"/>
+      <c r="BJ5" s="28" t="n"/>
+      <c r="BK5" s="28" t="n"/>
+      <c r="BL5" s="28" t="n"/>
+      <c r="BM5" s="28" t="n"/>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="28" t="n"/>
+      <c r="BQ5" s="28" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>一期零件下单采购</t>
         </is>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="31">
         <f>'时间节点计划表'!E3</f>
         <v/>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="31">
         <f>IF(COUNT('时间节点计划表'!F3),'时间节点计划表'!F3,"")</f>
         <v/>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="32">
         <f>IF(OR(D6="",E6=""),"待填",E6-D6)</f>
         <v/>
       </c>
@@ -3923,6 +3967,22 @@
       </c>
       <c r="BO6" s="23">
         <f>IF(AND(COUNT($E6),N(BO$2)=N($E6)),$E6,IF(AND(COUNT($E6),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E6))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP6" s="23">
+        <f>IF(AND(COUNT($E6),N(BP$2)=N($E6)),$E6,IF(AND(COUNT($E6),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E6))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ6" s="23">
+        <f>IF(AND(COUNT($E6),N(BQ$2)=N($E6)),$E6,IF(AND(COUNT($E6),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E6))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR6" s="23">
+        <f>IF(AND(COUNT($E6),N(BR$2)=N($E6)),$E6,IF(AND(COUNT($E6),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E6))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS6" s="23">
+        <f>IF(AND(COUNT($E6),N(BS$2)=N($E6)),$E6,IF(AND(COUNT($E6),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E6))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -3955,92 +4015,96 @@
         <f>D7</f>
         <v/>
       </c>
-      <c r="H7" s="31" t="n"/>
+      <c r="H7" s="26" t="n"/>
       <c r="I7" s="26" t="n"/>
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
-      <c r="L7" s="26" t="n"/>
-      <c r="M7" s="26" t="n"/>
-      <c r="N7" s="26" t="n"/>
-      <c r="O7" s="26" t="n"/>
-      <c r="P7" s="26" t="n"/>
-      <c r="Q7" s="26" t="n"/>
-      <c r="R7" s="26" t="n"/>
-      <c r="S7" s="26" t="n"/>
-      <c r="T7" s="26" t="n"/>
-      <c r="U7" s="26" t="n"/>
-      <c r="V7" s="26" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
-      <c r="Y7" s="26" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="26" t="n"/>
-      <c r="AB7" s="26" t="n"/>
-      <c r="AC7" s="26" t="n"/>
-      <c r="AD7" s="26" t="n"/>
-      <c r="AE7" s="26" t="n"/>
-      <c r="AF7" s="26" t="n"/>
-      <c r="AG7" s="26" t="n"/>
-      <c r="AH7" s="26" t="n"/>
-      <c r="AI7" s="26" t="n"/>
-      <c r="AJ7" s="26" t="n"/>
-      <c r="AK7" s="26" t="n"/>
-      <c r="AL7" s="26" t="n"/>
-      <c r="AM7" s="26" t="n"/>
-      <c r="AN7" s="26" t="n"/>
-      <c r="AO7" s="26" t="n"/>
-      <c r="AP7" s="26" t="n"/>
-      <c r="AQ7" s="26" t="n"/>
-      <c r="AR7" s="26" t="n"/>
-      <c r="AS7" s="26" t="n"/>
-      <c r="AT7" s="26" t="n"/>
-      <c r="AU7" s="26" t="n"/>
-      <c r="AV7" s="26" t="n"/>
-      <c r="AW7" s="26" t="n"/>
-      <c r="AX7" s="26" t="n"/>
-      <c r="AY7" s="26" t="n"/>
-      <c r="AZ7" s="26" t="n"/>
-      <c r="BA7" s="26" t="n"/>
-      <c r="BB7" s="26" t="n"/>
-      <c r="BC7" s="26" t="n"/>
-      <c r="BD7" s="26" t="n"/>
-      <c r="BE7" s="26" t="n"/>
-      <c r="BF7" s="26" t="n"/>
-      <c r="BG7" s="26" t="n"/>
-      <c r="BH7" s="26" t="n"/>
-      <c r="BI7" s="26" t="n"/>
-      <c r="BJ7" s="26" t="n"/>
-      <c r="BK7" s="26" t="n"/>
-      <c r="BL7" s="26" t="n"/>
-      <c r="BM7" s="26" t="n"/>
-      <c r="BN7" s="26" t="n"/>
-      <c r="BO7" s="26" t="n"/>
+      <c r="L7" s="27" t="n"/>
+      <c r="M7" s="28" t="n"/>
+      <c r="N7" s="28" t="n"/>
+      <c r="O7" s="28" t="n"/>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n"/>
+      <c r="R7" s="28" t="n"/>
+      <c r="S7" s="28" t="n"/>
+      <c r="T7" s="28" t="n"/>
+      <c r="U7" s="28" t="n"/>
+      <c r="V7" s="28" t="n"/>
+      <c r="W7" s="28" t="n"/>
+      <c r="X7" s="28" t="n"/>
+      <c r="Y7" s="28" t="n"/>
+      <c r="Z7" s="28" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="28" t="n"/>
+      <c r="AD7" s="28" t="n"/>
+      <c r="AE7" s="28" t="n"/>
+      <c r="AF7" s="28" t="n"/>
+      <c r="AG7" s="28" t="n"/>
+      <c r="AH7" s="28" t="n"/>
+      <c r="AI7" s="28" t="n"/>
+      <c r="AJ7" s="28" t="n"/>
+      <c r="AK7" s="28" t="n"/>
+      <c r="AL7" s="28" t="n"/>
+      <c r="AM7" s="28" t="n"/>
+      <c r="AN7" s="28" t="n"/>
+      <c r="AO7" s="28" t="n"/>
+      <c r="AP7" s="28" t="n"/>
+      <c r="AQ7" s="28" t="n"/>
+      <c r="AR7" s="28" t="n"/>
+      <c r="AS7" s="28" t="n"/>
+      <c r="AT7" s="28" t="n"/>
+      <c r="AU7" s="28" t="n"/>
+      <c r="AV7" s="28" t="n"/>
+      <c r="AW7" s="28" t="n"/>
+      <c r="AX7" s="28" t="n"/>
+      <c r="AY7" s="28" t="n"/>
+      <c r="AZ7" s="28" t="n"/>
+      <c r="BA7" s="28" t="n"/>
+      <c r="BB7" s="28" t="n"/>
+      <c r="BC7" s="28" t="n"/>
+      <c r="BD7" s="28" t="n"/>
+      <c r="BE7" s="28" t="n"/>
+      <c r="BF7" s="28" t="n"/>
+      <c r="BG7" s="28" t="n"/>
+      <c r="BH7" s="28" t="n"/>
+      <c r="BI7" s="28" t="n"/>
+      <c r="BJ7" s="28" t="n"/>
+      <c r="BK7" s="28" t="n"/>
+      <c r="BL7" s="28" t="n"/>
+      <c r="BM7" s="28" t="n"/>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="28" t="n"/>
+      <c r="BQ7" s="28" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>一期标准件下单采购</t>
         </is>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="31">
         <f>'时间节点计划表'!E4</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="31">
         <f>IF(COUNT('时间节点计划表'!F4),'时间节点计划表'!F4,"")</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="32">
         <f>IF(OR(D8="",E8=""),"待填",E8-D8)</f>
         <v/>
       </c>
@@ -4286,6 +4350,22 @@
       </c>
       <c r="BO8" s="23">
         <f>IF(AND(COUNT($E8),N(BO$2)=N($E8)),$E8,IF(AND(COUNT($E8),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E8))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP8" s="23">
+        <f>IF(AND(COUNT($E8),N(BP$2)=N($E8)),$E8,IF(AND(COUNT($E8),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E8))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ8" s="23">
+        <f>IF(AND(COUNT($E8),N(BQ$2)=N($E8)),$E8,IF(AND(COUNT($E8),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E8))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR8" s="23">
+        <f>IF(AND(COUNT($E8),N(BR$2)=N($E8)),$E8,IF(AND(COUNT($E8),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E8))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS8" s="23">
+        <f>IF(AND(COUNT($E8),N(BS$2)=N($E8)),$E8,IF(AND(COUNT($E8),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E8))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -4318,92 +4398,96 @@
         <f>D9</f>
         <v/>
       </c>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="32" t="n"/>
-      <c r="J9" s="32" t="n"/>
-      <c r="K9" s="32" t="n"/>
-      <c r="L9" s="32" t="n"/>
-      <c r="M9" s="32" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="32" t="n"/>
-      <c r="P9" s="32" t="n"/>
-      <c r="Q9" s="32" t="n"/>
-      <c r="R9" s="32" t="n"/>
-      <c r="S9" s="32" t="n"/>
-      <c r="T9" s="32" t="n"/>
-      <c r="U9" s="32" t="n"/>
-      <c r="V9" s="32" t="n"/>
-      <c r="W9" s="32" t="n"/>
-      <c r="X9" s="32" t="n"/>
-      <c r="Y9" s="32" t="n"/>
-      <c r="Z9" s="32" t="n"/>
-      <c r="AA9" s="32" t="n"/>
-      <c r="AB9" s="32" t="n"/>
-      <c r="AC9" s="31" t="n"/>
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="26" t="n"/>
+      <c r="J9" s="26" t="n"/>
+      <c r="K9" s="26" t="n"/>
+      <c r="L9" s="26" t="n"/>
+      <c r="M9" s="26" t="n"/>
+      <c r="N9" s="26" t="n"/>
+      <c r="O9" s="26" t="n"/>
+      <c r="P9" s="26" t="n"/>
+      <c r="Q9" s="26" t="n"/>
+      <c r="R9" s="26" t="n"/>
+      <c r="S9" s="26" t="n"/>
+      <c r="T9" s="26" t="n"/>
+      <c r="U9" s="26" t="n"/>
+      <c r="V9" s="26" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="26" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="26" t="n"/>
+      <c r="AB9" s="26" t="n"/>
+      <c r="AC9" s="26" t="n"/>
       <c r="AD9" s="26" t="n"/>
       <c r="AE9" s="26" t="n"/>
       <c r="AF9" s="26" t="n"/>
-      <c r="AG9" s="26" t="n"/>
-      <c r="AH9" s="26" t="n"/>
-      <c r="AI9" s="26" t="n"/>
-      <c r="AJ9" s="26" t="n"/>
-      <c r="AK9" s="26" t="n"/>
-      <c r="AL9" s="26" t="n"/>
-      <c r="AM9" s="26" t="n"/>
-      <c r="AN9" s="26" t="n"/>
-      <c r="AO9" s="26" t="n"/>
-      <c r="AP9" s="26" t="n"/>
-      <c r="AQ9" s="26" t="n"/>
-      <c r="AR9" s="26" t="n"/>
-      <c r="AS9" s="26" t="n"/>
-      <c r="AT9" s="26" t="n"/>
-      <c r="AU9" s="26" t="n"/>
-      <c r="AV9" s="26" t="n"/>
-      <c r="AW9" s="26" t="n"/>
-      <c r="AX9" s="26" t="n"/>
-      <c r="AY9" s="26" t="n"/>
-      <c r="AZ9" s="26" t="n"/>
-      <c r="BA9" s="26" t="n"/>
-      <c r="BB9" s="26" t="n"/>
-      <c r="BC9" s="26" t="n"/>
-      <c r="BD9" s="26" t="n"/>
-      <c r="BE9" s="26" t="n"/>
-      <c r="BF9" s="26" t="n"/>
-      <c r="BG9" s="26" t="n"/>
-      <c r="BH9" s="26" t="n"/>
-      <c r="BI9" s="26" t="n"/>
-      <c r="BJ9" s="26" t="n"/>
-      <c r="BK9" s="26" t="n"/>
-      <c r="BL9" s="26" t="n"/>
-      <c r="BM9" s="26" t="n"/>
-      <c r="BN9" s="26" t="n"/>
-      <c r="BO9" s="26" t="n"/>
+      <c r="AG9" s="27" t="n"/>
+      <c r="AH9" s="28" t="n"/>
+      <c r="AI9" s="28" t="n"/>
+      <c r="AJ9" s="28" t="n"/>
+      <c r="AK9" s="28" t="n"/>
+      <c r="AL9" s="28" t="n"/>
+      <c r="AM9" s="28" t="n"/>
+      <c r="AN9" s="28" t="n"/>
+      <c r="AO9" s="28" t="n"/>
+      <c r="AP9" s="28" t="n"/>
+      <c r="AQ9" s="28" t="n"/>
+      <c r="AR9" s="28" t="n"/>
+      <c r="AS9" s="28" t="n"/>
+      <c r="AT9" s="28" t="n"/>
+      <c r="AU9" s="28" t="n"/>
+      <c r="AV9" s="28" t="n"/>
+      <c r="AW9" s="28" t="n"/>
+      <c r="AX9" s="28" t="n"/>
+      <c r="AY9" s="28" t="n"/>
+      <c r="AZ9" s="28" t="n"/>
+      <c r="BA9" s="28" t="n"/>
+      <c r="BB9" s="28" t="n"/>
+      <c r="BC9" s="28" t="n"/>
+      <c r="BD9" s="28" t="n"/>
+      <c r="BE9" s="28" t="n"/>
+      <c r="BF9" s="28" t="n"/>
+      <c r="BG9" s="28" t="n"/>
+      <c r="BH9" s="28" t="n"/>
+      <c r="BI9" s="28" t="n"/>
+      <c r="BJ9" s="28" t="n"/>
+      <c r="BK9" s="28" t="n"/>
+      <c r="BL9" s="28" t="n"/>
+      <c r="BM9" s="28" t="n"/>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="28" t="n"/>
+      <c r="BQ9" s="28" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>装配线布局完成</t>
         </is>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="31">
         <f>'时间节点计划表'!E5</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="31">
         <f>IF(COUNT('时间节点计划表'!F5),'时间节点计划表'!F5,"")</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="32">
         <f>IF(OR(D10="",E10=""),"待填",E10-D10)</f>
         <v/>
       </c>
@@ -4649,6 +4733,22 @@
       </c>
       <c r="BO10" s="23">
         <f>IF(AND(COUNT($E10),N(BO$2)=N($E10)),$E10,IF(AND(COUNT($E10),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E10))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP10" s="23">
+        <f>IF(AND(COUNT($E10),N(BP$2)=N($E10)),$E10,IF(AND(COUNT($E10),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E10))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ10" s="23">
+        <f>IF(AND(COUNT($E10),N(BQ$2)=N($E10)),$E10,IF(AND(COUNT($E10),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E10))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR10" s="23">
+        <f>IF(AND(COUNT($E10),N(BR$2)=N($E10)),$E10,IF(AND(COUNT($E10),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E10))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS10" s="23">
+        <f>IF(AND(COUNT($E10),N(BS$2)=N($E10)),$E10,IF(AND(COUNT($E10),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E10))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -4681,92 +4781,96 @@
         <f>D11</f>
         <v/>
       </c>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="32" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="32" t="n"/>
-      <c r="M11" s="32" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="32" t="n"/>
-      <c r="P11" s="32" t="n"/>
-      <c r="Q11" s="32" t="n"/>
-      <c r="R11" s="32" t="n"/>
-      <c r="S11" s="32" t="n"/>
-      <c r="T11" s="32" t="n"/>
-      <c r="U11" s="32" t="n"/>
-      <c r="V11" s="32" t="n"/>
-      <c r="W11" s="32" t="n"/>
-      <c r="X11" s="31" t="n"/>
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="26" t="n"/>
+      <c r="J11" s="26" t="n"/>
+      <c r="K11" s="26" t="n"/>
+      <c r="L11" s="26" t="n"/>
+      <c r="M11" s="26" t="n"/>
+      <c r="N11" s="26" t="n"/>
+      <c r="O11" s="26" t="n"/>
+      <c r="P11" s="26" t="n"/>
+      <c r="Q11" s="26" t="n"/>
+      <c r="R11" s="26" t="n"/>
+      <c r="S11" s="26" t="n"/>
+      <c r="T11" s="26" t="n"/>
+      <c r="U11" s="26" t="n"/>
+      <c r="V11" s="26" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
       <c r="Y11" s="26" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="26" t="n"/>
-      <c r="AB11" s="26" t="n"/>
-      <c r="AC11" s="26" t="n"/>
-      <c r="AD11" s="26" t="n"/>
-      <c r="AE11" s="26" t="n"/>
-      <c r="AF11" s="26" t="n"/>
-      <c r="AG11" s="26" t="n"/>
-      <c r="AH11" s="26" t="n"/>
-      <c r="AI11" s="26" t="n"/>
-      <c r="AJ11" s="26" t="n"/>
-      <c r="AK11" s="26" t="n"/>
-      <c r="AL11" s="26" t="n"/>
-      <c r="AM11" s="26" t="n"/>
-      <c r="AN11" s="26" t="n"/>
-      <c r="AO11" s="26" t="n"/>
-      <c r="AP11" s="26" t="n"/>
-      <c r="AQ11" s="26" t="n"/>
-      <c r="AR11" s="26" t="n"/>
-      <c r="AS11" s="26" t="n"/>
-      <c r="AT11" s="26" t="n"/>
-      <c r="AU11" s="26" t="n"/>
-      <c r="AV11" s="26" t="n"/>
-      <c r="AW11" s="26" t="n"/>
-      <c r="AX11" s="26" t="n"/>
-      <c r="AY11" s="26" t="n"/>
-      <c r="AZ11" s="26" t="n"/>
-      <c r="BA11" s="26" t="n"/>
-      <c r="BB11" s="26" t="n"/>
-      <c r="BC11" s="26" t="n"/>
-      <c r="BD11" s="26" t="n"/>
-      <c r="BE11" s="26" t="n"/>
-      <c r="BF11" s="26" t="n"/>
-      <c r="BG11" s="26" t="n"/>
-      <c r="BH11" s="26" t="n"/>
-      <c r="BI11" s="26" t="n"/>
-      <c r="BJ11" s="26" t="n"/>
-      <c r="BK11" s="26" t="n"/>
-      <c r="BL11" s="26" t="n"/>
-      <c r="BM11" s="26" t="n"/>
-      <c r="BN11" s="26" t="n"/>
-      <c r="BO11" s="26" t="n"/>
+      <c r="AB11" s="27" t="n"/>
+      <c r="AC11" s="28" t="n"/>
+      <c r="AD11" s="28" t="n"/>
+      <c r="AE11" s="28" t="n"/>
+      <c r="AF11" s="28" t="n"/>
+      <c r="AG11" s="28" t="n"/>
+      <c r="AH11" s="28" t="n"/>
+      <c r="AI11" s="28" t="n"/>
+      <c r="AJ11" s="28" t="n"/>
+      <c r="AK11" s="28" t="n"/>
+      <c r="AL11" s="28" t="n"/>
+      <c r="AM11" s="28" t="n"/>
+      <c r="AN11" s="28" t="n"/>
+      <c r="AO11" s="28" t="n"/>
+      <c r="AP11" s="28" t="n"/>
+      <c r="AQ11" s="28" t="n"/>
+      <c r="AR11" s="28" t="n"/>
+      <c r="AS11" s="28" t="n"/>
+      <c r="AT11" s="28" t="n"/>
+      <c r="AU11" s="28" t="n"/>
+      <c r="AV11" s="28" t="n"/>
+      <c r="AW11" s="28" t="n"/>
+      <c r="AX11" s="28" t="n"/>
+      <c r="AY11" s="28" t="n"/>
+      <c r="AZ11" s="28" t="n"/>
+      <c r="BA11" s="28" t="n"/>
+      <c r="BB11" s="28" t="n"/>
+      <c r="BC11" s="28" t="n"/>
+      <c r="BD11" s="28" t="n"/>
+      <c r="BE11" s="28" t="n"/>
+      <c r="BF11" s="28" t="n"/>
+      <c r="BG11" s="28" t="n"/>
+      <c r="BH11" s="28" t="n"/>
+      <c r="BI11" s="28" t="n"/>
+      <c r="BJ11" s="28" t="n"/>
+      <c r="BK11" s="28" t="n"/>
+      <c r="BL11" s="28" t="n"/>
+      <c r="BM11" s="28" t="n"/>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="28" t="n"/>
+      <c r="BQ11" s="28" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>装配工具到位</t>
         </is>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="31">
         <f>'时间节点计划表'!E6</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="31">
         <f>IF(COUNT('时间节点计划表'!F6),'时间节点计划表'!F6,"")</f>
         <v/>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="32">
         <f>IF(OR(D12="",E12=""),"待填",E12-D12)</f>
         <v/>
       </c>
@@ -5012,6 +5116,22 @@
       </c>
       <c r="BO12" s="23">
         <f>IF(AND(COUNT($E12),N(BO$2)=N($E12)),$E12,IF(AND(COUNT($E12),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E12))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP12" s="23">
+        <f>IF(AND(COUNT($E12),N(BP$2)=N($E12)),$E12,IF(AND(COUNT($E12),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E12))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ12" s="23">
+        <f>IF(AND(COUNT($E12),N(BQ$2)=N($E12)),$E12,IF(AND(COUNT($E12),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E12))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR12" s="23">
+        <f>IF(AND(COUNT($E12),N(BR$2)=N($E12)),$E12,IF(AND(COUNT($E12),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E12))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS12" s="23">
+        <f>IF(AND(COUNT($E12),N(BS$2)=N($E12)),$E12,IF(AND(COUNT($E12),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E12))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -5044,92 +5164,96 @@
         <f>D13</f>
         <v/>
       </c>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="32" t="n"/>
-      <c r="J13" s="32" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="32" t="n"/>
-      <c r="M13" s="32" t="n"/>
-      <c r="N13" s="32" t="n"/>
-      <c r="O13" s="32" t="n"/>
-      <c r="P13" s="32" t="n"/>
-      <c r="Q13" s="32" t="n"/>
-      <c r="R13" s="32" t="n"/>
-      <c r="S13" s="32" t="n"/>
-      <c r="T13" s="32" t="n"/>
-      <c r="U13" s="32" t="n"/>
-      <c r="V13" s="32" t="n"/>
-      <c r="W13" s="32" t="n"/>
-      <c r="X13" s="32" t="n"/>
-      <c r="Y13" s="32" t="n"/>
-      <c r="Z13" s="32" t="n"/>
-      <c r="AA13" s="32" t="n"/>
-      <c r="AB13" s="32" t="n"/>
-      <c r="AC13" s="32" t="n"/>
-      <c r="AD13" s="32" t="n"/>
-      <c r="AE13" s="32" t="n"/>
-      <c r="AF13" s="32" t="n"/>
-      <c r="AG13" s="32" t="n"/>
-      <c r="AH13" s="32" t="n"/>
-      <c r="AI13" s="32" t="n"/>
-      <c r="AJ13" s="32" t="n"/>
-      <c r="AK13" s="32" t="n"/>
-      <c r="AL13" s="31" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="26" t="n"/>
+      <c r="K13" s="26" t="n"/>
+      <c r="L13" s="26" t="n"/>
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="26" t="n"/>
+      <c r="O13" s="26" t="n"/>
+      <c r="P13" s="26" t="n"/>
+      <c r="Q13" s="26" t="n"/>
+      <c r="R13" s="26" t="n"/>
+      <c r="S13" s="26" t="n"/>
+      <c r="T13" s="26" t="n"/>
+      <c r="U13" s="26" t="n"/>
+      <c r="V13" s="26" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="26" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="26" t="n"/>
+      <c r="AB13" s="26" t="n"/>
+      <c r="AC13" s="26" t="n"/>
+      <c r="AD13" s="26" t="n"/>
+      <c r="AE13" s="26" t="n"/>
+      <c r="AF13" s="26" t="n"/>
+      <c r="AG13" s="26" t="n"/>
+      <c r="AH13" s="26" t="n"/>
+      <c r="AI13" s="26" t="n"/>
+      <c r="AJ13" s="26" t="n"/>
+      <c r="AK13" s="26" t="n"/>
+      <c r="AL13" s="26" t="n"/>
       <c r="AM13" s="26" t="n"/>
       <c r="AN13" s="26" t="n"/>
       <c r="AO13" s="26" t="n"/>
-      <c r="AP13" s="26" t="n"/>
-      <c r="AQ13" s="26" t="n"/>
-      <c r="AR13" s="26" t="n"/>
-      <c r="AS13" s="26" t="n"/>
-      <c r="AT13" s="26" t="n"/>
-      <c r="AU13" s="26" t="n"/>
-      <c r="AV13" s="26" t="n"/>
-      <c r="AW13" s="26" t="n"/>
-      <c r="AX13" s="26" t="n"/>
-      <c r="AY13" s="26" t="n"/>
-      <c r="AZ13" s="26" t="n"/>
-      <c r="BA13" s="26" t="n"/>
-      <c r="BB13" s="26" t="n"/>
-      <c r="BC13" s="26" t="n"/>
-      <c r="BD13" s="26" t="n"/>
-      <c r="BE13" s="26" t="n"/>
-      <c r="BF13" s="26" t="n"/>
-      <c r="BG13" s="26" t="n"/>
-      <c r="BH13" s="26" t="n"/>
-      <c r="BI13" s="26" t="n"/>
-      <c r="BJ13" s="26" t="n"/>
-      <c r="BK13" s="26" t="n"/>
-      <c r="BL13" s="26" t="n"/>
-      <c r="BM13" s="26" t="n"/>
-      <c r="BN13" s="26" t="n"/>
-      <c r="BO13" s="26" t="n"/>
+      <c r="AP13" s="27" t="n"/>
+      <c r="AQ13" s="28" t="n"/>
+      <c r="AR13" s="28" t="n"/>
+      <c r="AS13" s="28" t="n"/>
+      <c r="AT13" s="28" t="n"/>
+      <c r="AU13" s="28" t="n"/>
+      <c r="AV13" s="28" t="n"/>
+      <c r="AW13" s="28" t="n"/>
+      <c r="AX13" s="28" t="n"/>
+      <c r="AY13" s="28" t="n"/>
+      <c r="AZ13" s="28" t="n"/>
+      <c r="BA13" s="28" t="n"/>
+      <c r="BB13" s="28" t="n"/>
+      <c r="BC13" s="28" t="n"/>
+      <c r="BD13" s="28" t="n"/>
+      <c r="BE13" s="28" t="n"/>
+      <c r="BF13" s="28" t="n"/>
+      <c r="BG13" s="28" t="n"/>
+      <c r="BH13" s="28" t="n"/>
+      <c r="BI13" s="28" t="n"/>
+      <c r="BJ13" s="28" t="n"/>
+      <c r="BK13" s="28" t="n"/>
+      <c r="BL13" s="28" t="n"/>
+      <c r="BM13" s="28" t="n"/>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="28" t="n"/>
+      <c r="BQ13" s="28" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>PAB060·零件到位</t>
         </is>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="31">
         <f>'时间节点计划表'!E7</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="31">
         <f>IF(COUNT('时间节点计划表'!F7),'时间节点计划表'!F7,"")</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="32">
         <f>IF(OR(D14="",E14=""),"待填",E14-D14)</f>
         <v/>
       </c>
@@ -5375,6 +5499,22 @@
       </c>
       <c r="BO14" s="23">
         <f>IF(AND(COUNT($E14),N(BO$2)=N($E14)),$E14,IF(AND(COUNT($E14),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E14))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP14" s="23">
+        <f>IF(AND(COUNT($E14),N(BP$2)=N($E14)),$E14,IF(AND(COUNT($E14),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E14))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ14" s="23">
+        <f>IF(AND(COUNT($E14),N(BQ$2)=N($E14)),$E14,IF(AND(COUNT($E14),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E14))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR14" s="23">
+        <f>IF(AND(COUNT($E14),N(BR$2)=N($E14)),$E14,IF(AND(COUNT($E14),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E14))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS14" s="23">
+        <f>IF(AND(COUNT($E14),N(BS$2)=N($E14)),$E14,IF(AND(COUNT($E14),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E14))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -5407,92 +5547,96 @@
         <f>D15</f>
         <v/>
       </c>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="32" t="n"/>
-      <c r="J15" s="32" t="n"/>
-      <c r="K15" s="31" t="n"/>
+      <c r="H15" s="26" t="n"/>
+      <c r="I15" s="26" t="n"/>
+      <c r="J15" s="26" t="n"/>
+      <c r="K15" s="26" t="n"/>
       <c r="L15" s="26" t="n"/>
       <c r="M15" s="26" t="n"/>
       <c r="N15" s="26" t="n"/>
-      <c r="O15" s="26" t="n"/>
-      <c r="P15" s="26" t="n"/>
-      <c r="Q15" s="26" t="n"/>
-      <c r="R15" s="26" t="n"/>
-      <c r="S15" s="26" t="n"/>
-      <c r="T15" s="26" t="n"/>
-      <c r="U15" s="26" t="n"/>
-      <c r="V15" s="26" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
-      <c r="Y15" s="26" t="n"/>
-      <c r="Z15" s="26" t="n"/>
-      <c r="AA15" s="26" t="n"/>
-      <c r="AB15" s="26" t="n"/>
-      <c r="AC15" s="26" t="n"/>
-      <c r="AD15" s="26" t="n"/>
-      <c r="AE15" s="26" t="n"/>
-      <c r="AF15" s="26" t="n"/>
-      <c r="AG15" s="26" t="n"/>
-      <c r="AH15" s="26" t="n"/>
-      <c r="AI15" s="26" t="n"/>
-      <c r="AJ15" s="26" t="n"/>
-      <c r="AK15" s="26" t="n"/>
-      <c r="AL15" s="26" t="n"/>
-      <c r="AM15" s="26" t="n"/>
-      <c r="AN15" s="26" t="n"/>
-      <c r="AO15" s="26" t="n"/>
-      <c r="AP15" s="26" t="n"/>
-      <c r="AQ15" s="26" t="n"/>
-      <c r="AR15" s="26" t="n"/>
-      <c r="AS15" s="26" t="n"/>
-      <c r="AT15" s="26" t="n"/>
-      <c r="AU15" s="26" t="n"/>
-      <c r="AV15" s="26" t="n"/>
-      <c r="AW15" s="26" t="n"/>
-      <c r="AX15" s="26" t="n"/>
-      <c r="AY15" s="26" t="n"/>
-      <c r="AZ15" s="26" t="n"/>
-      <c r="BA15" s="26" t="n"/>
-      <c r="BB15" s="26" t="n"/>
-      <c r="BC15" s="26" t="n"/>
-      <c r="BD15" s="26" t="n"/>
-      <c r="BE15" s="26" t="n"/>
-      <c r="BF15" s="26" t="n"/>
-      <c r="BG15" s="26" t="n"/>
-      <c r="BH15" s="26" t="n"/>
-      <c r="BI15" s="26" t="n"/>
-      <c r="BJ15" s="26" t="n"/>
-      <c r="BK15" s="26" t="n"/>
-      <c r="BL15" s="26" t="n"/>
-      <c r="BM15" s="26" t="n"/>
-      <c r="BN15" s="26" t="n"/>
-      <c r="BO15" s="26" t="n"/>
+      <c r="O15" s="27" t="n"/>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n"/>
+      <c r="R15" s="28" t="n"/>
+      <c r="S15" s="28" t="n"/>
+      <c r="T15" s="28" t="n"/>
+      <c r="U15" s="28" t="n"/>
+      <c r="V15" s="28" t="n"/>
+      <c r="W15" s="28" t="n"/>
+      <c r="X15" s="28" t="n"/>
+      <c r="Y15" s="28" t="n"/>
+      <c r="Z15" s="28" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="28" t="n"/>
+      <c r="AD15" s="28" t="n"/>
+      <c r="AE15" s="28" t="n"/>
+      <c r="AF15" s="28" t="n"/>
+      <c r="AG15" s="28" t="n"/>
+      <c r="AH15" s="28" t="n"/>
+      <c r="AI15" s="28" t="n"/>
+      <c r="AJ15" s="28" t="n"/>
+      <c r="AK15" s="28" t="n"/>
+      <c r="AL15" s="28" t="n"/>
+      <c r="AM15" s="28" t="n"/>
+      <c r="AN15" s="28" t="n"/>
+      <c r="AO15" s="28" t="n"/>
+      <c r="AP15" s="28" t="n"/>
+      <c r="AQ15" s="28" t="n"/>
+      <c r="AR15" s="28" t="n"/>
+      <c r="AS15" s="28" t="n"/>
+      <c r="AT15" s="28" t="n"/>
+      <c r="AU15" s="28" t="n"/>
+      <c r="AV15" s="28" t="n"/>
+      <c r="AW15" s="28" t="n"/>
+      <c r="AX15" s="28" t="n"/>
+      <c r="AY15" s="28" t="n"/>
+      <c r="AZ15" s="28" t="n"/>
+      <c r="BA15" s="28" t="n"/>
+      <c r="BB15" s="28" t="n"/>
+      <c r="BC15" s="28" t="n"/>
+      <c r="BD15" s="28" t="n"/>
+      <c r="BE15" s="28" t="n"/>
+      <c r="BF15" s="28" t="n"/>
+      <c r="BG15" s="28" t="n"/>
+      <c r="BH15" s="28" t="n"/>
+      <c r="BI15" s="28" t="n"/>
+      <c r="BJ15" s="28" t="n"/>
+      <c r="BK15" s="28" t="n"/>
+      <c r="BL15" s="28" t="n"/>
+      <c r="BM15" s="28" t="n"/>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="28" t="n"/>
+      <c r="BQ15" s="28" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>PAB060·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="31">
         <f>'时间节点计划表'!E8</f>
         <v/>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="31">
         <f>IF(COUNT('时间节点计划表'!F8),'时间节点计划表'!F8,"")</f>
         <v/>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="32">
         <f>IF(OR(D16="",E16=""),"待填",E16-D16)</f>
         <v/>
       </c>
@@ -5738,6 +5882,22 @@
       </c>
       <c r="BO16" s="23">
         <f>IF(AND(COUNT($E16),N(BO$2)=N($E16)),$E16,IF(AND(COUNT($E16),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E16))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP16" s="23">
+        <f>IF(AND(COUNT($E16),N(BP$2)=N($E16)),$E16,IF(AND(COUNT($E16),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E16))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ16" s="23">
+        <f>IF(AND(COUNT($E16),N(BQ$2)=N($E16)),$E16,IF(AND(COUNT($E16),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E16))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR16" s="23">
+        <f>IF(AND(COUNT($E16),N(BR$2)=N($E16)),$E16,IF(AND(COUNT($E16),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E16))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS16" s="23">
+        <f>IF(AND(COUNT($E16),N(BS$2)=N($E16)),$E16,IF(AND(COUNT($E16),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E16))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -5770,92 +5930,96 @@
         <f>D17</f>
         <v/>
       </c>
-      <c r="H17" s="32" t="n"/>
-      <c r="I17" s="32" t="n"/>
-      <c r="J17" s="32" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="32" t="n"/>
-      <c r="M17" s="32" t="n"/>
-      <c r="N17" s="32" t="n"/>
-      <c r="O17" s="32" t="n"/>
-      <c r="P17" s="32" t="n"/>
-      <c r="Q17" s="32" t="n"/>
-      <c r="R17" s="32" t="n"/>
-      <c r="S17" s="32" t="n"/>
-      <c r="T17" s="32" t="n"/>
-      <c r="U17" s="32" t="n"/>
-      <c r="V17" s="32" t="n"/>
-      <c r="W17" s="32" t="n"/>
-      <c r="X17" s="32" t="n"/>
-      <c r="Y17" s="32" t="n"/>
-      <c r="Z17" s="32" t="n"/>
-      <c r="AA17" s="32" t="n"/>
-      <c r="AB17" s="32" t="n"/>
-      <c r="AC17" s="31" t="n"/>
+      <c r="H17" s="26" t="n"/>
+      <c r="I17" s="26" t="n"/>
+      <c r="J17" s="26" t="n"/>
+      <c r="K17" s="26" t="n"/>
+      <c r="L17" s="26" t="n"/>
+      <c r="M17" s="26" t="n"/>
+      <c r="N17" s="26" t="n"/>
+      <c r="O17" s="26" t="n"/>
+      <c r="P17" s="26" t="n"/>
+      <c r="Q17" s="26" t="n"/>
+      <c r="R17" s="26" t="n"/>
+      <c r="S17" s="26" t="n"/>
+      <c r="T17" s="26" t="n"/>
+      <c r="U17" s="26" t="n"/>
+      <c r="V17" s="26" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="26" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="26" t="n"/>
+      <c r="AB17" s="26" t="n"/>
+      <c r="AC17" s="26" t="n"/>
       <c r="AD17" s="26" t="n"/>
       <c r="AE17" s="26" t="n"/>
       <c r="AF17" s="26" t="n"/>
-      <c r="AG17" s="26" t="n"/>
-      <c r="AH17" s="26" t="n"/>
-      <c r="AI17" s="26" t="n"/>
-      <c r="AJ17" s="26" t="n"/>
-      <c r="AK17" s="26" t="n"/>
-      <c r="AL17" s="26" t="n"/>
-      <c r="AM17" s="26" t="n"/>
-      <c r="AN17" s="26" t="n"/>
-      <c r="AO17" s="26" t="n"/>
-      <c r="AP17" s="26" t="n"/>
-      <c r="AQ17" s="26" t="n"/>
-      <c r="AR17" s="26" t="n"/>
-      <c r="AS17" s="26" t="n"/>
-      <c r="AT17" s="26" t="n"/>
-      <c r="AU17" s="26" t="n"/>
-      <c r="AV17" s="26" t="n"/>
-      <c r="AW17" s="26" t="n"/>
-      <c r="AX17" s="26" t="n"/>
-      <c r="AY17" s="26" t="n"/>
-      <c r="AZ17" s="26" t="n"/>
-      <c r="BA17" s="26" t="n"/>
-      <c r="BB17" s="26" t="n"/>
-      <c r="BC17" s="26" t="n"/>
-      <c r="BD17" s="26" t="n"/>
-      <c r="BE17" s="26" t="n"/>
-      <c r="BF17" s="26" t="n"/>
-      <c r="BG17" s="26" t="n"/>
-      <c r="BH17" s="26" t="n"/>
-      <c r="BI17" s="26" t="n"/>
-      <c r="BJ17" s="26" t="n"/>
-      <c r="BK17" s="26" t="n"/>
-      <c r="BL17" s="26" t="n"/>
-      <c r="BM17" s="26" t="n"/>
-      <c r="BN17" s="26" t="n"/>
-      <c r="BO17" s="26" t="n"/>
+      <c r="AG17" s="27" t="n"/>
+      <c r="AH17" s="28" t="n"/>
+      <c r="AI17" s="28" t="n"/>
+      <c r="AJ17" s="28" t="n"/>
+      <c r="AK17" s="28" t="n"/>
+      <c r="AL17" s="28" t="n"/>
+      <c r="AM17" s="28" t="n"/>
+      <c r="AN17" s="28" t="n"/>
+      <c r="AO17" s="28" t="n"/>
+      <c r="AP17" s="28" t="n"/>
+      <c r="AQ17" s="28" t="n"/>
+      <c r="AR17" s="28" t="n"/>
+      <c r="AS17" s="28" t="n"/>
+      <c r="AT17" s="28" t="n"/>
+      <c r="AU17" s="28" t="n"/>
+      <c r="AV17" s="28" t="n"/>
+      <c r="AW17" s="28" t="n"/>
+      <c r="AX17" s="28" t="n"/>
+      <c r="AY17" s="28" t="n"/>
+      <c r="AZ17" s="28" t="n"/>
+      <c r="BA17" s="28" t="n"/>
+      <c r="BB17" s="28" t="n"/>
+      <c r="BC17" s="28" t="n"/>
+      <c r="BD17" s="28" t="n"/>
+      <c r="BE17" s="28" t="n"/>
+      <c r="BF17" s="28" t="n"/>
+      <c r="BG17" s="28" t="n"/>
+      <c r="BH17" s="28" t="n"/>
+      <c r="BI17" s="28" t="n"/>
+      <c r="BJ17" s="28" t="n"/>
+      <c r="BK17" s="28" t="n"/>
+      <c r="BL17" s="28" t="n"/>
+      <c r="BM17" s="28" t="n"/>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="28" t="n"/>
+      <c r="BQ17" s="28" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>PAB060·工装实物到位</t>
         </is>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="31">
         <f>'时间节点计划表'!E9</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="31">
         <f>IF(COUNT('时间节点计划表'!F9),'时间节点计划表'!F9,"")</f>
         <v/>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="32">
         <f>IF(OR(D18="",E18=""),"待填",E18-D18)</f>
         <v/>
       </c>
@@ -6101,6 +6265,22 @@
       </c>
       <c r="BO18" s="23">
         <f>IF(AND(COUNT($E18),N(BO$2)=N($E18)),$E18,IF(AND(COUNT($E18),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E18))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP18" s="23">
+        <f>IF(AND(COUNT($E18),N(BP$2)=N($E18)),$E18,IF(AND(COUNT($E18),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E18))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ18" s="23">
+        <f>IF(AND(COUNT($E18),N(BQ$2)=N($E18)),$E18,IF(AND(COUNT($E18),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E18))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR18" s="23">
+        <f>IF(AND(COUNT($E18),N(BR$2)=N($E18)),$E18,IF(AND(COUNT($E18),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E18))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS18" s="23">
+        <f>IF(AND(COUNT($E18),N(BS$2)=N($E18)),$E18,IF(AND(COUNT($E18),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E18))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -6133,92 +6313,96 @@
         <f>D19</f>
         <v/>
       </c>
-      <c r="H19" s="32" t="n"/>
-      <c r="I19" s="32" t="n"/>
-      <c r="J19" s="32" t="n"/>
-      <c r="K19" s="32" t="n"/>
-      <c r="L19" s="32" t="n"/>
-      <c r="M19" s="32" t="n"/>
-      <c r="N19" s="32" t="n"/>
-      <c r="O19" s="32" t="n"/>
-      <c r="P19" s="32" t="n"/>
-      <c r="Q19" s="32" t="n"/>
-      <c r="R19" s="32" t="n"/>
-      <c r="S19" s="32" t="n"/>
-      <c r="T19" s="32" t="n"/>
-      <c r="U19" s="32" t="n"/>
-      <c r="V19" s="32" t="n"/>
-      <c r="W19" s="32" t="n"/>
-      <c r="X19" s="32" t="n"/>
-      <c r="Y19" s="32" t="n"/>
-      <c r="Z19" s="32" t="n"/>
-      <c r="AA19" s="32" t="n"/>
-      <c r="AB19" s="32" t="n"/>
-      <c r="AC19" s="32" t="n"/>
-      <c r="AD19" s="32" t="n"/>
-      <c r="AE19" s="32" t="n"/>
-      <c r="AF19" s="32" t="n"/>
-      <c r="AG19" s="32" t="n"/>
-      <c r="AH19" s="32" t="n"/>
-      <c r="AI19" s="32" t="n"/>
-      <c r="AJ19" s="32" t="n"/>
-      <c r="AK19" s="32" t="n"/>
-      <c r="AL19" s="31" t="n"/>
+      <c r="H19" s="26" t="n"/>
+      <c r="I19" s="26" t="n"/>
+      <c r="J19" s="26" t="n"/>
+      <c r="K19" s="26" t="n"/>
+      <c r="L19" s="26" t="n"/>
+      <c r="M19" s="26" t="n"/>
+      <c r="N19" s="26" t="n"/>
+      <c r="O19" s="26" t="n"/>
+      <c r="P19" s="26" t="n"/>
+      <c r="Q19" s="26" t="n"/>
+      <c r="R19" s="26" t="n"/>
+      <c r="S19" s="26" t="n"/>
+      <c r="T19" s="26" t="n"/>
+      <c r="U19" s="26" t="n"/>
+      <c r="V19" s="26" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="26" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="26" t="n"/>
+      <c r="AB19" s="26" t="n"/>
+      <c r="AC19" s="26" t="n"/>
+      <c r="AD19" s="26" t="n"/>
+      <c r="AE19" s="26" t="n"/>
+      <c r="AF19" s="26" t="n"/>
+      <c r="AG19" s="26" t="n"/>
+      <c r="AH19" s="26" t="n"/>
+      <c r="AI19" s="26" t="n"/>
+      <c r="AJ19" s="26" t="n"/>
+      <c r="AK19" s="26" t="n"/>
+      <c r="AL19" s="26" t="n"/>
       <c r="AM19" s="26" t="n"/>
       <c r="AN19" s="26" t="n"/>
       <c r="AO19" s="26" t="n"/>
-      <c r="AP19" s="26" t="n"/>
-      <c r="AQ19" s="26" t="n"/>
-      <c r="AR19" s="26" t="n"/>
-      <c r="AS19" s="26" t="n"/>
-      <c r="AT19" s="26" t="n"/>
-      <c r="AU19" s="26" t="n"/>
-      <c r="AV19" s="26" t="n"/>
-      <c r="AW19" s="26" t="n"/>
-      <c r="AX19" s="26" t="n"/>
-      <c r="AY19" s="26" t="n"/>
-      <c r="AZ19" s="26" t="n"/>
-      <c r="BA19" s="26" t="n"/>
-      <c r="BB19" s="26" t="n"/>
-      <c r="BC19" s="26" t="n"/>
-      <c r="BD19" s="26" t="n"/>
-      <c r="BE19" s="26" t="n"/>
-      <c r="BF19" s="26" t="n"/>
-      <c r="BG19" s="26" t="n"/>
-      <c r="BH19" s="26" t="n"/>
-      <c r="BI19" s="26" t="n"/>
-      <c r="BJ19" s="26" t="n"/>
-      <c r="BK19" s="26" t="n"/>
-      <c r="BL19" s="26" t="n"/>
-      <c r="BM19" s="26" t="n"/>
-      <c r="BN19" s="26" t="n"/>
-      <c r="BO19" s="26" t="n"/>
+      <c r="AP19" s="27" t="n"/>
+      <c r="AQ19" s="28" t="n"/>
+      <c r="AR19" s="28" t="n"/>
+      <c r="AS19" s="28" t="n"/>
+      <c r="AT19" s="28" t="n"/>
+      <c r="AU19" s="28" t="n"/>
+      <c r="AV19" s="28" t="n"/>
+      <c r="AW19" s="28" t="n"/>
+      <c r="AX19" s="28" t="n"/>
+      <c r="AY19" s="28" t="n"/>
+      <c r="AZ19" s="28" t="n"/>
+      <c r="BA19" s="28" t="n"/>
+      <c r="BB19" s="28" t="n"/>
+      <c r="BC19" s="28" t="n"/>
+      <c r="BD19" s="28" t="n"/>
+      <c r="BE19" s="28" t="n"/>
+      <c r="BF19" s="28" t="n"/>
+      <c r="BG19" s="28" t="n"/>
+      <c r="BH19" s="28" t="n"/>
+      <c r="BI19" s="28" t="n"/>
+      <c r="BJ19" s="28" t="n"/>
+      <c r="BK19" s="28" t="n"/>
+      <c r="BL19" s="28" t="n"/>
+      <c r="BM19" s="28" t="n"/>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="28" t="n"/>
+      <c r="BQ19" s="28" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>PAB060·排针机安装调试</t>
         </is>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="31">
         <f>'时间节点计划表'!E10</f>
         <v/>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="31">
         <f>IF(COUNT('时间节点计划表'!F10),'时间节点计划表'!F10,"")</f>
         <v/>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="32">
         <f>IF(OR(D20="",E20=""),"待填",E20-D20)</f>
         <v/>
       </c>
@@ -6464,6 +6648,22 @@
       </c>
       <c r="BO20" s="23">
         <f>IF(AND(COUNT($E20),N(BO$2)=N($E20)),$E20,IF(AND(COUNT($E20),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E20))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP20" s="23">
+        <f>IF(AND(COUNT($E20),N(BP$2)=N($E20)),$E20,IF(AND(COUNT($E20),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E20))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ20" s="23">
+        <f>IF(AND(COUNT($E20),N(BQ$2)=N($E20)),$E20,IF(AND(COUNT($E20),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E20))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR20" s="23">
+        <f>IF(AND(COUNT($E20),N(BR$2)=N($E20)),$E20,IF(AND(COUNT($E20),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E20))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS20" s="23">
+        <f>IF(AND(COUNT($E20),N(BS$2)=N($E20)),$E20,IF(AND(COUNT($E20),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E20))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -6496,92 +6696,96 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
-      <c r="O21" s="32" t="n"/>
-      <c r="P21" s="32" t="n"/>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="32" t="n"/>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="n"/>
-      <c r="U21" s="32" t="n"/>
-      <c r="V21" s="32" t="n"/>
-      <c r="W21" s="32" t="n"/>
-      <c r="X21" s="32" t="n"/>
-      <c r="Y21" s="32" t="n"/>
-      <c r="Z21" s="32" t="n"/>
-      <c r="AA21" s="32" t="n"/>
-      <c r="AB21" s="32" t="n"/>
-      <c r="AC21" s="32" t="n"/>
-      <c r="AD21" s="32" t="n"/>
-      <c r="AE21" s="32" t="n"/>
-      <c r="AF21" s="32" t="n"/>
-      <c r="AG21" s="32" t="n"/>
-      <c r="AH21" s="32" t="n"/>
-      <c r="AI21" s="32" t="n"/>
-      <c r="AJ21" s="32" t="n"/>
-      <c r="AK21" s="32" t="n"/>
-      <c r="AL21" s="32" t="n"/>
-      <c r="AM21" s="32" t="n"/>
-      <c r="AN21" s="31" t="n"/>
+      <c r="H21" s="26" t="n"/>
+      <c r="I21" s="26" t="n"/>
+      <c r="J21" s="26" t="n"/>
+      <c r="K21" s="26" t="n"/>
+      <c r="L21" s="26" t="n"/>
+      <c r="M21" s="26" t="n"/>
+      <c r="N21" s="26" t="n"/>
+      <c r="O21" s="26" t="n"/>
+      <c r="P21" s="26" t="n"/>
+      <c r="Q21" s="26" t="n"/>
+      <c r="R21" s="26" t="n"/>
+      <c r="S21" s="26" t="n"/>
+      <c r="T21" s="26" t="n"/>
+      <c r="U21" s="26" t="n"/>
+      <c r="V21" s="26" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="26" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="26" t="n"/>
+      <c r="AB21" s="26" t="n"/>
+      <c r="AC21" s="26" t="n"/>
+      <c r="AD21" s="26" t="n"/>
+      <c r="AE21" s="26" t="n"/>
+      <c r="AF21" s="26" t="n"/>
+      <c r="AG21" s="26" t="n"/>
+      <c r="AH21" s="26" t="n"/>
+      <c r="AI21" s="26" t="n"/>
+      <c r="AJ21" s="26" t="n"/>
+      <c r="AK21" s="26" t="n"/>
+      <c r="AL21" s="26" t="n"/>
+      <c r="AM21" s="26" t="n"/>
+      <c r="AN21" s="26" t="n"/>
       <c r="AO21" s="26" t="n"/>
       <c r="AP21" s="26" t="n"/>
       <c r="AQ21" s="26" t="n"/>
-      <c r="AR21" s="26" t="n"/>
-      <c r="AS21" s="26" t="n"/>
-      <c r="AT21" s="26" t="n"/>
-      <c r="AU21" s="26" t="n"/>
-      <c r="AV21" s="26" t="n"/>
-      <c r="AW21" s="26" t="n"/>
-      <c r="AX21" s="26" t="n"/>
-      <c r="AY21" s="26" t="n"/>
-      <c r="AZ21" s="26" t="n"/>
-      <c r="BA21" s="26" t="n"/>
-      <c r="BB21" s="26" t="n"/>
-      <c r="BC21" s="26" t="n"/>
-      <c r="BD21" s="26" t="n"/>
-      <c r="BE21" s="26" t="n"/>
-      <c r="BF21" s="26" t="n"/>
-      <c r="BG21" s="26" t="n"/>
-      <c r="BH21" s="26" t="n"/>
-      <c r="BI21" s="26" t="n"/>
-      <c r="BJ21" s="26" t="n"/>
-      <c r="BK21" s="26" t="n"/>
-      <c r="BL21" s="26" t="n"/>
-      <c r="BM21" s="26" t="n"/>
-      <c r="BN21" s="26" t="n"/>
-      <c r="BO21" s="26" t="n"/>
+      <c r="AR21" s="27" t="n"/>
+      <c r="AS21" s="28" t="n"/>
+      <c r="AT21" s="28" t="n"/>
+      <c r="AU21" s="28" t="n"/>
+      <c r="AV21" s="28" t="n"/>
+      <c r="AW21" s="28" t="n"/>
+      <c r="AX21" s="28" t="n"/>
+      <c r="AY21" s="28" t="n"/>
+      <c r="AZ21" s="28" t="n"/>
+      <c r="BA21" s="28" t="n"/>
+      <c r="BB21" s="28" t="n"/>
+      <c r="BC21" s="28" t="n"/>
+      <c r="BD21" s="28" t="n"/>
+      <c r="BE21" s="28" t="n"/>
+      <c r="BF21" s="28" t="n"/>
+      <c r="BG21" s="28" t="n"/>
+      <c r="BH21" s="28" t="n"/>
+      <c r="BI21" s="28" t="n"/>
+      <c r="BJ21" s="28" t="n"/>
+      <c r="BK21" s="28" t="n"/>
+      <c r="BL21" s="28" t="n"/>
+      <c r="BM21" s="28" t="n"/>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="28" t="n"/>
+      <c r="BQ21" s="28" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>PAB060·单级样机</t>
         </is>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="31">
         <f>'时间节点计划表'!E11</f>
         <v/>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="31">
         <f>IF(COUNT('时间节点计划表'!F11),'时间节点计划表'!F11,"")</f>
         <v/>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="32">
         <f>IF(OR(D22="",E22=""),"待填",E22-D22)</f>
         <v/>
       </c>
@@ -6827,6 +7031,22 @@
       </c>
       <c r="BO22" s="23">
         <f>IF(AND(COUNT($E22),N(BO$2)=N($E22)),$E22,IF(AND(COUNT($E22),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E22))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP22" s="23">
+        <f>IF(AND(COUNT($E22),N(BP$2)=N($E22)),$E22,IF(AND(COUNT($E22),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E22))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ22" s="23">
+        <f>IF(AND(COUNT($E22),N(BQ$2)=N($E22)),$E22,IF(AND(COUNT($E22),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E22))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR22" s="23">
+        <f>IF(AND(COUNT($E22),N(BR$2)=N($E22)),$E22,IF(AND(COUNT($E22),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E22))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS22" s="23">
+        <f>IF(AND(COUNT($E22),N(BS$2)=N($E22)),$E22,IF(AND(COUNT($E22),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E22))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -6859,92 +7079,96 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="32" t="n"/>
-      <c r="X23" s="32" t="n"/>
-      <c r="Y23" s="32" t="n"/>
-      <c r="Z23" s="32" t="n"/>
-      <c r="AA23" s="32" t="n"/>
-      <c r="AB23" s="32" t="n"/>
-      <c r="AC23" s="32" t="n"/>
-      <c r="AD23" s="32" t="n"/>
-      <c r="AE23" s="32" t="n"/>
-      <c r="AF23" s="32" t="n"/>
-      <c r="AG23" s="32" t="n"/>
-      <c r="AH23" s="32" t="n"/>
-      <c r="AI23" s="32" t="n"/>
-      <c r="AJ23" s="32" t="n"/>
-      <c r="AK23" s="32" t="n"/>
-      <c r="AL23" s="32" t="n"/>
-      <c r="AM23" s="32" t="n"/>
-      <c r="AN23" s="32" t="n"/>
-      <c r="AO23" s="32" t="n"/>
-      <c r="AP23" s="31" t="n"/>
+      <c r="H23" s="26" t="n"/>
+      <c r="I23" s="26" t="n"/>
+      <c r="J23" s="26" t="n"/>
+      <c r="K23" s="26" t="n"/>
+      <c r="L23" s="26" t="n"/>
+      <c r="M23" s="26" t="n"/>
+      <c r="N23" s="26" t="n"/>
+      <c r="O23" s="26" t="n"/>
+      <c r="P23" s="26" t="n"/>
+      <c r="Q23" s="26" t="n"/>
+      <c r="R23" s="26" t="n"/>
+      <c r="S23" s="26" t="n"/>
+      <c r="T23" s="26" t="n"/>
+      <c r="U23" s="26" t="n"/>
+      <c r="V23" s="26" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="26" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="26" t="n"/>
+      <c r="AB23" s="26" t="n"/>
+      <c r="AC23" s="26" t="n"/>
+      <c r="AD23" s="26" t="n"/>
+      <c r="AE23" s="26" t="n"/>
+      <c r="AF23" s="26" t="n"/>
+      <c r="AG23" s="26" t="n"/>
+      <c r="AH23" s="26" t="n"/>
+      <c r="AI23" s="26" t="n"/>
+      <c r="AJ23" s="26" t="n"/>
+      <c r="AK23" s="26" t="n"/>
+      <c r="AL23" s="26" t="n"/>
+      <c r="AM23" s="26" t="n"/>
+      <c r="AN23" s="26" t="n"/>
+      <c r="AO23" s="26" t="n"/>
+      <c r="AP23" s="26" t="n"/>
       <c r="AQ23" s="26" t="n"/>
       <c r="AR23" s="26" t="n"/>
       <c r="AS23" s="26" t="n"/>
-      <c r="AT23" s="26" t="n"/>
-      <c r="AU23" s="26" t="n"/>
-      <c r="AV23" s="26" t="n"/>
-      <c r="AW23" s="26" t="n"/>
-      <c r="AX23" s="26" t="n"/>
-      <c r="AY23" s="26" t="n"/>
-      <c r="AZ23" s="26" t="n"/>
-      <c r="BA23" s="26" t="n"/>
-      <c r="BB23" s="26" t="n"/>
-      <c r="BC23" s="26" t="n"/>
-      <c r="BD23" s="26" t="n"/>
-      <c r="BE23" s="26" t="n"/>
-      <c r="BF23" s="26" t="n"/>
-      <c r="BG23" s="26" t="n"/>
-      <c r="BH23" s="26" t="n"/>
-      <c r="BI23" s="26" t="n"/>
-      <c r="BJ23" s="26" t="n"/>
-      <c r="BK23" s="26" t="n"/>
-      <c r="BL23" s="26" t="n"/>
-      <c r="BM23" s="26" t="n"/>
-      <c r="BN23" s="26" t="n"/>
-      <c r="BO23" s="26" t="n"/>
+      <c r="AT23" s="27" t="n"/>
+      <c r="AU23" s="28" t="n"/>
+      <c r="AV23" s="28" t="n"/>
+      <c r="AW23" s="28" t="n"/>
+      <c r="AX23" s="28" t="n"/>
+      <c r="AY23" s="28" t="n"/>
+      <c r="AZ23" s="28" t="n"/>
+      <c r="BA23" s="28" t="n"/>
+      <c r="BB23" s="28" t="n"/>
+      <c r="BC23" s="28" t="n"/>
+      <c r="BD23" s="28" t="n"/>
+      <c r="BE23" s="28" t="n"/>
+      <c r="BF23" s="28" t="n"/>
+      <c r="BG23" s="28" t="n"/>
+      <c r="BH23" s="28" t="n"/>
+      <c r="BI23" s="28" t="n"/>
+      <c r="BJ23" s="28" t="n"/>
+      <c r="BK23" s="28" t="n"/>
+      <c r="BL23" s="28" t="n"/>
+      <c r="BM23" s="28" t="n"/>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="28" t="n"/>
+      <c r="BQ23" s="28" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>PAB060·双级样机</t>
         </is>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="31">
         <f>'时间节点计划表'!E12</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="31">
         <f>IF(COUNT('时间节点计划表'!F12),'时间节点计划表'!F12,"")</f>
         <v/>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="32">
         <f>IF(OR(D24="",E24=""),"待填",E24-D24)</f>
         <v/>
       </c>
@@ -7190,6 +7414,22 @@
       </c>
       <c r="BO24" s="23">
         <f>IF(AND(COUNT($E24),N(BO$2)=N($E24)),$E24,IF(AND(COUNT($E24),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E24))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP24" s="23">
+        <f>IF(AND(COUNT($E24),N(BP$2)=N($E24)),$E24,IF(AND(COUNT($E24),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E24))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ24" s="23">
+        <f>IF(AND(COUNT($E24),N(BQ$2)=N($E24)),$E24,IF(AND(COUNT($E24),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E24))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR24" s="23">
+        <f>IF(AND(COUNT($E24),N(BR$2)=N($E24)),$E24,IF(AND(COUNT($E24),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E24))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS24" s="23">
+        <f>IF(AND(COUNT($E24),N(BS$2)=N($E24)),$E24,IF(AND(COUNT($E24),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E24))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -7222,92 +7462,96 @@
         <f>D25</f>
         <v/>
       </c>
-      <c r="H25" s="32" t="n"/>
-      <c r="I25" s="32" t="n"/>
-      <c r="J25" s="32" t="n"/>
-      <c r="K25" s="32" t="n"/>
-      <c r="L25" s="32" t="n"/>
-      <c r="M25" s="32" t="n"/>
-      <c r="N25" s="32" t="n"/>
-      <c r="O25" s="32" t="n"/>
-      <c r="P25" s="32" t="n"/>
-      <c r="Q25" s="32" t="n"/>
-      <c r="R25" s="32" t="n"/>
-      <c r="S25" s="32" t="n"/>
-      <c r="T25" s="32" t="n"/>
-      <c r="U25" s="32" t="n"/>
-      <c r="V25" s="32" t="n"/>
-      <c r="W25" s="32" t="n"/>
-      <c r="X25" s="32" t="n"/>
-      <c r="Y25" s="32" t="n"/>
-      <c r="Z25" s="32" t="n"/>
-      <c r="AA25" s="32" t="n"/>
-      <c r="AB25" s="32" t="n"/>
-      <c r="AC25" s="32" t="n"/>
-      <c r="AD25" s="32" t="n"/>
-      <c r="AE25" s="32" t="n"/>
-      <c r="AF25" s="32" t="n"/>
-      <c r="AG25" s="32" t="n"/>
-      <c r="AH25" s="32" t="n"/>
-      <c r="AI25" s="32" t="n"/>
-      <c r="AJ25" s="32" t="n"/>
-      <c r="AK25" s="32" t="n"/>
-      <c r="AL25" s="32" t="n"/>
-      <c r="AM25" s="32" t="n"/>
-      <c r="AN25" s="32" t="n"/>
-      <c r="AO25" s="31" t="n"/>
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="26" t="n"/>
+      <c r="J25" s="26" t="n"/>
+      <c r="K25" s="26" t="n"/>
+      <c r="L25" s="26" t="n"/>
+      <c r="M25" s="26" t="n"/>
+      <c r="N25" s="26" t="n"/>
+      <c r="O25" s="26" t="n"/>
+      <c r="P25" s="26" t="n"/>
+      <c r="Q25" s="26" t="n"/>
+      <c r="R25" s="26" t="n"/>
+      <c r="S25" s="26" t="n"/>
+      <c r="T25" s="26" t="n"/>
+      <c r="U25" s="26" t="n"/>
+      <c r="V25" s="26" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="26" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="26" t="n"/>
+      <c r="AB25" s="26" t="n"/>
+      <c r="AC25" s="26" t="n"/>
+      <c r="AD25" s="26" t="n"/>
+      <c r="AE25" s="26" t="n"/>
+      <c r="AF25" s="26" t="n"/>
+      <c r="AG25" s="26" t="n"/>
+      <c r="AH25" s="26" t="n"/>
+      <c r="AI25" s="26" t="n"/>
+      <c r="AJ25" s="26" t="n"/>
+      <c r="AK25" s="26" t="n"/>
+      <c r="AL25" s="26" t="n"/>
+      <c r="AM25" s="26" t="n"/>
+      <c r="AN25" s="26" t="n"/>
+      <c r="AO25" s="26" t="n"/>
       <c r="AP25" s="26" t="n"/>
       <c r="AQ25" s="26" t="n"/>
       <c r="AR25" s="26" t="n"/>
-      <c r="AS25" s="26" t="n"/>
-      <c r="AT25" s="26" t="n"/>
-      <c r="AU25" s="26" t="n"/>
-      <c r="AV25" s="26" t="n"/>
-      <c r="AW25" s="26" t="n"/>
-      <c r="AX25" s="26" t="n"/>
-      <c r="AY25" s="26" t="n"/>
-      <c r="AZ25" s="26" t="n"/>
-      <c r="BA25" s="26" t="n"/>
-      <c r="BB25" s="26" t="n"/>
-      <c r="BC25" s="26" t="n"/>
-      <c r="BD25" s="26" t="n"/>
-      <c r="BE25" s="26" t="n"/>
-      <c r="BF25" s="26" t="n"/>
-      <c r="BG25" s="26" t="n"/>
-      <c r="BH25" s="26" t="n"/>
-      <c r="BI25" s="26" t="n"/>
-      <c r="BJ25" s="26" t="n"/>
-      <c r="BK25" s="26" t="n"/>
-      <c r="BL25" s="26" t="n"/>
-      <c r="BM25" s="26" t="n"/>
-      <c r="BN25" s="26" t="n"/>
-      <c r="BO25" s="26" t="n"/>
+      <c r="AS25" s="27" t="n"/>
+      <c r="AT25" s="28" t="n"/>
+      <c r="AU25" s="28" t="n"/>
+      <c r="AV25" s="28" t="n"/>
+      <c r="AW25" s="28" t="n"/>
+      <c r="AX25" s="28" t="n"/>
+      <c r="AY25" s="28" t="n"/>
+      <c r="AZ25" s="28" t="n"/>
+      <c r="BA25" s="28" t="n"/>
+      <c r="BB25" s="28" t="n"/>
+      <c r="BC25" s="28" t="n"/>
+      <c r="BD25" s="28" t="n"/>
+      <c r="BE25" s="28" t="n"/>
+      <c r="BF25" s="28" t="n"/>
+      <c r="BG25" s="28" t="n"/>
+      <c r="BH25" s="28" t="n"/>
+      <c r="BI25" s="28" t="n"/>
+      <c r="BJ25" s="28" t="n"/>
+      <c r="BK25" s="28" t="n"/>
+      <c r="BL25" s="28" t="n"/>
+      <c r="BM25" s="28" t="n"/>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="28" t="n"/>
+      <c r="BQ25" s="28" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="B26" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C26" s="28" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>PAB090·零件到位</t>
         </is>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="31">
         <f>'时间节点计划表'!E13</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="31">
         <f>IF(COUNT('时间节点计划表'!F13),'时间节点计划表'!F13,"")</f>
         <v/>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="32">
         <f>IF(OR(D26="",E26=""),"待填",E26-D26)</f>
         <v/>
       </c>
@@ -7553,6 +7797,22 @@
       </c>
       <c r="BO26" s="23">
         <f>IF(AND(COUNT($E26),N(BO$2)=N($E26)),$E26,IF(AND(COUNT($E26),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E26))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP26" s="23">
+        <f>IF(AND(COUNT($E26),N(BP$2)=N($E26)),$E26,IF(AND(COUNT($E26),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E26))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ26" s="23">
+        <f>IF(AND(COUNT($E26),N(BQ$2)=N($E26)),$E26,IF(AND(COUNT($E26),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E26))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR26" s="23">
+        <f>IF(AND(COUNT($E26),N(BR$2)=N($E26)),$E26,IF(AND(COUNT($E26),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E26))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS26" s="23">
+        <f>IF(AND(COUNT($E26),N(BS$2)=N($E26)),$E26,IF(AND(COUNT($E26),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E26))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -7585,92 +7845,96 @@
         <f>D27</f>
         <v/>
       </c>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="32" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="32" t="n"/>
-      <c r="M27" s="32" t="n"/>
-      <c r="N27" s="32" t="n"/>
-      <c r="O27" s="31" t="n"/>
+      <c r="H27" s="26" t="n"/>
+      <c r="I27" s="26" t="n"/>
+      <c r="J27" s="26" t="n"/>
+      <c r="K27" s="26" t="n"/>
+      <c r="L27" s="26" t="n"/>
+      <c r="M27" s="26" t="n"/>
+      <c r="N27" s="26" t="n"/>
+      <c r="O27" s="26" t="n"/>
       <c r="P27" s="26" t="n"/>
       <c r="Q27" s="26" t="n"/>
       <c r="R27" s="26" t="n"/>
-      <c r="S27" s="26" t="n"/>
-      <c r="T27" s="26" t="n"/>
-      <c r="U27" s="26" t="n"/>
-      <c r="V27" s="26" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
-      <c r="Y27" s="26" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="26" t="n"/>
-      <c r="AB27" s="26" t="n"/>
-      <c r="AC27" s="26" t="n"/>
-      <c r="AD27" s="26" t="n"/>
-      <c r="AE27" s="26" t="n"/>
-      <c r="AF27" s="26" t="n"/>
-      <c r="AG27" s="26" t="n"/>
-      <c r="AH27" s="26" t="n"/>
-      <c r="AI27" s="26" t="n"/>
-      <c r="AJ27" s="26" t="n"/>
-      <c r="AK27" s="26" t="n"/>
-      <c r="AL27" s="26" t="n"/>
-      <c r="AM27" s="26" t="n"/>
-      <c r="AN27" s="26" t="n"/>
-      <c r="AO27" s="26" t="n"/>
-      <c r="AP27" s="26" t="n"/>
-      <c r="AQ27" s="26" t="n"/>
-      <c r="AR27" s="26" t="n"/>
-      <c r="AS27" s="26" t="n"/>
-      <c r="AT27" s="26" t="n"/>
-      <c r="AU27" s="26" t="n"/>
-      <c r="AV27" s="26" t="n"/>
-      <c r="AW27" s="26" t="n"/>
-      <c r="AX27" s="26" t="n"/>
-      <c r="AY27" s="26" t="n"/>
-      <c r="AZ27" s="26" t="n"/>
-      <c r="BA27" s="26" t="n"/>
-      <c r="BB27" s="26" t="n"/>
-      <c r="BC27" s="26" t="n"/>
-      <c r="BD27" s="26" t="n"/>
-      <c r="BE27" s="26" t="n"/>
-      <c r="BF27" s="26" t="n"/>
-      <c r="BG27" s="26" t="n"/>
-      <c r="BH27" s="26" t="n"/>
-      <c r="BI27" s="26" t="n"/>
-      <c r="BJ27" s="26" t="n"/>
-      <c r="BK27" s="26" t="n"/>
-      <c r="BL27" s="26" t="n"/>
-      <c r="BM27" s="26" t="n"/>
-      <c r="BN27" s="26" t="n"/>
-      <c r="BO27" s="26" t="n"/>
+      <c r="S27" s="27" t="n"/>
+      <c r="T27" s="28" t="n"/>
+      <c r="U27" s="28" t="n"/>
+      <c r="V27" s="28" t="n"/>
+      <c r="W27" s="28" t="n"/>
+      <c r="X27" s="28" t="n"/>
+      <c r="Y27" s="28" t="n"/>
+      <c r="Z27" s="28" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="28" t="n"/>
+      <c r="AD27" s="28" t="n"/>
+      <c r="AE27" s="28" t="n"/>
+      <c r="AF27" s="28" t="n"/>
+      <c r="AG27" s="28" t="n"/>
+      <c r="AH27" s="28" t="n"/>
+      <c r="AI27" s="28" t="n"/>
+      <c r="AJ27" s="28" t="n"/>
+      <c r="AK27" s="28" t="n"/>
+      <c r="AL27" s="28" t="n"/>
+      <c r="AM27" s="28" t="n"/>
+      <c r="AN27" s="28" t="n"/>
+      <c r="AO27" s="28" t="n"/>
+      <c r="AP27" s="28" t="n"/>
+      <c r="AQ27" s="28" t="n"/>
+      <c r="AR27" s="28" t="n"/>
+      <c r="AS27" s="28" t="n"/>
+      <c r="AT27" s="28" t="n"/>
+      <c r="AU27" s="28" t="n"/>
+      <c r="AV27" s="28" t="n"/>
+      <c r="AW27" s="28" t="n"/>
+      <c r="AX27" s="28" t="n"/>
+      <c r="AY27" s="28" t="n"/>
+      <c r="AZ27" s="28" t="n"/>
+      <c r="BA27" s="28" t="n"/>
+      <c r="BB27" s="28" t="n"/>
+      <c r="BC27" s="28" t="n"/>
+      <c r="BD27" s="28" t="n"/>
+      <c r="BE27" s="28" t="n"/>
+      <c r="BF27" s="28" t="n"/>
+      <c r="BG27" s="28" t="n"/>
+      <c r="BH27" s="28" t="n"/>
+      <c r="BI27" s="28" t="n"/>
+      <c r="BJ27" s="28" t="n"/>
+      <c r="BK27" s="28" t="n"/>
+      <c r="BL27" s="28" t="n"/>
+      <c r="BM27" s="28" t="n"/>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="28" t="n"/>
+      <c r="BQ27" s="28" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>PAB090·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="31">
         <f>'时间节点计划表'!E14</f>
         <v/>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="31">
         <f>IF(COUNT('时间节点计划表'!F14),'时间节点计划表'!F14,"")</f>
         <v/>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="32">
         <f>IF(OR(D28="",E28=""),"待填",E28-D28)</f>
         <v/>
       </c>
@@ -7916,6 +8180,22 @@
       </c>
       <c r="BO28" s="23">
         <f>IF(AND(COUNT($E28),N(BO$2)=N($E28)),$E28,IF(AND(COUNT($E28),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E28))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP28" s="23">
+        <f>IF(AND(COUNT($E28),N(BP$2)=N($E28)),$E28,IF(AND(COUNT($E28),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E28))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ28" s="23">
+        <f>IF(AND(COUNT($E28),N(BQ$2)=N($E28)),$E28,IF(AND(COUNT($E28),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E28))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR28" s="23">
+        <f>IF(AND(COUNT($E28),N(BR$2)=N($E28)),$E28,IF(AND(COUNT($E28),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E28))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS28" s="23">
+        <f>IF(AND(COUNT($E28),N(BS$2)=N($E28)),$E28,IF(AND(COUNT($E28),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E28))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -7948,92 +8228,96 @@
         <f>D29</f>
         <v/>
       </c>
-      <c r="H29" s="32" t="n"/>
-      <c r="I29" s="32" t="n"/>
-      <c r="J29" s="32" t="n"/>
-      <c r="K29" s="32" t="n"/>
-      <c r="L29" s="32" t="n"/>
-      <c r="M29" s="32" t="n"/>
-      <c r="N29" s="32" t="n"/>
-      <c r="O29" s="32" t="n"/>
-      <c r="P29" s="32" t="n"/>
-      <c r="Q29" s="32" t="n"/>
-      <c r="R29" s="32" t="n"/>
-      <c r="S29" s="32" t="n"/>
-      <c r="T29" s="32" t="n"/>
-      <c r="U29" s="32" t="n"/>
-      <c r="V29" s="32" t="n"/>
-      <c r="W29" s="32" t="n"/>
-      <c r="X29" s="32" t="n"/>
-      <c r="Y29" s="32" t="n"/>
-      <c r="Z29" s="32" t="n"/>
-      <c r="AA29" s="32" t="n"/>
-      <c r="AB29" s="32" t="n"/>
-      <c r="AC29" s="32" t="n"/>
-      <c r="AD29" s="32" t="n"/>
-      <c r="AE29" s="32" t="n"/>
-      <c r="AF29" s="32" t="n"/>
-      <c r="AG29" s="32" t="n"/>
-      <c r="AH29" s="31" t="n"/>
+      <c r="H29" s="26" t="n"/>
+      <c r="I29" s="26" t="n"/>
+      <c r="J29" s="26" t="n"/>
+      <c r="K29" s="26" t="n"/>
+      <c r="L29" s="26" t="n"/>
+      <c r="M29" s="26" t="n"/>
+      <c r="N29" s="26" t="n"/>
+      <c r="O29" s="26" t="n"/>
+      <c r="P29" s="26" t="n"/>
+      <c r="Q29" s="26" t="n"/>
+      <c r="R29" s="26" t="n"/>
+      <c r="S29" s="26" t="n"/>
+      <c r="T29" s="26" t="n"/>
+      <c r="U29" s="26" t="n"/>
+      <c r="V29" s="26" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="26" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="26" t="n"/>
+      <c r="AB29" s="26" t="n"/>
+      <c r="AC29" s="26" t="n"/>
+      <c r="AD29" s="26" t="n"/>
+      <c r="AE29" s="26" t="n"/>
+      <c r="AF29" s="26" t="n"/>
+      <c r="AG29" s="26" t="n"/>
+      <c r="AH29" s="26" t="n"/>
       <c r="AI29" s="26" t="n"/>
       <c r="AJ29" s="26" t="n"/>
       <c r="AK29" s="26" t="n"/>
-      <c r="AL29" s="26" t="n"/>
-      <c r="AM29" s="26" t="n"/>
-      <c r="AN29" s="26" t="n"/>
-      <c r="AO29" s="26" t="n"/>
-      <c r="AP29" s="26" t="n"/>
-      <c r="AQ29" s="26" t="n"/>
-      <c r="AR29" s="26" t="n"/>
-      <c r="AS29" s="26" t="n"/>
-      <c r="AT29" s="26" t="n"/>
-      <c r="AU29" s="26" t="n"/>
-      <c r="AV29" s="26" t="n"/>
-      <c r="AW29" s="26" t="n"/>
-      <c r="AX29" s="26" t="n"/>
-      <c r="AY29" s="26" t="n"/>
-      <c r="AZ29" s="26" t="n"/>
-      <c r="BA29" s="26" t="n"/>
-      <c r="BB29" s="26" t="n"/>
-      <c r="BC29" s="26" t="n"/>
-      <c r="BD29" s="26" t="n"/>
-      <c r="BE29" s="26" t="n"/>
-      <c r="BF29" s="26" t="n"/>
-      <c r="BG29" s="26" t="n"/>
-      <c r="BH29" s="26" t="n"/>
-      <c r="BI29" s="26" t="n"/>
-      <c r="BJ29" s="26" t="n"/>
-      <c r="BK29" s="26" t="n"/>
-      <c r="BL29" s="26" t="n"/>
-      <c r="BM29" s="26" t="n"/>
-      <c r="BN29" s="26" t="n"/>
-      <c r="BO29" s="26" t="n"/>
+      <c r="AL29" s="27" t="n"/>
+      <c r="AM29" s="28" t="n"/>
+      <c r="AN29" s="28" t="n"/>
+      <c r="AO29" s="28" t="n"/>
+      <c r="AP29" s="28" t="n"/>
+      <c r="AQ29" s="28" t="n"/>
+      <c r="AR29" s="28" t="n"/>
+      <c r="AS29" s="28" t="n"/>
+      <c r="AT29" s="28" t="n"/>
+      <c r="AU29" s="28" t="n"/>
+      <c r="AV29" s="28" t="n"/>
+      <c r="AW29" s="28" t="n"/>
+      <c r="AX29" s="28" t="n"/>
+      <c r="AY29" s="28" t="n"/>
+      <c r="AZ29" s="28" t="n"/>
+      <c r="BA29" s="28" t="n"/>
+      <c r="BB29" s="28" t="n"/>
+      <c r="BC29" s="28" t="n"/>
+      <c r="BD29" s="28" t="n"/>
+      <c r="BE29" s="28" t="n"/>
+      <c r="BF29" s="28" t="n"/>
+      <c r="BG29" s="28" t="n"/>
+      <c r="BH29" s="28" t="n"/>
+      <c r="BI29" s="28" t="n"/>
+      <c r="BJ29" s="28" t="n"/>
+      <c r="BK29" s="28" t="n"/>
+      <c r="BL29" s="28" t="n"/>
+      <c r="BM29" s="28" t="n"/>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="28" t="n"/>
+      <c r="BQ29" s="28" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>PAB090·工装实物到位</t>
         </is>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="31">
         <f>'时间节点计划表'!E15</f>
         <v/>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="31">
         <f>IF(COUNT('时间节点计划表'!F15),'时间节点计划表'!F15,"")</f>
         <v/>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="32">
         <f>IF(OR(D30="",E30=""),"待填",E30-D30)</f>
         <v/>
       </c>
@@ -8279,6 +8563,22 @@
       </c>
       <c r="BO30" s="23">
         <f>IF(AND(COUNT($E30),N(BO$2)=N($E30)),$E30,IF(AND(COUNT($E30),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E30))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP30" s="23">
+        <f>IF(AND(COUNT($E30),N(BP$2)=N($E30)),$E30,IF(AND(COUNT($E30),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E30))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ30" s="23">
+        <f>IF(AND(COUNT($E30),N(BQ$2)=N($E30)),$E30,IF(AND(COUNT($E30),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E30))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR30" s="23">
+        <f>IF(AND(COUNT($E30),N(BR$2)=N($E30)),$E30,IF(AND(COUNT($E30),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E30))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS30" s="23">
+        <f>IF(AND(COUNT($E30),N(BS$2)=N($E30)),$E30,IF(AND(COUNT($E30),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E30))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -8311,92 +8611,96 @@
         <f>D31</f>
         <v/>
       </c>
-      <c r="H31" s="32" t="n"/>
-      <c r="I31" s="32" t="n"/>
-      <c r="J31" s="32" t="n"/>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
-      <c r="T31" s="32" t="n"/>
-      <c r="U31" s="32" t="n"/>
-      <c r="V31" s="32" t="n"/>
-      <c r="W31" s="32" t="n"/>
-      <c r="X31" s="32" t="n"/>
-      <c r="Y31" s="32" t="n"/>
-      <c r="Z31" s="32" t="n"/>
-      <c r="AA31" s="32" t="n"/>
-      <c r="AB31" s="32" t="n"/>
-      <c r="AC31" s="32" t="n"/>
-      <c r="AD31" s="32" t="n"/>
-      <c r="AE31" s="32" t="n"/>
-      <c r="AF31" s="32" t="n"/>
-      <c r="AG31" s="32" t="n"/>
-      <c r="AH31" s="32" t="n"/>
-      <c r="AI31" s="32" t="n"/>
-      <c r="AJ31" s="32" t="n"/>
-      <c r="AK31" s="32" t="n"/>
-      <c r="AL31" s="32" t="n"/>
-      <c r="AM31" s="32" t="n"/>
-      <c r="AN31" s="32" t="n"/>
-      <c r="AO31" s="31" t="n"/>
+      <c r="H31" s="26" t="n"/>
+      <c r="I31" s="26" t="n"/>
+      <c r="J31" s="26" t="n"/>
+      <c r="K31" s="26" t="n"/>
+      <c r="L31" s="26" t="n"/>
+      <c r="M31" s="26" t="n"/>
+      <c r="N31" s="26" t="n"/>
+      <c r="O31" s="26" t="n"/>
+      <c r="P31" s="26" t="n"/>
+      <c r="Q31" s="26" t="n"/>
+      <c r="R31" s="26" t="n"/>
+      <c r="S31" s="26" t="n"/>
+      <c r="T31" s="26" t="n"/>
+      <c r="U31" s="26" t="n"/>
+      <c r="V31" s="26" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="26" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="26" t="n"/>
+      <c r="AB31" s="26" t="n"/>
+      <c r="AC31" s="26" t="n"/>
+      <c r="AD31" s="26" t="n"/>
+      <c r="AE31" s="26" t="n"/>
+      <c r="AF31" s="26" t="n"/>
+      <c r="AG31" s="26" t="n"/>
+      <c r="AH31" s="26" t="n"/>
+      <c r="AI31" s="26" t="n"/>
+      <c r="AJ31" s="26" t="n"/>
+      <c r="AK31" s="26" t="n"/>
+      <c r="AL31" s="26" t="n"/>
+      <c r="AM31" s="26" t="n"/>
+      <c r="AN31" s="26" t="n"/>
+      <c r="AO31" s="26" t="n"/>
       <c r="AP31" s="26" t="n"/>
       <c r="AQ31" s="26" t="n"/>
       <c r="AR31" s="26" t="n"/>
-      <c r="AS31" s="26" t="n"/>
-      <c r="AT31" s="26" t="n"/>
-      <c r="AU31" s="26" t="n"/>
-      <c r="AV31" s="26" t="n"/>
-      <c r="AW31" s="26" t="n"/>
-      <c r="AX31" s="26" t="n"/>
-      <c r="AY31" s="26" t="n"/>
-      <c r="AZ31" s="26" t="n"/>
-      <c r="BA31" s="26" t="n"/>
-      <c r="BB31" s="26" t="n"/>
-      <c r="BC31" s="26" t="n"/>
-      <c r="BD31" s="26" t="n"/>
-      <c r="BE31" s="26" t="n"/>
-      <c r="BF31" s="26" t="n"/>
-      <c r="BG31" s="26" t="n"/>
-      <c r="BH31" s="26" t="n"/>
-      <c r="BI31" s="26" t="n"/>
-      <c r="BJ31" s="26" t="n"/>
-      <c r="BK31" s="26" t="n"/>
-      <c r="BL31" s="26" t="n"/>
-      <c r="BM31" s="26" t="n"/>
-      <c r="BN31" s="26" t="n"/>
-      <c r="BO31" s="26" t="n"/>
+      <c r="AS31" s="27" t="n"/>
+      <c r="AT31" s="28" t="n"/>
+      <c r="AU31" s="28" t="n"/>
+      <c r="AV31" s="28" t="n"/>
+      <c r="AW31" s="28" t="n"/>
+      <c r="AX31" s="28" t="n"/>
+      <c r="AY31" s="28" t="n"/>
+      <c r="AZ31" s="28" t="n"/>
+      <c r="BA31" s="28" t="n"/>
+      <c r="BB31" s="28" t="n"/>
+      <c r="BC31" s="28" t="n"/>
+      <c r="BD31" s="28" t="n"/>
+      <c r="BE31" s="28" t="n"/>
+      <c r="BF31" s="28" t="n"/>
+      <c r="BG31" s="28" t="n"/>
+      <c r="BH31" s="28" t="n"/>
+      <c r="BI31" s="28" t="n"/>
+      <c r="BJ31" s="28" t="n"/>
+      <c r="BK31" s="28" t="n"/>
+      <c r="BL31" s="28" t="n"/>
+      <c r="BM31" s="28" t="n"/>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="28" t="n"/>
+      <c r="BQ31" s="28" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t>PAB090·排针机安装调试</t>
         </is>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="31">
         <f>'时间节点计划表'!E16</f>
         <v/>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="31">
         <f>IF(COUNT('时间节点计划表'!F16),'时间节点计划表'!F16,"")</f>
         <v/>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="32">
         <f>IF(OR(D32="",E32=""),"待填",E32-D32)</f>
         <v/>
       </c>
@@ -8642,6 +8946,22 @@
       </c>
       <c r="BO32" s="23">
         <f>IF(AND(COUNT($E32),N(BO$2)=N($E32)),$E32,IF(AND(COUNT($E32),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E32))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP32" s="23">
+        <f>IF(AND(COUNT($E32),N(BP$2)=N($E32)),$E32,IF(AND(COUNT($E32),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E32))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ32" s="23">
+        <f>IF(AND(COUNT($E32),N(BQ$2)=N($E32)),$E32,IF(AND(COUNT($E32),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E32))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR32" s="23">
+        <f>IF(AND(COUNT($E32),N(BR$2)=N($E32)),$E32,IF(AND(COUNT($E32),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E32))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS32" s="23">
+        <f>IF(AND(COUNT($E32),N(BS$2)=N($E32)),$E32,IF(AND(COUNT($E32),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E32))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -8674,92 +8994,96 @@
         <f>D33</f>
         <v/>
       </c>
-      <c r="H33" s="32" t="n"/>
-      <c r="I33" s="32" t="n"/>
-      <c r="J33" s="32" t="n"/>
-      <c r="K33" s="32" t="n"/>
-      <c r="L33" s="32" t="n"/>
-      <c r="M33" s="32" t="n"/>
-      <c r="N33" s="32" t="n"/>
-      <c r="O33" s="32" t="n"/>
-      <c r="P33" s="32" t="n"/>
-      <c r="Q33" s="32" t="n"/>
-      <c r="R33" s="32" t="n"/>
-      <c r="S33" s="32" t="n"/>
-      <c r="T33" s="32" t="n"/>
-      <c r="U33" s="32" t="n"/>
-      <c r="V33" s="32" t="n"/>
-      <c r="W33" s="32" t="n"/>
-      <c r="X33" s="32" t="n"/>
-      <c r="Y33" s="32" t="n"/>
-      <c r="Z33" s="32" t="n"/>
-      <c r="AA33" s="32" t="n"/>
-      <c r="AB33" s="32" t="n"/>
-      <c r="AC33" s="32" t="n"/>
-      <c r="AD33" s="32" t="n"/>
-      <c r="AE33" s="32" t="n"/>
-      <c r="AF33" s="32" t="n"/>
-      <c r="AG33" s="32" t="n"/>
-      <c r="AH33" s="32" t="n"/>
-      <c r="AI33" s="32" t="n"/>
-      <c r="AJ33" s="32" t="n"/>
-      <c r="AK33" s="32" t="n"/>
-      <c r="AL33" s="32" t="n"/>
-      <c r="AM33" s="32" t="n"/>
-      <c r="AN33" s="32" t="n"/>
-      <c r="AO33" s="32" t="n"/>
-      <c r="AP33" s="32" t="n"/>
-      <c r="AQ33" s="31" t="n"/>
+      <c r="H33" s="26" t="n"/>
+      <c r="I33" s="26" t="n"/>
+      <c r="J33" s="26" t="n"/>
+      <c r="K33" s="26" t="n"/>
+      <c r="L33" s="26" t="n"/>
+      <c r="M33" s="26" t="n"/>
+      <c r="N33" s="26" t="n"/>
+      <c r="O33" s="26" t="n"/>
+      <c r="P33" s="26" t="n"/>
+      <c r="Q33" s="26" t="n"/>
+      <c r="R33" s="26" t="n"/>
+      <c r="S33" s="26" t="n"/>
+      <c r="T33" s="26" t="n"/>
+      <c r="U33" s="26" t="n"/>
+      <c r="V33" s="26" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="26" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="26" t="n"/>
+      <c r="AB33" s="26" t="n"/>
+      <c r="AC33" s="26" t="n"/>
+      <c r="AD33" s="26" t="n"/>
+      <c r="AE33" s="26" t="n"/>
+      <c r="AF33" s="26" t="n"/>
+      <c r="AG33" s="26" t="n"/>
+      <c r="AH33" s="26" t="n"/>
+      <c r="AI33" s="26" t="n"/>
+      <c r="AJ33" s="26" t="n"/>
+      <c r="AK33" s="26" t="n"/>
+      <c r="AL33" s="26" t="n"/>
+      <c r="AM33" s="26" t="n"/>
+      <c r="AN33" s="26" t="n"/>
+      <c r="AO33" s="26" t="n"/>
+      <c r="AP33" s="26" t="n"/>
+      <c r="AQ33" s="26" t="n"/>
       <c r="AR33" s="26" t="n"/>
       <c r="AS33" s="26" t="n"/>
       <c r="AT33" s="26" t="n"/>
-      <c r="AU33" s="26" t="n"/>
-      <c r="AV33" s="26" t="n"/>
-      <c r="AW33" s="26" t="n"/>
-      <c r="AX33" s="26" t="n"/>
-      <c r="AY33" s="26" t="n"/>
-      <c r="AZ33" s="26" t="n"/>
-      <c r="BA33" s="26" t="n"/>
-      <c r="BB33" s="26" t="n"/>
-      <c r="BC33" s="26" t="n"/>
-      <c r="BD33" s="26" t="n"/>
-      <c r="BE33" s="26" t="n"/>
-      <c r="BF33" s="26" t="n"/>
-      <c r="BG33" s="26" t="n"/>
-      <c r="BH33" s="26" t="n"/>
-      <c r="BI33" s="26" t="n"/>
-      <c r="BJ33" s="26" t="n"/>
-      <c r="BK33" s="26" t="n"/>
-      <c r="BL33" s="26" t="n"/>
-      <c r="BM33" s="26" t="n"/>
-      <c r="BN33" s="26" t="n"/>
-      <c r="BO33" s="26" t="n"/>
+      <c r="AU33" s="27" t="n"/>
+      <c r="AV33" s="28" t="n"/>
+      <c r="AW33" s="28" t="n"/>
+      <c r="AX33" s="28" t="n"/>
+      <c r="AY33" s="28" t="n"/>
+      <c r="AZ33" s="28" t="n"/>
+      <c r="BA33" s="28" t="n"/>
+      <c r="BB33" s="28" t="n"/>
+      <c r="BC33" s="28" t="n"/>
+      <c r="BD33" s="28" t="n"/>
+      <c r="BE33" s="28" t="n"/>
+      <c r="BF33" s="28" t="n"/>
+      <c r="BG33" s="28" t="n"/>
+      <c r="BH33" s="28" t="n"/>
+      <c r="BI33" s="28" t="n"/>
+      <c r="BJ33" s="28" t="n"/>
+      <c r="BK33" s="28" t="n"/>
+      <c r="BL33" s="28" t="n"/>
+      <c r="BM33" s="28" t="n"/>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="28" t="n"/>
+      <c r="BQ33" s="28" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>PAB090·单级样机</t>
         </is>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="31">
         <f>'时间节点计划表'!E17</f>
         <v/>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="31">
         <f>IF(COUNT('时间节点计划表'!F17),'时间节点计划表'!F17,"")</f>
         <v/>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="32">
         <f>IF(OR(D34="",E34=""),"待填",E34-D34)</f>
         <v/>
       </c>
@@ -9005,6 +9329,22 @@
       </c>
       <c r="BO34" s="23">
         <f>IF(AND(COUNT($E34),N(BO$2)=N($E34)),$E34,IF(AND(COUNT($E34),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E34))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP34" s="23">
+        <f>IF(AND(COUNT($E34),N(BP$2)=N($E34)),$E34,IF(AND(COUNT($E34),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E34))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ34" s="23">
+        <f>IF(AND(COUNT($E34),N(BQ$2)=N($E34)),$E34,IF(AND(COUNT($E34),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E34))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR34" s="23">
+        <f>IF(AND(COUNT($E34),N(BR$2)=N($E34)),$E34,IF(AND(COUNT($E34),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E34))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS34" s="23">
+        <f>IF(AND(COUNT($E34),N(BS$2)=N($E34)),$E34,IF(AND(COUNT($E34),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E34))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -9037,92 +9377,96 @@
         <f>D35</f>
         <v/>
       </c>
-      <c r="H35" s="32" t="n"/>
-      <c r="I35" s="32" t="n"/>
-      <c r="J35" s="32" t="n"/>
-      <c r="K35" s="32" t="n"/>
-      <c r="L35" s="32" t="n"/>
-      <c r="M35" s="32" t="n"/>
-      <c r="N35" s="32" t="n"/>
-      <c r="O35" s="32" t="n"/>
-      <c r="P35" s="32" t="n"/>
-      <c r="Q35" s="32" t="n"/>
-      <c r="R35" s="32" t="n"/>
-      <c r="S35" s="32" t="n"/>
-      <c r="T35" s="32" t="n"/>
-      <c r="U35" s="32" t="n"/>
-      <c r="V35" s="32" t="n"/>
-      <c r="W35" s="32" t="n"/>
-      <c r="X35" s="32" t="n"/>
-      <c r="Y35" s="32" t="n"/>
-      <c r="Z35" s="32" t="n"/>
-      <c r="AA35" s="32" t="n"/>
-      <c r="AB35" s="32" t="n"/>
-      <c r="AC35" s="32" t="n"/>
-      <c r="AD35" s="32" t="n"/>
-      <c r="AE35" s="32" t="n"/>
-      <c r="AF35" s="32" t="n"/>
-      <c r="AG35" s="32" t="n"/>
-      <c r="AH35" s="32" t="n"/>
-      <c r="AI35" s="32" t="n"/>
-      <c r="AJ35" s="32" t="n"/>
-      <c r="AK35" s="32" t="n"/>
-      <c r="AL35" s="32" t="n"/>
-      <c r="AM35" s="32" t="n"/>
-      <c r="AN35" s="32" t="n"/>
-      <c r="AO35" s="32" t="n"/>
-      <c r="AP35" s="32" t="n"/>
-      <c r="AQ35" s="32" t="n"/>
-      <c r="AR35" s="31" t="n"/>
+      <c r="H35" s="26" t="n"/>
+      <c r="I35" s="26" t="n"/>
+      <c r="J35" s="26" t="n"/>
+      <c r="K35" s="26" t="n"/>
+      <c r="L35" s="26" t="n"/>
+      <c r="M35" s="26" t="n"/>
+      <c r="N35" s="26" t="n"/>
+      <c r="O35" s="26" t="n"/>
+      <c r="P35" s="26" t="n"/>
+      <c r="Q35" s="26" t="n"/>
+      <c r="R35" s="26" t="n"/>
+      <c r="S35" s="26" t="n"/>
+      <c r="T35" s="26" t="n"/>
+      <c r="U35" s="26" t="n"/>
+      <c r="V35" s="26" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="26" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="26" t="n"/>
+      <c r="AB35" s="26" t="n"/>
+      <c r="AC35" s="26" t="n"/>
+      <c r="AD35" s="26" t="n"/>
+      <c r="AE35" s="26" t="n"/>
+      <c r="AF35" s="26" t="n"/>
+      <c r="AG35" s="26" t="n"/>
+      <c r="AH35" s="26" t="n"/>
+      <c r="AI35" s="26" t="n"/>
+      <c r="AJ35" s="26" t="n"/>
+      <c r="AK35" s="26" t="n"/>
+      <c r="AL35" s="26" t="n"/>
+      <c r="AM35" s="26" t="n"/>
+      <c r="AN35" s="26" t="n"/>
+      <c r="AO35" s="26" t="n"/>
+      <c r="AP35" s="26" t="n"/>
+      <c r="AQ35" s="26" t="n"/>
+      <c r="AR35" s="26" t="n"/>
       <c r="AS35" s="26" t="n"/>
       <c r="AT35" s="26" t="n"/>
       <c r="AU35" s="26" t="n"/>
-      <c r="AV35" s="26" t="n"/>
-      <c r="AW35" s="26" t="n"/>
-      <c r="AX35" s="26" t="n"/>
-      <c r="AY35" s="26" t="n"/>
-      <c r="AZ35" s="26" t="n"/>
-      <c r="BA35" s="26" t="n"/>
-      <c r="BB35" s="26" t="n"/>
-      <c r="BC35" s="26" t="n"/>
-      <c r="BD35" s="26" t="n"/>
-      <c r="BE35" s="26" t="n"/>
-      <c r="BF35" s="26" t="n"/>
-      <c r="BG35" s="26" t="n"/>
-      <c r="BH35" s="26" t="n"/>
-      <c r="BI35" s="26" t="n"/>
-      <c r="BJ35" s="26" t="n"/>
-      <c r="BK35" s="26" t="n"/>
-      <c r="BL35" s="26" t="n"/>
-      <c r="BM35" s="26" t="n"/>
-      <c r="BN35" s="26" t="n"/>
-      <c r="BO35" s="26" t="n"/>
+      <c r="AV35" s="27" t="n"/>
+      <c r="AW35" s="28" t="n"/>
+      <c r="AX35" s="28" t="n"/>
+      <c r="AY35" s="28" t="n"/>
+      <c r="AZ35" s="28" t="n"/>
+      <c r="BA35" s="28" t="n"/>
+      <c r="BB35" s="28" t="n"/>
+      <c r="BC35" s="28" t="n"/>
+      <c r="BD35" s="28" t="n"/>
+      <c r="BE35" s="28" t="n"/>
+      <c r="BF35" s="28" t="n"/>
+      <c r="BG35" s="28" t="n"/>
+      <c r="BH35" s="28" t="n"/>
+      <c r="BI35" s="28" t="n"/>
+      <c r="BJ35" s="28" t="n"/>
+      <c r="BK35" s="28" t="n"/>
+      <c r="BL35" s="28" t="n"/>
+      <c r="BM35" s="28" t="n"/>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="28" t="n"/>
+      <c r="BQ35" s="28" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B36" s="27" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C36" s="28" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>PAB090·双级样机</t>
         </is>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="31">
         <f>'时间节点计划表'!E18</f>
         <v/>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="31">
         <f>IF(COUNT('时间节点计划表'!F18),'时间节点计划表'!F18,"")</f>
         <v/>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="32">
         <f>IF(OR(D36="",E36=""),"待填",E36-D36)</f>
         <v/>
       </c>
@@ -9368,6 +9712,22 @@
       </c>
       <c r="BO36" s="23">
         <f>IF(AND(COUNT($E36),N(BO$2)=N($E36)),$E36,IF(AND(COUNT($E36),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E36))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP36" s="23">
+        <f>IF(AND(COUNT($E36),N(BP$2)=N($E36)),$E36,IF(AND(COUNT($E36),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E36))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ36" s="23">
+        <f>IF(AND(COUNT($E36),N(BQ$2)=N($E36)),$E36,IF(AND(COUNT($E36),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E36))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR36" s="23">
+        <f>IF(AND(COUNT($E36),N(BR$2)=N($E36)),$E36,IF(AND(COUNT($E36),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E36))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS36" s="23">
+        <f>IF(AND(COUNT($E36),N(BS$2)=N($E36)),$E36,IF(AND(COUNT($E36),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E36))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -9400,92 +9760,96 @@
         <f>D37</f>
         <v/>
       </c>
-      <c r="H37" s="32" t="n"/>
-      <c r="I37" s="32" t="n"/>
-      <c r="J37" s="32" t="n"/>
-      <c r="K37" s="32" t="n"/>
-      <c r="L37" s="32" t="n"/>
-      <c r="M37" s="32" t="n"/>
-      <c r="N37" s="32" t="n"/>
-      <c r="O37" s="32" t="n"/>
-      <c r="P37" s="32" t="n"/>
-      <c r="Q37" s="32" t="n"/>
-      <c r="R37" s="32" t="n"/>
-      <c r="S37" s="32" t="n"/>
-      <c r="T37" s="32" t="n"/>
-      <c r="U37" s="32" t="n"/>
-      <c r="V37" s="32" t="n"/>
-      <c r="W37" s="32" t="n"/>
-      <c r="X37" s="32" t="n"/>
-      <c r="Y37" s="32" t="n"/>
-      <c r="Z37" s="32" t="n"/>
-      <c r="AA37" s="32" t="n"/>
-      <c r="AB37" s="32" t="n"/>
-      <c r="AC37" s="32" t="n"/>
-      <c r="AD37" s="32" t="n"/>
-      <c r="AE37" s="32" t="n"/>
-      <c r="AF37" s="32" t="n"/>
-      <c r="AG37" s="32" t="n"/>
-      <c r="AH37" s="32" t="n"/>
-      <c r="AI37" s="32" t="n"/>
-      <c r="AJ37" s="32" t="n"/>
-      <c r="AK37" s="32" t="n"/>
-      <c r="AL37" s="32" t="n"/>
-      <c r="AM37" s="32" t="n"/>
-      <c r="AN37" s="32" t="n"/>
-      <c r="AO37" s="32" t="n"/>
-      <c r="AP37" s="32" t="n"/>
-      <c r="AQ37" s="32" t="n"/>
-      <c r="AR37" s="32" t="n"/>
-      <c r="AS37" s="32" t="n"/>
-      <c r="AT37" s="32" t="n"/>
-      <c r="AU37" s="32" t="n"/>
-      <c r="AV37" s="32" t="n"/>
-      <c r="AW37" s="32" t="n"/>
-      <c r="AX37" s="32" t="n"/>
-      <c r="AY37" s="32" t="n"/>
-      <c r="AZ37" s="31" t="n"/>
+      <c r="H37" s="26" t="n"/>
+      <c r="I37" s="26" t="n"/>
+      <c r="J37" s="26" t="n"/>
+      <c r="K37" s="26" t="n"/>
+      <c r="L37" s="26" t="n"/>
+      <c r="M37" s="26" t="n"/>
+      <c r="N37" s="26" t="n"/>
+      <c r="O37" s="26" t="n"/>
+      <c r="P37" s="26" t="n"/>
+      <c r="Q37" s="26" t="n"/>
+      <c r="R37" s="26" t="n"/>
+      <c r="S37" s="26" t="n"/>
+      <c r="T37" s="26" t="n"/>
+      <c r="U37" s="26" t="n"/>
+      <c r="V37" s="26" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="26" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="26" t="n"/>
+      <c r="AB37" s="26" t="n"/>
+      <c r="AC37" s="26" t="n"/>
+      <c r="AD37" s="26" t="n"/>
+      <c r="AE37" s="26" t="n"/>
+      <c r="AF37" s="26" t="n"/>
+      <c r="AG37" s="26" t="n"/>
+      <c r="AH37" s="26" t="n"/>
+      <c r="AI37" s="26" t="n"/>
+      <c r="AJ37" s="26" t="n"/>
+      <c r="AK37" s="26" t="n"/>
+      <c r="AL37" s="26" t="n"/>
+      <c r="AM37" s="26" t="n"/>
+      <c r="AN37" s="26" t="n"/>
+      <c r="AO37" s="26" t="n"/>
+      <c r="AP37" s="26" t="n"/>
+      <c r="AQ37" s="26" t="n"/>
+      <c r="AR37" s="26" t="n"/>
+      <c r="AS37" s="26" t="n"/>
+      <c r="AT37" s="26" t="n"/>
+      <c r="AU37" s="26" t="n"/>
+      <c r="AV37" s="26" t="n"/>
+      <c r="AW37" s="26" t="n"/>
+      <c r="AX37" s="26" t="n"/>
+      <c r="AY37" s="26" t="n"/>
+      <c r="AZ37" s="26" t="n"/>
       <c r="BA37" s="26" t="n"/>
       <c r="BB37" s="26" t="n"/>
       <c r="BC37" s="26" t="n"/>
-      <c r="BD37" s="26" t="n"/>
-      <c r="BE37" s="26" t="n"/>
-      <c r="BF37" s="26" t="n"/>
-      <c r="BG37" s="26" t="n"/>
-      <c r="BH37" s="26" t="n"/>
-      <c r="BI37" s="26" t="n"/>
-      <c r="BJ37" s="26" t="n"/>
-      <c r="BK37" s="26" t="n"/>
-      <c r="BL37" s="26" t="n"/>
-      <c r="BM37" s="26" t="n"/>
-      <c r="BN37" s="26" t="n"/>
-      <c r="BO37" s="26" t="n"/>
+      <c r="BD37" s="27" t="n"/>
+      <c r="BE37" s="28" t="n"/>
+      <c r="BF37" s="28" t="n"/>
+      <c r="BG37" s="28" t="n"/>
+      <c r="BH37" s="28" t="n"/>
+      <c r="BI37" s="28" t="n"/>
+      <c r="BJ37" s="28" t="n"/>
+      <c r="BK37" s="28" t="n"/>
+      <c r="BL37" s="28" t="n"/>
+      <c r="BM37" s="28" t="n"/>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="28" t="n"/>
+      <c r="BQ37" s="28" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>PAB115·零件到位</t>
         </is>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="31">
         <f>'时间节点计划表'!E19</f>
         <v/>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="31">
         <f>IF(COUNT('时间节点计划表'!F19),'时间节点计划表'!F19,"")</f>
         <v/>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="32">
         <f>IF(OR(D38="",E38=""),"待填",E38-D38)</f>
         <v/>
       </c>
@@ -9731,6 +10095,22 @@
       </c>
       <c r="BO38" s="23">
         <f>IF(AND(COUNT($E38),N(BO$2)=N($E38)),$E38,IF(AND(COUNT($E38),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E38))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP38" s="23">
+        <f>IF(AND(COUNT($E38),N(BP$2)=N($E38)),$E38,IF(AND(COUNT($E38),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E38))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ38" s="23">
+        <f>IF(AND(COUNT($E38),N(BQ$2)=N($E38)),$E38,IF(AND(COUNT($E38),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E38))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR38" s="23">
+        <f>IF(AND(COUNT($E38),N(BR$2)=N($E38)),$E38,IF(AND(COUNT($E38),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E38))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS38" s="23">
+        <f>IF(AND(COUNT($E38),N(BS$2)=N($E38)),$E38,IF(AND(COUNT($E38),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E38))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -9763,92 +10143,96 @@
         <f>D39</f>
         <v/>
       </c>
-      <c r="H39" s="32" t="n"/>
-      <c r="I39" s="32" t="n"/>
-      <c r="J39" s="32" t="n"/>
-      <c r="K39" s="32" t="n"/>
-      <c r="L39" s="32" t="n"/>
-      <c r="M39" s="32" t="n"/>
-      <c r="N39" s="32" t="n"/>
-      <c r="O39" s="32" t="n"/>
-      <c r="P39" s="32" t="n"/>
-      <c r="Q39" s="32" t="n"/>
-      <c r="R39" s="31" t="n"/>
+      <c r="H39" s="26" t="n"/>
+      <c r="I39" s="26" t="n"/>
+      <c r="J39" s="26" t="n"/>
+      <c r="K39" s="26" t="n"/>
+      <c r="L39" s="26" t="n"/>
+      <c r="M39" s="26" t="n"/>
+      <c r="N39" s="26" t="n"/>
+      <c r="O39" s="26" t="n"/>
+      <c r="P39" s="26" t="n"/>
+      <c r="Q39" s="26" t="n"/>
+      <c r="R39" s="26" t="n"/>
       <c r="S39" s="26" t="n"/>
       <c r="T39" s="26" t="n"/>
       <c r="U39" s="26" t="n"/>
-      <c r="V39" s="26" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="26" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="26" t="n"/>
-      <c r="AB39" s="26" t="n"/>
-      <c r="AC39" s="26" t="n"/>
-      <c r="AD39" s="26" t="n"/>
-      <c r="AE39" s="26" t="n"/>
-      <c r="AF39" s="26" t="n"/>
-      <c r="AG39" s="26" t="n"/>
-      <c r="AH39" s="26" t="n"/>
-      <c r="AI39" s="26" t="n"/>
-      <c r="AJ39" s="26" t="n"/>
-      <c r="AK39" s="26" t="n"/>
-      <c r="AL39" s="26" t="n"/>
-      <c r="AM39" s="26" t="n"/>
-      <c r="AN39" s="26" t="n"/>
-      <c r="AO39" s="26" t="n"/>
-      <c r="AP39" s="26" t="n"/>
-      <c r="AQ39" s="26" t="n"/>
-      <c r="AR39" s="26" t="n"/>
-      <c r="AS39" s="26" t="n"/>
-      <c r="AT39" s="26" t="n"/>
-      <c r="AU39" s="26" t="n"/>
-      <c r="AV39" s="26" t="n"/>
-      <c r="AW39" s="26" t="n"/>
-      <c r="AX39" s="26" t="n"/>
-      <c r="AY39" s="26" t="n"/>
-      <c r="AZ39" s="26" t="n"/>
-      <c r="BA39" s="26" t="n"/>
-      <c r="BB39" s="26" t="n"/>
-      <c r="BC39" s="26" t="n"/>
-      <c r="BD39" s="26" t="n"/>
-      <c r="BE39" s="26" t="n"/>
-      <c r="BF39" s="26" t="n"/>
-      <c r="BG39" s="26" t="n"/>
-      <c r="BH39" s="26" t="n"/>
-      <c r="BI39" s="26" t="n"/>
-      <c r="BJ39" s="26" t="n"/>
-      <c r="BK39" s="26" t="n"/>
-      <c r="BL39" s="26" t="n"/>
-      <c r="BM39" s="26" t="n"/>
-      <c r="BN39" s="26" t="n"/>
-      <c r="BO39" s="26" t="n"/>
+      <c r="V39" s="27" t="n"/>
+      <c r="W39" s="28" t="n"/>
+      <c r="X39" s="28" t="n"/>
+      <c r="Y39" s="28" t="n"/>
+      <c r="Z39" s="28" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="28" t="n"/>
+      <c r="AD39" s="28" t="n"/>
+      <c r="AE39" s="28" t="n"/>
+      <c r="AF39" s="28" t="n"/>
+      <c r="AG39" s="28" t="n"/>
+      <c r="AH39" s="28" t="n"/>
+      <c r="AI39" s="28" t="n"/>
+      <c r="AJ39" s="28" t="n"/>
+      <c r="AK39" s="28" t="n"/>
+      <c r="AL39" s="28" t="n"/>
+      <c r="AM39" s="28" t="n"/>
+      <c r="AN39" s="28" t="n"/>
+      <c r="AO39" s="28" t="n"/>
+      <c r="AP39" s="28" t="n"/>
+      <c r="AQ39" s="28" t="n"/>
+      <c r="AR39" s="28" t="n"/>
+      <c r="AS39" s="28" t="n"/>
+      <c r="AT39" s="28" t="n"/>
+      <c r="AU39" s="28" t="n"/>
+      <c r="AV39" s="28" t="n"/>
+      <c r="AW39" s="28" t="n"/>
+      <c r="AX39" s="28" t="n"/>
+      <c r="AY39" s="28" t="n"/>
+      <c r="AZ39" s="28" t="n"/>
+      <c r="BA39" s="28" t="n"/>
+      <c r="BB39" s="28" t="n"/>
+      <c r="BC39" s="28" t="n"/>
+      <c r="BD39" s="28" t="n"/>
+      <c r="BE39" s="28" t="n"/>
+      <c r="BF39" s="28" t="n"/>
+      <c r="BG39" s="28" t="n"/>
+      <c r="BH39" s="28" t="n"/>
+      <c r="BI39" s="28" t="n"/>
+      <c r="BJ39" s="28" t="n"/>
+      <c r="BK39" s="28" t="n"/>
+      <c r="BL39" s="28" t="n"/>
+      <c r="BM39" s="28" t="n"/>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="28" t="n"/>
+      <c r="BQ39" s="28" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B40" s="27" t="inlineStr">
+      <c r="B40" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>PAB115·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="31">
         <f>'时间节点计划表'!E20</f>
         <v/>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="31">
         <f>IF(COUNT('时间节点计划表'!F20),'时间节点计划表'!F20,"")</f>
         <v/>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="32">
         <f>IF(OR(D40="",E40=""),"待填",E40-D40)</f>
         <v/>
       </c>
@@ -10094,6 +10478,22 @@
       </c>
       <c r="BO40" s="23">
         <f>IF(AND(COUNT($E40),N(BO$2)=N($E40)),$E40,IF(AND(COUNT($E40),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E40))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP40" s="23">
+        <f>IF(AND(COUNT($E40),N(BP$2)=N($E40)),$E40,IF(AND(COUNT($E40),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E40))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ40" s="23">
+        <f>IF(AND(COUNT($E40),N(BQ$2)=N($E40)),$E40,IF(AND(COUNT($E40),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E40))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR40" s="23">
+        <f>IF(AND(COUNT($E40),N(BR$2)=N($E40)),$E40,IF(AND(COUNT($E40),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E40))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS40" s="23">
+        <f>IF(AND(COUNT($E40),N(BS$2)=N($E40)),$E40,IF(AND(COUNT($E40),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E40))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -10126,92 +10526,96 @@
         <f>D41</f>
         <v/>
       </c>
-      <c r="H41" s="32" t="n"/>
-      <c r="I41" s="32" t="n"/>
-      <c r="J41" s="32" t="n"/>
-      <c r="K41" s="32" t="n"/>
-      <c r="L41" s="32" t="n"/>
-      <c r="M41" s="32" t="n"/>
-      <c r="N41" s="32" t="n"/>
-      <c r="O41" s="32" t="n"/>
-      <c r="P41" s="32" t="n"/>
-      <c r="Q41" s="32" t="n"/>
-      <c r="R41" s="32" t="n"/>
-      <c r="S41" s="32" t="n"/>
-      <c r="T41" s="32" t="n"/>
-      <c r="U41" s="32" t="n"/>
-      <c r="V41" s="32" t="n"/>
-      <c r="W41" s="32" t="n"/>
-      <c r="X41" s="32" t="n"/>
-      <c r="Y41" s="32" t="n"/>
-      <c r="Z41" s="32" t="n"/>
-      <c r="AA41" s="32" t="n"/>
-      <c r="AB41" s="32" t="n"/>
-      <c r="AC41" s="32" t="n"/>
-      <c r="AD41" s="32" t="n"/>
-      <c r="AE41" s="32" t="n"/>
-      <c r="AF41" s="32" t="n"/>
-      <c r="AG41" s="32" t="n"/>
-      <c r="AH41" s="32" t="n"/>
-      <c r="AI41" s="32" t="n"/>
-      <c r="AJ41" s="32" t="n"/>
-      <c r="AK41" s="32" t="n"/>
-      <c r="AL41" s="32" t="n"/>
-      <c r="AM41" s="31" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="K41" s="26" t="n"/>
+      <c r="L41" s="26" t="n"/>
+      <c r="M41" s="26" t="n"/>
+      <c r="N41" s="26" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="26" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
+      <c r="T41" s="26" t="n"/>
+      <c r="U41" s="26" t="n"/>
+      <c r="V41" s="26" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="26" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="26" t="n"/>
+      <c r="AB41" s="26" t="n"/>
+      <c r="AC41" s="26" t="n"/>
+      <c r="AD41" s="26" t="n"/>
+      <c r="AE41" s="26" t="n"/>
+      <c r="AF41" s="26" t="n"/>
+      <c r="AG41" s="26" t="n"/>
+      <c r="AH41" s="26" t="n"/>
+      <c r="AI41" s="26" t="n"/>
+      <c r="AJ41" s="26" t="n"/>
+      <c r="AK41" s="26" t="n"/>
+      <c r="AL41" s="26" t="n"/>
+      <c r="AM41" s="26" t="n"/>
       <c r="AN41" s="26" t="n"/>
       <c r="AO41" s="26" t="n"/>
       <c r="AP41" s="26" t="n"/>
-      <c r="AQ41" s="26" t="n"/>
-      <c r="AR41" s="26" t="n"/>
-      <c r="AS41" s="26" t="n"/>
-      <c r="AT41" s="26" t="n"/>
-      <c r="AU41" s="26" t="n"/>
-      <c r="AV41" s="26" t="n"/>
-      <c r="AW41" s="26" t="n"/>
-      <c r="AX41" s="26" t="n"/>
-      <c r="AY41" s="26" t="n"/>
-      <c r="AZ41" s="26" t="n"/>
-      <c r="BA41" s="26" t="n"/>
-      <c r="BB41" s="26" t="n"/>
-      <c r="BC41" s="26" t="n"/>
-      <c r="BD41" s="26" t="n"/>
-      <c r="BE41" s="26" t="n"/>
-      <c r="BF41" s="26" t="n"/>
-      <c r="BG41" s="26" t="n"/>
-      <c r="BH41" s="26" t="n"/>
-      <c r="BI41" s="26" t="n"/>
-      <c r="BJ41" s="26" t="n"/>
-      <c r="BK41" s="26" t="n"/>
-      <c r="BL41" s="26" t="n"/>
-      <c r="BM41" s="26" t="n"/>
-      <c r="BN41" s="26" t="n"/>
-      <c r="BO41" s="26" t="n"/>
+      <c r="AQ41" s="27" t="n"/>
+      <c r="AR41" s="28" t="n"/>
+      <c r="AS41" s="28" t="n"/>
+      <c r="AT41" s="28" t="n"/>
+      <c r="AU41" s="28" t="n"/>
+      <c r="AV41" s="28" t="n"/>
+      <c r="AW41" s="28" t="n"/>
+      <c r="AX41" s="28" t="n"/>
+      <c r="AY41" s="28" t="n"/>
+      <c r="AZ41" s="28" t="n"/>
+      <c r="BA41" s="28" t="n"/>
+      <c r="BB41" s="28" t="n"/>
+      <c r="BC41" s="28" t="n"/>
+      <c r="BD41" s="28" t="n"/>
+      <c r="BE41" s="28" t="n"/>
+      <c r="BF41" s="28" t="n"/>
+      <c r="BG41" s="28" t="n"/>
+      <c r="BH41" s="28" t="n"/>
+      <c r="BI41" s="28" t="n"/>
+      <c r="BJ41" s="28" t="n"/>
+      <c r="BK41" s="28" t="n"/>
+      <c r="BL41" s="28" t="n"/>
+      <c r="BM41" s="28" t="n"/>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="28" t="n"/>
+      <c r="BQ41" s="28" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="27" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B42" s="27" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C42" s="28" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>PAB115·工装实物到位</t>
         </is>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="31">
         <f>'时间节点计划表'!E21</f>
         <v/>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="31">
         <f>IF(COUNT('时间节点计划表'!F21),'时间节点计划表'!F21,"")</f>
         <v/>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="32">
         <f>IF(OR(D42="",E42=""),"待填",E42-D42)</f>
         <v/>
       </c>
@@ -10457,6 +10861,22 @@
       </c>
       <c r="BO42" s="23">
         <f>IF(AND(COUNT($E42),N(BO$2)=N($E42)),$E42,IF(AND(COUNT($E42),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E42))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP42" s="23">
+        <f>IF(AND(COUNT($E42),N(BP$2)=N($E42)),$E42,IF(AND(COUNT($E42),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E42))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ42" s="23">
+        <f>IF(AND(COUNT($E42),N(BQ$2)=N($E42)),$E42,IF(AND(COUNT($E42),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E42))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR42" s="23">
+        <f>IF(AND(COUNT($E42),N(BR$2)=N($E42)),$E42,IF(AND(COUNT($E42),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E42))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS42" s="23">
+        <f>IF(AND(COUNT($E42),N(BS$2)=N($E42)),$E42,IF(AND(COUNT($E42),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E42))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -10489,92 +10909,96 @@
         <f>D43</f>
         <v/>
       </c>
-      <c r="H43" s="32" t="n"/>
-      <c r="I43" s="32" t="n"/>
-      <c r="J43" s="32" t="n"/>
-      <c r="K43" s="32" t="n"/>
-      <c r="L43" s="32" t="n"/>
-      <c r="M43" s="32" t="n"/>
-      <c r="N43" s="32" t="n"/>
-      <c r="O43" s="32" t="n"/>
-      <c r="P43" s="32" t="n"/>
-      <c r="Q43" s="32" t="n"/>
-      <c r="R43" s="32" t="n"/>
-      <c r="S43" s="32" t="n"/>
-      <c r="T43" s="32" t="n"/>
-      <c r="U43" s="32" t="n"/>
-      <c r="V43" s="32" t="n"/>
-      <c r="W43" s="32" t="n"/>
-      <c r="X43" s="32" t="n"/>
-      <c r="Y43" s="32" t="n"/>
-      <c r="Z43" s="32" t="n"/>
-      <c r="AA43" s="32" t="n"/>
-      <c r="AB43" s="32" t="n"/>
-      <c r="AC43" s="32" t="n"/>
-      <c r="AD43" s="32" t="n"/>
-      <c r="AE43" s="32" t="n"/>
-      <c r="AF43" s="32" t="n"/>
-      <c r="AG43" s="32" t="n"/>
-      <c r="AH43" s="32" t="n"/>
-      <c r="AI43" s="32" t="n"/>
-      <c r="AJ43" s="32" t="n"/>
-      <c r="AK43" s="32" t="n"/>
-      <c r="AL43" s="32" t="n"/>
-      <c r="AM43" s="32" t="n"/>
-      <c r="AN43" s="32" t="n"/>
-      <c r="AO43" s="32" t="n"/>
-      <c r="AP43" s="32" t="n"/>
-      <c r="AQ43" s="32" t="n"/>
-      <c r="AR43" s="32" t="n"/>
-      <c r="AS43" s="32" t="n"/>
-      <c r="AT43" s="32" t="n"/>
-      <c r="AU43" s="32" t="n"/>
-      <c r="AV43" s="32" t="n"/>
-      <c r="AW43" s="32" t="n"/>
-      <c r="AX43" s="32" t="n"/>
-      <c r="AY43" s="32" t="n"/>
-      <c r="AZ43" s="31" t="n"/>
+      <c r="H43" s="26" t="n"/>
+      <c r="I43" s="26" t="n"/>
+      <c r="J43" s="26" t="n"/>
+      <c r="K43" s="26" t="n"/>
+      <c r="L43" s="26" t="n"/>
+      <c r="M43" s="26" t="n"/>
+      <c r="N43" s="26" t="n"/>
+      <c r="O43" s="26" t="n"/>
+      <c r="P43" s="26" t="n"/>
+      <c r="Q43" s="26" t="n"/>
+      <c r="R43" s="26" t="n"/>
+      <c r="S43" s="26" t="n"/>
+      <c r="T43" s="26" t="n"/>
+      <c r="U43" s="26" t="n"/>
+      <c r="V43" s="26" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="26" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="26" t="n"/>
+      <c r="AB43" s="26" t="n"/>
+      <c r="AC43" s="26" t="n"/>
+      <c r="AD43" s="26" t="n"/>
+      <c r="AE43" s="26" t="n"/>
+      <c r="AF43" s="26" t="n"/>
+      <c r="AG43" s="26" t="n"/>
+      <c r="AH43" s="26" t="n"/>
+      <c r="AI43" s="26" t="n"/>
+      <c r="AJ43" s="26" t="n"/>
+      <c r="AK43" s="26" t="n"/>
+      <c r="AL43" s="26" t="n"/>
+      <c r="AM43" s="26" t="n"/>
+      <c r="AN43" s="26" t="n"/>
+      <c r="AO43" s="26" t="n"/>
+      <c r="AP43" s="26" t="n"/>
+      <c r="AQ43" s="26" t="n"/>
+      <c r="AR43" s="26" t="n"/>
+      <c r="AS43" s="26" t="n"/>
+      <c r="AT43" s="26" t="n"/>
+      <c r="AU43" s="26" t="n"/>
+      <c r="AV43" s="26" t="n"/>
+      <c r="AW43" s="26" t="n"/>
+      <c r="AX43" s="26" t="n"/>
+      <c r="AY43" s="26" t="n"/>
+      <c r="AZ43" s="26" t="n"/>
       <c r="BA43" s="26" t="n"/>
       <c r="BB43" s="26" t="n"/>
       <c r="BC43" s="26" t="n"/>
-      <c r="BD43" s="26" t="n"/>
-      <c r="BE43" s="26" t="n"/>
-      <c r="BF43" s="26" t="n"/>
-      <c r="BG43" s="26" t="n"/>
-      <c r="BH43" s="26" t="n"/>
-      <c r="BI43" s="26" t="n"/>
-      <c r="BJ43" s="26" t="n"/>
-      <c r="BK43" s="26" t="n"/>
-      <c r="BL43" s="26" t="n"/>
-      <c r="BM43" s="26" t="n"/>
-      <c r="BN43" s="26" t="n"/>
-      <c r="BO43" s="26" t="n"/>
+      <c r="BD43" s="27" t="n"/>
+      <c r="BE43" s="28" t="n"/>
+      <c r="BF43" s="28" t="n"/>
+      <c r="BG43" s="28" t="n"/>
+      <c r="BH43" s="28" t="n"/>
+      <c r="BI43" s="28" t="n"/>
+      <c r="BJ43" s="28" t="n"/>
+      <c r="BK43" s="28" t="n"/>
+      <c r="BL43" s="28" t="n"/>
+      <c r="BM43" s="28" t="n"/>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="28" t="n"/>
+      <c r="BQ43" s="28" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="27" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B44" s="27" t="inlineStr">
+      <c r="B44" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>PAB115·排针机安装调试</t>
         </is>
       </c>
-      <c r="D44" s="29">
+      <c r="D44" s="31">
         <f>'时间节点计划表'!E22</f>
         <v/>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="31">
         <f>IF(COUNT('时间节点计划表'!F22),'时间节点计划表'!F22,"")</f>
         <v/>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="32">
         <f>IF(OR(D44="",E44=""),"待填",E44-D44)</f>
         <v/>
       </c>
@@ -10820,6 +11244,22 @@
       </c>
       <c r="BO44" s="23">
         <f>IF(AND(COUNT($E44),N(BO$2)=N($E44)),$E44,IF(AND(COUNT($E44),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E44))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP44" s="23">
+        <f>IF(AND(COUNT($E44),N(BP$2)=N($E44)),$E44,IF(AND(COUNT($E44),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E44))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ44" s="23">
+        <f>IF(AND(COUNT($E44),N(BQ$2)=N($E44)),$E44,IF(AND(COUNT($E44),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E44))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR44" s="23">
+        <f>IF(AND(COUNT($E44),N(BR$2)=N($E44)),$E44,IF(AND(COUNT($E44),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E44))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS44" s="23">
+        <f>IF(AND(COUNT($E44),N(BS$2)=N($E44)),$E44,IF(AND(COUNT($E44),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E44))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -10852,92 +11292,96 @@
         <f>D45</f>
         <v/>
       </c>
-      <c r="H45" s="32" t="n"/>
-      <c r="I45" s="32" t="n"/>
-      <c r="J45" s="32" t="n"/>
-      <c r="K45" s="32" t="n"/>
-      <c r="L45" s="32" t="n"/>
-      <c r="M45" s="32" t="n"/>
-      <c r="N45" s="32" t="n"/>
-      <c r="O45" s="32" t="n"/>
-      <c r="P45" s="32" t="n"/>
-      <c r="Q45" s="32" t="n"/>
-      <c r="R45" s="32" t="n"/>
-      <c r="S45" s="32" t="n"/>
-      <c r="T45" s="32" t="n"/>
-      <c r="U45" s="32" t="n"/>
-      <c r="V45" s="32" t="n"/>
-      <c r="W45" s="32" t="n"/>
-      <c r="X45" s="32" t="n"/>
-      <c r="Y45" s="32" t="n"/>
-      <c r="Z45" s="32" t="n"/>
-      <c r="AA45" s="32" t="n"/>
-      <c r="AB45" s="32" t="n"/>
-      <c r="AC45" s="32" t="n"/>
-      <c r="AD45" s="32" t="n"/>
-      <c r="AE45" s="32" t="n"/>
-      <c r="AF45" s="32" t="n"/>
-      <c r="AG45" s="32" t="n"/>
-      <c r="AH45" s="32" t="n"/>
-      <c r="AI45" s="32" t="n"/>
-      <c r="AJ45" s="32" t="n"/>
-      <c r="AK45" s="32" t="n"/>
-      <c r="AL45" s="32" t="n"/>
-      <c r="AM45" s="32" t="n"/>
-      <c r="AN45" s="32" t="n"/>
-      <c r="AO45" s="32" t="n"/>
-      <c r="AP45" s="32" t="n"/>
-      <c r="AQ45" s="32" t="n"/>
-      <c r="AR45" s="32" t="n"/>
-      <c r="AS45" s="32" t="n"/>
-      <c r="AT45" s="32" t="n"/>
-      <c r="AU45" s="32" t="n"/>
-      <c r="AV45" s="32" t="n"/>
-      <c r="AW45" s="32" t="n"/>
-      <c r="AX45" s="32" t="n"/>
-      <c r="AY45" s="32" t="n"/>
-      <c r="AZ45" s="32" t="n"/>
-      <c r="BA45" s="31" t="n"/>
+      <c r="H45" s="26" t="n"/>
+      <c r="I45" s="26" t="n"/>
+      <c r="J45" s="26" t="n"/>
+      <c r="K45" s="26" t="n"/>
+      <c r="L45" s="26" t="n"/>
+      <c r="M45" s="26" t="n"/>
+      <c r="N45" s="26" t="n"/>
+      <c r="O45" s="26" t="n"/>
+      <c r="P45" s="26" t="n"/>
+      <c r="Q45" s="26" t="n"/>
+      <c r="R45" s="26" t="n"/>
+      <c r="S45" s="26" t="n"/>
+      <c r="T45" s="26" t="n"/>
+      <c r="U45" s="26" t="n"/>
+      <c r="V45" s="26" t="n"/>
+      <c r="W45" s="26" t="n"/>
+      <c r="X45" s="26" t="n"/>
+      <c r="Y45" s="26" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="26" t="n"/>
+      <c r="AB45" s="26" t="n"/>
+      <c r="AC45" s="26" t="n"/>
+      <c r="AD45" s="26" t="n"/>
+      <c r="AE45" s="26" t="n"/>
+      <c r="AF45" s="26" t="n"/>
+      <c r="AG45" s="26" t="n"/>
+      <c r="AH45" s="26" t="n"/>
+      <c r="AI45" s="26" t="n"/>
+      <c r="AJ45" s="26" t="n"/>
+      <c r="AK45" s="26" t="n"/>
+      <c r="AL45" s="26" t="n"/>
+      <c r="AM45" s="26" t="n"/>
+      <c r="AN45" s="26" t="n"/>
+      <c r="AO45" s="26" t="n"/>
+      <c r="AP45" s="26" t="n"/>
+      <c r="AQ45" s="26" t="n"/>
+      <c r="AR45" s="26" t="n"/>
+      <c r="AS45" s="26" t="n"/>
+      <c r="AT45" s="26" t="n"/>
+      <c r="AU45" s="26" t="n"/>
+      <c r="AV45" s="26" t="n"/>
+      <c r="AW45" s="26" t="n"/>
+      <c r="AX45" s="26" t="n"/>
+      <c r="AY45" s="26" t="n"/>
+      <c r="AZ45" s="26" t="n"/>
+      <c r="BA45" s="26" t="n"/>
       <c r="BB45" s="26" t="n"/>
       <c r="BC45" s="26" t="n"/>
       <c r="BD45" s="26" t="n"/>
-      <c r="BE45" s="26" t="n"/>
-      <c r="BF45" s="26" t="n"/>
-      <c r="BG45" s="26" t="n"/>
-      <c r="BH45" s="26" t="n"/>
-      <c r="BI45" s="26" t="n"/>
-      <c r="BJ45" s="26" t="n"/>
-      <c r="BK45" s="26" t="n"/>
-      <c r="BL45" s="26" t="n"/>
-      <c r="BM45" s="26" t="n"/>
-      <c r="BN45" s="26" t="n"/>
-      <c r="BO45" s="26" t="n"/>
+      <c r="BE45" s="27" t="n"/>
+      <c r="BF45" s="28" t="n"/>
+      <c r="BG45" s="28" t="n"/>
+      <c r="BH45" s="28" t="n"/>
+      <c r="BI45" s="28" t="n"/>
+      <c r="BJ45" s="28" t="n"/>
+      <c r="BK45" s="28" t="n"/>
+      <c r="BL45" s="28" t="n"/>
+      <c r="BM45" s="28" t="n"/>
+      <c r="BN45" s="28" t="n"/>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="28" t="n"/>
+      <c r="BQ45" s="28" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="27" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B46" s="27" t="inlineStr">
+      <c r="B46" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C46" s="28" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>PAB115·单级样机</t>
         </is>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="31">
         <f>'时间节点计划表'!E23</f>
         <v/>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="31">
         <f>IF(COUNT('时间节点计划表'!F23),'时间节点计划表'!F23,"")</f>
         <v/>
       </c>
-      <c r="F46" s="30">
+      <c r="F46" s="32">
         <f>IF(OR(D46="",E46=""),"待填",E46-D46)</f>
         <v/>
       </c>
@@ -11183,6 +11627,22 @@
       </c>
       <c r="BO46" s="23">
         <f>IF(AND(COUNT($E46),N(BO$2)=N($E46)),$E46,IF(AND(COUNT($E46),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E46))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP46" s="23">
+        <f>IF(AND(COUNT($E46),N(BP$2)=N($E46)),$E46,IF(AND(COUNT($E46),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E46))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ46" s="23">
+        <f>IF(AND(COUNT($E46),N(BQ$2)=N($E46)),$E46,IF(AND(COUNT($E46),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E46))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR46" s="23">
+        <f>IF(AND(COUNT($E46),N(BR$2)=N($E46)),$E46,IF(AND(COUNT($E46),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E46))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS46" s="23">
+        <f>IF(AND(COUNT($E46),N(BS$2)=N($E46)),$E46,IF(AND(COUNT($E46),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E46))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -11215,92 +11675,96 @@
         <f>D47</f>
         <v/>
       </c>
-      <c r="H47" s="32" t="n"/>
-      <c r="I47" s="32" t="n"/>
-      <c r="J47" s="32" t="n"/>
-      <c r="K47" s="32" t="n"/>
-      <c r="L47" s="32" t="n"/>
-      <c r="M47" s="32" t="n"/>
-      <c r="N47" s="32" t="n"/>
-      <c r="O47" s="32" t="n"/>
-      <c r="P47" s="32" t="n"/>
-      <c r="Q47" s="32" t="n"/>
-      <c r="R47" s="32" t="n"/>
-      <c r="S47" s="32" t="n"/>
-      <c r="T47" s="32" t="n"/>
-      <c r="U47" s="32" t="n"/>
-      <c r="V47" s="32" t="n"/>
-      <c r="W47" s="32" t="n"/>
-      <c r="X47" s="32" t="n"/>
-      <c r="Y47" s="32" t="n"/>
-      <c r="Z47" s="32" t="n"/>
-      <c r="AA47" s="32" t="n"/>
-      <c r="AB47" s="32" t="n"/>
-      <c r="AC47" s="32" t="n"/>
-      <c r="AD47" s="32" t="n"/>
-      <c r="AE47" s="32" t="n"/>
-      <c r="AF47" s="32" t="n"/>
-      <c r="AG47" s="32" t="n"/>
-      <c r="AH47" s="32" t="n"/>
-      <c r="AI47" s="32" t="n"/>
-      <c r="AJ47" s="32" t="n"/>
-      <c r="AK47" s="32" t="n"/>
-      <c r="AL47" s="32" t="n"/>
-      <c r="AM47" s="32" t="n"/>
-      <c r="AN47" s="32" t="n"/>
-      <c r="AO47" s="32" t="n"/>
-      <c r="AP47" s="32" t="n"/>
-      <c r="AQ47" s="32" t="n"/>
-      <c r="AR47" s="32" t="n"/>
-      <c r="AS47" s="32" t="n"/>
-      <c r="AT47" s="32" t="n"/>
-      <c r="AU47" s="32" t="n"/>
-      <c r="AV47" s="32" t="n"/>
-      <c r="AW47" s="32" t="n"/>
-      <c r="AX47" s="32" t="n"/>
-      <c r="AY47" s="32" t="n"/>
-      <c r="AZ47" s="32" t="n"/>
-      <c r="BA47" s="32" t="n"/>
-      <c r="BB47" s="32" t="n"/>
-      <c r="BC47" s="31" t="n"/>
+      <c r="H47" s="26" t="n"/>
+      <c r="I47" s="26" t="n"/>
+      <c r="J47" s="26" t="n"/>
+      <c r="K47" s="26" t="n"/>
+      <c r="L47" s="26" t="n"/>
+      <c r="M47" s="26" t="n"/>
+      <c r="N47" s="26" t="n"/>
+      <c r="O47" s="26" t="n"/>
+      <c r="P47" s="26" t="n"/>
+      <c r="Q47" s="26" t="n"/>
+      <c r="R47" s="26" t="n"/>
+      <c r="S47" s="26" t="n"/>
+      <c r="T47" s="26" t="n"/>
+      <c r="U47" s="26" t="n"/>
+      <c r="V47" s="26" t="n"/>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="26" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="26" t="n"/>
+      <c r="AB47" s="26" t="n"/>
+      <c r="AC47" s="26" t="n"/>
+      <c r="AD47" s="26" t="n"/>
+      <c r="AE47" s="26" t="n"/>
+      <c r="AF47" s="26" t="n"/>
+      <c r="AG47" s="26" t="n"/>
+      <c r="AH47" s="26" t="n"/>
+      <c r="AI47" s="26" t="n"/>
+      <c r="AJ47" s="26" t="n"/>
+      <c r="AK47" s="26" t="n"/>
+      <c r="AL47" s="26" t="n"/>
+      <c r="AM47" s="26" t="n"/>
+      <c r="AN47" s="26" t="n"/>
+      <c r="AO47" s="26" t="n"/>
+      <c r="AP47" s="26" t="n"/>
+      <c r="AQ47" s="26" t="n"/>
+      <c r="AR47" s="26" t="n"/>
+      <c r="AS47" s="26" t="n"/>
+      <c r="AT47" s="26" t="n"/>
+      <c r="AU47" s="26" t="n"/>
+      <c r="AV47" s="26" t="n"/>
+      <c r="AW47" s="26" t="n"/>
+      <c r="AX47" s="26" t="n"/>
+      <c r="AY47" s="26" t="n"/>
+      <c r="AZ47" s="26" t="n"/>
+      <c r="BA47" s="26" t="n"/>
+      <c r="BB47" s="26" t="n"/>
+      <c r="BC47" s="26" t="n"/>
       <c r="BD47" s="26" t="n"/>
       <c r="BE47" s="26" t="n"/>
       <c r="BF47" s="26" t="n"/>
-      <c r="BG47" s="26" t="n"/>
-      <c r="BH47" s="26" t="n"/>
-      <c r="BI47" s="26" t="n"/>
-      <c r="BJ47" s="26" t="n"/>
-      <c r="BK47" s="26" t="n"/>
-      <c r="BL47" s="26" t="n"/>
-      <c r="BM47" s="26" t="n"/>
-      <c r="BN47" s="26" t="n"/>
-      <c r="BO47" s="26" t="n"/>
+      <c r="BG47" s="27" t="n"/>
+      <c r="BH47" s="28" t="n"/>
+      <c r="BI47" s="28" t="n"/>
+      <c r="BJ47" s="28" t="n"/>
+      <c r="BK47" s="28" t="n"/>
+      <c r="BL47" s="28" t="n"/>
+      <c r="BM47" s="28" t="n"/>
+      <c r="BN47" s="28" t="n"/>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="28" t="n"/>
+      <c r="BQ47" s="28" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="27" t="inlineStr">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B48" s="27" t="inlineStr">
+      <c r="B48" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C48" s="28" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>PAB115·双级样机</t>
         </is>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="31">
         <f>'时间节点计划表'!E24</f>
         <v/>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="31">
         <f>IF(COUNT('时间节点计划表'!F24),'时间节点计划表'!F24,"")</f>
         <v/>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="32">
         <f>IF(OR(D48="",E48=""),"待填",E48-D48)</f>
         <v/>
       </c>
@@ -11546,6 +12010,22 @@
       </c>
       <c r="BO48" s="23">
         <f>IF(AND(COUNT($E48),N(BO$2)=N($E48)),$E48,IF(AND(COUNT($E48),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E48))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP48" s="23">
+        <f>IF(AND(COUNT($E48),N(BP$2)=N($E48)),$E48,IF(AND(COUNT($E48),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E48))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ48" s="23">
+        <f>IF(AND(COUNT($E48),N(BQ$2)=N($E48)),$E48,IF(AND(COUNT($E48),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E48))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR48" s="23">
+        <f>IF(AND(COUNT($E48),N(BR$2)=N($E48)),$E48,IF(AND(COUNT($E48),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E48))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS48" s="23">
+        <f>IF(AND(COUNT($E48),N(BS$2)=N($E48)),$E48,IF(AND(COUNT($E48),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E48))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -11578,92 +12058,96 @@
         <f>D49</f>
         <v/>
       </c>
-      <c r="H49" s="32" t="n"/>
-      <c r="I49" s="32" t="n"/>
-      <c r="J49" s="32" t="n"/>
-      <c r="K49" s="32" t="n"/>
-      <c r="L49" s="32" t="n"/>
-      <c r="M49" s="32" t="n"/>
-      <c r="N49" s="32" t="n"/>
-      <c r="O49" s="32" t="n"/>
-      <c r="P49" s="32" t="n"/>
-      <c r="Q49" s="32" t="n"/>
-      <c r="R49" s="32" t="n"/>
-      <c r="S49" s="32" t="n"/>
-      <c r="T49" s="32" t="n"/>
-      <c r="U49" s="32" t="n"/>
-      <c r="V49" s="32" t="n"/>
-      <c r="W49" s="32" t="n"/>
-      <c r="X49" s="32" t="n"/>
-      <c r="Y49" s="32" t="n"/>
-      <c r="Z49" s="32" t="n"/>
-      <c r="AA49" s="32" t="n"/>
-      <c r="AB49" s="32" t="n"/>
-      <c r="AC49" s="32" t="n"/>
-      <c r="AD49" s="32" t="n"/>
-      <c r="AE49" s="32" t="n"/>
-      <c r="AF49" s="32" t="n"/>
-      <c r="AG49" s="32" t="n"/>
-      <c r="AH49" s="32" t="n"/>
-      <c r="AI49" s="32" t="n"/>
-      <c r="AJ49" s="32" t="n"/>
-      <c r="AK49" s="32" t="n"/>
-      <c r="AL49" s="32" t="n"/>
-      <c r="AM49" s="32" t="n"/>
-      <c r="AN49" s="32" t="n"/>
-      <c r="AO49" s="32" t="n"/>
-      <c r="AP49" s="32" t="n"/>
-      <c r="AQ49" s="32" t="n"/>
-      <c r="AR49" s="32" t="n"/>
-      <c r="AS49" s="32" t="n"/>
-      <c r="AT49" s="32" t="n"/>
-      <c r="AU49" s="32" t="n"/>
-      <c r="AV49" s="32" t="n"/>
-      <c r="AW49" s="32" t="n"/>
-      <c r="AX49" s="32" t="n"/>
-      <c r="AY49" s="32" t="n"/>
-      <c r="AZ49" s="32" t="n"/>
-      <c r="BA49" s="32" t="n"/>
-      <c r="BB49" s="32" t="n"/>
-      <c r="BC49" s="32" t="n"/>
-      <c r="BD49" s="31" t="n"/>
+      <c r="H49" s="26" t="n"/>
+      <c r="I49" s="26" t="n"/>
+      <c r="J49" s="26" t="n"/>
+      <c r="K49" s="26" t="n"/>
+      <c r="L49" s="26" t="n"/>
+      <c r="M49" s="26" t="n"/>
+      <c r="N49" s="26" t="n"/>
+      <c r="O49" s="26" t="n"/>
+      <c r="P49" s="26" t="n"/>
+      <c r="Q49" s="26" t="n"/>
+      <c r="R49" s="26" t="n"/>
+      <c r="S49" s="26" t="n"/>
+      <c r="T49" s="26" t="n"/>
+      <c r="U49" s="26" t="n"/>
+      <c r="V49" s="26" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="26" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="26" t="n"/>
+      <c r="AB49" s="26" t="n"/>
+      <c r="AC49" s="26" t="n"/>
+      <c r="AD49" s="26" t="n"/>
+      <c r="AE49" s="26" t="n"/>
+      <c r="AF49" s="26" t="n"/>
+      <c r="AG49" s="26" t="n"/>
+      <c r="AH49" s="26" t="n"/>
+      <c r="AI49" s="26" t="n"/>
+      <c r="AJ49" s="26" t="n"/>
+      <c r="AK49" s="26" t="n"/>
+      <c r="AL49" s="26" t="n"/>
+      <c r="AM49" s="26" t="n"/>
+      <c r="AN49" s="26" t="n"/>
+      <c r="AO49" s="26" t="n"/>
+      <c r="AP49" s="26" t="n"/>
+      <c r="AQ49" s="26" t="n"/>
+      <c r="AR49" s="26" t="n"/>
+      <c r="AS49" s="26" t="n"/>
+      <c r="AT49" s="26" t="n"/>
+      <c r="AU49" s="26" t="n"/>
+      <c r="AV49" s="26" t="n"/>
+      <c r="AW49" s="26" t="n"/>
+      <c r="AX49" s="26" t="n"/>
+      <c r="AY49" s="26" t="n"/>
+      <c r="AZ49" s="26" t="n"/>
+      <c r="BA49" s="26" t="n"/>
+      <c r="BB49" s="26" t="n"/>
+      <c r="BC49" s="26" t="n"/>
+      <c r="BD49" s="26" t="n"/>
       <c r="BE49" s="26" t="n"/>
       <c r="BF49" s="26" t="n"/>
       <c r="BG49" s="26" t="n"/>
-      <c r="BH49" s="26" t="n"/>
-      <c r="BI49" s="26" t="n"/>
-      <c r="BJ49" s="26" t="n"/>
-      <c r="BK49" s="26" t="n"/>
-      <c r="BL49" s="26" t="n"/>
-      <c r="BM49" s="26" t="n"/>
-      <c r="BN49" s="26" t="n"/>
-      <c r="BO49" s="26" t="n"/>
+      <c r="BH49" s="27" t="n"/>
+      <c r="BI49" s="28" t="n"/>
+      <c r="BJ49" s="28" t="n"/>
+      <c r="BK49" s="28" t="n"/>
+      <c r="BL49" s="28" t="n"/>
+      <c r="BM49" s="28" t="n"/>
+      <c r="BN49" s="28" t="n"/>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="28" t="n"/>
+      <c r="BQ49" s="28" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B50" s="27" t="inlineStr">
+      <c r="B50" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C50" s="28" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>PAB142·零件到位</t>
         </is>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="31">
         <f>'时间节点计划表'!E25</f>
         <v/>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="31">
         <f>IF(COUNT('时间节点计划表'!F25),'时间节点计划表'!F25,"")</f>
         <v/>
       </c>
-      <c r="F50" s="30">
+      <c r="F50" s="32">
         <f>IF(OR(D50="",E50=""),"待填",E50-D50)</f>
         <v/>
       </c>
@@ -11909,6 +12393,22 @@
       </c>
       <c r="BO50" s="23">
         <f>IF(AND(COUNT($E50),N(BO$2)=N($E50)),$E50,IF(AND(COUNT($E50),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E50))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP50" s="23">
+        <f>IF(AND(COUNT($E50),N(BP$2)=N($E50)),$E50,IF(AND(COUNT($E50),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E50))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ50" s="23">
+        <f>IF(AND(COUNT($E50),N(BQ$2)=N($E50)),$E50,IF(AND(COUNT($E50),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E50))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR50" s="23">
+        <f>IF(AND(COUNT($E50),N(BR$2)=N($E50)),$E50,IF(AND(COUNT($E50),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E50))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS50" s="23">
+        <f>IF(AND(COUNT($E50),N(BS$2)=N($E50)),$E50,IF(AND(COUNT($E50),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E50))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -11941,92 +12441,96 @@
         <f>D51</f>
         <v/>
       </c>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="32" t="n"/>
-      <c r="J51" s="32" t="n"/>
-      <c r="K51" s="32" t="n"/>
-      <c r="L51" s="32" t="n"/>
-      <c r="M51" s="32" t="n"/>
-      <c r="N51" s="32" t="n"/>
-      <c r="O51" s="32" t="n"/>
-      <c r="P51" s="32" t="n"/>
-      <c r="Q51" s="32" t="n"/>
-      <c r="R51" s="31" t="n"/>
+      <c r="H51" s="26" t="n"/>
+      <c r="I51" s="26" t="n"/>
+      <c r="J51" s="26" t="n"/>
+      <c r="K51" s="26" t="n"/>
+      <c r="L51" s="26" t="n"/>
+      <c r="M51" s="26" t="n"/>
+      <c r="N51" s="26" t="n"/>
+      <c r="O51" s="26" t="n"/>
+      <c r="P51" s="26" t="n"/>
+      <c r="Q51" s="26" t="n"/>
+      <c r="R51" s="26" t="n"/>
       <c r="S51" s="26" t="n"/>
       <c r="T51" s="26" t="n"/>
       <c r="U51" s="26" t="n"/>
-      <c r="V51" s="26" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="26" t="n"/>
-      <c r="Z51" s="26" t="n"/>
-      <c r="AA51" s="26" t="n"/>
-      <c r="AB51" s="26" t="n"/>
-      <c r="AC51" s="26" t="n"/>
-      <c r="AD51" s="26" t="n"/>
-      <c r="AE51" s="26" t="n"/>
-      <c r="AF51" s="26" t="n"/>
-      <c r="AG51" s="26" t="n"/>
-      <c r="AH51" s="26" t="n"/>
-      <c r="AI51" s="26" t="n"/>
-      <c r="AJ51" s="26" t="n"/>
-      <c r="AK51" s="26" t="n"/>
-      <c r="AL51" s="26" t="n"/>
-      <c r="AM51" s="26" t="n"/>
-      <c r="AN51" s="26" t="n"/>
-      <c r="AO51" s="26" t="n"/>
-      <c r="AP51" s="26" t="n"/>
-      <c r="AQ51" s="26" t="n"/>
-      <c r="AR51" s="26" t="n"/>
-      <c r="AS51" s="26" t="n"/>
-      <c r="AT51" s="26" t="n"/>
-      <c r="AU51" s="26" t="n"/>
-      <c r="AV51" s="26" t="n"/>
-      <c r="AW51" s="26" t="n"/>
-      <c r="AX51" s="26" t="n"/>
-      <c r="AY51" s="26" t="n"/>
-      <c r="AZ51" s="26" t="n"/>
-      <c r="BA51" s="26" t="n"/>
-      <c r="BB51" s="26" t="n"/>
-      <c r="BC51" s="26" t="n"/>
-      <c r="BD51" s="26" t="n"/>
-      <c r="BE51" s="26" t="n"/>
-      <c r="BF51" s="26" t="n"/>
-      <c r="BG51" s="26" t="n"/>
-      <c r="BH51" s="26" t="n"/>
-      <c r="BI51" s="26" t="n"/>
-      <c r="BJ51" s="26" t="n"/>
-      <c r="BK51" s="26" t="n"/>
-      <c r="BL51" s="26" t="n"/>
-      <c r="BM51" s="26" t="n"/>
-      <c r="BN51" s="26" t="n"/>
-      <c r="BO51" s="26" t="n"/>
+      <c r="V51" s="27" t="n"/>
+      <c r="W51" s="28" t="n"/>
+      <c r="X51" s="28" t="n"/>
+      <c r="Y51" s="28" t="n"/>
+      <c r="Z51" s="28" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="28" t="n"/>
+      <c r="AD51" s="28" t="n"/>
+      <c r="AE51" s="28" t="n"/>
+      <c r="AF51" s="28" t="n"/>
+      <c r="AG51" s="28" t="n"/>
+      <c r="AH51" s="28" t="n"/>
+      <c r="AI51" s="28" t="n"/>
+      <c r="AJ51" s="28" t="n"/>
+      <c r="AK51" s="28" t="n"/>
+      <c r="AL51" s="28" t="n"/>
+      <c r="AM51" s="28" t="n"/>
+      <c r="AN51" s="28" t="n"/>
+      <c r="AO51" s="28" t="n"/>
+      <c r="AP51" s="28" t="n"/>
+      <c r="AQ51" s="28" t="n"/>
+      <c r="AR51" s="28" t="n"/>
+      <c r="AS51" s="28" t="n"/>
+      <c r="AT51" s="28" t="n"/>
+      <c r="AU51" s="28" t="n"/>
+      <c r="AV51" s="28" t="n"/>
+      <c r="AW51" s="28" t="n"/>
+      <c r="AX51" s="28" t="n"/>
+      <c r="AY51" s="28" t="n"/>
+      <c r="AZ51" s="28" t="n"/>
+      <c r="BA51" s="28" t="n"/>
+      <c r="BB51" s="28" t="n"/>
+      <c r="BC51" s="28" t="n"/>
+      <c r="BD51" s="28" t="n"/>
+      <c r="BE51" s="28" t="n"/>
+      <c r="BF51" s="28" t="n"/>
+      <c r="BG51" s="28" t="n"/>
+      <c r="BH51" s="28" t="n"/>
+      <c r="BI51" s="28" t="n"/>
+      <c r="BJ51" s="28" t="n"/>
+      <c r="BK51" s="28" t="n"/>
+      <c r="BL51" s="28" t="n"/>
+      <c r="BM51" s="28" t="n"/>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="28" t="n"/>
+      <c r="BQ51" s="28" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B52" s="27" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C52" s="28" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>PAB142·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="31">
         <f>'时间节点计划表'!E26</f>
         <v/>
       </c>
-      <c r="E52" s="29">
+      <c r="E52" s="31">
         <f>IF(COUNT('时间节点计划表'!F26),'时间节点计划表'!F26,"")</f>
         <v/>
       </c>
-      <c r="F52" s="30">
+      <c r="F52" s="32">
         <f>IF(OR(D52="",E52=""),"待填",E52-D52)</f>
         <v/>
       </c>
@@ -12272,6 +12776,22 @@
       </c>
       <c r="BO52" s="23">
         <f>IF(AND(COUNT($E52),N(BO$2)=N($E52)),$E52,IF(AND(COUNT($E52),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E52))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP52" s="23">
+        <f>IF(AND(COUNT($E52),N(BP$2)=N($E52)),$E52,IF(AND(COUNT($E52),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E52))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ52" s="23">
+        <f>IF(AND(COUNT($E52),N(BQ$2)=N($E52)),$E52,IF(AND(COUNT($E52),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E52))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR52" s="23">
+        <f>IF(AND(COUNT($E52),N(BR$2)=N($E52)),$E52,IF(AND(COUNT($E52),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E52))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS52" s="23">
+        <f>IF(AND(COUNT($E52),N(BS$2)=N($E52)),$E52,IF(AND(COUNT($E52),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E52))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -12304,92 +12824,96 @@
         <f>D53</f>
         <v/>
       </c>
-      <c r="H53" s="32" t="n"/>
-      <c r="I53" s="32" t="n"/>
-      <c r="J53" s="32" t="n"/>
-      <c r="K53" s="32" t="n"/>
-      <c r="L53" s="32" t="n"/>
-      <c r="M53" s="32" t="n"/>
-      <c r="N53" s="32" t="n"/>
-      <c r="O53" s="32" t="n"/>
-      <c r="P53" s="32" t="n"/>
-      <c r="Q53" s="32" t="n"/>
-      <c r="R53" s="32" t="n"/>
-      <c r="S53" s="32" t="n"/>
-      <c r="T53" s="32" t="n"/>
-      <c r="U53" s="32" t="n"/>
-      <c r="V53" s="32" t="n"/>
-      <c r="W53" s="32" t="n"/>
-      <c r="X53" s="32" t="n"/>
-      <c r="Y53" s="32" t="n"/>
-      <c r="Z53" s="32" t="n"/>
-      <c r="AA53" s="32" t="n"/>
-      <c r="AB53" s="32" t="n"/>
-      <c r="AC53" s="32" t="n"/>
-      <c r="AD53" s="32" t="n"/>
-      <c r="AE53" s="32" t="n"/>
-      <c r="AF53" s="32" t="n"/>
-      <c r="AG53" s="32" t="n"/>
-      <c r="AH53" s="32" t="n"/>
-      <c r="AI53" s="32" t="n"/>
-      <c r="AJ53" s="32" t="n"/>
-      <c r="AK53" s="32" t="n"/>
-      <c r="AL53" s="32" t="n"/>
-      <c r="AM53" s="32" t="n"/>
-      <c r="AN53" s="32" t="n"/>
-      <c r="AO53" s="32" t="n"/>
-      <c r="AP53" s="32" t="n"/>
-      <c r="AQ53" s="31" t="n"/>
+      <c r="H53" s="26" t="n"/>
+      <c r="I53" s="26" t="n"/>
+      <c r="J53" s="26" t="n"/>
+      <c r="K53" s="26" t="n"/>
+      <c r="L53" s="26" t="n"/>
+      <c r="M53" s="26" t="n"/>
+      <c r="N53" s="26" t="n"/>
+      <c r="O53" s="26" t="n"/>
+      <c r="P53" s="26" t="n"/>
+      <c r="Q53" s="26" t="n"/>
+      <c r="R53" s="26" t="n"/>
+      <c r="S53" s="26" t="n"/>
+      <c r="T53" s="26" t="n"/>
+      <c r="U53" s="26" t="n"/>
+      <c r="V53" s="26" t="n"/>
+      <c r="W53" s="26" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="26" t="n"/>
+      <c r="Z53" s="26" t="n"/>
+      <c r="AA53" s="26" t="n"/>
+      <c r="AB53" s="26" t="n"/>
+      <c r="AC53" s="26" t="n"/>
+      <c r="AD53" s="26" t="n"/>
+      <c r="AE53" s="26" t="n"/>
+      <c r="AF53" s="26" t="n"/>
+      <c r="AG53" s="26" t="n"/>
+      <c r="AH53" s="26" t="n"/>
+      <c r="AI53" s="26" t="n"/>
+      <c r="AJ53" s="26" t="n"/>
+      <c r="AK53" s="26" t="n"/>
+      <c r="AL53" s="26" t="n"/>
+      <c r="AM53" s="26" t="n"/>
+      <c r="AN53" s="26" t="n"/>
+      <c r="AO53" s="26" t="n"/>
+      <c r="AP53" s="26" t="n"/>
+      <c r="AQ53" s="26" t="n"/>
       <c r="AR53" s="26" t="n"/>
       <c r="AS53" s="26" t="n"/>
       <c r="AT53" s="26" t="n"/>
-      <c r="AU53" s="26" t="n"/>
-      <c r="AV53" s="26" t="n"/>
-      <c r="AW53" s="26" t="n"/>
-      <c r="AX53" s="26" t="n"/>
-      <c r="AY53" s="26" t="n"/>
-      <c r="AZ53" s="26" t="n"/>
-      <c r="BA53" s="26" t="n"/>
-      <c r="BB53" s="26" t="n"/>
-      <c r="BC53" s="26" t="n"/>
-      <c r="BD53" s="26" t="n"/>
-      <c r="BE53" s="26" t="n"/>
-      <c r="BF53" s="26" t="n"/>
-      <c r="BG53" s="26" t="n"/>
-      <c r="BH53" s="26" t="n"/>
-      <c r="BI53" s="26" t="n"/>
-      <c r="BJ53" s="26" t="n"/>
-      <c r="BK53" s="26" t="n"/>
-      <c r="BL53" s="26" t="n"/>
-      <c r="BM53" s="26" t="n"/>
-      <c r="BN53" s="26" t="n"/>
-      <c r="BO53" s="26" t="n"/>
+      <c r="AU53" s="27" t="n"/>
+      <c r="AV53" s="28" t="n"/>
+      <c r="AW53" s="28" t="n"/>
+      <c r="AX53" s="28" t="n"/>
+      <c r="AY53" s="28" t="n"/>
+      <c r="AZ53" s="28" t="n"/>
+      <c r="BA53" s="28" t="n"/>
+      <c r="BB53" s="28" t="n"/>
+      <c r="BC53" s="28" t="n"/>
+      <c r="BD53" s="28" t="n"/>
+      <c r="BE53" s="28" t="n"/>
+      <c r="BF53" s="28" t="n"/>
+      <c r="BG53" s="28" t="n"/>
+      <c r="BH53" s="28" t="n"/>
+      <c r="BI53" s="28" t="n"/>
+      <c r="BJ53" s="28" t="n"/>
+      <c r="BK53" s="28" t="n"/>
+      <c r="BL53" s="28" t="n"/>
+      <c r="BM53" s="28" t="n"/>
+      <c r="BN53" s="28" t="n"/>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="28" t="n"/>
+      <c r="BQ53" s="28" t="n"/>
+      <c r="BR53" s="28" t="n"/>
+      <c r="BS53" s="28" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="27" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B54" s="27" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C54" s="28" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>PAB142·工装实物到位</t>
         </is>
       </c>
-      <c r="D54" s="29">
+      <c r="D54" s="31">
         <f>'时间节点计划表'!E27</f>
         <v/>
       </c>
-      <c r="E54" s="29">
+      <c r="E54" s="31">
         <f>IF(COUNT('时间节点计划表'!F27),'时间节点计划表'!F27,"")</f>
         <v/>
       </c>
-      <c r="F54" s="30">
+      <c r="F54" s="32">
         <f>IF(OR(D54="",E54=""),"待填",E54-D54)</f>
         <v/>
       </c>
@@ -12635,6 +13159,22 @@
       </c>
       <c r="BO54" s="23">
         <f>IF(AND(COUNT($E54),N(BO$2)=N($E54)),$E54,IF(AND(COUNT($E54),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E54))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP54" s="23">
+        <f>IF(AND(COUNT($E54),N(BP$2)=N($E54)),$E54,IF(AND(COUNT($E54),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E54))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ54" s="23">
+        <f>IF(AND(COUNT($E54),N(BQ$2)=N($E54)),$E54,IF(AND(COUNT($E54),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E54))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR54" s="23">
+        <f>IF(AND(COUNT($E54),N(BR$2)=N($E54)),$E54,IF(AND(COUNT($E54),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E54))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS54" s="23">
+        <f>IF(AND(COUNT($E54),N(BS$2)=N($E54)),$E54,IF(AND(COUNT($E54),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E54))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -12667,92 +13207,96 @@
         <f>D55</f>
         <v/>
       </c>
-      <c r="H55" s="32" t="n"/>
-      <c r="I55" s="32" t="n"/>
-      <c r="J55" s="32" t="n"/>
-      <c r="K55" s="32" t="n"/>
-      <c r="L55" s="32" t="n"/>
-      <c r="M55" s="32" t="n"/>
-      <c r="N55" s="32" t="n"/>
-      <c r="O55" s="32" t="n"/>
-      <c r="P55" s="32" t="n"/>
-      <c r="Q55" s="32" t="n"/>
-      <c r="R55" s="32" t="n"/>
-      <c r="S55" s="32" t="n"/>
-      <c r="T55" s="32" t="n"/>
-      <c r="U55" s="32" t="n"/>
-      <c r="V55" s="32" t="n"/>
-      <c r="W55" s="32" t="n"/>
-      <c r="X55" s="32" t="n"/>
-      <c r="Y55" s="32" t="n"/>
-      <c r="Z55" s="32" t="n"/>
-      <c r="AA55" s="32" t="n"/>
-      <c r="AB55" s="32" t="n"/>
-      <c r="AC55" s="32" t="n"/>
-      <c r="AD55" s="32" t="n"/>
-      <c r="AE55" s="32" t="n"/>
-      <c r="AF55" s="32" t="n"/>
-      <c r="AG55" s="32" t="n"/>
-      <c r="AH55" s="32" t="n"/>
-      <c r="AI55" s="32" t="n"/>
-      <c r="AJ55" s="32" t="n"/>
-      <c r="AK55" s="32" t="n"/>
-      <c r="AL55" s="32" t="n"/>
-      <c r="AM55" s="32" t="n"/>
-      <c r="AN55" s="32" t="n"/>
-      <c r="AO55" s="32" t="n"/>
-      <c r="AP55" s="32" t="n"/>
-      <c r="AQ55" s="32" t="n"/>
-      <c r="AR55" s="32" t="n"/>
-      <c r="AS55" s="32" t="n"/>
-      <c r="AT55" s="32" t="n"/>
-      <c r="AU55" s="32" t="n"/>
-      <c r="AV55" s="32" t="n"/>
-      <c r="AW55" s="32" t="n"/>
-      <c r="AX55" s="32" t="n"/>
-      <c r="AY55" s="32" t="n"/>
-      <c r="AZ55" s="32" t="n"/>
-      <c r="BA55" s="32" t="n"/>
-      <c r="BB55" s="32" t="n"/>
-      <c r="BC55" s="32" t="n"/>
-      <c r="BD55" s="31" t="n"/>
+      <c r="H55" s="26" t="n"/>
+      <c r="I55" s="26" t="n"/>
+      <c r="J55" s="26" t="n"/>
+      <c r="K55" s="26" t="n"/>
+      <c r="L55" s="26" t="n"/>
+      <c r="M55" s="26" t="n"/>
+      <c r="N55" s="26" t="n"/>
+      <c r="O55" s="26" t="n"/>
+      <c r="P55" s="26" t="n"/>
+      <c r="Q55" s="26" t="n"/>
+      <c r="R55" s="26" t="n"/>
+      <c r="S55" s="26" t="n"/>
+      <c r="T55" s="26" t="n"/>
+      <c r="U55" s="26" t="n"/>
+      <c r="V55" s="26" t="n"/>
+      <c r="W55" s="26" t="n"/>
+      <c r="X55" s="26" t="n"/>
+      <c r="Y55" s="26" t="n"/>
+      <c r="Z55" s="26" t="n"/>
+      <c r="AA55" s="26" t="n"/>
+      <c r="AB55" s="26" t="n"/>
+      <c r="AC55" s="26" t="n"/>
+      <c r="AD55" s="26" t="n"/>
+      <c r="AE55" s="26" t="n"/>
+      <c r="AF55" s="26" t="n"/>
+      <c r="AG55" s="26" t="n"/>
+      <c r="AH55" s="26" t="n"/>
+      <c r="AI55" s="26" t="n"/>
+      <c r="AJ55" s="26" t="n"/>
+      <c r="AK55" s="26" t="n"/>
+      <c r="AL55" s="26" t="n"/>
+      <c r="AM55" s="26" t="n"/>
+      <c r="AN55" s="26" t="n"/>
+      <c r="AO55" s="26" t="n"/>
+      <c r="AP55" s="26" t="n"/>
+      <c r="AQ55" s="26" t="n"/>
+      <c r="AR55" s="26" t="n"/>
+      <c r="AS55" s="26" t="n"/>
+      <c r="AT55" s="26" t="n"/>
+      <c r="AU55" s="26" t="n"/>
+      <c r="AV55" s="26" t="n"/>
+      <c r="AW55" s="26" t="n"/>
+      <c r="AX55" s="26" t="n"/>
+      <c r="AY55" s="26" t="n"/>
+      <c r="AZ55" s="26" t="n"/>
+      <c r="BA55" s="26" t="n"/>
+      <c r="BB55" s="26" t="n"/>
+      <c r="BC55" s="26" t="n"/>
+      <c r="BD55" s="26" t="n"/>
       <c r="BE55" s="26" t="n"/>
       <c r="BF55" s="26" t="n"/>
       <c r="BG55" s="26" t="n"/>
-      <c r="BH55" s="26" t="n"/>
-      <c r="BI55" s="26" t="n"/>
-      <c r="BJ55" s="26" t="n"/>
-      <c r="BK55" s="26" t="n"/>
-      <c r="BL55" s="26" t="n"/>
-      <c r="BM55" s="26" t="n"/>
-      <c r="BN55" s="26" t="n"/>
-      <c r="BO55" s="26" t="n"/>
+      <c r="BH55" s="27" t="n"/>
+      <c r="BI55" s="28" t="n"/>
+      <c r="BJ55" s="28" t="n"/>
+      <c r="BK55" s="28" t="n"/>
+      <c r="BL55" s="28" t="n"/>
+      <c r="BM55" s="28" t="n"/>
+      <c r="BN55" s="28" t="n"/>
+      <c r="BO55" s="28" t="n"/>
+      <c r="BP55" s="28" t="n"/>
+      <c r="BQ55" s="28" t="n"/>
+      <c r="BR55" s="28" t="n"/>
+      <c r="BS55" s="28" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
+      <c r="A56" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B56" s="27" t="inlineStr">
+      <c r="B56" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C56" s="28" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>PAB142·排针机安装调试</t>
         </is>
       </c>
-      <c r="D56" s="29">
+      <c r="D56" s="31">
         <f>'时间节点计划表'!E28</f>
         <v/>
       </c>
-      <c r="E56" s="29">
+      <c r="E56" s="31">
         <f>IF(COUNT('时间节点计划表'!F28),'时间节点计划表'!F28,"")</f>
         <v/>
       </c>
-      <c r="F56" s="30">
+      <c r="F56" s="32">
         <f>IF(OR(D56="",E56=""),"待填",E56-D56)</f>
         <v/>
       </c>
@@ -12998,6 +13542,22 @@
       </c>
       <c r="BO56" s="23">
         <f>IF(AND(COUNT($E56),N(BO$2)=N($E56)),$E56,IF(AND(COUNT($E56),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E56))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP56" s="23">
+        <f>IF(AND(COUNT($E56),N(BP$2)=N($E56)),$E56,IF(AND(COUNT($E56),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E56))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ56" s="23">
+        <f>IF(AND(COUNT($E56),N(BQ$2)=N($E56)),$E56,IF(AND(COUNT($E56),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E56))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR56" s="23">
+        <f>IF(AND(COUNT($E56),N(BR$2)=N($E56)),$E56,IF(AND(COUNT($E56),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E56))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS56" s="23">
+        <f>IF(AND(COUNT($E56),N(BS$2)=N($E56)),$E56,IF(AND(COUNT($E56),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E56))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -13030,92 +13590,96 @@
         <f>D57</f>
         <v/>
       </c>
-      <c r="H57" s="32" t="n"/>
-      <c r="I57" s="32" t="n"/>
-      <c r="J57" s="32" t="n"/>
-      <c r="K57" s="32" t="n"/>
-      <c r="L57" s="32" t="n"/>
-      <c r="M57" s="32" t="n"/>
-      <c r="N57" s="32" t="n"/>
-      <c r="O57" s="32" t="n"/>
-      <c r="P57" s="32" t="n"/>
-      <c r="Q57" s="32" t="n"/>
-      <c r="R57" s="32" t="n"/>
-      <c r="S57" s="32" t="n"/>
-      <c r="T57" s="32" t="n"/>
-      <c r="U57" s="32" t="n"/>
-      <c r="V57" s="32" t="n"/>
-      <c r="W57" s="32" t="n"/>
-      <c r="X57" s="32" t="n"/>
-      <c r="Y57" s="32" t="n"/>
-      <c r="Z57" s="32" t="n"/>
-      <c r="AA57" s="32" t="n"/>
-      <c r="AB57" s="32" t="n"/>
-      <c r="AC57" s="32" t="n"/>
-      <c r="AD57" s="32" t="n"/>
-      <c r="AE57" s="32" t="n"/>
-      <c r="AF57" s="32" t="n"/>
-      <c r="AG57" s="32" t="n"/>
-      <c r="AH57" s="32" t="n"/>
-      <c r="AI57" s="32" t="n"/>
-      <c r="AJ57" s="32" t="n"/>
-      <c r="AK57" s="32" t="n"/>
-      <c r="AL57" s="32" t="n"/>
-      <c r="AM57" s="32" t="n"/>
-      <c r="AN57" s="32" t="n"/>
-      <c r="AO57" s="32" t="n"/>
-      <c r="AP57" s="32" t="n"/>
-      <c r="AQ57" s="32" t="n"/>
-      <c r="AR57" s="32" t="n"/>
-      <c r="AS57" s="32" t="n"/>
-      <c r="AT57" s="32" t="n"/>
-      <c r="AU57" s="32" t="n"/>
-      <c r="AV57" s="32" t="n"/>
-      <c r="AW57" s="32" t="n"/>
-      <c r="AX57" s="32" t="n"/>
-      <c r="AY57" s="32" t="n"/>
-      <c r="AZ57" s="32" t="n"/>
-      <c r="BA57" s="32" t="n"/>
-      <c r="BB57" s="32" t="n"/>
-      <c r="BC57" s="32" t="n"/>
-      <c r="BD57" s="32" t="n"/>
-      <c r="BE57" s="31" t="n"/>
+      <c r="H57" s="26" t="n"/>
+      <c r="I57" s="26" t="n"/>
+      <c r="J57" s="26" t="n"/>
+      <c r="K57" s="26" t="n"/>
+      <c r="L57" s="26" t="n"/>
+      <c r="M57" s="26" t="n"/>
+      <c r="N57" s="26" t="n"/>
+      <c r="O57" s="26" t="n"/>
+      <c r="P57" s="26" t="n"/>
+      <c r="Q57" s="26" t="n"/>
+      <c r="R57" s="26" t="n"/>
+      <c r="S57" s="26" t="n"/>
+      <c r="T57" s="26" t="n"/>
+      <c r="U57" s="26" t="n"/>
+      <c r="V57" s="26" t="n"/>
+      <c r="W57" s="26" t="n"/>
+      <c r="X57" s="26" t="n"/>
+      <c r="Y57" s="26" t="n"/>
+      <c r="Z57" s="26" t="n"/>
+      <c r="AA57" s="26" t="n"/>
+      <c r="AB57" s="26" t="n"/>
+      <c r="AC57" s="26" t="n"/>
+      <c r="AD57" s="26" t="n"/>
+      <c r="AE57" s="26" t="n"/>
+      <c r="AF57" s="26" t="n"/>
+      <c r="AG57" s="26" t="n"/>
+      <c r="AH57" s="26" t="n"/>
+      <c r="AI57" s="26" t="n"/>
+      <c r="AJ57" s="26" t="n"/>
+      <c r="AK57" s="26" t="n"/>
+      <c r="AL57" s="26" t="n"/>
+      <c r="AM57" s="26" t="n"/>
+      <c r="AN57" s="26" t="n"/>
+      <c r="AO57" s="26" t="n"/>
+      <c r="AP57" s="26" t="n"/>
+      <c r="AQ57" s="26" t="n"/>
+      <c r="AR57" s="26" t="n"/>
+      <c r="AS57" s="26" t="n"/>
+      <c r="AT57" s="26" t="n"/>
+      <c r="AU57" s="26" t="n"/>
+      <c r="AV57" s="26" t="n"/>
+      <c r="AW57" s="26" t="n"/>
+      <c r="AX57" s="26" t="n"/>
+      <c r="AY57" s="26" t="n"/>
+      <c r="AZ57" s="26" t="n"/>
+      <c r="BA57" s="26" t="n"/>
+      <c r="BB57" s="26" t="n"/>
+      <c r="BC57" s="26" t="n"/>
+      <c r="BD57" s="26" t="n"/>
+      <c r="BE57" s="26" t="n"/>
       <c r="BF57" s="26" t="n"/>
       <c r="BG57" s="26" t="n"/>
       <c r="BH57" s="26" t="n"/>
-      <c r="BI57" s="26" t="n"/>
-      <c r="BJ57" s="26" t="n"/>
-      <c r="BK57" s="26" t="n"/>
-      <c r="BL57" s="26" t="n"/>
-      <c r="BM57" s="26" t="n"/>
-      <c r="BN57" s="26" t="n"/>
-      <c r="BO57" s="26" t="n"/>
+      <c r="BI57" s="27" t="n"/>
+      <c r="BJ57" s="28" t="n"/>
+      <c r="BK57" s="28" t="n"/>
+      <c r="BL57" s="28" t="n"/>
+      <c r="BM57" s="28" t="n"/>
+      <c r="BN57" s="28" t="n"/>
+      <c r="BO57" s="28" t="n"/>
+      <c r="BP57" s="28" t="n"/>
+      <c r="BQ57" s="28" t="n"/>
+      <c r="BR57" s="28" t="n"/>
+      <c r="BS57" s="28" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
+      <c r="A58" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B58" s="27" t="inlineStr">
+      <c r="B58" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C58" s="28" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
         <is>
           <t>PAB142·单级样机</t>
         </is>
       </c>
-      <c r="D58" s="29">
+      <c r="D58" s="31">
         <f>'时间节点计划表'!E29</f>
         <v/>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="31">
         <f>IF(COUNT('时间节点计划表'!F29),'时间节点计划表'!F29,"")</f>
         <v/>
       </c>
-      <c r="F58" s="30">
+      <c r="F58" s="32">
         <f>IF(OR(D58="",E58=""),"待填",E58-D58)</f>
         <v/>
       </c>
@@ -13361,6 +13925,22 @@
       </c>
       <c r="BO58" s="23">
         <f>IF(AND(COUNT($E58),N(BO$2)=N($E58)),$E58,IF(AND(COUNT($E58),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E58))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP58" s="23">
+        <f>IF(AND(COUNT($E58),N(BP$2)=N($E58)),$E58,IF(AND(COUNT($E58),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E58))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ58" s="23">
+        <f>IF(AND(COUNT($E58),N(BQ$2)=N($E58)),$E58,IF(AND(COUNT($E58),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E58))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR58" s="23">
+        <f>IF(AND(COUNT($E58),N(BR$2)=N($E58)),$E58,IF(AND(COUNT($E58),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E58))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS58" s="23">
+        <f>IF(AND(COUNT($E58),N(BS$2)=N($E58)),$E58,IF(AND(COUNT($E58),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E58))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -13393,92 +13973,96 @@
         <f>D59</f>
         <v/>
       </c>
-      <c r="H59" s="32" t="n"/>
-      <c r="I59" s="32" t="n"/>
-      <c r="J59" s="32" t="n"/>
-      <c r="K59" s="32" t="n"/>
-      <c r="L59" s="32" t="n"/>
-      <c r="M59" s="32" t="n"/>
-      <c r="N59" s="32" t="n"/>
-      <c r="O59" s="32" t="n"/>
-      <c r="P59" s="32" t="n"/>
-      <c r="Q59" s="32" t="n"/>
-      <c r="R59" s="32" t="n"/>
-      <c r="S59" s="32" t="n"/>
-      <c r="T59" s="32" t="n"/>
-      <c r="U59" s="32" t="n"/>
-      <c r="V59" s="32" t="n"/>
-      <c r="W59" s="32" t="n"/>
-      <c r="X59" s="32" t="n"/>
-      <c r="Y59" s="32" t="n"/>
-      <c r="Z59" s="32" t="n"/>
-      <c r="AA59" s="32" t="n"/>
-      <c r="AB59" s="32" t="n"/>
-      <c r="AC59" s="32" t="n"/>
-      <c r="AD59" s="32" t="n"/>
-      <c r="AE59" s="32" t="n"/>
-      <c r="AF59" s="32" t="n"/>
-      <c r="AG59" s="32" t="n"/>
-      <c r="AH59" s="32" t="n"/>
-      <c r="AI59" s="32" t="n"/>
-      <c r="AJ59" s="32" t="n"/>
-      <c r="AK59" s="32" t="n"/>
-      <c r="AL59" s="32" t="n"/>
-      <c r="AM59" s="32" t="n"/>
-      <c r="AN59" s="32" t="n"/>
-      <c r="AO59" s="32" t="n"/>
-      <c r="AP59" s="32" t="n"/>
-      <c r="AQ59" s="32" t="n"/>
-      <c r="AR59" s="32" t="n"/>
-      <c r="AS59" s="32" t="n"/>
-      <c r="AT59" s="32" t="n"/>
-      <c r="AU59" s="32" t="n"/>
-      <c r="AV59" s="32" t="n"/>
-      <c r="AW59" s="32" t="n"/>
-      <c r="AX59" s="32" t="n"/>
-      <c r="AY59" s="32" t="n"/>
-      <c r="AZ59" s="32" t="n"/>
-      <c r="BA59" s="32" t="n"/>
-      <c r="BB59" s="32" t="n"/>
-      <c r="BC59" s="32" t="n"/>
-      <c r="BD59" s="32" t="n"/>
-      <c r="BE59" s="32" t="n"/>
-      <c r="BF59" s="32" t="n"/>
-      <c r="BG59" s="31" t="n"/>
+      <c r="H59" s="26" t="n"/>
+      <c r="I59" s="26" t="n"/>
+      <c r="J59" s="26" t="n"/>
+      <c r="K59" s="26" t="n"/>
+      <c r="L59" s="26" t="n"/>
+      <c r="M59" s="26" t="n"/>
+      <c r="N59" s="26" t="n"/>
+      <c r="O59" s="26" t="n"/>
+      <c r="P59" s="26" t="n"/>
+      <c r="Q59" s="26" t="n"/>
+      <c r="R59" s="26" t="n"/>
+      <c r="S59" s="26" t="n"/>
+      <c r="T59" s="26" t="n"/>
+      <c r="U59" s="26" t="n"/>
+      <c r="V59" s="26" t="n"/>
+      <c r="W59" s="26" t="n"/>
+      <c r="X59" s="26" t="n"/>
+      <c r="Y59" s="26" t="n"/>
+      <c r="Z59" s="26" t="n"/>
+      <c r="AA59" s="26" t="n"/>
+      <c r="AB59" s="26" t="n"/>
+      <c r="AC59" s="26" t="n"/>
+      <c r="AD59" s="26" t="n"/>
+      <c r="AE59" s="26" t="n"/>
+      <c r="AF59" s="26" t="n"/>
+      <c r="AG59" s="26" t="n"/>
+      <c r="AH59" s="26" t="n"/>
+      <c r="AI59" s="26" t="n"/>
+      <c r="AJ59" s="26" t="n"/>
+      <c r="AK59" s="26" t="n"/>
+      <c r="AL59" s="26" t="n"/>
+      <c r="AM59" s="26" t="n"/>
+      <c r="AN59" s="26" t="n"/>
+      <c r="AO59" s="26" t="n"/>
+      <c r="AP59" s="26" t="n"/>
+      <c r="AQ59" s="26" t="n"/>
+      <c r="AR59" s="26" t="n"/>
+      <c r="AS59" s="26" t="n"/>
+      <c r="AT59" s="26" t="n"/>
+      <c r="AU59" s="26" t="n"/>
+      <c r="AV59" s="26" t="n"/>
+      <c r="AW59" s="26" t="n"/>
+      <c r="AX59" s="26" t="n"/>
+      <c r="AY59" s="26" t="n"/>
+      <c r="AZ59" s="26" t="n"/>
+      <c r="BA59" s="26" t="n"/>
+      <c r="BB59" s="26" t="n"/>
+      <c r="BC59" s="26" t="n"/>
+      <c r="BD59" s="26" t="n"/>
+      <c r="BE59" s="26" t="n"/>
+      <c r="BF59" s="26" t="n"/>
+      <c r="BG59" s="26" t="n"/>
       <c r="BH59" s="26" t="n"/>
       <c r="BI59" s="26" t="n"/>
       <c r="BJ59" s="26" t="n"/>
-      <c r="BK59" s="26" t="n"/>
-      <c r="BL59" s="26" t="n"/>
-      <c r="BM59" s="26" t="n"/>
-      <c r="BN59" s="26" t="n"/>
-      <c r="BO59" s="26" t="n"/>
+      <c r="BK59" s="27" t="n"/>
+      <c r="BL59" s="28" t="n"/>
+      <c r="BM59" s="28" t="n"/>
+      <c r="BN59" s="28" t="n"/>
+      <c r="BO59" s="28" t="n"/>
+      <c r="BP59" s="28" t="n"/>
+      <c r="BQ59" s="28" t="n"/>
+      <c r="BR59" s="28" t="n"/>
+      <c r="BS59" s="28" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
+      <c r="A60" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B60" s="27" t="inlineStr">
+      <c r="B60" s="29" t="inlineStr">
         <is>
           <t>第一期</t>
         </is>
       </c>
-      <c r="C60" s="28" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>PAB142·双级样机</t>
         </is>
       </c>
-      <c r="D60" s="29">
+      <c r="D60" s="31">
         <f>'时间节点计划表'!E30</f>
         <v/>
       </c>
-      <c r="E60" s="29">
+      <c r="E60" s="31">
         <f>IF(COUNT('时间节点计划表'!F30),'时间节点计划表'!F30,"")</f>
         <v/>
       </c>
-      <c r="F60" s="30">
+      <c r="F60" s="32">
         <f>IF(OR(D60="",E60=""),"待填",E60-D60)</f>
         <v/>
       </c>
@@ -13724,6 +14308,22 @@
       </c>
       <c r="BO60" s="23">
         <f>IF(AND(COUNT($E60),N(BO$2)=N($E60)),$E60,IF(AND(COUNT($E60),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E60))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP60" s="23">
+        <f>IF(AND(COUNT($E60),N(BP$2)=N($E60)),$E60,IF(AND(COUNT($E60),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E60))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ60" s="23">
+        <f>IF(AND(COUNT($E60),N(BQ$2)=N($E60)),$E60,IF(AND(COUNT($E60),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E60))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR60" s="23">
+        <f>IF(AND(COUNT($E60),N(BR$2)=N($E60)),$E60,IF(AND(COUNT($E60),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E60))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS60" s="23">
+        <f>IF(AND(COUNT($E60),N(BS$2)=N($E60)),$E60,IF(AND(COUNT($E60),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E60))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -13756,92 +14356,96 @@
         <f>D61</f>
         <v/>
       </c>
-      <c r="H61" s="32" t="n"/>
-      <c r="I61" s="32" t="n"/>
-      <c r="J61" s="32" t="n"/>
-      <c r="K61" s="32" t="n"/>
-      <c r="L61" s="32" t="n"/>
-      <c r="M61" s="32" t="n"/>
-      <c r="N61" s="32" t="n"/>
-      <c r="O61" s="32" t="n"/>
-      <c r="P61" s="32" t="n"/>
-      <c r="Q61" s="32" t="n"/>
-      <c r="R61" s="32" t="n"/>
-      <c r="S61" s="32" t="n"/>
-      <c r="T61" s="32" t="n"/>
-      <c r="U61" s="31" t="n"/>
+      <c r="H61" s="26" t="n"/>
+      <c r="I61" s="26" t="n"/>
+      <c r="J61" s="26" t="n"/>
+      <c r="K61" s="26" t="n"/>
+      <c r="L61" s="26" t="n"/>
+      <c r="M61" s="26" t="n"/>
+      <c r="N61" s="26" t="n"/>
+      <c r="O61" s="26" t="n"/>
+      <c r="P61" s="26" t="n"/>
+      <c r="Q61" s="26" t="n"/>
+      <c r="R61" s="26" t="n"/>
+      <c r="S61" s="26" t="n"/>
+      <c r="T61" s="26" t="n"/>
+      <c r="U61" s="26" t="n"/>
       <c r="V61" s="26" t="n"/>
       <c r="W61" s="26" t="n"/>
       <c r="X61" s="26" t="n"/>
-      <c r="Y61" s="26" t="n"/>
-      <c r="Z61" s="26" t="n"/>
-      <c r="AA61" s="26" t="n"/>
-      <c r="AB61" s="26" t="n"/>
-      <c r="AC61" s="26" t="n"/>
-      <c r="AD61" s="26" t="n"/>
-      <c r="AE61" s="26" t="n"/>
-      <c r="AF61" s="26" t="n"/>
-      <c r="AG61" s="26" t="n"/>
-      <c r="AH61" s="26" t="n"/>
-      <c r="AI61" s="26" t="n"/>
-      <c r="AJ61" s="26" t="n"/>
-      <c r="AK61" s="26" t="n"/>
-      <c r="AL61" s="26" t="n"/>
-      <c r="AM61" s="26" t="n"/>
-      <c r="AN61" s="26" t="n"/>
-      <c r="AO61" s="26" t="n"/>
-      <c r="AP61" s="26" t="n"/>
-      <c r="AQ61" s="26" t="n"/>
-      <c r="AR61" s="26" t="n"/>
-      <c r="AS61" s="26" t="n"/>
-      <c r="AT61" s="26" t="n"/>
-      <c r="AU61" s="26" t="n"/>
-      <c r="AV61" s="26" t="n"/>
-      <c r="AW61" s="26" t="n"/>
-      <c r="AX61" s="26" t="n"/>
-      <c r="AY61" s="26" t="n"/>
-      <c r="AZ61" s="26" t="n"/>
-      <c r="BA61" s="26" t="n"/>
-      <c r="BB61" s="26" t="n"/>
-      <c r="BC61" s="26" t="n"/>
-      <c r="BD61" s="26" t="n"/>
-      <c r="BE61" s="26" t="n"/>
-      <c r="BF61" s="26" t="n"/>
-      <c r="BG61" s="26" t="n"/>
-      <c r="BH61" s="26" t="n"/>
-      <c r="BI61" s="26" t="n"/>
-      <c r="BJ61" s="26" t="n"/>
-      <c r="BK61" s="26" t="n"/>
-      <c r="BL61" s="26" t="n"/>
-      <c r="BM61" s="26" t="n"/>
-      <c r="BN61" s="26" t="n"/>
-      <c r="BO61" s="26" t="n"/>
+      <c r="Y61" s="27" t="n"/>
+      <c r="Z61" s="28" t="n"/>
+      <c r="AA61" s="28" t="n"/>
+      <c r="AB61" s="28" t="n"/>
+      <c r="AC61" s="28" t="n"/>
+      <c r="AD61" s="28" t="n"/>
+      <c r="AE61" s="28" t="n"/>
+      <c r="AF61" s="28" t="n"/>
+      <c r="AG61" s="28" t="n"/>
+      <c r="AH61" s="28" t="n"/>
+      <c r="AI61" s="28" t="n"/>
+      <c r="AJ61" s="28" t="n"/>
+      <c r="AK61" s="28" t="n"/>
+      <c r="AL61" s="28" t="n"/>
+      <c r="AM61" s="28" t="n"/>
+      <c r="AN61" s="28" t="n"/>
+      <c r="AO61" s="28" t="n"/>
+      <c r="AP61" s="28" t="n"/>
+      <c r="AQ61" s="28" t="n"/>
+      <c r="AR61" s="28" t="n"/>
+      <c r="AS61" s="28" t="n"/>
+      <c r="AT61" s="28" t="n"/>
+      <c r="AU61" s="28" t="n"/>
+      <c r="AV61" s="28" t="n"/>
+      <c r="AW61" s="28" t="n"/>
+      <c r="AX61" s="28" t="n"/>
+      <c r="AY61" s="28" t="n"/>
+      <c r="AZ61" s="28" t="n"/>
+      <c r="BA61" s="28" t="n"/>
+      <c r="BB61" s="28" t="n"/>
+      <c r="BC61" s="28" t="n"/>
+      <c r="BD61" s="28" t="n"/>
+      <c r="BE61" s="28" t="n"/>
+      <c r="BF61" s="28" t="n"/>
+      <c r="BG61" s="28" t="n"/>
+      <c r="BH61" s="28" t="n"/>
+      <c r="BI61" s="28" t="n"/>
+      <c r="BJ61" s="28" t="n"/>
+      <c r="BK61" s="28" t="n"/>
+      <c r="BL61" s="28" t="n"/>
+      <c r="BM61" s="28" t="n"/>
+      <c r="BN61" s="28" t="n"/>
+      <c r="BO61" s="28" t="n"/>
+      <c r="BP61" s="28" t="n"/>
+      <c r="BQ61" s="28" t="n"/>
+      <c r="BR61" s="28" t="n"/>
+      <c r="BS61" s="28" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
+      <c r="A62" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B62" s="27" t="inlineStr">
+      <c r="B62" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C62" s="28" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>二期零件图纸整理归档</t>
         </is>
       </c>
-      <c r="D62" s="29">
+      <c r="D62" s="31">
         <f>'时间节点计划表'!E31</f>
         <v/>
       </c>
-      <c r="E62" s="29">
+      <c r="E62" s="31">
         <f>IF(COUNT('时间节点计划表'!F31),'时间节点计划表'!F31,"")</f>
         <v/>
       </c>
-      <c r="F62" s="30">
+      <c r="F62" s="32">
         <f>IF(OR(D62="",E62=""),"待填",E62-D62)</f>
         <v/>
       </c>
@@ -14087,6 +14691,22 @@
       </c>
       <c r="BO62" s="23">
         <f>IF(AND(COUNT($E62),N(BO$2)=N($E62)),$E62,IF(AND(COUNT($E62),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E62))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP62" s="23">
+        <f>IF(AND(COUNT($E62),N(BP$2)=N($E62)),$E62,IF(AND(COUNT($E62),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E62))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ62" s="23">
+        <f>IF(AND(COUNT($E62),N(BQ$2)=N($E62)),$E62,IF(AND(COUNT($E62),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E62))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR62" s="23">
+        <f>IF(AND(COUNT($E62),N(BR$2)=N($E62)),$E62,IF(AND(COUNT($E62),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E62))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS62" s="23">
+        <f>IF(AND(COUNT($E62),N(BS$2)=N($E62)),$E62,IF(AND(COUNT($E62),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E62))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -14119,92 +14739,96 @@
         <f>D63</f>
         <v/>
       </c>
-      <c r="H63" s="32" t="n"/>
-      <c r="I63" s="32" t="n"/>
-      <c r="J63" s="32" t="n"/>
-      <c r="K63" s="32" t="n"/>
-      <c r="L63" s="32" t="n"/>
-      <c r="M63" s="32" t="n"/>
-      <c r="N63" s="32" t="n"/>
-      <c r="O63" s="32" t="n"/>
-      <c r="P63" s="32" t="n"/>
-      <c r="Q63" s="32" t="n"/>
-      <c r="R63" s="32" t="n"/>
-      <c r="S63" s="32" t="n"/>
-      <c r="T63" s="32" t="n"/>
-      <c r="U63" s="32" t="n"/>
-      <c r="V63" s="32" t="n"/>
-      <c r="W63" s="32" t="n"/>
-      <c r="X63" s="31" t="n"/>
+      <c r="H63" s="26" t="n"/>
+      <c r="I63" s="26" t="n"/>
+      <c r="J63" s="26" t="n"/>
+      <c r="K63" s="26" t="n"/>
+      <c r="L63" s="26" t="n"/>
+      <c r="M63" s="26" t="n"/>
+      <c r="N63" s="26" t="n"/>
+      <c r="O63" s="26" t="n"/>
+      <c r="P63" s="26" t="n"/>
+      <c r="Q63" s="26" t="n"/>
+      <c r="R63" s="26" t="n"/>
+      <c r="S63" s="26" t="n"/>
+      <c r="T63" s="26" t="n"/>
+      <c r="U63" s="26" t="n"/>
+      <c r="V63" s="26" t="n"/>
+      <c r="W63" s="26" t="n"/>
+      <c r="X63" s="26" t="n"/>
       <c r="Y63" s="26" t="n"/>
       <c r="Z63" s="26" t="n"/>
       <c r="AA63" s="26" t="n"/>
-      <c r="AB63" s="26" t="n"/>
-      <c r="AC63" s="26" t="n"/>
-      <c r="AD63" s="26" t="n"/>
-      <c r="AE63" s="26" t="n"/>
-      <c r="AF63" s="26" t="n"/>
-      <c r="AG63" s="26" t="n"/>
-      <c r="AH63" s="26" t="n"/>
-      <c r="AI63" s="26" t="n"/>
-      <c r="AJ63" s="26" t="n"/>
-      <c r="AK63" s="26" t="n"/>
-      <c r="AL63" s="26" t="n"/>
-      <c r="AM63" s="26" t="n"/>
-      <c r="AN63" s="26" t="n"/>
-      <c r="AO63" s="26" t="n"/>
-      <c r="AP63" s="26" t="n"/>
-      <c r="AQ63" s="26" t="n"/>
-      <c r="AR63" s="26" t="n"/>
-      <c r="AS63" s="26" t="n"/>
-      <c r="AT63" s="26" t="n"/>
-      <c r="AU63" s="26" t="n"/>
-      <c r="AV63" s="26" t="n"/>
-      <c r="AW63" s="26" t="n"/>
-      <c r="AX63" s="26" t="n"/>
-      <c r="AY63" s="26" t="n"/>
-      <c r="AZ63" s="26" t="n"/>
-      <c r="BA63" s="26" t="n"/>
-      <c r="BB63" s="26" t="n"/>
-      <c r="BC63" s="26" t="n"/>
-      <c r="BD63" s="26" t="n"/>
-      <c r="BE63" s="26" t="n"/>
-      <c r="BF63" s="26" t="n"/>
-      <c r="BG63" s="26" t="n"/>
-      <c r="BH63" s="26" t="n"/>
-      <c r="BI63" s="26" t="n"/>
-      <c r="BJ63" s="26" t="n"/>
-      <c r="BK63" s="26" t="n"/>
-      <c r="BL63" s="26" t="n"/>
-      <c r="BM63" s="26" t="n"/>
-      <c r="BN63" s="26" t="n"/>
-      <c r="BO63" s="26" t="n"/>
+      <c r="AB63" s="27" t="n"/>
+      <c r="AC63" s="28" t="n"/>
+      <c r="AD63" s="28" t="n"/>
+      <c r="AE63" s="28" t="n"/>
+      <c r="AF63" s="28" t="n"/>
+      <c r="AG63" s="28" t="n"/>
+      <c r="AH63" s="28" t="n"/>
+      <c r="AI63" s="28" t="n"/>
+      <c r="AJ63" s="28" t="n"/>
+      <c r="AK63" s="28" t="n"/>
+      <c r="AL63" s="28" t="n"/>
+      <c r="AM63" s="28" t="n"/>
+      <c r="AN63" s="28" t="n"/>
+      <c r="AO63" s="28" t="n"/>
+      <c r="AP63" s="28" t="n"/>
+      <c r="AQ63" s="28" t="n"/>
+      <c r="AR63" s="28" t="n"/>
+      <c r="AS63" s="28" t="n"/>
+      <c r="AT63" s="28" t="n"/>
+      <c r="AU63" s="28" t="n"/>
+      <c r="AV63" s="28" t="n"/>
+      <c r="AW63" s="28" t="n"/>
+      <c r="AX63" s="28" t="n"/>
+      <c r="AY63" s="28" t="n"/>
+      <c r="AZ63" s="28" t="n"/>
+      <c r="BA63" s="28" t="n"/>
+      <c r="BB63" s="28" t="n"/>
+      <c r="BC63" s="28" t="n"/>
+      <c r="BD63" s="28" t="n"/>
+      <c r="BE63" s="28" t="n"/>
+      <c r="BF63" s="28" t="n"/>
+      <c r="BG63" s="28" t="n"/>
+      <c r="BH63" s="28" t="n"/>
+      <c r="BI63" s="28" t="n"/>
+      <c r="BJ63" s="28" t="n"/>
+      <c r="BK63" s="28" t="n"/>
+      <c r="BL63" s="28" t="n"/>
+      <c r="BM63" s="28" t="n"/>
+      <c r="BN63" s="28" t="n"/>
+      <c r="BO63" s="28" t="n"/>
+      <c r="BP63" s="28" t="n"/>
+      <c r="BQ63" s="28" t="n"/>
+      <c r="BR63" s="28" t="n"/>
+      <c r="BS63" s="28" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="27" t="inlineStr">
+      <c r="A64" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B64" s="27" t="inlineStr">
+      <c r="B64" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C64" s="28" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>二期零件下单采购</t>
         </is>
       </c>
-      <c r="D64" s="29">
+      <c r="D64" s="31">
         <f>'时间节点计划表'!E32</f>
         <v/>
       </c>
-      <c r="E64" s="29">
+      <c r="E64" s="31">
         <f>IF(COUNT('时间节点计划表'!F32),'时间节点计划表'!F32,"")</f>
         <v/>
       </c>
-      <c r="F64" s="30">
+      <c r="F64" s="32">
         <f>IF(OR(D64="",E64=""),"待填",E64-D64)</f>
         <v/>
       </c>
@@ -14450,6 +15074,22 @@
       </c>
       <c r="BO64" s="23">
         <f>IF(AND(COUNT($E64),N(BO$2)=N($E64)),$E64,IF(AND(COUNT($E64),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E64))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP64" s="23">
+        <f>IF(AND(COUNT($E64),N(BP$2)=N($E64)),$E64,IF(AND(COUNT($E64),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E64))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ64" s="23">
+        <f>IF(AND(COUNT($E64),N(BQ$2)=N($E64)),$E64,IF(AND(COUNT($E64),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E64))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR64" s="23">
+        <f>IF(AND(COUNT($E64),N(BR$2)=N($E64)),$E64,IF(AND(COUNT($E64),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E64))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS64" s="23">
+        <f>IF(AND(COUNT($E64),N(BS$2)=N($E64)),$E64,IF(AND(COUNT($E64),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E64))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -14482,92 +15122,96 @@
         <f>D65</f>
         <v/>
       </c>
-      <c r="H65" s="32" t="n"/>
-      <c r="I65" s="32" t="n"/>
-      <c r="J65" s="32" t="n"/>
-      <c r="K65" s="32" t="n"/>
-      <c r="L65" s="32" t="n"/>
-      <c r="M65" s="32" t="n"/>
-      <c r="N65" s="32" t="n"/>
-      <c r="O65" s="32" t="n"/>
-      <c r="P65" s="32" t="n"/>
-      <c r="Q65" s="32" t="n"/>
-      <c r="R65" s="32" t="n"/>
-      <c r="S65" s="32" t="n"/>
-      <c r="T65" s="32" t="n"/>
-      <c r="U65" s="32" t="n"/>
-      <c r="V65" s="32" t="n"/>
-      <c r="W65" s="32" t="n"/>
-      <c r="X65" s="31" t="n"/>
+      <c r="H65" s="26" t="n"/>
+      <c r="I65" s="26" t="n"/>
+      <c r="J65" s="26" t="n"/>
+      <c r="K65" s="26" t="n"/>
+      <c r="L65" s="26" t="n"/>
+      <c r="M65" s="26" t="n"/>
+      <c r="N65" s="26" t="n"/>
+      <c r="O65" s="26" t="n"/>
+      <c r="P65" s="26" t="n"/>
+      <c r="Q65" s="26" t="n"/>
+      <c r="R65" s="26" t="n"/>
+      <c r="S65" s="26" t="n"/>
+      <c r="T65" s="26" t="n"/>
+      <c r="U65" s="26" t="n"/>
+      <c r="V65" s="26" t="n"/>
+      <c r="W65" s="26" t="n"/>
+      <c r="X65" s="26" t="n"/>
       <c r="Y65" s="26" t="n"/>
       <c r="Z65" s="26" t="n"/>
       <c r="AA65" s="26" t="n"/>
-      <c r="AB65" s="26" t="n"/>
-      <c r="AC65" s="26" t="n"/>
-      <c r="AD65" s="26" t="n"/>
-      <c r="AE65" s="26" t="n"/>
-      <c r="AF65" s="26" t="n"/>
-      <c r="AG65" s="26" t="n"/>
-      <c r="AH65" s="26" t="n"/>
-      <c r="AI65" s="26" t="n"/>
-      <c r="AJ65" s="26" t="n"/>
-      <c r="AK65" s="26" t="n"/>
-      <c r="AL65" s="26" t="n"/>
-      <c r="AM65" s="26" t="n"/>
-      <c r="AN65" s="26" t="n"/>
-      <c r="AO65" s="26" t="n"/>
-      <c r="AP65" s="26" t="n"/>
-      <c r="AQ65" s="26" t="n"/>
-      <c r="AR65" s="26" t="n"/>
-      <c r="AS65" s="26" t="n"/>
-      <c r="AT65" s="26" t="n"/>
-      <c r="AU65" s="26" t="n"/>
-      <c r="AV65" s="26" t="n"/>
-      <c r="AW65" s="26" t="n"/>
-      <c r="AX65" s="26" t="n"/>
-      <c r="AY65" s="26" t="n"/>
-      <c r="AZ65" s="26" t="n"/>
-      <c r="BA65" s="26" t="n"/>
-      <c r="BB65" s="26" t="n"/>
-      <c r="BC65" s="26" t="n"/>
-      <c r="BD65" s="26" t="n"/>
-      <c r="BE65" s="26" t="n"/>
-      <c r="BF65" s="26" t="n"/>
-      <c r="BG65" s="26" t="n"/>
-      <c r="BH65" s="26" t="n"/>
-      <c r="BI65" s="26" t="n"/>
-      <c r="BJ65" s="26" t="n"/>
-      <c r="BK65" s="26" t="n"/>
-      <c r="BL65" s="26" t="n"/>
-      <c r="BM65" s="26" t="n"/>
-      <c r="BN65" s="26" t="n"/>
-      <c r="BO65" s="26" t="n"/>
+      <c r="AB65" s="27" t="n"/>
+      <c r="AC65" s="28" t="n"/>
+      <c r="AD65" s="28" t="n"/>
+      <c r="AE65" s="28" t="n"/>
+      <c r="AF65" s="28" t="n"/>
+      <c r="AG65" s="28" t="n"/>
+      <c r="AH65" s="28" t="n"/>
+      <c r="AI65" s="28" t="n"/>
+      <c r="AJ65" s="28" t="n"/>
+      <c r="AK65" s="28" t="n"/>
+      <c r="AL65" s="28" t="n"/>
+      <c r="AM65" s="28" t="n"/>
+      <c r="AN65" s="28" t="n"/>
+      <c r="AO65" s="28" t="n"/>
+      <c r="AP65" s="28" t="n"/>
+      <c r="AQ65" s="28" t="n"/>
+      <c r="AR65" s="28" t="n"/>
+      <c r="AS65" s="28" t="n"/>
+      <c r="AT65" s="28" t="n"/>
+      <c r="AU65" s="28" t="n"/>
+      <c r="AV65" s="28" t="n"/>
+      <c r="AW65" s="28" t="n"/>
+      <c r="AX65" s="28" t="n"/>
+      <c r="AY65" s="28" t="n"/>
+      <c r="AZ65" s="28" t="n"/>
+      <c r="BA65" s="28" t="n"/>
+      <c r="BB65" s="28" t="n"/>
+      <c r="BC65" s="28" t="n"/>
+      <c r="BD65" s="28" t="n"/>
+      <c r="BE65" s="28" t="n"/>
+      <c r="BF65" s="28" t="n"/>
+      <c r="BG65" s="28" t="n"/>
+      <c r="BH65" s="28" t="n"/>
+      <c r="BI65" s="28" t="n"/>
+      <c r="BJ65" s="28" t="n"/>
+      <c r="BK65" s="28" t="n"/>
+      <c r="BL65" s="28" t="n"/>
+      <c r="BM65" s="28" t="n"/>
+      <c r="BN65" s="28" t="n"/>
+      <c r="BO65" s="28" t="n"/>
+      <c r="BP65" s="28" t="n"/>
+      <c r="BQ65" s="28" t="n"/>
+      <c r="BR65" s="28" t="n"/>
+      <c r="BS65" s="28" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="27" t="inlineStr">
+      <c r="A66" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B66" s="27" t="inlineStr">
+      <c r="B66" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C66" s="28" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>二期标准件下单采购</t>
         </is>
       </c>
-      <c r="D66" s="29">
+      <c r="D66" s="31">
         <f>'时间节点计划表'!E33</f>
         <v/>
       </c>
-      <c r="E66" s="29">
+      <c r="E66" s="31">
         <f>IF(COUNT('时间节点计划表'!F33),'时间节点计划表'!F33,"")</f>
         <v/>
       </c>
-      <c r="F66" s="30">
+      <c r="F66" s="32">
         <f>IF(OR(D66="",E66=""),"待填",E66-D66)</f>
         <v/>
       </c>
@@ -14813,6 +15457,22 @@
       </c>
       <c r="BO66" s="23">
         <f>IF(AND(COUNT($E66),N(BO$2)=N($E66)),$E66,IF(AND(COUNT($E66),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E66))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP66" s="23">
+        <f>IF(AND(COUNT($E66),N(BP$2)=N($E66)),$E66,IF(AND(COUNT($E66),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E66))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ66" s="23">
+        <f>IF(AND(COUNT($E66),N(BQ$2)=N($E66)),$E66,IF(AND(COUNT($E66),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E66))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR66" s="23">
+        <f>IF(AND(COUNT($E66),N(BR$2)=N($E66)),$E66,IF(AND(COUNT($E66),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E66))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS66" s="23">
+        <f>IF(AND(COUNT($E66),N(BS$2)=N($E66)),$E66,IF(AND(COUNT($E66),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E66))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -14845,92 +15505,96 @@
         <f>D67</f>
         <v/>
       </c>
-      <c r="H67" s="32" t="n"/>
-      <c r="I67" s="32" t="n"/>
-      <c r="J67" s="32" t="n"/>
-      <c r="K67" s="32" t="n"/>
-      <c r="L67" s="32" t="n"/>
-      <c r="M67" s="32" t="n"/>
-      <c r="N67" s="32" t="n"/>
-      <c r="O67" s="32" t="n"/>
-      <c r="P67" s="32" t="n"/>
-      <c r="Q67" s="32" t="n"/>
-      <c r="R67" s="32" t="n"/>
-      <c r="S67" s="32" t="n"/>
-      <c r="T67" s="32" t="n"/>
-      <c r="U67" s="32" t="n"/>
-      <c r="V67" s="32" t="n"/>
-      <c r="W67" s="32" t="n"/>
-      <c r="X67" s="32" t="n"/>
-      <c r="Y67" s="32" t="n"/>
-      <c r="Z67" s="32" t="n"/>
-      <c r="AA67" s="32" t="n"/>
-      <c r="AB67" s="32" t="n"/>
-      <c r="AC67" s="32" t="n"/>
-      <c r="AD67" s="32" t="n"/>
-      <c r="AE67" s="32" t="n"/>
-      <c r="AF67" s="32" t="n"/>
-      <c r="AG67" s="32" t="n"/>
-      <c r="AH67" s="32" t="n"/>
-      <c r="AI67" s="32" t="n"/>
-      <c r="AJ67" s="32" t="n"/>
-      <c r="AK67" s="32" t="n"/>
-      <c r="AL67" s="32" t="n"/>
-      <c r="AM67" s="32" t="n"/>
-      <c r="AN67" s="32" t="n"/>
-      <c r="AO67" s="32" t="n"/>
-      <c r="AP67" s="32" t="n"/>
-      <c r="AQ67" s="32" t="n"/>
-      <c r="AR67" s="32" t="n"/>
-      <c r="AS67" s="32" t="n"/>
-      <c r="AT67" s="32" t="n"/>
-      <c r="AU67" s="32" t="n"/>
-      <c r="AV67" s="32" t="n"/>
-      <c r="AW67" s="32" t="n"/>
-      <c r="AX67" s="32" t="n"/>
-      <c r="AY67" s="32" t="n"/>
-      <c r="AZ67" s="32" t="n"/>
-      <c r="BA67" s="32" t="n"/>
-      <c r="BB67" s="32" t="n"/>
-      <c r="BC67" s="32" t="n"/>
-      <c r="BD67" s="32" t="n"/>
-      <c r="BE67" s="32" t="n"/>
-      <c r="BF67" s="32" t="n"/>
-      <c r="BG67" s="31" t="n"/>
+      <c r="H67" s="26" t="n"/>
+      <c r="I67" s="26" t="n"/>
+      <c r="J67" s="26" t="n"/>
+      <c r="K67" s="26" t="n"/>
+      <c r="L67" s="26" t="n"/>
+      <c r="M67" s="26" t="n"/>
+      <c r="N67" s="26" t="n"/>
+      <c r="O67" s="26" t="n"/>
+      <c r="P67" s="26" t="n"/>
+      <c r="Q67" s="26" t="n"/>
+      <c r="R67" s="26" t="n"/>
+      <c r="S67" s="26" t="n"/>
+      <c r="T67" s="26" t="n"/>
+      <c r="U67" s="26" t="n"/>
+      <c r="V67" s="26" t="n"/>
+      <c r="W67" s="26" t="n"/>
+      <c r="X67" s="26" t="n"/>
+      <c r="Y67" s="26" t="n"/>
+      <c r="Z67" s="26" t="n"/>
+      <c r="AA67" s="26" t="n"/>
+      <c r="AB67" s="26" t="n"/>
+      <c r="AC67" s="26" t="n"/>
+      <c r="AD67" s="26" t="n"/>
+      <c r="AE67" s="26" t="n"/>
+      <c r="AF67" s="26" t="n"/>
+      <c r="AG67" s="26" t="n"/>
+      <c r="AH67" s="26" t="n"/>
+      <c r="AI67" s="26" t="n"/>
+      <c r="AJ67" s="26" t="n"/>
+      <c r="AK67" s="26" t="n"/>
+      <c r="AL67" s="26" t="n"/>
+      <c r="AM67" s="26" t="n"/>
+      <c r="AN67" s="26" t="n"/>
+      <c r="AO67" s="26" t="n"/>
+      <c r="AP67" s="26" t="n"/>
+      <c r="AQ67" s="26" t="n"/>
+      <c r="AR67" s="26" t="n"/>
+      <c r="AS67" s="26" t="n"/>
+      <c r="AT67" s="26" t="n"/>
+      <c r="AU67" s="26" t="n"/>
+      <c r="AV67" s="26" t="n"/>
+      <c r="AW67" s="26" t="n"/>
+      <c r="AX67" s="26" t="n"/>
+      <c r="AY67" s="26" t="n"/>
+      <c r="AZ67" s="26" t="n"/>
+      <c r="BA67" s="26" t="n"/>
+      <c r="BB67" s="26" t="n"/>
+      <c r="BC67" s="26" t="n"/>
+      <c r="BD67" s="26" t="n"/>
+      <c r="BE67" s="26" t="n"/>
+      <c r="BF67" s="26" t="n"/>
+      <c r="BG67" s="26" t="n"/>
       <c r="BH67" s="26" t="n"/>
       <c r="BI67" s="26" t="n"/>
       <c r="BJ67" s="26" t="n"/>
-      <c r="BK67" s="26" t="n"/>
-      <c r="BL67" s="26" t="n"/>
-      <c r="BM67" s="26" t="n"/>
-      <c r="BN67" s="26" t="n"/>
-      <c r="BO67" s="26" t="n"/>
+      <c r="BK67" s="27" t="n"/>
+      <c r="BL67" s="28" t="n"/>
+      <c r="BM67" s="28" t="n"/>
+      <c r="BN67" s="28" t="n"/>
+      <c r="BO67" s="28" t="n"/>
+      <c r="BP67" s="28" t="n"/>
+      <c r="BQ67" s="28" t="n"/>
+      <c r="BR67" s="28" t="n"/>
+      <c r="BS67" s="28" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="27" t="inlineStr">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B68" s="27" t="inlineStr">
+      <c r="B68" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C68" s="28" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>PAB180·零件到位</t>
         </is>
       </c>
-      <c r="D68" s="29">
+      <c r="D68" s="31">
         <f>'时间节点计划表'!E34</f>
         <v/>
       </c>
-      <c r="E68" s="29">
+      <c r="E68" s="31">
         <f>IF(COUNT('时间节点计划表'!F34),'时间节点计划表'!F34,"")</f>
         <v/>
       </c>
-      <c r="F68" s="30">
+      <c r="F68" s="32">
         <f>IF(OR(D68="",E68=""),"待填",E68-D68)</f>
         <v/>
       </c>
@@ -15176,6 +15840,22 @@
       </c>
       <c r="BO68" s="23">
         <f>IF(AND(COUNT($E68),N(BO$2)=N($E68)),$E68,IF(AND(COUNT($E68),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E68))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP68" s="23">
+        <f>IF(AND(COUNT($E68),N(BP$2)=N($E68)),$E68,IF(AND(COUNT($E68),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E68))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ68" s="23">
+        <f>IF(AND(COUNT($E68),N(BQ$2)=N($E68)),$E68,IF(AND(COUNT($E68),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E68))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR68" s="23">
+        <f>IF(AND(COUNT($E68),N(BR$2)=N($E68)),$E68,IF(AND(COUNT($E68),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E68))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS68" s="23">
+        <f>IF(AND(COUNT($E68),N(BS$2)=N($E68)),$E68,IF(AND(COUNT($E68),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E68))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -15208,92 +15888,96 @@
         <f>D69</f>
         <v/>
       </c>
-      <c r="H69" s="32" t="n"/>
-      <c r="I69" s="32" t="n"/>
-      <c r="J69" s="32" t="n"/>
-      <c r="K69" s="32" t="n"/>
-      <c r="L69" s="32" t="n"/>
-      <c r="M69" s="32" t="n"/>
-      <c r="N69" s="32" t="n"/>
-      <c r="O69" s="32" t="n"/>
-      <c r="P69" s="32" t="n"/>
-      <c r="Q69" s="32" t="n"/>
-      <c r="R69" s="32" t="n"/>
-      <c r="S69" s="32" t="n"/>
-      <c r="T69" s="32" t="n"/>
-      <c r="U69" s="32" t="n"/>
-      <c r="V69" s="32" t="n"/>
-      <c r="W69" s="32" t="n"/>
-      <c r="X69" s="32" t="n"/>
-      <c r="Y69" s="31" t="n"/>
+      <c r="H69" s="26" t="n"/>
+      <c r="I69" s="26" t="n"/>
+      <c r="J69" s="26" t="n"/>
+      <c r="K69" s="26" t="n"/>
+      <c r="L69" s="26" t="n"/>
+      <c r="M69" s="26" t="n"/>
+      <c r="N69" s="26" t="n"/>
+      <c r="O69" s="26" t="n"/>
+      <c r="P69" s="26" t="n"/>
+      <c r="Q69" s="26" t="n"/>
+      <c r="R69" s="26" t="n"/>
+      <c r="S69" s="26" t="n"/>
+      <c r="T69" s="26" t="n"/>
+      <c r="U69" s="26" t="n"/>
+      <c r="V69" s="26" t="n"/>
+      <c r="W69" s="26" t="n"/>
+      <c r="X69" s="26" t="n"/>
+      <c r="Y69" s="26" t="n"/>
       <c r="Z69" s="26" t="n"/>
       <c r="AA69" s="26" t="n"/>
       <c r="AB69" s="26" t="n"/>
-      <c r="AC69" s="26" t="n"/>
-      <c r="AD69" s="26" t="n"/>
-      <c r="AE69" s="26" t="n"/>
-      <c r="AF69" s="26" t="n"/>
-      <c r="AG69" s="26" t="n"/>
-      <c r="AH69" s="26" t="n"/>
-      <c r="AI69" s="26" t="n"/>
-      <c r="AJ69" s="26" t="n"/>
-      <c r="AK69" s="26" t="n"/>
-      <c r="AL69" s="26" t="n"/>
-      <c r="AM69" s="26" t="n"/>
-      <c r="AN69" s="26" t="n"/>
-      <c r="AO69" s="26" t="n"/>
-      <c r="AP69" s="26" t="n"/>
-      <c r="AQ69" s="26" t="n"/>
-      <c r="AR69" s="26" t="n"/>
-      <c r="AS69" s="26" t="n"/>
-      <c r="AT69" s="26" t="n"/>
-      <c r="AU69" s="26" t="n"/>
-      <c r="AV69" s="26" t="n"/>
-      <c r="AW69" s="26" t="n"/>
-      <c r="AX69" s="26" t="n"/>
-      <c r="AY69" s="26" t="n"/>
-      <c r="AZ69" s="26" t="n"/>
-      <c r="BA69" s="26" t="n"/>
-      <c r="BB69" s="26" t="n"/>
-      <c r="BC69" s="26" t="n"/>
-      <c r="BD69" s="26" t="n"/>
-      <c r="BE69" s="26" t="n"/>
-      <c r="BF69" s="26" t="n"/>
-      <c r="BG69" s="26" t="n"/>
-      <c r="BH69" s="26" t="n"/>
-      <c r="BI69" s="26" t="n"/>
-      <c r="BJ69" s="26" t="n"/>
-      <c r="BK69" s="26" t="n"/>
-      <c r="BL69" s="26" t="n"/>
-      <c r="BM69" s="26" t="n"/>
-      <c r="BN69" s="26" t="n"/>
-      <c r="BO69" s="26" t="n"/>
+      <c r="AC69" s="27" t="n"/>
+      <c r="AD69" s="28" t="n"/>
+      <c r="AE69" s="28" t="n"/>
+      <c r="AF69" s="28" t="n"/>
+      <c r="AG69" s="28" t="n"/>
+      <c r="AH69" s="28" t="n"/>
+      <c r="AI69" s="28" t="n"/>
+      <c r="AJ69" s="28" t="n"/>
+      <c r="AK69" s="28" t="n"/>
+      <c r="AL69" s="28" t="n"/>
+      <c r="AM69" s="28" t="n"/>
+      <c r="AN69" s="28" t="n"/>
+      <c r="AO69" s="28" t="n"/>
+      <c r="AP69" s="28" t="n"/>
+      <c r="AQ69" s="28" t="n"/>
+      <c r="AR69" s="28" t="n"/>
+      <c r="AS69" s="28" t="n"/>
+      <c r="AT69" s="28" t="n"/>
+      <c r="AU69" s="28" t="n"/>
+      <c r="AV69" s="28" t="n"/>
+      <c r="AW69" s="28" t="n"/>
+      <c r="AX69" s="28" t="n"/>
+      <c r="AY69" s="28" t="n"/>
+      <c r="AZ69" s="28" t="n"/>
+      <c r="BA69" s="28" t="n"/>
+      <c r="BB69" s="28" t="n"/>
+      <c r="BC69" s="28" t="n"/>
+      <c r="BD69" s="28" t="n"/>
+      <c r="BE69" s="28" t="n"/>
+      <c r="BF69" s="28" t="n"/>
+      <c r="BG69" s="28" t="n"/>
+      <c r="BH69" s="28" t="n"/>
+      <c r="BI69" s="28" t="n"/>
+      <c r="BJ69" s="28" t="n"/>
+      <c r="BK69" s="28" t="n"/>
+      <c r="BL69" s="28" t="n"/>
+      <c r="BM69" s="28" t="n"/>
+      <c r="BN69" s="28" t="n"/>
+      <c r="BO69" s="28" t="n"/>
+      <c r="BP69" s="28" t="n"/>
+      <c r="BQ69" s="28" t="n"/>
+      <c r="BR69" s="28" t="n"/>
+      <c r="BS69" s="28" t="n"/>
     </row>
     <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="27" t="inlineStr">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B70" s="27" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C70" s="28" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>PAB180·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D70" s="29">
+      <c r="D70" s="31">
         <f>'时间节点计划表'!E35</f>
         <v/>
       </c>
-      <c r="E70" s="29">
+      <c r="E70" s="31">
         <f>IF(COUNT('时间节点计划表'!F35),'时间节点计划表'!F35,"")</f>
         <v/>
       </c>
-      <c r="F70" s="30">
+      <c r="F70" s="32">
         <f>IF(OR(D70="",E70=""),"待填",E70-D70)</f>
         <v/>
       </c>
@@ -15539,6 +16223,22 @@
       </c>
       <c r="BO70" s="23">
         <f>IF(AND(COUNT($E70),N(BO$2)=N($E70)),$E70,IF(AND(COUNT($E70),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E70))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP70" s="23">
+        <f>IF(AND(COUNT($E70),N(BP$2)=N($E70)),$E70,IF(AND(COUNT($E70),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E70))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ70" s="23">
+        <f>IF(AND(COUNT($E70),N(BQ$2)=N($E70)),$E70,IF(AND(COUNT($E70),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E70))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR70" s="23">
+        <f>IF(AND(COUNT($E70),N(BR$2)=N($E70)),$E70,IF(AND(COUNT($E70),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E70))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS70" s="23">
+        <f>IF(AND(COUNT($E70),N(BS$2)=N($E70)),$E70,IF(AND(COUNT($E70),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E70))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -15571,92 +16271,96 @@
         <f>D71</f>
         <v/>
       </c>
-      <c r="H71" s="32" t="n"/>
-      <c r="I71" s="32" t="n"/>
-      <c r="J71" s="32" t="n"/>
-      <c r="K71" s="32" t="n"/>
-      <c r="L71" s="32" t="n"/>
-      <c r="M71" s="32" t="n"/>
-      <c r="N71" s="32" t="n"/>
-      <c r="O71" s="32" t="n"/>
-      <c r="P71" s="32" t="n"/>
-      <c r="Q71" s="32" t="n"/>
-      <c r="R71" s="32" t="n"/>
-      <c r="S71" s="32" t="n"/>
-      <c r="T71" s="32" t="n"/>
-      <c r="U71" s="32" t="n"/>
-      <c r="V71" s="32" t="n"/>
-      <c r="W71" s="32" t="n"/>
-      <c r="X71" s="32" t="n"/>
-      <c r="Y71" s="32" t="n"/>
-      <c r="Z71" s="32" t="n"/>
-      <c r="AA71" s="32" t="n"/>
-      <c r="AB71" s="32" t="n"/>
-      <c r="AC71" s="32" t="n"/>
-      <c r="AD71" s="32" t="n"/>
-      <c r="AE71" s="32" t="n"/>
-      <c r="AF71" s="32" t="n"/>
-      <c r="AG71" s="32" t="n"/>
-      <c r="AH71" s="32" t="n"/>
-      <c r="AI71" s="32" t="n"/>
-      <c r="AJ71" s="32" t="n"/>
-      <c r="AK71" s="32" t="n"/>
-      <c r="AL71" s="32" t="n"/>
-      <c r="AM71" s="32" t="n"/>
-      <c r="AN71" s="32" t="n"/>
-      <c r="AO71" s="32" t="n"/>
-      <c r="AP71" s="32" t="n"/>
-      <c r="AQ71" s="32" t="n"/>
-      <c r="AR71" s="32" t="n"/>
-      <c r="AS71" s="32" t="n"/>
-      <c r="AT71" s="32" t="n"/>
-      <c r="AU71" s="32" t="n"/>
-      <c r="AV71" s="32" t="n"/>
-      <c r="AW71" s="32" t="n"/>
-      <c r="AX71" s="32" t="n"/>
-      <c r="AY71" s="32" t="n"/>
-      <c r="AZ71" s="31" t="n"/>
+      <c r="H71" s="26" t="n"/>
+      <c r="I71" s="26" t="n"/>
+      <c r="J71" s="26" t="n"/>
+      <c r="K71" s="26" t="n"/>
+      <c r="L71" s="26" t="n"/>
+      <c r="M71" s="26" t="n"/>
+      <c r="N71" s="26" t="n"/>
+      <c r="O71" s="26" t="n"/>
+      <c r="P71" s="26" t="n"/>
+      <c r="Q71" s="26" t="n"/>
+      <c r="R71" s="26" t="n"/>
+      <c r="S71" s="26" t="n"/>
+      <c r="T71" s="26" t="n"/>
+      <c r="U71" s="26" t="n"/>
+      <c r="V71" s="26" t="n"/>
+      <c r="W71" s="26" t="n"/>
+      <c r="X71" s="26" t="n"/>
+      <c r="Y71" s="26" t="n"/>
+      <c r="Z71" s="26" t="n"/>
+      <c r="AA71" s="26" t="n"/>
+      <c r="AB71" s="26" t="n"/>
+      <c r="AC71" s="26" t="n"/>
+      <c r="AD71" s="26" t="n"/>
+      <c r="AE71" s="26" t="n"/>
+      <c r="AF71" s="26" t="n"/>
+      <c r="AG71" s="26" t="n"/>
+      <c r="AH71" s="26" t="n"/>
+      <c r="AI71" s="26" t="n"/>
+      <c r="AJ71" s="26" t="n"/>
+      <c r="AK71" s="26" t="n"/>
+      <c r="AL71" s="26" t="n"/>
+      <c r="AM71" s="26" t="n"/>
+      <c r="AN71" s="26" t="n"/>
+      <c r="AO71" s="26" t="n"/>
+      <c r="AP71" s="26" t="n"/>
+      <c r="AQ71" s="26" t="n"/>
+      <c r="AR71" s="26" t="n"/>
+      <c r="AS71" s="26" t="n"/>
+      <c r="AT71" s="26" t="n"/>
+      <c r="AU71" s="26" t="n"/>
+      <c r="AV71" s="26" t="n"/>
+      <c r="AW71" s="26" t="n"/>
+      <c r="AX71" s="26" t="n"/>
+      <c r="AY71" s="26" t="n"/>
+      <c r="AZ71" s="26" t="n"/>
       <c r="BA71" s="26" t="n"/>
       <c r="BB71" s="26" t="n"/>
       <c r="BC71" s="26" t="n"/>
-      <c r="BD71" s="26" t="n"/>
-      <c r="BE71" s="26" t="n"/>
-      <c r="BF71" s="26" t="n"/>
-      <c r="BG71" s="26" t="n"/>
-      <c r="BH71" s="26" t="n"/>
-      <c r="BI71" s="26" t="n"/>
-      <c r="BJ71" s="26" t="n"/>
-      <c r="BK71" s="26" t="n"/>
-      <c r="BL71" s="26" t="n"/>
-      <c r="BM71" s="26" t="n"/>
-      <c r="BN71" s="26" t="n"/>
-      <c r="BO71" s="26" t="n"/>
+      <c r="BD71" s="27" t="n"/>
+      <c r="BE71" s="28" t="n"/>
+      <c r="BF71" s="28" t="n"/>
+      <c r="BG71" s="28" t="n"/>
+      <c r="BH71" s="28" t="n"/>
+      <c r="BI71" s="28" t="n"/>
+      <c r="BJ71" s="28" t="n"/>
+      <c r="BK71" s="28" t="n"/>
+      <c r="BL71" s="28" t="n"/>
+      <c r="BM71" s="28" t="n"/>
+      <c r="BN71" s="28" t="n"/>
+      <c r="BO71" s="28" t="n"/>
+      <c r="BP71" s="28" t="n"/>
+      <c r="BQ71" s="28" t="n"/>
+      <c r="BR71" s="28" t="n"/>
+      <c r="BS71" s="28" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
+      <c r="A72" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B72" s="27" t="inlineStr">
+      <c r="B72" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C72" s="28" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>PAB180·工装实物到位</t>
         </is>
       </c>
-      <c r="D72" s="29">
+      <c r="D72" s="31">
         <f>'时间节点计划表'!E36</f>
         <v/>
       </c>
-      <c r="E72" s="29">
+      <c r="E72" s="31">
         <f>IF(COUNT('时间节点计划表'!F36),'时间节点计划表'!F36,"")</f>
         <v/>
       </c>
-      <c r="F72" s="30">
+      <c r="F72" s="32">
         <f>IF(OR(D72="",E72=""),"待填",E72-D72)</f>
         <v/>
       </c>
@@ -15902,6 +16606,22 @@
       </c>
       <c r="BO72" s="23">
         <f>IF(AND(COUNT($E72),N(BO$2)=N($E72)),$E72,IF(AND(COUNT($E72),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E72))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP72" s="23">
+        <f>IF(AND(COUNT($E72),N(BP$2)=N($E72)),$E72,IF(AND(COUNT($E72),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E72))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ72" s="23">
+        <f>IF(AND(COUNT($E72),N(BQ$2)=N($E72)),$E72,IF(AND(COUNT($E72),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E72))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR72" s="23">
+        <f>IF(AND(COUNT($E72),N(BR$2)=N($E72)),$E72,IF(AND(COUNT($E72),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E72))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS72" s="23">
+        <f>IF(AND(COUNT($E72),N(BS$2)=N($E72)),$E72,IF(AND(COUNT($E72),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E72))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -15934,92 +16654,96 @@
         <f>D73</f>
         <v/>
       </c>
-      <c r="H73" s="32" t="n"/>
-      <c r="I73" s="32" t="n"/>
-      <c r="J73" s="32" t="n"/>
-      <c r="K73" s="32" t="n"/>
-      <c r="L73" s="32" t="n"/>
-      <c r="M73" s="32" t="n"/>
-      <c r="N73" s="32" t="n"/>
-      <c r="O73" s="32" t="n"/>
-      <c r="P73" s="32" t="n"/>
-      <c r="Q73" s="32" t="n"/>
-      <c r="R73" s="32" t="n"/>
-      <c r="S73" s="32" t="n"/>
-      <c r="T73" s="32" t="n"/>
-      <c r="U73" s="32" t="n"/>
-      <c r="V73" s="32" t="n"/>
-      <c r="W73" s="32" t="n"/>
-      <c r="X73" s="32" t="n"/>
-      <c r="Y73" s="32" t="n"/>
-      <c r="Z73" s="32" t="n"/>
-      <c r="AA73" s="32" t="n"/>
-      <c r="AB73" s="32" t="n"/>
-      <c r="AC73" s="32" t="n"/>
-      <c r="AD73" s="32" t="n"/>
-      <c r="AE73" s="32" t="n"/>
-      <c r="AF73" s="32" t="n"/>
-      <c r="AG73" s="32" t="n"/>
-      <c r="AH73" s="32" t="n"/>
-      <c r="AI73" s="32" t="n"/>
-      <c r="AJ73" s="32" t="n"/>
-      <c r="AK73" s="32" t="n"/>
-      <c r="AL73" s="32" t="n"/>
-      <c r="AM73" s="32" t="n"/>
-      <c r="AN73" s="32" t="n"/>
-      <c r="AO73" s="32" t="n"/>
-      <c r="AP73" s="32" t="n"/>
-      <c r="AQ73" s="32" t="n"/>
-      <c r="AR73" s="32" t="n"/>
-      <c r="AS73" s="32" t="n"/>
-      <c r="AT73" s="32" t="n"/>
-      <c r="AU73" s="32" t="n"/>
-      <c r="AV73" s="32" t="n"/>
-      <c r="AW73" s="32" t="n"/>
-      <c r="AX73" s="32" t="n"/>
-      <c r="AY73" s="32" t="n"/>
-      <c r="AZ73" s="32" t="n"/>
-      <c r="BA73" s="32" t="n"/>
-      <c r="BB73" s="32" t="n"/>
-      <c r="BC73" s="32" t="n"/>
-      <c r="BD73" s="32" t="n"/>
-      <c r="BE73" s="32" t="n"/>
-      <c r="BF73" s="32" t="n"/>
-      <c r="BG73" s="31" t="n"/>
+      <c r="H73" s="26" t="n"/>
+      <c r="I73" s="26" t="n"/>
+      <c r="J73" s="26" t="n"/>
+      <c r="K73" s="26" t="n"/>
+      <c r="L73" s="26" t="n"/>
+      <c r="M73" s="26" t="n"/>
+      <c r="N73" s="26" t="n"/>
+      <c r="O73" s="26" t="n"/>
+      <c r="P73" s="26" t="n"/>
+      <c r="Q73" s="26" t="n"/>
+      <c r="R73" s="26" t="n"/>
+      <c r="S73" s="26" t="n"/>
+      <c r="T73" s="26" t="n"/>
+      <c r="U73" s="26" t="n"/>
+      <c r="V73" s="26" t="n"/>
+      <c r="W73" s="26" t="n"/>
+      <c r="X73" s="26" t="n"/>
+      <c r="Y73" s="26" t="n"/>
+      <c r="Z73" s="26" t="n"/>
+      <c r="AA73" s="26" t="n"/>
+      <c r="AB73" s="26" t="n"/>
+      <c r="AC73" s="26" t="n"/>
+      <c r="AD73" s="26" t="n"/>
+      <c r="AE73" s="26" t="n"/>
+      <c r="AF73" s="26" t="n"/>
+      <c r="AG73" s="26" t="n"/>
+      <c r="AH73" s="26" t="n"/>
+      <c r="AI73" s="26" t="n"/>
+      <c r="AJ73" s="26" t="n"/>
+      <c r="AK73" s="26" t="n"/>
+      <c r="AL73" s="26" t="n"/>
+      <c r="AM73" s="26" t="n"/>
+      <c r="AN73" s="26" t="n"/>
+      <c r="AO73" s="26" t="n"/>
+      <c r="AP73" s="26" t="n"/>
+      <c r="AQ73" s="26" t="n"/>
+      <c r="AR73" s="26" t="n"/>
+      <c r="AS73" s="26" t="n"/>
+      <c r="AT73" s="26" t="n"/>
+      <c r="AU73" s="26" t="n"/>
+      <c r="AV73" s="26" t="n"/>
+      <c r="AW73" s="26" t="n"/>
+      <c r="AX73" s="26" t="n"/>
+      <c r="AY73" s="26" t="n"/>
+      <c r="AZ73" s="26" t="n"/>
+      <c r="BA73" s="26" t="n"/>
+      <c r="BB73" s="26" t="n"/>
+      <c r="BC73" s="26" t="n"/>
+      <c r="BD73" s="26" t="n"/>
+      <c r="BE73" s="26" t="n"/>
+      <c r="BF73" s="26" t="n"/>
+      <c r="BG73" s="26" t="n"/>
       <c r="BH73" s="26" t="n"/>
       <c r="BI73" s="26" t="n"/>
       <c r="BJ73" s="26" t="n"/>
-      <c r="BK73" s="26" t="n"/>
-      <c r="BL73" s="26" t="n"/>
-      <c r="BM73" s="26" t="n"/>
-      <c r="BN73" s="26" t="n"/>
-      <c r="BO73" s="26" t="n"/>
+      <c r="BK73" s="27" t="n"/>
+      <c r="BL73" s="28" t="n"/>
+      <c r="BM73" s="28" t="n"/>
+      <c r="BN73" s="28" t="n"/>
+      <c r="BO73" s="28" t="n"/>
+      <c r="BP73" s="28" t="n"/>
+      <c r="BQ73" s="28" t="n"/>
+      <c r="BR73" s="28" t="n"/>
+      <c r="BS73" s="28" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="27" t="inlineStr">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B74" s="27" t="inlineStr">
+      <c r="B74" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C74" s="28" t="inlineStr">
+      <c r="C74" s="30" t="inlineStr">
         <is>
           <t>PAB180·排针机安装调试</t>
         </is>
       </c>
-      <c r="D74" s="29">
+      <c r="D74" s="31">
         <f>'时间节点计划表'!E37</f>
         <v/>
       </c>
-      <c r="E74" s="29">
+      <c r="E74" s="31">
         <f>IF(COUNT('时间节点计划表'!F37),'时间节点计划表'!F37,"")</f>
         <v/>
       </c>
-      <c r="F74" s="30">
+      <c r="F74" s="32">
         <f>IF(OR(D74="",E74=""),"待填",E74-D74)</f>
         <v/>
       </c>
@@ -16265,6 +16989,22 @@
       </c>
       <c r="BO74" s="23">
         <f>IF(AND(COUNT($E74),N(BO$2)=N($E74)),$E74,IF(AND(COUNT($E74),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E74))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP74" s="23">
+        <f>IF(AND(COUNT($E74),N(BP$2)=N($E74)),$E74,IF(AND(COUNT($E74),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E74))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ74" s="23">
+        <f>IF(AND(COUNT($E74),N(BQ$2)=N($E74)),$E74,IF(AND(COUNT($E74),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E74))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR74" s="23">
+        <f>IF(AND(COUNT($E74),N(BR$2)=N($E74)),$E74,IF(AND(COUNT($E74),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E74))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS74" s="23">
+        <f>IF(AND(COUNT($E74),N(BS$2)=N($E74)),$E74,IF(AND(COUNT($E74),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E74))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -16297,92 +17037,96 @@
         <f>D75</f>
         <v/>
       </c>
-      <c r="H75" s="32" t="n"/>
-      <c r="I75" s="32" t="n"/>
-      <c r="J75" s="32" t="n"/>
-      <c r="K75" s="32" t="n"/>
-      <c r="L75" s="32" t="n"/>
-      <c r="M75" s="32" t="n"/>
-      <c r="N75" s="32" t="n"/>
-      <c r="O75" s="32" t="n"/>
-      <c r="P75" s="32" t="n"/>
-      <c r="Q75" s="32" t="n"/>
-      <c r="R75" s="32" t="n"/>
-      <c r="S75" s="32" t="n"/>
-      <c r="T75" s="32" t="n"/>
-      <c r="U75" s="32" t="n"/>
-      <c r="V75" s="32" t="n"/>
-      <c r="W75" s="32" t="n"/>
-      <c r="X75" s="32" t="n"/>
-      <c r="Y75" s="32" t="n"/>
-      <c r="Z75" s="32" t="n"/>
-      <c r="AA75" s="32" t="n"/>
-      <c r="AB75" s="32" t="n"/>
-      <c r="AC75" s="32" t="n"/>
-      <c r="AD75" s="32" t="n"/>
-      <c r="AE75" s="32" t="n"/>
-      <c r="AF75" s="32" t="n"/>
-      <c r="AG75" s="32" t="n"/>
-      <c r="AH75" s="32" t="n"/>
-      <c r="AI75" s="32" t="n"/>
-      <c r="AJ75" s="32" t="n"/>
-      <c r="AK75" s="32" t="n"/>
-      <c r="AL75" s="32" t="n"/>
-      <c r="AM75" s="32" t="n"/>
-      <c r="AN75" s="32" t="n"/>
-      <c r="AO75" s="32" t="n"/>
-      <c r="AP75" s="32" t="n"/>
-      <c r="AQ75" s="32" t="n"/>
-      <c r="AR75" s="32" t="n"/>
-      <c r="AS75" s="32" t="n"/>
-      <c r="AT75" s="32" t="n"/>
-      <c r="AU75" s="32" t="n"/>
-      <c r="AV75" s="32" t="n"/>
-      <c r="AW75" s="32" t="n"/>
-      <c r="AX75" s="32" t="n"/>
-      <c r="AY75" s="32" t="n"/>
-      <c r="AZ75" s="32" t="n"/>
-      <c r="BA75" s="32" t="n"/>
-      <c r="BB75" s="32" t="n"/>
-      <c r="BC75" s="32" t="n"/>
-      <c r="BD75" s="32" t="n"/>
-      <c r="BE75" s="32" t="n"/>
-      <c r="BF75" s="32" t="n"/>
-      <c r="BG75" s="32" t="n"/>
-      <c r="BH75" s="31" t="n"/>
+      <c r="H75" s="26" t="n"/>
+      <c r="I75" s="26" t="n"/>
+      <c r="J75" s="26" t="n"/>
+      <c r="K75" s="26" t="n"/>
+      <c r="L75" s="26" t="n"/>
+      <c r="M75" s="26" t="n"/>
+      <c r="N75" s="26" t="n"/>
+      <c r="O75" s="26" t="n"/>
+      <c r="P75" s="26" t="n"/>
+      <c r="Q75" s="26" t="n"/>
+      <c r="R75" s="26" t="n"/>
+      <c r="S75" s="26" t="n"/>
+      <c r="T75" s="26" t="n"/>
+      <c r="U75" s="26" t="n"/>
+      <c r="V75" s="26" t="n"/>
+      <c r="W75" s="26" t="n"/>
+      <c r="X75" s="26" t="n"/>
+      <c r="Y75" s="26" t="n"/>
+      <c r="Z75" s="26" t="n"/>
+      <c r="AA75" s="26" t="n"/>
+      <c r="AB75" s="26" t="n"/>
+      <c r="AC75" s="26" t="n"/>
+      <c r="AD75" s="26" t="n"/>
+      <c r="AE75" s="26" t="n"/>
+      <c r="AF75" s="26" t="n"/>
+      <c r="AG75" s="26" t="n"/>
+      <c r="AH75" s="26" t="n"/>
+      <c r="AI75" s="26" t="n"/>
+      <c r="AJ75" s="26" t="n"/>
+      <c r="AK75" s="26" t="n"/>
+      <c r="AL75" s="26" t="n"/>
+      <c r="AM75" s="26" t="n"/>
+      <c r="AN75" s="26" t="n"/>
+      <c r="AO75" s="26" t="n"/>
+      <c r="AP75" s="26" t="n"/>
+      <c r="AQ75" s="26" t="n"/>
+      <c r="AR75" s="26" t="n"/>
+      <c r="AS75" s="26" t="n"/>
+      <c r="AT75" s="26" t="n"/>
+      <c r="AU75" s="26" t="n"/>
+      <c r="AV75" s="26" t="n"/>
+      <c r="AW75" s="26" t="n"/>
+      <c r="AX75" s="26" t="n"/>
+      <c r="AY75" s="26" t="n"/>
+      <c r="AZ75" s="26" t="n"/>
+      <c r="BA75" s="26" t="n"/>
+      <c r="BB75" s="26" t="n"/>
+      <c r="BC75" s="26" t="n"/>
+      <c r="BD75" s="26" t="n"/>
+      <c r="BE75" s="26" t="n"/>
+      <c r="BF75" s="26" t="n"/>
+      <c r="BG75" s="26" t="n"/>
+      <c r="BH75" s="26" t="n"/>
       <c r="BI75" s="26" t="n"/>
       <c r="BJ75" s="26" t="n"/>
       <c r="BK75" s="26" t="n"/>
-      <c r="BL75" s="26" t="n"/>
-      <c r="BM75" s="26" t="n"/>
-      <c r="BN75" s="26" t="n"/>
-      <c r="BO75" s="26" t="n"/>
+      <c r="BL75" s="27" t="n"/>
+      <c r="BM75" s="28" t="n"/>
+      <c r="BN75" s="28" t="n"/>
+      <c r="BO75" s="28" t="n"/>
+      <c r="BP75" s="28" t="n"/>
+      <c r="BQ75" s="28" t="n"/>
+      <c r="BR75" s="28" t="n"/>
+      <c r="BS75" s="28" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B76" s="27" t="inlineStr">
+      <c r="B76" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C76" s="28" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>PAB180·单级样机</t>
         </is>
       </c>
-      <c r="D76" s="29">
+      <c r="D76" s="31">
         <f>'时间节点计划表'!E38</f>
         <v/>
       </c>
-      <c r="E76" s="29">
+      <c r="E76" s="31">
         <f>IF(COUNT('时间节点计划表'!F38),'时间节点计划表'!F38,"")</f>
         <v/>
       </c>
-      <c r="F76" s="30">
+      <c r="F76" s="32">
         <f>IF(OR(D76="",E76=""),"待填",E76-D76)</f>
         <v/>
       </c>
@@ -16628,6 +17372,22 @@
       </c>
       <c r="BO76" s="23">
         <f>IF(AND(COUNT($E76),N(BO$2)=N($E76)),$E76,IF(AND(COUNT($E76),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E76))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP76" s="23">
+        <f>IF(AND(COUNT($E76),N(BP$2)=N($E76)),$E76,IF(AND(COUNT($E76),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E76))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ76" s="23">
+        <f>IF(AND(COUNT($E76),N(BQ$2)=N($E76)),$E76,IF(AND(COUNT($E76),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E76))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR76" s="23">
+        <f>IF(AND(COUNT($E76),N(BR$2)=N($E76)),$E76,IF(AND(COUNT($E76),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E76))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS76" s="23">
+        <f>IF(AND(COUNT($E76),N(BS$2)=N($E76)),$E76,IF(AND(COUNT($E76),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E76))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -16660,92 +17420,96 @@
         <f>D77</f>
         <v/>
       </c>
-      <c r="H77" s="32" t="n"/>
-      <c r="I77" s="32" t="n"/>
-      <c r="J77" s="32" t="n"/>
-      <c r="K77" s="32" t="n"/>
-      <c r="L77" s="32" t="n"/>
-      <c r="M77" s="32" t="n"/>
-      <c r="N77" s="32" t="n"/>
-      <c r="O77" s="32" t="n"/>
-      <c r="P77" s="32" t="n"/>
-      <c r="Q77" s="32" t="n"/>
-      <c r="R77" s="32" t="n"/>
-      <c r="S77" s="32" t="n"/>
-      <c r="T77" s="32" t="n"/>
-      <c r="U77" s="32" t="n"/>
-      <c r="V77" s="32" t="n"/>
-      <c r="W77" s="32" t="n"/>
-      <c r="X77" s="32" t="n"/>
-      <c r="Y77" s="32" t="n"/>
-      <c r="Z77" s="32" t="n"/>
-      <c r="AA77" s="32" t="n"/>
-      <c r="AB77" s="32" t="n"/>
-      <c r="AC77" s="32" t="n"/>
-      <c r="AD77" s="32" t="n"/>
-      <c r="AE77" s="32" t="n"/>
-      <c r="AF77" s="32" t="n"/>
-      <c r="AG77" s="32" t="n"/>
-      <c r="AH77" s="32" t="n"/>
-      <c r="AI77" s="32" t="n"/>
-      <c r="AJ77" s="32" t="n"/>
-      <c r="AK77" s="32" t="n"/>
-      <c r="AL77" s="32" t="n"/>
-      <c r="AM77" s="32" t="n"/>
-      <c r="AN77" s="32" t="n"/>
-      <c r="AO77" s="32" t="n"/>
-      <c r="AP77" s="32" t="n"/>
-      <c r="AQ77" s="32" t="n"/>
-      <c r="AR77" s="32" t="n"/>
-      <c r="AS77" s="32" t="n"/>
-      <c r="AT77" s="32" t="n"/>
-      <c r="AU77" s="32" t="n"/>
-      <c r="AV77" s="32" t="n"/>
-      <c r="AW77" s="32" t="n"/>
-      <c r="AX77" s="32" t="n"/>
-      <c r="AY77" s="32" t="n"/>
-      <c r="AZ77" s="32" t="n"/>
-      <c r="BA77" s="32" t="n"/>
-      <c r="BB77" s="32" t="n"/>
-      <c r="BC77" s="32" t="n"/>
-      <c r="BD77" s="32" t="n"/>
-      <c r="BE77" s="32" t="n"/>
-      <c r="BF77" s="32" t="n"/>
-      <c r="BG77" s="32" t="n"/>
-      <c r="BH77" s="32" t="n"/>
-      <c r="BI77" s="32" t="n"/>
-      <c r="BJ77" s="32" t="n"/>
-      <c r="BK77" s="31" t="n"/>
+      <c r="H77" s="26" t="n"/>
+      <c r="I77" s="26" t="n"/>
+      <c r="J77" s="26" t="n"/>
+      <c r="K77" s="26" t="n"/>
+      <c r="L77" s="26" t="n"/>
+      <c r="M77" s="26" t="n"/>
+      <c r="N77" s="26" t="n"/>
+      <c r="O77" s="26" t="n"/>
+      <c r="P77" s="26" t="n"/>
+      <c r="Q77" s="26" t="n"/>
+      <c r="R77" s="26" t="n"/>
+      <c r="S77" s="26" t="n"/>
+      <c r="T77" s="26" t="n"/>
+      <c r="U77" s="26" t="n"/>
+      <c r="V77" s="26" t="n"/>
+      <c r="W77" s="26" t="n"/>
+      <c r="X77" s="26" t="n"/>
+      <c r="Y77" s="26" t="n"/>
+      <c r="Z77" s="26" t="n"/>
+      <c r="AA77" s="26" t="n"/>
+      <c r="AB77" s="26" t="n"/>
+      <c r="AC77" s="26" t="n"/>
+      <c r="AD77" s="26" t="n"/>
+      <c r="AE77" s="26" t="n"/>
+      <c r="AF77" s="26" t="n"/>
+      <c r="AG77" s="26" t="n"/>
+      <c r="AH77" s="26" t="n"/>
+      <c r="AI77" s="26" t="n"/>
+      <c r="AJ77" s="26" t="n"/>
+      <c r="AK77" s="26" t="n"/>
+      <c r="AL77" s="26" t="n"/>
+      <c r="AM77" s="26" t="n"/>
+      <c r="AN77" s="26" t="n"/>
+      <c r="AO77" s="26" t="n"/>
+      <c r="AP77" s="26" t="n"/>
+      <c r="AQ77" s="26" t="n"/>
+      <c r="AR77" s="26" t="n"/>
+      <c r="AS77" s="26" t="n"/>
+      <c r="AT77" s="26" t="n"/>
+      <c r="AU77" s="26" t="n"/>
+      <c r="AV77" s="26" t="n"/>
+      <c r="AW77" s="26" t="n"/>
+      <c r="AX77" s="26" t="n"/>
+      <c r="AY77" s="26" t="n"/>
+      <c r="AZ77" s="26" t="n"/>
+      <c r="BA77" s="26" t="n"/>
+      <c r="BB77" s="26" t="n"/>
+      <c r="BC77" s="26" t="n"/>
+      <c r="BD77" s="26" t="n"/>
+      <c r="BE77" s="26" t="n"/>
+      <c r="BF77" s="26" t="n"/>
+      <c r="BG77" s="26" t="n"/>
+      <c r="BH77" s="26" t="n"/>
+      <c r="BI77" s="26" t="n"/>
+      <c r="BJ77" s="26" t="n"/>
+      <c r="BK77" s="26" t="n"/>
       <c r="BL77" s="26" t="n"/>
       <c r="BM77" s="26" t="n"/>
       <c r="BN77" s="26" t="n"/>
-      <c r="BO77" s="26" t="n"/>
+      <c r="BO77" s="27" t="n"/>
+      <c r="BP77" s="28" t="n"/>
+      <c r="BQ77" s="28" t="n"/>
+      <c r="BR77" s="28" t="n"/>
+      <c r="BS77" s="28" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B78" s="27" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C78" s="28" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>PAB180·双级样机</t>
         </is>
       </c>
-      <c r="D78" s="29">
+      <c r="D78" s="31">
         <f>'时间节点计划表'!E39</f>
         <v/>
       </c>
-      <c r="E78" s="29">
+      <c r="E78" s="31">
         <f>IF(COUNT('时间节点计划表'!F39),'时间节点计划表'!F39,"")</f>
         <v/>
       </c>
-      <c r="F78" s="30">
+      <c r="F78" s="32">
         <f>IF(OR(D78="",E78=""),"待填",E78-D78)</f>
         <v/>
       </c>
@@ -16991,6 +17755,22 @@
       </c>
       <c r="BO78" s="23">
         <f>IF(AND(COUNT($E78),N(BO$2)=N($E78)),$E78,IF(AND(COUNT($E78),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E78))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP78" s="23">
+        <f>IF(AND(COUNT($E78),N(BP$2)=N($E78)),$E78,IF(AND(COUNT($E78),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E78))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ78" s="23">
+        <f>IF(AND(COUNT($E78),N(BQ$2)=N($E78)),$E78,IF(AND(COUNT($E78),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E78))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR78" s="23">
+        <f>IF(AND(COUNT($E78),N(BR$2)=N($E78)),$E78,IF(AND(COUNT($E78),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E78))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS78" s="23">
+        <f>IF(AND(COUNT($E78),N(BS$2)=N($E78)),$E78,IF(AND(COUNT($E78),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E78))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -17023,92 +17803,96 @@
         <f>D79</f>
         <v/>
       </c>
-      <c r="H79" s="32" t="n"/>
-      <c r="I79" s="32" t="n"/>
-      <c r="J79" s="32" t="n"/>
-      <c r="K79" s="32" t="n"/>
-      <c r="L79" s="32" t="n"/>
-      <c r="M79" s="32" t="n"/>
-      <c r="N79" s="32" t="n"/>
-      <c r="O79" s="32" t="n"/>
-      <c r="P79" s="32" t="n"/>
-      <c r="Q79" s="32" t="n"/>
-      <c r="R79" s="32" t="n"/>
-      <c r="S79" s="32" t="n"/>
-      <c r="T79" s="32" t="n"/>
-      <c r="U79" s="32" t="n"/>
-      <c r="V79" s="32" t="n"/>
-      <c r="W79" s="32" t="n"/>
-      <c r="X79" s="32" t="n"/>
-      <c r="Y79" s="32" t="n"/>
-      <c r="Z79" s="32" t="n"/>
-      <c r="AA79" s="32" t="n"/>
-      <c r="AB79" s="32" t="n"/>
-      <c r="AC79" s="32" t="n"/>
-      <c r="AD79" s="32" t="n"/>
-      <c r="AE79" s="32" t="n"/>
-      <c r="AF79" s="32" t="n"/>
-      <c r="AG79" s="32" t="n"/>
-      <c r="AH79" s="32" t="n"/>
-      <c r="AI79" s="32" t="n"/>
-      <c r="AJ79" s="32" t="n"/>
-      <c r="AK79" s="32" t="n"/>
-      <c r="AL79" s="32" t="n"/>
-      <c r="AM79" s="32" t="n"/>
-      <c r="AN79" s="32" t="n"/>
-      <c r="AO79" s="32" t="n"/>
-      <c r="AP79" s="32" t="n"/>
-      <c r="AQ79" s="32" t="n"/>
-      <c r="AR79" s="32" t="n"/>
-      <c r="AS79" s="32" t="n"/>
-      <c r="AT79" s="32" t="n"/>
-      <c r="AU79" s="32" t="n"/>
-      <c r="AV79" s="32" t="n"/>
-      <c r="AW79" s="32" t="n"/>
-      <c r="AX79" s="32" t="n"/>
-      <c r="AY79" s="32" t="n"/>
-      <c r="AZ79" s="32" t="n"/>
-      <c r="BA79" s="32" t="n"/>
-      <c r="BB79" s="32" t="n"/>
-      <c r="BC79" s="32" t="n"/>
-      <c r="BD79" s="32" t="n"/>
-      <c r="BE79" s="32" t="n"/>
-      <c r="BF79" s="32" t="n"/>
-      <c r="BG79" s="32" t="n"/>
-      <c r="BH79" s="32" t="n"/>
-      <c r="BI79" s="32" t="n"/>
-      <c r="BJ79" s="32" t="n"/>
-      <c r="BK79" s="32" t="n"/>
-      <c r="BL79" s="31" t="n"/>
+      <c r="H79" s="26" t="n"/>
+      <c r="I79" s="26" t="n"/>
+      <c r="J79" s="26" t="n"/>
+      <c r="K79" s="26" t="n"/>
+      <c r="L79" s="26" t="n"/>
+      <c r="M79" s="26" t="n"/>
+      <c r="N79" s="26" t="n"/>
+      <c r="O79" s="26" t="n"/>
+      <c r="P79" s="26" t="n"/>
+      <c r="Q79" s="26" t="n"/>
+      <c r="R79" s="26" t="n"/>
+      <c r="S79" s="26" t="n"/>
+      <c r="T79" s="26" t="n"/>
+      <c r="U79" s="26" t="n"/>
+      <c r="V79" s="26" t="n"/>
+      <c r="W79" s="26" t="n"/>
+      <c r="X79" s="26" t="n"/>
+      <c r="Y79" s="26" t="n"/>
+      <c r="Z79" s="26" t="n"/>
+      <c r="AA79" s="26" t="n"/>
+      <c r="AB79" s="26" t="n"/>
+      <c r="AC79" s="26" t="n"/>
+      <c r="AD79" s="26" t="n"/>
+      <c r="AE79" s="26" t="n"/>
+      <c r="AF79" s="26" t="n"/>
+      <c r="AG79" s="26" t="n"/>
+      <c r="AH79" s="26" t="n"/>
+      <c r="AI79" s="26" t="n"/>
+      <c r="AJ79" s="26" t="n"/>
+      <c r="AK79" s="26" t="n"/>
+      <c r="AL79" s="26" t="n"/>
+      <c r="AM79" s="26" t="n"/>
+      <c r="AN79" s="26" t="n"/>
+      <c r="AO79" s="26" t="n"/>
+      <c r="AP79" s="26" t="n"/>
+      <c r="AQ79" s="26" t="n"/>
+      <c r="AR79" s="26" t="n"/>
+      <c r="AS79" s="26" t="n"/>
+      <c r="AT79" s="26" t="n"/>
+      <c r="AU79" s="26" t="n"/>
+      <c r="AV79" s="26" t="n"/>
+      <c r="AW79" s="26" t="n"/>
+      <c r="AX79" s="26" t="n"/>
+      <c r="AY79" s="26" t="n"/>
+      <c r="AZ79" s="26" t="n"/>
+      <c r="BA79" s="26" t="n"/>
+      <c r="BB79" s="26" t="n"/>
+      <c r="BC79" s="26" t="n"/>
+      <c r="BD79" s="26" t="n"/>
+      <c r="BE79" s="26" t="n"/>
+      <c r="BF79" s="26" t="n"/>
+      <c r="BG79" s="26" t="n"/>
+      <c r="BH79" s="26" t="n"/>
+      <c r="BI79" s="26" t="n"/>
+      <c r="BJ79" s="26" t="n"/>
+      <c r="BK79" s="26" t="n"/>
+      <c r="BL79" s="26" t="n"/>
       <c r="BM79" s="26" t="n"/>
       <c r="BN79" s="26" t="n"/>
       <c r="BO79" s="26" t="n"/>
+      <c r="BP79" s="27" t="n"/>
+      <c r="BQ79" s="28" t="n"/>
+      <c r="BR79" s="28" t="n"/>
+      <c r="BS79" s="28" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="27" t="inlineStr">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B80" s="27" t="inlineStr">
+      <c r="B80" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C80" s="28" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <t>PAB220·零件到位</t>
         </is>
       </c>
-      <c r="D80" s="29">
+      <c r="D80" s="31">
         <f>'时间节点计划表'!E40</f>
         <v/>
       </c>
-      <c r="E80" s="29">
+      <c r="E80" s="31">
         <f>IF(COUNT('时间节点计划表'!F40),'时间节点计划表'!F40,"")</f>
         <v/>
       </c>
-      <c r="F80" s="30">
+      <c r="F80" s="32">
         <f>IF(OR(D80="",E80=""),"待填",E80-D80)</f>
         <v/>
       </c>
@@ -17354,6 +18138,22 @@
       </c>
       <c r="BO80" s="23">
         <f>IF(AND(COUNT($E80),N(BO$2)=N($E80)),$E80,IF(AND(COUNT($E80),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E80))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP80" s="23">
+        <f>IF(AND(COUNT($E80),N(BP$2)=N($E80)),$E80,IF(AND(COUNT($E80),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E80))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ80" s="23">
+        <f>IF(AND(COUNT($E80),N(BQ$2)=N($E80)),$E80,IF(AND(COUNT($E80),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E80))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR80" s="23">
+        <f>IF(AND(COUNT($E80),N(BR$2)=N($E80)),$E80,IF(AND(COUNT($E80),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E80))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS80" s="23">
+        <f>IF(AND(COUNT($E80),N(BS$2)=N($E80)),$E80,IF(AND(COUNT($E80),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E80))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -17386,92 +18186,96 @@
         <f>D81</f>
         <v/>
       </c>
-      <c r="H81" s="32" t="n"/>
-      <c r="I81" s="32" t="n"/>
-      <c r="J81" s="32" t="n"/>
-      <c r="K81" s="32" t="n"/>
-      <c r="L81" s="32" t="n"/>
-      <c r="M81" s="32" t="n"/>
-      <c r="N81" s="32" t="n"/>
-      <c r="O81" s="32" t="n"/>
-      <c r="P81" s="32" t="n"/>
-      <c r="Q81" s="32" t="n"/>
-      <c r="R81" s="32" t="n"/>
-      <c r="S81" s="32" t="n"/>
-      <c r="T81" s="32" t="n"/>
-      <c r="U81" s="32" t="n"/>
-      <c r="V81" s="32" t="n"/>
-      <c r="W81" s="32" t="n"/>
-      <c r="X81" s="32" t="n"/>
-      <c r="Y81" s="32" t="n"/>
-      <c r="Z81" s="32" t="n"/>
-      <c r="AA81" s="32" t="n"/>
-      <c r="AB81" s="31" t="n"/>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="26" t="n"/>
+      <c r="J81" s="26" t="n"/>
+      <c r="K81" s="26" t="n"/>
+      <c r="L81" s="26" t="n"/>
+      <c r="M81" s="26" t="n"/>
+      <c r="N81" s="26" t="n"/>
+      <c r="O81" s="26" t="n"/>
+      <c r="P81" s="26" t="n"/>
+      <c r="Q81" s="26" t="n"/>
+      <c r="R81" s="26" t="n"/>
+      <c r="S81" s="26" t="n"/>
+      <c r="T81" s="26" t="n"/>
+      <c r="U81" s="26" t="n"/>
+      <c r="V81" s="26" t="n"/>
+      <c r="W81" s="26" t="n"/>
+      <c r="X81" s="26" t="n"/>
+      <c r="Y81" s="26" t="n"/>
+      <c r="Z81" s="26" t="n"/>
+      <c r="AA81" s="26" t="n"/>
+      <c r="AB81" s="26" t="n"/>
       <c r="AC81" s="26" t="n"/>
       <c r="AD81" s="26" t="n"/>
       <c r="AE81" s="26" t="n"/>
-      <c r="AF81" s="26" t="n"/>
-      <c r="AG81" s="26" t="n"/>
-      <c r="AH81" s="26" t="n"/>
-      <c r="AI81" s="26" t="n"/>
-      <c r="AJ81" s="26" t="n"/>
-      <c r="AK81" s="26" t="n"/>
-      <c r="AL81" s="26" t="n"/>
-      <c r="AM81" s="26" t="n"/>
-      <c r="AN81" s="26" t="n"/>
-      <c r="AO81" s="26" t="n"/>
-      <c r="AP81" s="26" t="n"/>
-      <c r="AQ81" s="26" t="n"/>
-      <c r="AR81" s="26" t="n"/>
-      <c r="AS81" s="26" t="n"/>
-      <c r="AT81" s="26" t="n"/>
-      <c r="AU81" s="26" t="n"/>
-      <c r="AV81" s="26" t="n"/>
-      <c r="AW81" s="26" t="n"/>
-      <c r="AX81" s="26" t="n"/>
-      <c r="AY81" s="26" t="n"/>
-      <c r="AZ81" s="26" t="n"/>
-      <c r="BA81" s="26" t="n"/>
-      <c r="BB81" s="26" t="n"/>
-      <c r="BC81" s="26" t="n"/>
-      <c r="BD81" s="26" t="n"/>
-      <c r="BE81" s="26" t="n"/>
-      <c r="BF81" s="26" t="n"/>
-      <c r="BG81" s="26" t="n"/>
-      <c r="BH81" s="26" t="n"/>
-      <c r="BI81" s="26" t="n"/>
-      <c r="BJ81" s="26" t="n"/>
-      <c r="BK81" s="26" t="n"/>
-      <c r="BL81" s="26" t="n"/>
-      <c r="BM81" s="26" t="n"/>
-      <c r="BN81" s="26" t="n"/>
-      <c r="BO81" s="26" t="n"/>
+      <c r="AF81" s="27" t="n"/>
+      <c r="AG81" s="28" t="n"/>
+      <c r="AH81" s="28" t="n"/>
+      <c r="AI81" s="28" t="n"/>
+      <c r="AJ81" s="28" t="n"/>
+      <c r="AK81" s="28" t="n"/>
+      <c r="AL81" s="28" t="n"/>
+      <c r="AM81" s="28" t="n"/>
+      <c r="AN81" s="28" t="n"/>
+      <c r="AO81" s="28" t="n"/>
+      <c r="AP81" s="28" t="n"/>
+      <c r="AQ81" s="28" t="n"/>
+      <c r="AR81" s="28" t="n"/>
+      <c r="AS81" s="28" t="n"/>
+      <c r="AT81" s="28" t="n"/>
+      <c r="AU81" s="28" t="n"/>
+      <c r="AV81" s="28" t="n"/>
+      <c r="AW81" s="28" t="n"/>
+      <c r="AX81" s="28" t="n"/>
+      <c r="AY81" s="28" t="n"/>
+      <c r="AZ81" s="28" t="n"/>
+      <c r="BA81" s="28" t="n"/>
+      <c r="BB81" s="28" t="n"/>
+      <c r="BC81" s="28" t="n"/>
+      <c r="BD81" s="28" t="n"/>
+      <c r="BE81" s="28" t="n"/>
+      <c r="BF81" s="28" t="n"/>
+      <c r="BG81" s="28" t="n"/>
+      <c r="BH81" s="28" t="n"/>
+      <c r="BI81" s="28" t="n"/>
+      <c r="BJ81" s="28" t="n"/>
+      <c r="BK81" s="28" t="n"/>
+      <c r="BL81" s="28" t="n"/>
+      <c r="BM81" s="28" t="n"/>
+      <c r="BN81" s="28" t="n"/>
+      <c r="BO81" s="28" t="n"/>
+      <c r="BP81" s="28" t="n"/>
+      <c r="BQ81" s="28" t="n"/>
+      <c r="BR81" s="28" t="n"/>
+      <c r="BS81" s="28" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="27" t="inlineStr">
+      <c r="A82" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B82" s="27" t="inlineStr">
+      <c r="B82" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C82" s="28" t="inlineStr">
+      <c r="C82" s="30" t="inlineStr">
         <is>
           <t>PAB220·工装图纸绘制</t>
         </is>
       </c>
-      <c r="D82" s="29">
+      <c r="D82" s="31">
         <f>'时间节点计划表'!E41</f>
         <v/>
       </c>
-      <c r="E82" s="29">
+      <c r="E82" s="31">
         <f>IF(COUNT('时间节点计划表'!F41),'时间节点计划表'!F41,"")</f>
         <v/>
       </c>
-      <c r="F82" s="30">
+      <c r="F82" s="32">
         <f>IF(OR(D82="",E82=""),"待填",E82-D82)</f>
         <v/>
       </c>
@@ -17717,6 +18521,22 @@
       </c>
       <c r="BO82" s="23">
         <f>IF(AND(COUNT($E82),N(BO$2)=N($E82)),$E82,IF(AND(COUNT($E82),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E82))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP82" s="23">
+        <f>IF(AND(COUNT($E82),N(BP$2)=N($E82)),$E82,IF(AND(COUNT($E82),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E82))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ82" s="23">
+        <f>IF(AND(COUNT($E82),N(BQ$2)=N($E82)),$E82,IF(AND(COUNT($E82),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E82))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR82" s="23">
+        <f>IF(AND(COUNT($E82),N(BR$2)=N($E82)),$E82,IF(AND(COUNT($E82),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E82))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS82" s="23">
+        <f>IF(AND(COUNT($E82),N(BS$2)=N($E82)),$E82,IF(AND(COUNT($E82),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E82))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -17749,92 +18569,96 @@
         <f>D83</f>
         <v/>
       </c>
-      <c r="H83" s="32" t="n"/>
-      <c r="I83" s="32" t="n"/>
-      <c r="J83" s="32" t="n"/>
-      <c r="K83" s="32" t="n"/>
-      <c r="L83" s="32" t="n"/>
-      <c r="M83" s="32" t="n"/>
-      <c r="N83" s="32" t="n"/>
-      <c r="O83" s="32" t="n"/>
-      <c r="P83" s="32" t="n"/>
-      <c r="Q83" s="32" t="n"/>
-      <c r="R83" s="32" t="n"/>
-      <c r="S83" s="32" t="n"/>
-      <c r="T83" s="32" t="n"/>
-      <c r="U83" s="32" t="n"/>
-      <c r="V83" s="32" t="n"/>
-      <c r="W83" s="32" t="n"/>
-      <c r="X83" s="32" t="n"/>
-      <c r="Y83" s="32" t="n"/>
-      <c r="Z83" s="32" t="n"/>
-      <c r="AA83" s="32" t="n"/>
-      <c r="AB83" s="32" t="n"/>
-      <c r="AC83" s="32" t="n"/>
-      <c r="AD83" s="32" t="n"/>
-      <c r="AE83" s="32" t="n"/>
-      <c r="AF83" s="32" t="n"/>
-      <c r="AG83" s="32" t="n"/>
-      <c r="AH83" s="32" t="n"/>
-      <c r="AI83" s="32" t="n"/>
-      <c r="AJ83" s="32" t="n"/>
-      <c r="AK83" s="32" t="n"/>
-      <c r="AL83" s="32" t="n"/>
-      <c r="AM83" s="32" t="n"/>
-      <c r="AN83" s="32" t="n"/>
-      <c r="AO83" s="32" t="n"/>
-      <c r="AP83" s="32" t="n"/>
-      <c r="AQ83" s="32" t="n"/>
-      <c r="AR83" s="32" t="n"/>
-      <c r="AS83" s="32" t="n"/>
-      <c r="AT83" s="32" t="n"/>
-      <c r="AU83" s="32" t="n"/>
-      <c r="AV83" s="32" t="n"/>
-      <c r="AW83" s="32" t="n"/>
-      <c r="AX83" s="32" t="n"/>
-      <c r="AY83" s="32" t="n"/>
-      <c r="AZ83" s="32" t="n"/>
-      <c r="BA83" s="32" t="n"/>
-      <c r="BB83" s="31" t="n"/>
+      <c r="H83" s="26" t="n"/>
+      <c r="I83" s="26" t="n"/>
+      <c r="J83" s="26" t="n"/>
+      <c r="K83" s="26" t="n"/>
+      <c r="L83" s="26" t="n"/>
+      <c r="M83" s="26" t="n"/>
+      <c r="N83" s="26" t="n"/>
+      <c r="O83" s="26" t="n"/>
+      <c r="P83" s="26" t="n"/>
+      <c r="Q83" s="26" t="n"/>
+      <c r="R83" s="26" t="n"/>
+      <c r="S83" s="26" t="n"/>
+      <c r="T83" s="26" t="n"/>
+      <c r="U83" s="26" t="n"/>
+      <c r="V83" s="26" t="n"/>
+      <c r="W83" s="26" t="n"/>
+      <c r="X83" s="26" t="n"/>
+      <c r="Y83" s="26" t="n"/>
+      <c r="Z83" s="26" t="n"/>
+      <c r="AA83" s="26" t="n"/>
+      <c r="AB83" s="26" t="n"/>
+      <c r="AC83" s="26" t="n"/>
+      <c r="AD83" s="26" t="n"/>
+      <c r="AE83" s="26" t="n"/>
+      <c r="AF83" s="26" t="n"/>
+      <c r="AG83" s="26" t="n"/>
+      <c r="AH83" s="26" t="n"/>
+      <c r="AI83" s="26" t="n"/>
+      <c r="AJ83" s="26" t="n"/>
+      <c r="AK83" s="26" t="n"/>
+      <c r="AL83" s="26" t="n"/>
+      <c r="AM83" s="26" t="n"/>
+      <c r="AN83" s="26" t="n"/>
+      <c r="AO83" s="26" t="n"/>
+      <c r="AP83" s="26" t="n"/>
+      <c r="AQ83" s="26" t="n"/>
+      <c r="AR83" s="26" t="n"/>
+      <c r="AS83" s="26" t="n"/>
+      <c r="AT83" s="26" t="n"/>
+      <c r="AU83" s="26" t="n"/>
+      <c r="AV83" s="26" t="n"/>
+      <c r="AW83" s="26" t="n"/>
+      <c r="AX83" s="26" t="n"/>
+      <c r="AY83" s="26" t="n"/>
+      <c r="AZ83" s="26" t="n"/>
+      <c r="BA83" s="26" t="n"/>
+      <c r="BB83" s="26" t="n"/>
       <c r="BC83" s="26" t="n"/>
       <c r="BD83" s="26" t="n"/>
       <c r="BE83" s="26" t="n"/>
-      <c r="BF83" s="26" t="n"/>
-      <c r="BG83" s="26" t="n"/>
-      <c r="BH83" s="26" t="n"/>
-      <c r="BI83" s="26" t="n"/>
-      <c r="BJ83" s="26" t="n"/>
-      <c r="BK83" s="26" t="n"/>
-      <c r="BL83" s="26" t="n"/>
-      <c r="BM83" s="26" t="n"/>
-      <c r="BN83" s="26" t="n"/>
-      <c r="BO83" s="26" t="n"/>
+      <c r="BF83" s="27" t="n"/>
+      <c r="BG83" s="28" t="n"/>
+      <c r="BH83" s="28" t="n"/>
+      <c r="BI83" s="28" t="n"/>
+      <c r="BJ83" s="28" t="n"/>
+      <c r="BK83" s="28" t="n"/>
+      <c r="BL83" s="28" t="n"/>
+      <c r="BM83" s="28" t="n"/>
+      <c r="BN83" s="28" t="n"/>
+      <c r="BO83" s="28" t="n"/>
+      <c r="BP83" s="28" t="n"/>
+      <c r="BQ83" s="28" t="n"/>
+      <c r="BR83" s="28" t="n"/>
+      <c r="BS83" s="28" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="27" t="inlineStr">
+      <c r="A84" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B84" s="27" t="inlineStr">
+      <c r="B84" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C84" s="28" t="inlineStr">
+      <c r="C84" s="30" t="inlineStr">
         <is>
           <t>PAB220·工装实物到位</t>
         </is>
       </c>
-      <c r="D84" s="29">
+      <c r="D84" s="31">
         <f>'时间节点计划表'!E42</f>
         <v/>
       </c>
-      <c r="E84" s="29">
+      <c r="E84" s="31">
         <f>IF(COUNT('时间节点计划表'!F42),'时间节点计划表'!F42,"")</f>
         <v/>
       </c>
-      <c r="F84" s="30">
+      <c r="F84" s="32">
         <f>IF(OR(D84="",E84=""),"待填",E84-D84)</f>
         <v/>
       </c>
@@ -18080,6 +18904,22 @@
       </c>
       <c r="BO84" s="23">
         <f>IF(AND(COUNT($E84),N(BO$2)=N($E84)),$E84,IF(AND(COUNT($E84),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E84))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP84" s="23">
+        <f>IF(AND(COUNT($E84),N(BP$2)=N($E84)),$E84,IF(AND(COUNT($E84),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E84))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ84" s="23">
+        <f>IF(AND(COUNT($E84),N(BQ$2)=N($E84)),$E84,IF(AND(COUNT($E84),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E84))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR84" s="23">
+        <f>IF(AND(COUNT($E84),N(BR$2)=N($E84)),$E84,IF(AND(COUNT($E84),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E84))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS84" s="23">
+        <f>IF(AND(COUNT($E84),N(BS$2)=N($E84)),$E84,IF(AND(COUNT($E84),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E84))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -18112,92 +18952,96 @@
         <f>D85</f>
         <v/>
       </c>
-      <c r="H85" s="32" t="n"/>
-      <c r="I85" s="32" t="n"/>
-      <c r="J85" s="32" t="n"/>
-      <c r="K85" s="32" t="n"/>
-      <c r="L85" s="32" t="n"/>
-      <c r="M85" s="32" t="n"/>
-      <c r="N85" s="32" t="n"/>
-      <c r="O85" s="32" t="n"/>
-      <c r="P85" s="32" t="n"/>
-      <c r="Q85" s="32" t="n"/>
-      <c r="R85" s="32" t="n"/>
-      <c r="S85" s="32" t="n"/>
-      <c r="T85" s="32" t="n"/>
-      <c r="U85" s="32" t="n"/>
-      <c r="V85" s="32" t="n"/>
-      <c r="W85" s="32" t="n"/>
-      <c r="X85" s="32" t="n"/>
-      <c r="Y85" s="32" t="n"/>
-      <c r="Z85" s="32" t="n"/>
-      <c r="AA85" s="32" t="n"/>
-      <c r="AB85" s="32" t="n"/>
-      <c r="AC85" s="32" t="n"/>
-      <c r="AD85" s="32" t="n"/>
-      <c r="AE85" s="32" t="n"/>
-      <c r="AF85" s="32" t="n"/>
-      <c r="AG85" s="32" t="n"/>
-      <c r="AH85" s="32" t="n"/>
-      <c r="AI85" s="32" t="n"/>
-      <c r="AJ85" s="32" t="n"/>
-      <c r="AK85" s="32" t="n"/>
-      <c r="AL85" s="32" t="n"/>
-      <c r="AM85" s="32" t="n"/>
-      <c r="AN85" s="32" t="n"/>
-      <c r="AO85" s="32" t="n"/>
-      <c r="AP85" s="32" t="n"/>
-      <c r="AQ85" s="32" t="n"/>
-      <c r="AR85" s="32" t="n"/>
-      <c r="AS85" s="32" t="n"/>
-      <c r="AT85" s="32" t="n"/>
-      <c r="AU85" s="32" t="n"/>
-      <c r="AV85" s="32" t="n"/>
-      <c r="AW85" s="32" t="n"/>
-      <c r="AX85" s="32" t="n"/>
-      <c r="AY85" s="32" t="n"/>
-      <c r="AZ85" s="32" t="n"/>
-      <c r="BA85" s="32" t="n"/>
-      <c r="BB85" s="32" t="n"/>
-      <c r="BC85" s="32" t="n"/>
-      <c r="BD85" s="32" t="n"/>
-      <c r="BE85" s="32" t="n"/>
-      <c r="BF85" s="32" t="n"/>
-      <c r="BG85" s="32" t="n"/>
-      <c r="BH85" s="32" t="n"/>
-      <c r="BI85" s="32" t="n"/>
-      <c r="BJ85" s="32" t="n"/>
-      <c r="BK85" s="32" t="n"/>
-      <c r="BL85" s="31" t="n"/>
+      <c r="H85" s="26" t="n"/>
+      <c r="I85" s="26" t="n"/>
+      <c r="J85" s="26" t="n"/>
+      <c r="K85" s="26" t="n"/>
+      <c r="L85" s="26" t="n"/>
+      <c r="M85" s="26" t="n"/>
+      <c r="N85" s="26" t="n"/>
+      <c r="O85" s="26" t="n"/>
+      <c r="P85" s="26" t="n"/>
+      <c r="Q85" s="26" t="n"/>
+      <c r="R85" s="26" t="n"/>
+      <c r="S85" s="26" t="n"/>
+      <c r="T85" s="26" t="n"/>
+      <c r="U85" s="26" t="n"/>
+      <c r="V85" s="26" t="n"/>
+      <c r="W85" s="26" t="n"/>
+      <c r="X85" s="26" t="n"/>
+      <c r="Y85" s="26" t="n"/>
+      <c r="Z85" s="26" t="n"/>
+      <c r="AA85" s="26" t="n"/>
+      <c r="AB85" s="26" t="n"/>
+      <c r="AC85" s="26" t="n"/>
+      <c r="AD85" s="26" t="n"/>
+      <c r="AE85" s="26" t="n"/>
+      <c r="AF85" s="26" t="n"/>
+      <c r="AG85" s="26" t="n"/>
+      <c r="AH85" s="26" t="n"/>
+      <c r="AI85" s="26" t="n"/>
+      <c r="AJ85" s="26" t="n"/>
+      <c r="AK85" s="26" t="n"/>
+      <c r="AL85" s="26" t="n"/>
+      <c r="AM85" s="26" t="n"/>
+      <c r="AN85" s="26" t="n"/>
+      <c r="AO85" s="26" t="n"/>
+      <c r="AP85" s="26" t="n"/>
+      <c r="AQ85" s="26" t="n"/>
+      <c r="AR85" s="26" t="n"/>
+      <c r="AS85" s="26" t="n"/>
+      <c r="AT85" s="26" t="n"/>
+      <c r="AU85" s="26" t="n"/>
+      <c r="AV85" s="26" t="n"/>
+      <c r="AW85" s="26" t="n"/>
+      <c r="AX85" s="26" t="n"/>
+      <c r="AY85" s="26" t="n"/>
+      <c r="AZ85" s="26" t="n"/>
+      <c r="BA85" s="26" t="n"/>
+      <c r="BB85" s="26" t="n"/>
+      <c r="BC85" s="26" t="n"/>
+      <c r="BD85" s="26" t="n"/>
+      <c r="BE85" s="26" t="n"/>
+      <c r="BF85" s="26" t="n"/>
+      <c r="BG85" s="26" t="n"/>
+      <c r="BH85" s="26" t="n"/>
+      <c r="BI85" s="26" t="n"/>
+      <c r="BJ85" s="26" t="n"/>
+      <c r="BK85" s="26" t="n"/>
+      <c r="BL85" s="26" t="n"/>
       <c r="BM85" s="26" t="n"/>
       <c r="BN85" s="26" t="n"/>
       <c r="BO85" s="26" t="n"/>
+      <c r="BP85" s="27" t="n"/>
+      <c r="BQ85" s="28" t="n"/>
+      <c r="BR85" s="28" t="n"/>
+      <c r="BS85" s="28" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="27" t="inlineStr">
+      <c r="A86" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B86" s="27" t="inlineStr">
+      <c r="B86" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C86" s="28" t="inlineStr">
+      <c r="C86" s="30" t="inlineStr">
         <is>
           <t>PAB220·排针机安装调试</t>
         </is>
       </c>
-      <c r="D86" s="29">
+      <c r="D86" s="31">
         <f>'时间节点计划表'!E43</f>
         <v/>
       </c>
-      <c r="E86" s="29">
+      <c r="E86" s="31">
         <f>IF(COUNT('时间节点计划表'!F43),'时间节点计划表'!F43,"")</f>
         <v/>
       </c>
-      <c r="F86" s="30">
+      <c r="F86" s="32">
         <f>IF(OR(D86="",E86=""),"待填",E86-D86)</f>
         <v/>
       </c>
@@ -18443,6 +19287,22 @@
       </c>
       <c r="BO86" s="23">
         <f>IF(AND(COUNT($E86),N(BO$2)=N($E86)),$E86,IF(AND(COUNT($E86),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E86))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP86" s="23">
+        <f>IF(AND(COUNT($E86),N(BP$2)=N($E86)),$E86,IF(AND(COUNT($E86),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E86))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ86" s="23">
+        <f>IF(AND(COUNT($E86),N(BQ$2)=N($E86)),$E86,IF(AND(COUNT($E86),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E86))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR86" s="23">
+        <f>IF(AND(COUNT($E86),N(BR$2)=N($E86)),$E86,IF(AND(COUNT($E86),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E86))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS86" s="23">
+        <f>IF(AND(COUNT($E86),N(BS$2)=N($E86)),$E86,IF(AND(COUNT($E86),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E86))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -18475,92 +19335,96 @@
         <f>D87</f>
         <v/>
       </c>
-      <c r="H87" s="32" t="n"/>
-      <c r="I87" s="32" t="n"/>
-      <c r="J87" s="32" t="n"/>
-      <c r="K87" s="32" t="n"/>
-      <c r="L87" s="32" t="n"/>
-      <c r="M87" s="32" t="n"/>
-      <c r="N87" s="32" t="n"/>
-      <c r="O87" s="32" t="n"/>
-      <c r="P87" s="32" t="n"/>
-      <c r="Q87" s="32" t="n"/>
-      <c r="R87" s="32" t="n"/>
-      <c r="S87" s="32" t="n"/>
-      <c r="T87" s="32" t="n"/>
-      <c r="U87" s="32" t="n"/>
-      <c r="V87" s="32" t="n"/>
-      <c r="W87" s="32" t="n"/>
-      <c r="X87" s="32" t="n"/>
-      <c r="Y87" s="32" t="n"/>
-      <c r="Z87" s="32" t="n"/>
-      <c r="AA87" s="32" t="n"/>
-      <c r="AB87" s="32" t="n"/>
-      <c r="AC87" s="32" t="n"/>
-      <c r="AD87" s="32" t="n"/>
-      <c r="AE87" s="32" t="n"/>
-      <c r="AF87" s="32" t="n"/>
-      <c r="AG87" s="32" t="n"/>
-      <c r="AH87" s="32" t="n"/>
-      <c r="AI87" s="32" t="n"/>
-      <c r="AJ87" s="32" t="n"/>
-      <c r="AK87" s="32" t="n"/>
-      <c r="AL87" s="32" t="n"/>
-      <c r="AM87" s="32" t="n"/>
-      <c r="AN87" s="32" t="n"/>
-      <c r="AO87" s="32" t="n"/>
-      <c r="AP87" s="32" t="n"/>
-      <c r="AQ87" s="32" t="n"/>
-      <c r="AR87" s="32" t="n"/>
-      <c r="AS87" s="32" t="n"/>
-      <c r="AT87" s="32" t="n"/>
-      <c r="AU87" s="32" t="n"/>
-      <c r="AV87" s="32" t="n"/>
-      <c r="AW87" s="32" t="n"/>
-      <c r="AX87" s="32" t="n"/>
-      <c r="AY87" s="32" t="n"/>
-      <c r="AZ87" s="32" t="n"/>
-      <c r="BA87" s="32" t="n"/>
-      <c r="BB87" s="32" t="n"/>
-      <c r="BC87" s="32" t="n"/>
-      <c r="BD87" s="32" t="n"/>
-      <c r="BE87" s="32" t="n"/>
-      <c r="BF87" s="32" t="n"/>
-      <c r="BG87" s="32" t="n"/>
-      <c r="BH87" s="32" t="n"/>
-      <c r="BI87" s="32" t="n"/>
-      <c r="BJ87" s="32" t="n"/>
-      <c r="BK87" s="32" t="n"/>
-      <c r="BL87" s="32" t="n"/>
-      <c r="BM87" s="31" t="n"/>
+      <c r="H87" s="26" t="n"/>
+      <c r="I87" s="26" t="n"/>
+      <c r="J87" s="26" t="n"/>
+      <c r="K87" s="26" t="n"/>
+      <c r="L87" s="26" t="n"/>
+      <c r="M87" s="26" t="n"/>
+      <c r="N87" s="26" t="n"/>
+      <c r="O87" s="26" t="n"/>
+      <c r="P87" s="26" t="n"/>
+      <c r="Q87" s="26" t="n"/>
+      <c r="R87" s="26" t="n"/>
+      <c r="S87" s="26" t="n"/>
+      <c r="T87" s="26" t="n"/>
+      <c r="U87" s="26" t="n"/>
+      <c r="V87" s="26" t="n"/>
+      <c r="W87" s="26" t="n"/>
+      <c r="X87" s="26" t="n"/>
+      <c r="Y87" s="26" t="n"/>
+      <c r="Z87" s="26" t="n"/>
+      <c r="AA87" s="26" t="n"/>
+      <c r="AB87" s="26" t="n"/>
+      <c r="AC87" s="26" t="n"/>
+      <c r="AD87" s="26" t="n"/>
+      <c r="AE87" s="26" t="n"/>
+      <c r="AF87" s="26" t="n"/>
+      <c r="AG87" s="26" t="n"/>
+      <c r="AH87" s="26" t="n"/>
+      <c r="AI87" s="26" t="n"/>
+      <c r="AJ87" s="26" t="n"/>
+      <c r="AK87" s="26" t="n"/>
+      <c r="AL87" s="26" t="n"/>
+      <c r="AM87" s="26" t="n"/>
+      <c r="AN87" s="26" t="n"/>
+      <c r="AO87" s="26" t="n"/>
+      <c r="AP87" s="26" t="n"/>
+      <c r="AQ87" s="26" t="n"/>
+      <c r="AR87" s="26" t="n"/>
+      <c r="AS87" s="26" t="n"/>
+      <c r="AT87" s="26" t="n"/>
+      <c r="AU87" s="26" t="n"/>
+      <c r="AV87" s="26" t="n"/>
+      <c r="AW87" s="26" t="n"/>
+      <c r="AX87" s="26" t="n"/>
+      <c r="AY87" s="26" t="n"/>
+      <c r="AZ87" s="26" t="n"/>
+      <c r="BA87" s="26" t="n"/>
+      <c r="BB87" s="26" t="n"/>
+      <c r="BC87" s="26" t="n"/>
+      <c r="BD87" s="26" t="n"/>
+      <c r="BE87" s="26" t="n"/>
+      <c r="BF87" s="26" t="n"/>
+      <c r="BG87" s="26" t="n"/>
+      <c r="BH87" s="26" t="n"/>
+      <c r="BI87" s="26" t="n"/>
+      <c r="BJ87" s="26" t="n"/>
+      <c r="BK87" s="26" t="n"/>
+      <c r="BL87" s="26" t="n"/>
+      <c r="BM87" s="26" t="n"/>
       <c r="BN87" s="26" t="n"/>
       <c r="BO87" s="26" t="n"/>
+      <c r="BP87" s="26" t="n"/>
+      <c r="BQ87" s="27" t="n"/>
+      <c r="BR87" s="28" t="n"/>
+      <c r="BS87" s="28" t="n"/>
     </row>
     <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
+      <c r="A88" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B88" s="27" t="inlineStr">
+      <c r="B88" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C88" s="28" t="inlineStr">
+      <c r="C88" s="30" t="inlineStr">
         <is>
           <t>PAB220·单级样机</t>
         </is>
       </c>
-      <c r="D88" s="29">
+      <c r="D88" s="31">
         <f>'时间节点计划表'!E44</f>
         <v/>
       </c>
-      <c r="E88" s="29">
+      <c r="E88" s="31">
         <f>IF(COUNT('时间节点计划表'!F44),'时间节点计划表'!F44,"")</f>
         <v/>
       </c>
-      <c r="F88" s="30">
+      <c r="F88" s="32">
         <f>IF(OR(D88="",E88=""),"待填",E88-D88)</f>
         <v/>
       </c>
@@ -18806,6 +19670,22 @@
       </c>
       <c r="BO88" s="23">
         <f>IF(AND(COUNT($E88),N(BO$2)=N($E88)),$E88,IF(AND(COUNT($E88),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E88))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BP88" s="23">
+        <f>IF(AND(COUNT($E88),N(BP$2)=N($E88)),$E88,IF(AND(COUNT($E88),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E88))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ88" s="23">
+        <f>IF(AND(COUNT($E88),N(BQ$2)=N($E88)),$E88,IF(AND(COUNT($E88),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E88))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR88" s="23">
+        <f>IF(AND(COUNT($E88),N(BR$2)=N($E88)),$E88,IF(AND(COUNT($E88),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E88))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS88" s="23">
+        <f>IF(AND(COUNT($E88),N(BS$2)=N($E88)),$E88,IF(AND(COUNT($E88),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E88))," ",""))</f>
         <v/>
       </c>
     </row>
@@ -18838,92 +19718,96 @@
         <f>D89</f>
         <v/>
       </c>
-      <c r="H89" s="32" t="n"/>
-      <c r="I89" s="32" t="n"/>
-      <c r="J89" s="32" t="n"/>
-      <c r="K89" s="32" t="n"/>
-      <c r="L89" s="32" t="n"/>
-      <c r="M89" s="32" t="n"/>
-      <c r="N89" s="32" t="n"/>
-      <c r="O89" s="32" t="n"/>
-      <c r="P89" s="32" t="n"/>
-      <c r="Q89" s="32" t="n"/>
-      <c r="R89" s="32" t="n"/>
-      <c r="S89" s="32" t="n"/>
-      <c r="T89" s="32" t="n"/>
-      <c r="U89" s="32" t="n"/>
-      <c r="V89" s="32" t="n"/>
-      <c r="W89" s="32" t="n"/>
-      <c r="X89" s="32" t="n"/>
-      <c r="Y89" s="32" t="n"/>
-      <c r="Z89" s="32" t="n"/>
-      <c r="AA89" s="32" t="n"/>
-      <c r="AB89" s="32" t="n"/>
-      <c r="AC89" s="32" t="n"/>
-      <c r="AD89" s="32" t="n"/>
-      <c r="AE89" s="32" t="n"/>
-      <c r="AF89" s="32" t="n"/>
-      <c r="AG89" s="32" t="n"/>
-      <c r="AH89" s="32" t="n"/>
-      <c r="AI89" s="32" t="n"/>
-      <c r="AJ89" s="32" t="n"/>
-      <c r="AK89" s="32" t="n"/>
-      <c r="AL89" s="32" t="n"/>
-      <c r="AM89" s="32" t="n"/>
-      <c r="AN89" s="32" t="n"/>
-      <c r="AO89" s="32" t="n"/>
-      <c r="AP89" s="32" t="n"/>
-      <c r="AQ89" s="32" t="n"/>
-      <c r="AR89" s="32" t="n"/>
-      <c r="AS89" s="32" t="n"/>
-      <c r="AT89" s="32" t="n"/>
-      <c r="AU89" s="32" t="n"/>
-      <c r="AV89" s="32" t="n"/>
-      <c r="AW89" s="32" t="n"/>
-      <c r="AX89" s="32" t="n"/>
-      <c r="AY89" s="32" t="n"/>
-      <c r="AZ89" s="32" t="n"/>
-      <c r="BA89" s="32" t="n"/>
-      <c r="BB89" s="32" t="n"/>
-      <c r="BC89" s="32" t="n"/>
-      <c r="BD89" s="32" t="n"/>
-      <c r="BE89" s="32" t="n"/>
-      <c r="BF89" s="32" t="n"/>
-      <c r="BG89" s="32" t="n"/>
-      <c r="BH89" s="32" t="n"/>
-      <c r="BI89" s="32" t="n"/>
-      <c r="BJ89" s="32" t="n"/>
-      <c r="BK89" s="32" t="n"/>
-      <c r="BL89" s="32" t="n"/>
-      <c r="BM89" s="32" t="n"/>
-      <c r="BN89" s="32" t="n"/>
-      <c r="BO89" s="31" t="n"/>
+      <c r="H89" s="26" t="n"/>
+      <c r="I89" s="26" t="n"/>
+      <c r="J89" s="26" t="n"/>
+      <c r="K89" s="26" t="n"/>
+      <c r="L89" s="26" t="n"/>
+      <c r="M89" s="26" t="n"/>
+      <c r="N89" s="26" t="n"/>
+      <c r="O89" s="26" t="n"/>
+      <c r="P89" s="26" t="n"/>
+      <c r="Q89" s="26" t="n"/>
+      <c r="R89" s="26" t="n"/>
+      <c r="S89" s="26" t="n"/>
+      <c r="T89" s="26" t="n"/>
+      <c r="U89" s="26" t="n"/>
+      <c r="V89" s="26" t="n"/>
+      <c r="W89" s="26" t="n"/>
+      <c r="X89" s="26" t="n"/>
+      <c r="Y89" s="26" t="n"/>
+      <c r="Z89" s="26" t="n"/>
+      <c r="AA89" s="26" t="n"/>
+      <c r="AB89" s="26" t="n"/>
+      <c r="AC89" s="26" t="n"/>
+      <c r="AD89" s="26" t="n"/>
+      <c r="AE89" s="26" t="n"/>
+      <c r="AF89" s="26" t="n"/>
+      <c r="AG89" s="26" t="n"/>
+      <c r="AH89" s="26" t="n"/>
+      <c r="AI89" s="26" t="n"/>
+      <c r="AJ89" s="26" t="n"/>
+      <c r="AK89" s="26" t="n"/>
+      <c r="AL89" s="26" t="n"/>
+      <c r="AM89" s="26" t="n"/>
+      <c r="AN89" s="26" t="n"/>
+      <c r="AO89" s="26" t="n"/>
+      <c r="AP89" s="26" t="n"/>
+      <c r="AQ89" s="26" t="n"/>
+      <c r="AR89" s="26" t="n"/>
+      <c r="AS89" s="26" t="n"/>
+      <c r="AT89" s="26" t="n"/>
+      <c r="AU89" s="26" t="n"/>
+      <c r="AV89" s="26" t="n"/>
+      <c r="AW89" s="26" t="n"/>
+      <c r="AX89" s="26" t="n"/>
+      <c r="AY89" s="26" t="n"/>
+      <c r="AZ89" s="26" t="n"/>
+      <c r="BA89" s="26" t="n"/>
+      <c r="BB89" s="26" t="n"/>
+      <c r="BC89" s="26" t="n"/>
+      <c r="BD89" s="26" t="n"/>
+      <c r="BE89" s="26" t="n"/>
+      <c r="BF89" s="26" t="n"/>
+      <c r="BG89" s="26" t="n"/>
+      <c r="BH89" s="26" t="n"/>
+      <c r="BI89" s="26" t="n"/>
+      <c r="BJ89" s="26" t="n"/>
+      <c r="BK89" s="26" t="n"/>
+      <c r="BL89" s="26" t="n"/>
+      <c r="BM89" s="26" t="n"/>
+      <c r="BN89" s="26" t="n"/>
+      <c r="BO89" s="26" t="n"/>
+      <c r="BP89" s="26" t="n"/>
+      <c r="BQ89" s="26" t="n"/>
+      <c r="BR89" s="26" t="n"/>
+      <c r="BS89" s="27" t="n"/>
     </row>
     <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="27" t="inlineStr">
+      <c r="A90" s="29" t="inlineStr">
         <is>
           <t>实际</t>
         </is>
       </c>
-      <c r="B90" s="27" t="inlineStr">
+      <c r="B90" s="29" t="inlineStr">
         <is>
           <t>第二期</t>
         </is>
       </c>
-      <c r="C90" s="28" t="inlineStr">
+      <c r="C90" s="30" t="inlineStr">
         <is>
           <t>PAB220·双级样机</t>
         </is>
       </c>
-      <c r="D90" s="29">
+      <c r="D90" s="31">
         <f>'时间节点计划表'!E45</f>
         <v/>
       </c>
-      <c r="E90" s="29">
+      <c r="E90" s="31">
         <f>IF(COUNT('时间节点计划表'!F45),'时间节点计划表'!F45,"")</f>
         <v/>
       </c>
-      <c r="F90" s="30">
+      <c r="F90" s="32">
         <f>IF(OR(D90="",E90=""),"待填",E90-D90)</f>
         <v/>
       </c>
@@ -19171,6 +20055,22 @@
         <f>IF(AND(COUNT($E90),N(BO$2)=N($E90)),$E90,IF(AND(COUNT($E90),N(BO$2)&gt;=N($G$2),N(BO$2)&lt;N($E90))," ",""))</f>
         <v/>
       </c>
+      <c r="BP90" s="23">
+        <f>IF(AND(COUNT($E90),N(BP$2)=N($E90)),$E90,IF(AND(COUNT($E90),N(BP$2)&gt;=N($G$2),N(BP$2)&lt;N($E90))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BQ90" s="23">
+        <f>IF(AND(COUNT($E90),N(BQ$2)=N($E90)),$E90,IF(AND(COUNT($E90),N(BQ$2)&gt;=N($G$2),N(BQ$2)&lt;N($E90))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BR90" s="23">
+        <f>IF(AND(COUNT($E90),N(BR$2)=N($E90)),$E90,IF(AND(COUNT($E90),N(BR$2)&gt;=N($G$2),N(BR$2)&lt;N($E90))," ",""))</f>
+        <v/>
+      </c>
+      <c r="BS90" s="23">
+        <f>IF(AND(COUNT($E90),N(BS$2)=N($E90)),$E90,IF(AND(COUNT($E90),N(BS$2)&gt;=N($G$2),N(BS$2)&lt;N($E90))," ",""))</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="14" t="inlineStr">
@@ -19200,57 +20100,58 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="G73:BG73"/>
-    <mergeCell ref="G77:BK77"/>
-    <mergeCell ref="G25:AO25"/>
-    <mergeCell ref="G23:AP23"/>
-    <mergeCell ref="G9:AC9"/>
-    <mergeCell ref="G33:AQ33"/>
-    <mergeCell ref="G31:AO31"/>
-    <mergeCell ref="O1:AR1"/>
-    <mergeCell ref="G29:AH29"/>
-    <mergeCell ref="AS1:BO1"/>
-    <mergeCell ref="G57:BE57"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G59:BG59"/>
-    <mergeCell ref="G17:AC17"/>
-    <mergeCell ref="G89:BO89"/>
-    <mergeCell ref="G79:BL79"/>
-    <mergeCell ref="G65:X65"/>
-    <mergeCell ref="G47:BC47"/>
-    <mergeCell ref="G81:AB81"/>
-    <mergeCell ref="G67:BG67"/>
-    <mergeCell ref="G83:BB83"/>
-    <mergeCell ref="G85:BL85"/>
-    <mergeCell ref="G51:R51"/>
-    <mergeCell ref="G19:AL19"/>
-    <mergeCell ref="G21:AN21"/>
-    <mergeCell ref="G15:K15"/>
-    <mergeCell ref="G55:BD55"/>
-    <mergeCell ref="G13:AL13"/>
-    <mergeCell ref="G43:AZ43"/>
-    <mergeCell ref="G63:X63"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G71:AZ71"/>
+  <mergeCells count="49">
+    <mergeCell ref="G57:BI57"/>
+    <mergeCell ref="G79:BP79"/>
+    <mergeCell ref="G17:AG17"/>
+    <mergeCell ref="G65:AB65"/>
+    <mergeCell ref="G47:BG47"/>
+    <mergeCell ref="G67:BK67"/>
+    <mergeCell ref="G83:BF83"/>
+    <mergeCell ref="G81:AF81"/>
+    <mergeCell ref="G51:V51"/>
+    <mergeCell ref="G85:BP85"/>
+    <mergeCell ref="G89:BS89"/>
+    <mergeCell ref="G21:AR21"/>
+    <mergeCell ref="G13:AP13"/>
+    <mergeCell ref="G19:AP19"/>
+    <mergeCell ref="G63:AB63"/>
+    <mergeCell ref="G15:O15"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="G43:BD43"/>
+    <mergeCell ref="G41:AQ41"/>
+    <mergeCell ref="G71:BD71"/>
+    <mergeCell ref="G49:BH49"/>
+    <mergeCell ref="G27:S27"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G87:BQ87"/>
+    <mergeCell ref="G11:AB11"/>
+    <mergeCell ref="G1:R1"/>
+    <mergeCell ref="G75:BL75"/>
+    <mergeCell ref="G61:Y61"/>
+    <mergeCell ref="G69:AC69"/>
+    <mergeCell ref="G35:AV35"/>
+    <mergeCell ref="G39:V39"/>
+    <mergeCell ref="G45:BE45"/>
+    <mergeCell ref="G53:AU53"/>
+    <mergeCell ref="G37:BD37"/>
     <mergeCell ref="A92:F92"/>
-    <mergeCell ref="G41:AM41"/>
-    <mergeCell ref="G49:BD49"/>
-    <mergeCell ref="G27:O27"/>
-    <mergeCell ref="G87:BM87"/>
+    <mergeCell ref="G55:BH55"/>
+    <mergeCell ref="G25:AS25"/>
+    <mergeCell ref="G23:AT23"/>
+    <mergeCell ref="S1:AV1"/>
+    <mergeCell ref="G9:AG9"/>
+    <mergeCell ref="G73:BK73"/>
+    <mergeCell ref="G77:BO77"/>
+    <mergeCell ref="AW1:BS1"/>
+    <mergeCell ref="G33:AU33"/>
+    <mergeCell ref="G31:AS31"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:N1"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="G75:BH75"/>
-    <mergeCell ref="G69:Y69"/>
-    <mergeCell ref="G45:BA45"/>
-    <mergeCell ref="G39:R39"/>
-    <mergeCell ref="G61:U61"/>
-    <mergeCell ref="G35:AR35"/>
-    <mergeCell ref="G53:AQ53"/>
-    <mergeCell ref="G37:AZ37"/>
+    <mergeCell ref="G29:AL29"/>
+    <mergeCell ref="G7:L7"/>
+    <mergeCell ref="G59:BK59"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:BO90">
+  <conditionalFormatting sqref="G3:BS90">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>AND($A3="预估",ISNUMBER(G3))</formula>
     </cfRule>
